--- a/data/xlsx/KNF_Rejestr_firm_inwestycyjnych.xlsx
+++ b/data/xlsx/KNF_Rejestr_firm_inwestycyjnych.xlsx
@@ -95,7 +95,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ul. Świdnicka 121/61, 50-066 Wrocław</t>
+          <t>os. Marszałkowska 1/1, 00-590 Warszawa</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -105,22 +105,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0000058203</t>
+          <t>0000000008</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1282319462</t>
+          <t>1234805466</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>282477841</t>
+          <t>234963846</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2018-11-13</t>
+          <t>13/11/2018</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -130,7 +130,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>83100650768</t>
+          <t>60021406849</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -140,7 +140,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Pawlak</t>
+          <t>Pawlak-Sikora</t>
         </is>
       </c>
     </row>
@@ -152,7 +152,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ul Legnicka 138, 54-203 Wrocław</t>
+          <t>ul Krakowskie Przedmieście 18, 00-071 Warszawa</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -162,22 +162,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0000058300</t>
+          <t>0000000105</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1282398651</t>
+          <t>1234884655</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>282557037</t>
+          <t>235043036</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2022-07-20</t>
+          <t>2022/20/07</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -187,7 +187,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>84110752154</t>
+          <t>61032108236</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -209,7 +209,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ulica Święty Marcin 155, 61-806 Poznań</t>
+          <t>ulica Floriańska 35, 31-019 Kraków</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -219,22 +219,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0000058397</t>
+          <t>0000000202</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1282477847</t>
+          <t>1234963840</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>282636222</t>
+          <t>235122221</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2019-06-19</t>
+          <t>19-06-2019</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -244,7 +244,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>85120853501</t>
+          <t>62042809586</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -266,7 +266,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Głogowska 172, 60-734 Poznań</t>
+          <t>Długa 52, 31-147 Kraków</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -276,22 +276,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0000058494</t>
+          <t>0000000299</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1282557032</t>
+          <t>1235043030</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>282715418</t>
+          <t>235201417</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2022-12-10</t>
+          <t>2022-10-12</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -301,7 +301,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>86010954892</t>
+          <t>63050710972</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -323,7 +323,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ul. Długa 9/23, 80-831 Gdańsk</t>
+          <t>ul. Piotrkowska 69/53, 90-102 Łódź</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -333,22 +333,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0000058591</t>
+          <t>0000000396</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1282636228</t>
+          <t>1235122226</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>282794607</t>
+          <t>235280606</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2019-03-28</t>
+          <t>20190328</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -358,7 +358,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>87021056249</t>
+          <t>64061412321</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -380,7 +380,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ul Grunwaldzka 26, 80-236 Gdańsk</t>
+          <t>ul Zachodnia 86, 90-402 Łódź</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -390,22 +390,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0000058688</t>
+          <t>0000000493</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1282715413</t>
+          <t>1235201411</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>282873790</t>
+          <t>235359791</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2018-02-08</t>
+          <t>08/02/2018</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -415,7 +415,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>88031157634</t>
+          <t>65072113717</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -437,7 +437,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ulica Jagiellońska 43, 70-435 Szczecin</t>
+          <t>ulica Świdnicka 103, 50-066 Wrocław</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -447,22 +447,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0000058785</t>
+          <t>0000000590</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1282794602</t>
+          <t>1235280600</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>282952986</t>
+          <t>235438987</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2017-08-15</t>
+          <t>2017/15/08</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -472,7 +472,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>89041258982</t>
+          <t>66082815068</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -489,52 +489,52 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Vistula iFntech S.A.</t>
+          <t>Vistula Fintech S.A.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Wyszyńskiego 60, 70-200 Szczecin</t>
+          <t>Legnicka 120, 54-203 Wrocław</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>przyjmoanwie i przekazywanie zleceń</t>
+          <t>przymjoanwie i przekazywanie zlceeń</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0000058882</t>
+          <t>0000000687</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1282873796</t>
+          <t>1235359796</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>283032176</t>
+          <t>235518172</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2018-11-23</t>
+          <t>23-11-2018</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>DIF/418/2026</t>
+          <t>DFI/418/2026</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>90051360370</t>
+          <t>67090716451</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Micha</t>
+          <t>Michał</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -551,7 +551,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ul. Mariacka 77/75, 40-014 Katowice</t>
+          <t>ul. Święty Marcin 137/15, 61-806 Poznań</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -561,22 +561,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0000058979</t>
+          <t>0000000784</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1282952981</t>
+          <t>1235438981</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>283111361</t>
+          <t>235597361</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2018-06-05</t>
+          <t>2018-05-06</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>91061461727</t>
+          <t>68101417802</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>os. Warszawska 94, 40-009 Katowice</t>
+          <t>ul Głogowska 154, 60-734 Poznań</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -618,22 +618,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0000059076</t>
+          <t>0000000881</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1283032171</t>
+          <t>1235518177</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>283190550</t>
+          <t>235676557</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2021-05-31</t>
+          <t>20210531</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -643,7 +643,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>92071563113</t>
+          <t>69112119190</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ulica Krakowskie Przedmieście 111, 20-002 Lublin</t>
+          <t>ulica Długa 171, 80-831 Gdańsk</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -675,22 +675,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0000059173</t>
+          <t>0000000978</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1283111367</t>
+          <t>1235597366</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>283269748</t>
+          <t>235755742</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2021-08-05</t>
+          <t>05/08/2021</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>93081664461</t>
+          <t>70122820541</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Narutowicza 128, 20-004 Lublin</t>
+          <t>Grunwaldzka 8, 80-236 Gdańsk</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -732,22 +732,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0000059270</t>
+          <t>0000001075</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1283190556</t>
+          <t>2235676551</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>283348933</t>
+          <t>235834938</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
+          <t>2021/12/10</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>94091765856</t>
+          <t>71010721939</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ul. Lipowa 145/37, 15-424 Białystok</t>
+          <t>ul. Jagiellońska 25/67, 70-435 Szczecin</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -789,22 +789,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0000059367</t>
+          <t>0000001172</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1283269743</t>
+          <t>1235755747</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>283428129</t>
+          <t>235914123</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2021-12-30</t>
+          <t>30-12-2021</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>95101867207</t>
+          <t>72021423289</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ul Sienkiewicza 162, 15-092 Białystok</t>
+          <t>ul Wyszyńskiego 42, 70-200 Szczecin</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -846,22 +846,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0000059464</t>
+          <t>0000001269</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1283348939</t>
+          <t>1235834932</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>283507314</t>
+          <t>235993312</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2022-12-10</t>
+          <t>2022-10-12</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>96111968593</t>
+          <t>73032124675</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ulica Gdańska 179, 85-005 Bydgoszcz</t>
+          <t>ulica Mariacka 59, 40-014 Katowice</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -903,22 +903,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0000059561</t>
+          <t>0000001366</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1283428124</t>
+          <t>1235914128</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>283586503</t>
+          <t>236072502</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>20241209</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>97122069949</t>
+          <t>74042826025</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -950,7 +950,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Dworcowa 16, 85-009 Bydgoszcz</t>
+          <t>Warszawska 76, 40-009 Katowice</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -960,22 +960,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0000059658</t>
+          <t>0000001463</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1283586509</t>
+          <t>1235993317</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>283665697</t>
+          <t>236151696</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
+          <t>15/06/2023</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>98012171333</t>
+          <t>75050727418</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ul. Szeroka 33/89, 87-100 Toruń</t>
+          <t>ul. Krakowskie Przedmieście 93/29, 20-002 Lublin</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1017,22 +1017,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0000059755</t>
+          <t>0000001560</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1283586509</t>
+          <t>1236072507</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>283744882</t>
+          <t>236230881</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2019-12-23</t>
+          <t>2019/23/12</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>99022272681</t>
+          <t>76061428767</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ul Chełmińska 50, 87-100 Toruń</t>
+          <t>ul Narutowicza 110, 20-004 Lublin</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1074,22 +1074,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0000059852</t>
+          <t>0000001657</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1283665692</t>
+          <t>1236151690</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>283824078</t>
+          <t>236310077</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2025-01-31</t>
+          <t/>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>00232374072</t>
+          <t>77072130157</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ulica 3 Maja 67, 35-030 Rzeszów</t>
+          <t>ulica Lipowa 127, 15-424 Białystok</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1131,22 +1131,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0000059949</t>
+          <t>0000001754</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1283744888</t>
+          <t>1236230886</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>283903263</t>
+          <t>236389268</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2021-06-11</t>
+          <t>2021-11-06</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>01242475429</t>
+          <t>78082831506</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1188,22 +1188,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0000060046</t>
+          <t>0000001851</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1283824073</t>
+          <t>1236310071</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>283982452</t>
+          <t>236468453</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2022-03-27</t>
+          <t>20220327</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>02252576814</t>
+          <t>79090732890</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ul. Sienkiewicza 101/51, 25-007 Kielce</t>
+          <t>ul. Gdańska 161/81, 85-005 Bydgoszcz</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1245,22 +1245,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0000060143</t>
+          <t>0000001948</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1283903269</t>
+          <t>1236389262</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>284061642</t>
+          <t>236547649</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>22/04/2025</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>03262678163</t>
+          <t>80101434241</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ul Warszawska 118, 25-512 Kielce</t>
+          <t>ul Dworcowa 178, 85-009 Bydgoszcz</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1302,22 +1302,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0000060240</t>
+          <t>0000002045</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1283982458</t>
+          <t>1236468458</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>284140838</t>
+          <t>236626834</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2020-03-14</t>
+          <t>2020/14/03</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>04272779558</t>
+          <t>81112135637</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ulica Kościuszki 135, 10-504 Olsztyn</t>
+          <t>ulica Szeroka 15, 87-100 Toruń</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1359,22 +1359,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0000060337</t>
+          <t>0000002142</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1284061648</t>
+          <t>1236547643</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>284220023</t>
+          <t>236785219</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2019-09-25</t>
+          <t>25-09-2019</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>05282880908</t>
+          <t>82122836987</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Dąbrowszczaków 152, 10-540 Olsztyn</t>
+          <t>Chełmińska 32, 87-100 Toruń</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1416,22 +1416,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0000060434</t>
+          <t>0000002239</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1284140833</t>
+          <t>1236626839</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>284299214</t>
+          <t>236785219</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2023-07-15</t>
+          <t>2023-15-07</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>60090182297</t>
+          <t>83010738376</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ul. Krakowska 169/13, 45-018 Opole</t>
+          <t>ul. 3 Maja 49/43, 35-030 Rzeszów</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1473,22 +1473,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>0000060531</t>
+          <t>0000002336</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1284220029</t>
+          <t>1236706024</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>284457593</t>
+          <t>236864404</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2021-05-13</t>
+          <t>20210513</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>61100283647</t>
+          <t>84021439724</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ul Ozimska 6, 45-057 Opole</t>
+          <t>ul Piłsudskiego 66, 35-074 Rzeszów</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1530,22 +1530,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0000060628</t>
+          <t>0000002433</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1284378405</t>
+          <t>1236785213</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>284457593</t>
+          <t>236943598</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>10/06/2024</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>62110385033</t>
+          <t>85032141114</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ulica Bohaterów Westerplatte 23, 65-034 Zielona Góra</t>
+          <t>ulica Sienkiewicza 83, 25-007 Kielce</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1587,22 +1587,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0000060725</t>
+          <t>0000002530</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1284378405</t>
+          <t>1236864409</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>284536789</t>
+          <t>237022788</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2019-05-09</t>
+          <t>2019/09/05</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>63120486381</t>
+          <t>86042842464</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Kupiecka 40, 65-058 Zielona Góra</t>
+          <t>Warszawska 100, 25-512 Kielce</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1644,22 +1644,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0000060822</t>
+          <t>0000002627</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1284457599</t>
+          <t>1236943592</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>284615974</t>
+          <t>237101973</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2018-07-07</t>
+          <t>07-07-2018</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>64010587771</t>
+          <t>87050743857</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ul. Świętojańska 57/65, 81-372 Gdynia</t>
+          <t>ul. Kościuszki 117/5, 10-504 Olsztyn</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1701,22 +1701,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>0000060919</t>
+          <t>0000002724</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1284536784</t>
+          <t>1237022782</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>284695163</t>
+          <t>237181162</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2017-06-21</t>
+          <t>2017-21-06</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>65020689129</t>
+          <t>88061445206</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ul 10 Lutego 74, 81-364 Gdynia</t>
+          <t>os. Dąbrowszczaków 134, 10-540 Olsztyn</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1758,22 +1758,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0000061016</t>
+          <t>0000002821</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1284695169</t>
+          <t>1237101978</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>284774359</t>
+          <t>237260358</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2022-12-20</t>
+          <t>20221220</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>66030790517</t>
+          <t>89072146593</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ulica Bolesława Prusa 91, 05-800 Pruszków</t>
+          <t>ulica Krakowska 151, 45-018 Opole</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1815,22 +1815,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0000061113</t>
+          <t>0000002918</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1284695169</t>
+          <t>1237181167</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>284853544</t>
+          <t>237339545</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2017-02-19</t>
+          <t>19/02/2017</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>67040891865</t>
+          <t>90082847941</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Kościuszki 108, 05-500 Piaseczno</t>
+          <t>Ozimska 168, 45-057 Opole</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1872,22 +1872,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0000061210</t>
+          <t>0000003015</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1284774354</t>
+          <t>1237260352</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>285091119</t>
+          <t>237418730</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2023-02-08</t>
+          <t>2023/08/02</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>68050993251</t>
+          <t>91090749335</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ul. Sienkiewicza 125/27, 32-020 Wieliczka</t>
+          <t>ul. Bohaterów Westerplatte 5/57, 65-034 Zielona Góra</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1929,22 +1929,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0000061307</t>
+          <t>0000003112</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1284932735</t>
+          <t>1237418735</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>285091119</t>
+          <t>237577115</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2018-01-28</t>
+          <t>28-01-2018</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>69061094607</t>
+          <t>92101450680</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ul Dąbrowskiego 142, 32-600 Oświęcim</t>
+          <t>ul Kupiecka 22, 65-058 Zielona Góra</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1986,22 +1986,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0000061404</t>
+          <t>0000003209</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1284932735</t>
+          <t>1237418735</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>285091119</t>
+          <t>237577115</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2022-06-21</t>
+          <t>2022-21-06</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>70071195992</t>
+          <t>93112152077</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ulica Rynek 159, 38-400 Krosno</t>
+          <t>ulica Świętojańska 39, 81-372 Gdynia</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2043,22 +2043,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>0000061501</t>
+          <t>0000003306</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1285011925</t>
+          <t>1237497924</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>285170304</t>
+          <t>237656300</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2021-12-12</t>
+          <t>20211212</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>71081297340</t>
+          <t>94122853426</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Mickiewicza 176, 39-300 Mielec</t>
+          <t>10 Lutego 56, 81-364 Gdynia</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2100,22 +2100,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0000061598</t>
+          <t>0000003403</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1285091114</t>
+          <t>1237656305</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>285328685</t>
+          <t>237735494</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2020-03-08</t>
+          <t>08/03/2020</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>72091398735</t>
+          <t>95010754814</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ul. Długa 13/79, 58-100 Świdnica</t>
+          <t>ul. Bolesława Prusa 73/19, 05-800 Pruszków</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2157,22 +2157,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0000061695</t>
+          <t>0000003500</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1285249495</t>
+          <t>1237656305</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>285328685</t>
+          <t>237893879</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
+          <t>2023/04/09</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>73101400080</t>
+          <t>96021456164</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2214,22 +2214,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>0000061792</t>
+          <t>0000003597</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1285249495</t>
+          <t>1237735499</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>285407870</t>
+          <t>237893879</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>07-09-2024</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>74111501475</t>
+          <t>97032157550</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>os. Chrobrego 47, 62-200 Gniezno</t>
+          <t>ulica Sienkiewicza 107, 32-020 Wieliczka</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2271,22 +2271,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>0000061889</t>
+          <t>000000369</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1285328680</t>
+          <t>1237814684</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>285566255</t>
+          <t>237973064</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2018-04-26</t>
+          <t>2018-26-04</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>75121602822</t>
+          <t>98042858909</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Słowiańska 64, 64-100 Leszno</t>
+          <t>Dąbrowskiego 124, 32-600 Oświęcim</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2328,22 +2328,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>0000061986</t>
+          <t>0000003791</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1285407876</t>
+          <t>1237893873</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>285566255</t>
+          <t>338052254</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2017-04-11</t>
+          <t>20170411</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>76011704213</t>
+          <t>99050760297</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ul. Gdańska 81/41, 83-110 Tczew</t>
+          <t>ul. Rynek 141/71, 38-400 Krosno</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2385,22 +2385,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0000062083</t>
+          <t>0000003888</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1285487065</t>
+          <t>1237973069</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>285645440</t>
+          <t>238210635</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>13/06/2024</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>77021805561</t>
+          <t>00261461640</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Pawlak</t>
+          <t>Pawlak-Sikora</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ul Sobieskiego 98, 84-200 Wejherowo</t>
+          <t>ul Mickiewicza 158, 39-300 Mielec</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2442,22 +2442,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0000062180</t>
+          <t>0000003985</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1285566250</t>
+          <t>1238052259</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>285724636</t>
+          <t>238210635</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2021-08-06</t>
+          <t>2021/06/08</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>78031906956</t>
+          <t>01272163037</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ulica Głęboka 115, 43-400 Cieszyn</t>
+          <t>175, 58-100 Świdnica</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2499,22 +2499,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>0000062277</t>
+          <t>0000004082</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1285645446</t>
+          <t>1238131444</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>285803821</t>
+          <t>238289826</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>08-04-2025</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>79042008303</t>
+          <t>02282864387</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2546,7 +2546,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Małachowskiego 132, 42-500 Będzin</t>
+          <t>Wojska Polskiego 12, 57-300 Kłodzko</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>0000062374</t>
+          <t>0000004179</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1285724631</t>
+          <t>1238289820</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>285883010</t>
+          <t>238369011</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2019-12-28</t>
+          <t>2019-28-12</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>80052109698</t>
+          <t>03290765770</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ul. Królowej Jadwigi 149/3, 88-100 Inowrocław</t>
+          <t>ul. Chrobrego 29/33, 62-200 Gniezno</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2613,22 +2613,22 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>0000062471</t>
+          <t>0000004276</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1285803827</t>
+          <t>1238289820</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>285962206</t>
+          <t>238448207</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>20241014</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>81062211049</t>
+          <t>04301467122</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ul Wybickiego 166, 86-300 Grudziądz</t>
+          <t>ul Słowiańska 46, 64-100 Leszno</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2670,22 +2670,22 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>0000062568</t>
+          <t>0000004373</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1285883016</t>
+          <t>1238369016</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>286041394</t>
+          <t>238527390</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>26/01/2025</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>82072312434</t>
+          <t>05312168518</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2717,7 +2717,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ulica Czarnieckiego 3, 14-100 Ostróda</t>
+          <t>ulica Gdańska 63, 83-110 Tczew</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2727,22 +2727,22 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>0000062665</t>
+          <t>0000004470</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1285962201</t>
+          <t>1238448201</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>286199770</t>
+          <t>238606586</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2023/03/10</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>83082413782</t>
+          <t>60122869864</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Warszawska 20, 11-500 Giżycko</t>
+          <t>Sobieskiego 80, 84-200 Wejherowo</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2784,22 +2784,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>0000062762</t>
+          <t>0000004567</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1286120585</t>
+          <t>1238527395</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>286199770</t>
+          <t>238685775</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2020-09-15</t>
+          <t>15-09-2020</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>84092515178</t>
+          <t>61010771256</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ul. Lubelska 37/55, 24-100 Puławy</t>
+          <t>ul. Głęboka 97/85, 43-400 Cieszyn</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2841,22 +2841,22 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>0000062859</t>
+          <t>0000004664</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1286120585</t>
+          <t>1238606580</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>286278966</t>
+          <t>238764960</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2017-12-06</t>
+          <t>2017-06-12</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>85102616528</t>
+          <t>72021472604</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ul Staszica 54, 22-400 Zamość</t>
+          <t>114, 42-500 Będzin</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2898,22 +2898,22 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0000062956</t>
+          <t>0000004761</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1286199776</t>
+          <t>1238764965</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>286358151</t>
+          <t>238844156</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2020-03-29</t>
+          <t>20200329</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>86112717913</t>
+          <t>63032173991</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -2945,7 +2945,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ulica 3 Maja 71, 16-300 Augustów</t>
+          <t>ulica Królowej Jadwigi 131, 88-100 Inowrocław</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2955,22 +2955,22 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>0000063053</t>
+          <t>0000004858</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1286278961</t>
+          <t>1238764965</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>286437347</t>
+          <t>238923341</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>04/03/2024</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>87122819262</t>
+          <t>64042875341</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Kościuszki 88, 16-400 Suwałki</t>
+          <t>Wybickiego 148, 86-300 Grudziądz</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3012,22 +3012,22 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>0000063150</t>
+          <t>0000004955</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1286358157</t>
+          <t>1238844150</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>286516532</t>
+          <t>239002531</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2023-03-05</t>
+          <t>2023/05/03</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>88010120651</t>
+          <t>65050776734</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ul. Piastowska 105/17, 48-300 Nysa</t>
+          <t>ul. Czarnieckiego 165/47, 14-100 Ostróda</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3069,22 +3069,22 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>0000063247</t>
+          <t>0000005052</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1286437342</t>
+          <t>1238923346</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>286595721</t>
+          <t>239081720</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2019-01-10</t>
+          <t>10-01-2019</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>89020222009</t>
+          <t>66061478084</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ul Długa 122, 49-300 Brzeg</t>
+          <t>ul Warszawska 2, 11-500 Giżycko</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3126,17 +3126,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>0000063344</t>
+          <t>0000005149</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1286516538</t>
+          <t>1239002536</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>286674917</t>
+          <t>239160916</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>90030323394</t>
+          <t>67072179470</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ulica Rynek 139, 68-200 Żary</t>
+          <t>ulica Lubelska 19, 24-100 Puławy</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3183,22 +3183,22 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>0000063441</t>
+          <t>0000005246</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1286595727</t>
+          <t>1239081725</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>286754102</t>
+          <t>239240101</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2020-12-12</t>
+          <t>20201212</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>91040424741</t>
+          <t>68082880822</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Sikorskiego 156, 66-200 Świebodzin</t>
+          <t>Staszica 36, 22-400 Zamość</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3240,22 +3240,22 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>0000063538</t>
+          <t>0000005343</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1286674912</t>
+          <t>1239160910</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>286833296</t>
+          <t>239319297</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2017-09-14</t>
+          <t>14/09/2017</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>02050526137</t>
+          <t>69090782216</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ul. Armii Krajowej 173/69, 78-100 Kołobrzeg</t>
+          <t>53/9, 16-300 Augustów</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3297,22 +3297,22 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0000063635</t>
+          <t>0000005440</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1286754108</t>
+          <t>1239240106</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>286912481</t>
+          <t>239398486</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2025/02/08</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>93060627485</t>
+          <t>70101483567</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3344,42 +3344,42 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ul Piłsudskiego 10, 73-110 Stargard</t>
+          <t>ul Kościuszki 70, 16-400 Suwałki</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>wykonywain zleceń na rachunek klientów</t>
+          <t>wykonywain lzeceń na rachunek klientów</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>0000063732</t>
+          <t>0000005537</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1286833291</t>
+          <t>1239319291</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>286991670</t>
+          <t>239477671</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2018-03-10</t>
+          <t>10-03-2018</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>DFI/221/2021</t>
+          <t>IDF/221/2021</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>94070728870</t>
+          <t>71112184953</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Czarnekci</t>
+          <t>Czarnecki</t>
         </is>
       </c>
     </row>
@@ -3401,7 +3401,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>27, 27-600 Sandomierz</t>
+          <t>os. Piastowska 87, 48-300 Nysa</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3411,22 +3411,22 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>0000063829</t>
+          <t>0000005634</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1286912487</t>
+          <t>1239398480</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>287070860</t>
+          <t>239556867</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2018-07-23</t>
+          <t>2018-23-07</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>95080830221</t>
+          <t>72122886303</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Sienkiewicza 44, 27-400 Ostrowiec Świętokrzyski</t>
+          <t>Długa 104, 49-300 Brzeg</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3468,22 +3468,22 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>0000063926</t>
+          <t>0000005731</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1286991676</t>
+          <t>1239477676</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>287150056</t>
+          <t>239636052</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2022-03-25</t>
+          <t>20220325</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>96090931616</t>
+          <t>73010787692</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ul. Marszałkowska 61/31, 00-590 Warszawa</t>
+          <t>ul. Rynek 121/61, 68-200 Żary</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3525,22 +3525,22 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>0000064023</t>
+          <t>0000005828</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1287070866</t>
+          <t>2239556861</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>287229243</t>
+          <t>239715248</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2019-05-19</t>
+          <t>19/05/2019</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>97101032966</t>
+          <t>74021489041</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -3572,7 +3572,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ul Krakowskie Przedmieście 78, 00-071 Warszawa</t>
+          <t>ul Sikorskiego 138, 66-200 Świebodzin</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3582,22 +3582,22 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>0000064120</t>
+          <t>0000005925</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1287150051</t>
+          <t>1239636057</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>287308439</t>
+          <t>239794437</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2017-07-21</t>
+          <t>2017/21/07</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3607,7 +3607,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>98111134352</t>
+          <t>75032190430</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -3629,7 +3629,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ulica Floriańska 95, 31-019 Kraków</t>
+          <t>ulica Armii Krajowej 155, 78-100 Kołobrzeg</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3639,22 +3639,22 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>0000064217</t>
+          <t>0000006022</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1287229249</t>
+          <t>1239715242</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>287387628</t>
+          <t>239873622</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2022-12-20</t>
+          <t>20-12-2022</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>99121235709</t>
+          <t>76042891780</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Długa 112, 31-147 Kraków</t>
+          <t>Piłsudskiego 172, 73-110 Stargard</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3696,22 +3696,22 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>0000064314</t>
+          <t>0000006119</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1287308434</t>
+          <t>1239794431</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>287466813</t>
+          <t>239952818</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2023-03-28</t>
+          <t>2023-28-03</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>00211337096</t>
+          <t>77050793174</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ul. Piotrkowska 129/83, 90-102 Łódź</t>
+          <t>ul. Mickiewicza 9/23, 27-600 Sandomierz</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3753,22 +3753,22 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>0000064411</t>
+          <t>0000006216</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1287387623</t>
+          <t>1239873627</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>287546009</t>
+          <t>240032008</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>202308310743</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>01221438443</t>
+          <t>78061494522</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ul Zachodnia 146, 90-402 Łódź</t>
+          <t>ul Sienkiewicza 26, 27-400 Ostrowiec Świętokrzyski</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3810,22 +3810,22 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>0000064508</t>
+          <t>0000006313</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1287466819</t>
+          <t>1239952812</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>287625192</t>
+          <t>240111191</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2017-06-02</t>
+          <t>02/06/2017</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3835,7 +3835,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>02231539838</t>
+          <t>79072195918</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -3857,7 +3857,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ulica Świdnicka 163, 50-066 Wrocław</t>
+          <t>ulica Marszałkowska 43, 00-590 Warszawa</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3867,22 +3867,22 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>0000064605</t>
+          <t>0000006410</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2287546004</t>
+          <t>1240032000</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>287704388</t>
+          <t>240190380</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2020-10-25</t>
+          <t>2020/25/10</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>03241641180</t>
+          <t>80082897268</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -3914,7 +3914,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>os. Legnicka 180, 54-203 Wrocław</t>
+          <t>Krakowskie Przedmieście 60, 00-071 Warszawa</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3924,22 +3924,22 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>0000064702</t>
+          <t>0000006507</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1287625198</t>
+          <t>1240111194</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>287783577</t>
+          <t>240269578</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2017-11-11</t>
+          <t>11-11-2017</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>04251742575</t>
+          <t>81090798651</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -3971,7 +3971,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ul. Święty Marcin 17/45, 61-806 Poznań</t>
+          <t>ul. Floriańska 77/75, 31-019 Kraków</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3981,22 +3981,22 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>0000064799</t>
+          <t>0000006604</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1287704383</t>
+          <t>1240190383</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>287862762</t>
+          <t>240348763</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2018-08-31</t>
+          <t>2018-31-08</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>05261843922</t>
+          <t>82101400006</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ul Głogowska 34, 60-734 Poznań</t>
+          <t>ul Długa 94, 31-147 Kraków</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4038,22 +4038,22 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>0000064896</t>
+          <t>0000006701</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1287783572</t>
+          <t>1240269570</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>287941958</t>
+          <t>240427959</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2024-04-28</t>
+          <t>20240428</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4063,7 +4063,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>60071945314</t>
+          <t>83112101393</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4085,7 +4085,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ulica Długa 51, 80-831 Gdańsk</t>
+          <t>ulica Piotrkowska 111, 90-102 Łódź</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4095,22 +4095,22 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>0000064993</t>
+          <t>0000006798</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1287862768</t>
+          <t>1240348766</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>288021148</t>
+          <t>240507144</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>15/05/2024</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>61082046661</t>
+          <t>84122802742</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Grunwaldzka 68, 80-236 Gdańsk</t>
+          <t>Zachodnia 128, 90-402 Łódź</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4152,22 +4152,22 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>0000065090</t>
+          <t>0000006895</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1287941953</t>
+          <t>1240427951</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>288100333</t>
+          <t>240586333</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025/14/08</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>62092148057</t>
+          <t>85010704131</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ul. Jagiellońska 85/7, 70-435 Szczecin</t>
+          <t>ul. Świdnicka 145/37, 50-066 Wrocław</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4209,22 +4209,22 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>0000065187</t>
+          <t>0000006992</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1288021143</t>
+          <t>1240507147</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>288179524</t>
+          <t>240665529</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2020-06-24</t>
+          <t>24-06-2020</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>63102249407</t>
+          <t>86021405480</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ul Wyszyńskiego 102, 70-200 Szczecin</t>
+          <t>ul Legnicka 162, 54-203 Wrocław</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4266,22 +4266,22 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>0000065284</t>
+          <t>0000007089</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1288100339</t>
+          <t>1240586336</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>288337905</t>
+          <t>240744714</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2023-11-05</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>64112350796</t>
+          <t>87032106876</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -4313,7 +4313,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ulica Mariacka 119, 40-014 Katowice</t>
+          <t>ulica Święty Marcin 179, 61-806 Poznań</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4323,22 +4323,22 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>0000065381</t>
+          <t>0000007186</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1288258715</t>
+          <t>1240665521</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>288337905</t>
+          <t>240903093</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2021-02-05</t>
+          <t>20210205</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>65122452144</t>
+          <t>88042808226</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -4370,7 +4370,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Warszawska 136, 40-009 Katowice</t>
+          <t>Głogowska 16, 60-734 Poznań</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4380,22 +4380,22 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>0000065478</t>
+          <t>0000007283</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1288258715</t>
+          <t>1240744717</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>288417099</t>
+          <t>240903093</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2022-03-27</t>
+          <t>27/03/2022</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -4405,7 +4405,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>66012553534</t>
+          <t>89050709619</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ul. Krakowskie Przedmieście 153/59, 20-002 Lublin</t>
+          <t>ul. Długa 33/89, 80-831 Gdańsk</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4437,22 +4437,22 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>0000065575</t>
+          <t>0000007380</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1288337900</t>
+          <t>1240823902</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>288496288</t>
+          <t>240982282</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2019-06-15</t>
+          <t>2019/15/06</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>67022654882</t>
+          <t>90061410960</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>ul Narutowicza 170, 20-004 Lublin</t>
+          <t>ul Grunwaldzka 50, 80-236 Gdańsk</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -4494,22 +4494,22 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>0000065672</t>
+          <t>0000007477</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>1288417094</t>
+          <t>1240903096</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>288575473</t>
+          <t>241061472</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2022-06-17</t>
+          <t>17-06-2022</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>68032756278</t>
+          <t>91072112357</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ulica Lipowa 7, 15-424 Białystok</t>
+          <t>ulica Jagiellońska 67, 70-435 Szczecin</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4551,22 +4551,22 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>0000065769</t>
+          <t>0000007574</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>1288496283</t>
+          <t>1240982285</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>288654669</t>
+          <t>241140668</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2023-07-09</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>69042857625</t>
+          <t>92082813706</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Sienkiewicza 24, 15-092 Białystok</t>
+          <t>Wyszyńskiego 84, 70-200 Szczecin</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4608,22 +4608,22 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0000065866</t>
+          <t>0000007671</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>1288575479</t>
+          <t>1241061475</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>288733854</t>
+          <t>241219855</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2022-06-03</t>
+          <t>20220603</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>70050159016</t>
+          <t>93090715091</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ul. Gdańska 41/21, 85-005 Bydgoszcz</t>
+          <t>ul. Mariacka 101/51, 40-014 Katowice</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4665,22 +4665,22 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>0000065963</t>
+          <t>0000007768</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>1288654664</t>
+          <t>1241140660</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>288892239</t>
+          <t>241299044</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2019-12-31</t>
+          <t>31/12/2019</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>71060260367</t>
+          <t>94101416442</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Pawlak</t>
+          <t>Pawlak-Sikora</t>
         </is>
       </c>
     </row>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ul Dworcowa 58, 85-009 Bydgoszcz</t>
+          <t>ul Warszawska 118, 40-009 Katowice</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -4722,22 +4722,22 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>0000066060</t>
+          <t>0000007865</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>1288813045</t>
+          <t>1241219858</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>288892239</t>
+          <t>241457425</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2017-07-12</t>
+          <t>2017/12/07</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>72070361752</t>
+          <t>95112117838</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -4769,7 +4769,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ulica Szeroka 75, 87-100 Toruń</t>
+          <t>ulica Krakowskie Przedmieście 135, 20-002 Lublin</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -4779,22 +4779,22 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>0000066157</t>
+          <t>0000007962</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>1288813045</t>
+          <t>1241299047</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>288971424</t>
+          <t>241457425</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2017-05-13</t>
+          <t>13-05-2017</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4804,7 +4804,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>73080463100</t>
+          <t>96122819189</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -4836,22 +4836,22 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>0000066254</t>
+          <t>0000008059</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>1288892234</t>
+          <t>1241378232</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>289050614</t>
+          <t>241536610</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2017-08-11</t>
+          <t>2017-11-08</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>74090564496</t>
+          <t>97010720570</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ul. 3 Maja 109/73, 35-030 Rzeszów</t>
+          <t>ul. Lipowa 169/13, 15-424 Białystok</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4893,22 +4893,22 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>0000066351</t>
+          <t>0000008156</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>1289129807</t>
+          <t>1241457428</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>289129801</t>
+          <t>241615806</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2017-12-21</t>
+          <t>20171221</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>75100665846</t>
+          <t>98021421928</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>ul Piłsudskiego 126, 35-074 Rzeszów</t>
+          <t>ul Sienkiewicza 6, 15-092 Białystok</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4950,22 +4950,22 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>0000066448</t>
+          <t>0000008253</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>1289129807</t>
+          <t>1241536613</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>289208995</t>
+          <t>241694993</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2020-12-21</t>
+          <t>21/12/2020</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4975,7 +4975,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>76110767232</t>
+          <t>99032123315</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>ulica Sienkiewicza 143, 25-007 Kielce</t>
+          <t>ulica Gdańska 23, 85-005 Bydgoszcz</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>0000066545</t>
+          <t>0000008350</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>289288184</t>
+          <t>241774189</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2020-10-18</t>
+          <t>2020/18/10</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>77120868580</t>
+          <t>00242824660</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Warszawska 160, 25-512 Kielce</t>
+          <t>os. Dworcowa 40, 85-009 Bydgoszcz</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5064,22 +5064,22 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>0000066642</t>
+          <t>000000844</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>1289208990</t>
+          <t>1241694996</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>289446565</t>
+          <t>241853374</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2021-08-26</t>
+          <t>26-08-2021</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>78010969970</t>
+          <t>01250726054</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ul. Kościuszki 177/35, 10-504 Olsztyn</t>
+          <t>ul. Szeroka 57/65, 87-100 Toruń</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5121,22 +5121,22 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>0000066739</t>
+          <t>0000008544</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>1289367375</t>
+          <t>1241774181</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>289446565</t>
+          <t>242090949</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2018-09-20</t>
+          <t>2018-20-09</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>79021071320</t>
+          <t>02261427402</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ul Dąbrowszczaków 14, 10-540 Olsztyn</t>
+          <t>ul Chełmińska 74, 87-100 Toruń</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -5178,22 +5178,22 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>0000066836</t>
+          <t>0000008641</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>1289367375</t>
+          <t>1241853377</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>389525750</t>
+          <t>342090949</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>20251017</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>80031172714</t>
+          <t>03272128799</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -5225,7 +5225,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ulica Krakowska 31, 45-018 Opole</t>
+          <t>ulica 3 Maja 91, 35-030 Rzeszów</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -5235,22 +5235,22 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>0000066933</t>
+          <t>0000008738</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>1289446560</t>
+          <t>1241932562</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>289604946</t>
+          <t>242090949</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2021-11-18</t>
+          <t>18/11/2021</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -5260,7 +5260,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>81041274063</t>
+          <t>04282830142</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Ozimska 48, 45-057 Opole</t>
+          <t>Piłsudskiego 108, 35-074 Rzeszów</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -5292,22 +5292,22 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>0000067030</t>
+          <t>0000008835</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>1289525756</t>
+          <t>1242011752</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>289684135</t>
+          <t>242170134</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2019-01-11</t>
+          <t>2019/11/01</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>82051375458</t>
+          <t>05290731535</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -5339,7 +5339,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ul. Bohaterów Westerplatte 65/87, 65-034 Zielona Góra</t>
+          <t>ul. Sienkiewicza 125/27, 25-007 Kielce</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -5349,22 +5349,22 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0000067127</t>
+          <t>0000008932</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>1289604941</t>
+          <t>1242090941</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>289763320</t>
+          <t>242249321</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>29-08-2024</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -5374,7 +5374,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>83061476805</t>
+          <t>60101432883</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ul Kupiecka 82, 65-058 Zielona Góra</t>
+          <t>ul Warszawska 142, 25-512 Kielce</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -5406,22 +5406,22 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>0000067224</t>
+          <t>0000009029</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>1289684130</t>
+          <t>1242170137</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>289842516</t>
+          <t>242328517</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-23-04</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>84071578192</t>
+          <t>61112134270</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ulica Świętojańska 99, 81-372 Gdynia</t>
+          <t>ulica Kościuszki 159, 10-504 Olsztyn</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -5463,22 +5463,22 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>0000067321</t>
+          <t>0000009126</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>1289763326</t>
+          <t>1242249324</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>289921701</t>
+          <t>242407702</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2023-01-15</t>
+          <t>20230115</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>85081679549</t>
+          <t>62122835629</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>10 Lutego 116, 81-364 Gdynia</t>
+          <t>Dąbrowszczaków 176, 10-540 Olsztyn</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -5520,22 +5520,22 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>0000067418</t>
+          <t>0000009223</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>1289842511</t>
+          <t>1242407705</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>290080089</t>
+          <t>242566085</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2017-01-16</t>
+          <t>16/01/2017</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -5545,7 +5545,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>86091780937</t>
+          <t>63010737018</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>os. Bolesława Prusa 133/49, 05-800 Pruszków</t>
+          <t>ul. Krakowska 13/79, 45-018 Opole</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -5577,22 +5577,22 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>0000067515</t>
+          <t>0000009320</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>1289921707</t>
+          <t>1242407705</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>290080089</t>
+          <t>242566085</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2020-11-15</t>
+          <t>2020/15/11</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -5602,7 +5602,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>87101882289</t>
+          <t>64021438367</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ul Kościuszki 150, 05-500 Piaseczno</t>
+          <t>ul Ozimska 30, 45-057 Opole</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -5634,22 +5634,22 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>0000067612</t>
+          <t>0000009417</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>1290000893</t>
+          <t>1242486892</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>290159276</t>
+          <t>242645270</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2022-01-04</t>
+          <t>04-01-2022</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>88111983674</t>
+          <t>75032139753</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -5681,7 +5681,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ulica Sienkiewicza 167, 32-020 Wieliczka</t>
+          <t>ulica Bohaterów Westerplatte 47, 65-034 Zielona Góra</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -5691,22 +5691,22 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>0000067709</t>
+          <t>0000009514</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>1290080082</t>
+          <t>1242566088</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>290238461</t>
+          <t>242724466</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2019-03-16</t>
+          <t>2019-16-03</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -5716,7 +5716,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>89122085021</t>
+          <t>66042841106</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Dąbrowskiego 4, 32-600 Oświęcim</t>
+          <t>Kupiecka 64, 65-058 Zielona Góra</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -5748,22 +5748,22 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>0000067806</t>
+          <t>0000009611</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>1290238465</t>
+          <t>1242645273</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>290317657</t>
+          <t>242803651</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>20240416</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>90012186410</t>
+          <t>67050742490</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>21/11, 38-400 Krosno</t>
+          <t>ul. Świętojańska 81/41, 81-372 Gdynia</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -5805,22 +5805,22 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>0000067903</t>
+          <t>0000009708</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>1290238465</t>
+          <t>1242724469</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>290396846</t>
+          <t>242882840</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2018-05-28</t>
+          <t>28/05/2018</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>91022287768</t>
+          <t>68061443848</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -5862,22 +5862,22 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>0000068000</t>
+          <t>0000009805</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>1290317650</t>
+          <t>1242803654</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>290476031</t>
+          <t>242962036</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2022-04-16</t>
+          <t>2022/16/04</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -5887,7 +5887,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>92032389154</t>
+          <t>69072145235</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -5909,7 +5909,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>ulica Długa 55, 58-100 Świdnica</t>
+          <t>ulica Bolesława Prusa 115, 05-800 Pruszków</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -5919,22 +5919,22 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>0000068097</t>
+          <t>0000009902</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>1290476035</t>
+          <t>1242882843</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>290555227</t>
+          <t>243041226</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>01-12-2022</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -5944,7 +5944,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>93042490504</t>
+          <t>70082846584</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Wojska Polskiego 72, 57-300 Kłodzko</t>
+          <t>Kościuszki 132, 05-500 Piaseczno</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -5976,22 +5976,22 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>0000068194</t>
+          <t>0000009999</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>1290476035</t>
+          <t>1242962039</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>290634412</t>
+          <t>243120411</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6001,7 +6001,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>94052591890</t>
+          <t>71090747977</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>ul. Chrobrego 89/63, 62-200 Gniezno</t>
+          <t>ul. Sienkiewicza 149/3, 32-020 Wieliczka</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6033,22 +6033,22 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>0000068291</t>
+          <t>0000010096</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>1290555220</t>
+          <t>1243041229</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>290713608</t>
+          <t>243199602</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>20240325</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>95062693248</t>
+          <t>72101449329</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>ul Słowiańska 106, 64-100 Leszno</t>
+          <t>ul Dąbrowskiego 166, 32-600 Oświęcim</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6090,22 +6090,22 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>0000068388</t>
+          <t>0000010193</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>1290634416</t>
+          <t>1243120414</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>290792795</t>
+          <t>243278796</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>22/08/2024</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6115,7 +6115,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>96072794633</t>
+          <t>73112150718</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -6137,7 +6137,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>ulica Gdańska 123, 83-110 Tczew</t>
+          <t>ulica Rynek 3, 38-400 Krosno</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>0000068485</t>
+          <t>0000010290</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>1290713601</t>
+          <t>1243199605</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2021-08-19</t>
+          <t>2021/19/08</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -6172,7 +6172,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>97082895981</t>
+          <t>74122852069</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -6189,12 +6189,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Baltic eMd Supply Holding S.A.</t>
+          <t>Baltic Med Supply Holding S.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>140, 84-200 Wejherowo</t>
+          <t>Mickiewicza 20, 39-300 Mielec</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -6204,22 +6204,22 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>0000068582</t>
+          <t>0000010387</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>1290792799</t>
+          <t>1243278799</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>290951176</t>
+          <t>243437177</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>17-08-2025</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -6229,7 +6229,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>98090197373</t>
+          <t>75010753457</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -6239,7 +6239,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>Wiśniewski</t>
+          <t>Wiśinewski</t>
         </is>
       </c>
     </row>
@@ -6251,7 +6251,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>ul. Głęboka 157/25, 43-400 Cieszyn</t>
+          <t>ul. Długa 37/55, 58-100 Świdnica</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -6261,22 +6261,22 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>0000068679</t>
+          <t>0000010484</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>1290871984</t>
+          <t>1243357984</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>291030366</t>
+          <t>243516362</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2020-11-26</t>
+          <t>2020-26-11</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -6286,7 +6286,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>99100298723</t>
+          <t>76021454805</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -6308,7 +6308,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>ul Małachowskiego 174, 42-500 Będzin</t>
+          <t>ul Wojska Polskiego 54, 57-300 Kłodzko</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -6318,22 +6318,22 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>0000068776</t>
+          <t>0000010581</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>1291109557</t>
+          <t>2243516365</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>291109553</t>
+          <t>243595551</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2019-05-13</t>
+          <t>20190513</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -6343,7 +6343,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>00310300117</t>
+          <t>77032156193</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>ulica Królowej Jadwigi 11, 88-100 Inowrocław</t>
+          <t>ulica Chrobrego 71, 62-200 Gniezno</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -6375,22 +6375,22 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>0000068873</t>
+          <t>0000010678</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>1291109557</t>
+          <t>1243516365</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>291188742</t>
+          <t>243674747</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2024-11-27</t>
+          <t>27/11/2024</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>01320401465</t>
+          <t>78042857542</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Wybickiego 28, 86-300 Grudziądz</t>
+          <t>Słowiańska 88, 64-100 Leszno</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -6432,22 +6432,22 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>0000068970</t>
+          <t>0000010775</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>1291109557</t>
+          <t>1243595554</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>291267938</t>
+          <t>243753932</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2023-10-13</t>
+          <t>2023/13/10</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>02210502855</t>
+          <t>79050758935</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -6479,7 +6479,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>ul. Czarnieckiego 45/77, 14-100 Ostróda</t>
+          <t>105/17, 83-110 Tczew</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -6489,22 +6489,22 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>0000069067</t>
+          <t>0000010872</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>1291188746</t>
+          <t>1243753935</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>291347123</t>
+          <t>243833128</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2021-08-03</t>
+          <t>03-08-2021</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>03220604203</t>
+          <t>80061460287</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>ul Warszawska 62, 11-500 Giżycko</t>
+          <t>ul Sobieskiego 122, 84-200 Wejherowo</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -6546,22 +6546,22 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>0000069164</t>
+          <t/>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>1291267931</t>
+          <t>1243753935</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>291426319</t>
+          <t>243912313</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2024-01-06</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -6571,7 +6571,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>04230705599</t>
+          <t>81072161673</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>Szymanski</t>
+          <t>Szymański</t>
         </is>
       </c>
     </row>
@@ -6593,7 +6593,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>79, 24-100 Puławy</t>
+          <t>ulica Głęboka 139, 43-400 Cieszyn</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -6603,22 +6603,22 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>0000069261</t>
+          <t>0000011066</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>1291347127</t>
+          <t>1243833120</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>291505504</t>
+          <t>243991502</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2021-02-07</t>
+          <t>20210207</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -6628,7 +6628,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>05240806946</t>
+          <t>82082863023</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -6650,7 +6650,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Staszica 96, 22-400 Zamość</t>
+          <t>Małachowskiego 156, 42-500 Będzin</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -6660,22 +6660,22 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>0000069358</t>
+          <t>0000011163</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>1291426312</t>
+          <t>1243912316</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>291584691</t>
+          <t>244070690</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2023-11-30</t>
+          <t>30/11/2023</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -6685,7 +6685,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>60050908338</t>
+          <t>83090764416</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>ul. 3 Maja 113/39, 16-300 Augustów</t>
+          <t>os. Królowej Jadwigi 173/69, 88-100 Inowrocław</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -6717,22 +6717,22 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>0000069455</t>
+          <t>0000011260</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>1291505508</t>
+          <t>1243991505</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>291663887</t>
+          <t>244149888</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025/17/08</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>61061009685</t>
+          <t>84101465768</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -6764,7 +6764,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>ul Kościuszki 130, 16-400 Suwałki</t>
+          <t>ul Wybickiego 10, 86-300 Grudziądz</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -6774,22 +6774,22 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>0000069552</t>
+          <t>0000011357</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>1291584695</t>
+          <t>1244070693</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>291743072</t>
+          <t>244229073</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2023-01-04</t>
+          <t>04-01-2023</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -6799,7 +6799,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>62071111074</t>
+          <t>85112167155</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -6831,22 +6831,22 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>0000069649</t>
+          <t>0000011454</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>1291663880</t>
+          <t>1244149880</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>291822268</t>
+          <t>244308269</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2023-07-04</t>
+          <t>2023-04-07</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>63081212421</t>
+          <t>86122868504</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -6888,22 +6888,22 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>0000069746</t>
+          <t>0000011551</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>1291743076</t>
+          <t>1244229076</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>291901453</t>
+          <t>244387458</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2021-01-07</t>
+          <t>20210107</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -6913,7 +6913,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>64091313816</t>
+          <t>87010769893</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -6935,7 +6935,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>ul. Rynek 1/1, 68-200 Żary</t>
+          <t>ul. Lubelska 61/31, 24-100 Puławy</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -6945,22 +6945,22 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>0000069843</t>
+          <t>0000011648</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>1291822261</t>
+          <t>1244308261</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>291980642</t>
+          <t>244466643</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2021-04-21</t>
+          <t>21/04/2021</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -6970,7 +6970,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>65101415168</t>
+          <t>88021471245</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -6980,7 +6980,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>Pawlak</t>
+          <t>Pawlak-Sikora</t>
         </is>
       </c>
     </row>
@@ -6992,7 +6992,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>18, 66-200 Świebodzin</t>
+          <t>ul Staszica 78, 22-400 Zamość</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7002,22 +7002,22 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>0000069940</t>
+          <t>0000011745</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>1291901457</t>
+          <t>1244387450</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>292059834</t>
+          <t>244545839</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2023-06-09</t>
+          <t>2023/09/06</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7027,7 +7027,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>66111516553</t>
+          <t>89032172631</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>ulica Armii Krajowej 35, 78-100 Kołobrzeg</t>
+          <t>ulica 3 Maja 95, 16-300 Augustów</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -7059,22 +7059,22 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>0000070037</t>
+          <t>0000011842</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>1291980646</t>
+          <t>1244466646</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>292218215</t>
+          <t>244625024</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2022-02-05</t>
+          <t>05-02-2022</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>67121617900</t>
+          <t>90042873980</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Piłsudskiego 52, 73-110 Stargard</t>
+          <t>Kościuszki 112, 16-400 Suwałki</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -7116,22 +7116,22 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>0000070134</t>
+          <t>0000011939</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>1292059838</t>
+          <t>1244545831</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>292218215</t>
+          <t>244783409</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2018-06-10</t>
+          <t>2018-10-06</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>68011719292</t>
+          <t>91050775374</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -7163,7 +7163,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>ul. Mickiewicza 69/53, 27-600 Sandomierz</t>
+          <t>ul. Piastowska 129/83, 48-300 Nysa</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -7173,22 +7173,22 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>0000070231</t>
+          <t>0000012036</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>1292139023</t>
+          <t>1244625027</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>292297404</t>
+          <t>244783409</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2018-01-23</t>
+          <t>20180123</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>69021820642</t>
+          <t>92061476722</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -7220,7 +7220,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>os. Sienkiewicza 86, 27-400 Ostrowiec Świętokrzyski</t>
+          <t>ul Długa 146, 49-300 Brzeg</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -7230,22 +7230,22 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>0000070328</t>
+          <t>0000012133</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>1292218219</t>
+          <t>1244704212</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>292376598</t>
+          <t>244862592</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>18/08/2024</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -7255,7 +7255,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>70031922037</t>
+          <t>93072178119</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -7277,7 +7277,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>ulica Marszałkowska 103, 00-590 Warszawa</t>
+          <t>163, 68-200 Żary</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -7287,22 +7287,22 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>0000070425</t>
+          <t>0000012230</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>1292297408</t>
+          <t>1244783401</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>292455783</t>
+          <t>244941788</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2020-01-18</t>
+          <t>2020/18/01</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -7312,7 +7312,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>71042023384</t>
+          <t>94082879469</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -7334,7 +7334,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Krakowskie Przedmieście 120, 00-071 Warszawa</t>
+          <t>Sikorskiego 180, 66-200 Świebodzin</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -7344,22 +7344,22 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>0000070522</t>
+          <t>0000012327</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>1292376591</t>
+          <t>1244862595</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>292534979</t>
+          <t>245020978</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>12-11-2024</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -7369,7 +7369,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>72052124779</t>
+          <t>95090780855</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>ul. Floriańska 137/15, 31-019 Kraków</t>
+          <t>ul. Armii Krajowej 17/45, 78-100 Kołobrzeg</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -7401,22 +7401,22 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>0000070619</t>
+          <t>0000012424</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>1292455787</t>
+          <t>1244941780</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>292614164</t>
+          <t>245100163</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2018-03-04</t>
+          <t>2018-04-03</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>73062226127</t>
+          <t>96101482207</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -7448,7 +7448,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>ul Długa 154, 31-147 Kraków</t>
+          <t>ul Piłsudskiego 34, 73-110 Stargard</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -7458,22 +7458,22 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>0000070716</t>
+          <t>0000012521</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>1292534972</t>
+          <t>1245020970</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>292693353</t>
+          <t>245179354</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2020-08-14</t>
+          <t>20200814</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -7483,7 +7483,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>74072327512</t>
+          <t>97112183594</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -7505,7 +7505,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>ulica Piotrkowska 171, 90-102 Łódź</t>
+          <t>ulica Mickiewicza 51, 27-600 Sandomierz</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -7515,22 +7515,22 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>0000070813</t>
+          <t>0000012618</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>1292614168</t>
+          <t>1245100166</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>292772549</t>
+          <t>245337735</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2019-11-06</t>
+          <t>06/11/2019</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>75082428860</t>
+          <t>98122884943</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -7562,7 +7562,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Zachodnia 8, 90-402 Łódź</t>
+          <t>Sienkiewicza 68, 27-400 Ostrowiec Świętokrzyski</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -7572,22 +7572,22 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>0000070910</t>
+          <t>0000012715</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>1292693357</t>
+          <t>1245179357</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>292851734</t>
+          <t>245337735</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025/20/05</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -7597,7 +7597,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>76092530259</t>
+          <t>99010786332</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -7619,7 +7619,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>ul. Świdnicka 25/67, 50-066 Wrocław</t>
+          <t>ul. Marszałkowska 85/7, 00-590 Warszawa</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -7629,22 +7629,22 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>0000071007</t>
+          <t>0000012812</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>1292772542</t>
+          <t>1245258542</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>293089300</t>
+          <t>245416920</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2022-05-02</t>
+          <t>02-05-2022</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -7654,7 +7654,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>77102631609</t>
+          <t>00221487686</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>ul Legnicka 42, 54-203 Wrocław</t>
+          <t>ul Krakowskie Przedmieście 102, 00-071 Warszawa</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -7686,22 +7686,22 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>0000071104</t>
+          <t>0000012909</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>1292851738</t>
+          <t>1245337738</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>293089300</t>
+          <t>245575305</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2017-01-03</t>
+          <t>2017-03-01</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -7711,7 +7711,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>78112732995</t>
+          <t>01232189073</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -7733,7 +7733,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>ulica Święty Marcin 59, 61-806 Poznań</t>
+          <t>ulica Floriańska 119, 31-019 Kraków</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -7743,22 +7743,22 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>0000071201</t>
+          <t>0000013006</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>1292930923</t>
+          <t>1245416923</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>293089300</t>
+          <t>245575305</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2018-08-19</t>
+          <t>20180819</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -7768,7 +7768,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>79122834343</t>
+          <t>02242890425</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -7790,7 +7790,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Głogowska 76, 60-734 Poznań</t>
+          <t>Długa 136, 31-147 Kraków</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -7800,22 +7800,22 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>0000071298</t>
+          <t>0000013103</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>1293010113</t>
+          <t>1245496112</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>293168494</t>
+          <t>245654499</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2020-07-26</t>
+          <t>26/07/2020</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -7825,7 +7825,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>80010135738</t>
+          <t>03250791818</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -7847,7 +7847,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>ul. Długa 93/29, 80-831 Gdańsk</t>
+          <t>ul. Piotrkowska 153/59, 90-102 Łódź</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -7857,22 +7857,22 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>0000071395</t>
+          <t>000001320</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>1293089304</t>
+          <t>1245575308</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>293326875</t>
+          <t>245733684</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2019-01-20</t>
+          <t>2019/20/01</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>81020237087</t>
+          <t>04261493168</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -7914,22 +7914,22 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>0000071492</t>
+          <t>0000013297</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>1293168498</t>
+          <t>1245654491</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>293326875</t>
+          <t>245892069</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2023-07-26</t>
+          <t>26-07-2023</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -7939,7 +7939,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>82030338472</t>
+          <t>05272194554</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -7961,7 +7961,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>ulica Jagiellońska 127, 70-435 Szczecin</t>
+          <t>ulica Świdnicka 7, 50-066 Wrocław</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -7971,22 +7971,22 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>0000071589</t>
+          <t>0000013394</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>1293247683</t>
+          <t>1245733687</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>293406060</t>
+          <t>245892069</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2025-01-27</t>
+          <t>2025-27-01</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -7996,7 +7996,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>83040439829</t>
+          <t>60082895909</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -8018,7 +8018,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Wyszyńskiego 144, 70-200 Szczecin</t>
+          <t>Legnicka 24, 54-203 Wrocław</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -8028,22 +8028,22 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>0000071686</t>
+          <t>0000013491</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>1293326879</t>
+          <t>1245812872</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>293564445</t>
+          <t>345971254</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2019-03-16</t>
+          <t>20190316</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -8053,7 +8053,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>84050541218</t>
+          <t>61090797294</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>ul. Mariacka 161/81, 40-014 Katowice</t>
+          <t>ul. Święty Marcin 41/21, 61-806 Poznań</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -8085,22 +8085,22 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>0000071783</t>
+          <t>0000013588</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>1293406064</t>
+          <t>1245892061</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>293564445</t>
+          <t>246050444</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2017-05-13</t>
+          <t>13/05/2017</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -8110,7 +8110,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>85060642566</t>
+          <t>62101498645</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>ul Warszawska 178, 40-009 Katowice</t>
+          <t>ul Głogowska 58, 60-734 Poznań</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -8142,22 +8142,22 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>0000071880</t>
+          <t>0000013685</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>1293485253</t>
+          <t>1245971257</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>293643630</t>
+          <t>246129631</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2019-10-25</t>
+          <t>2019/25/10</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -8167,7 +8167,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>86070743951</t>
+          <t>63112100035</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -8189,7 +8189,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>ulica Krakowskie Przedmieście 15, 20-002 Lublin</t>
+          <t>ulica Długa 75, 80-831 Gdańsk</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -8199,22 +8199,22 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>0000071977</t>
+          <t>0000013782</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>1293564449</t>
+          <t>1246050447</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>293722826</t>
+          <t>246208827</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2017-06-30</t>
+          <t>30-06-2017</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -8224,7 +8224,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>87080845309</t>
+          <t>64122801385</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -8246,7 +8246,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Narutowicza 32, 20-004 Lublin</t>
+          <t>Grunwaldzka 92, 80-236 Gdańsk</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -8256,22 +8256,22 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>0000072074</t>
+          <t>0000013879</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>1293643634</t>
+          <t>1246129634</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>293802011</t>
+          <t>246288016</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2024-28-12</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -8281,7 +8281,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>88090946695</t>
+          <t>65010702773</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -8303,7 +8303,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>ul. Lipowa 49/43, 15-424 Białystok</t>
+          <t>ul. Jagiellońska 109/73, 70-435 Szczecin</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -8313,22 +8313,22 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>0000072171</t>
+          <t>0000013976</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>1293802015</t>
+          <t>1246288019</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>293881200</t>
+          <t>246367201</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2020-08-17</t>
+          <t>20200817</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -8338,7 +8338,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>89101048045</t>
+          <t>66021404122</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -8360,7 +8360,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>ul Sienkiewicza 66, 15-092 Białystok</t>
+          <t>os. Wyszyńskiego 126, 70-200 Szczecin</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -8370,22 +8370,22 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>0000072268</t>
+          <t>0000014073</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>1293802015</t>
+          <t>1246288019</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>293960394</t>
+          <t>246446395</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
+          <t>09/09/2021</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>90111149439</t>
+          <t>67032105518</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -8417,7 +8417,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>ulica Gdańska 83, 85-005 Bydgoszcz</t>
+          <t>ulica Mariacka 143, 40-014 Katowice</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -8427,22 +8427,22 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>0000072365</t>
+          <t>0000014170</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>1293881204</t>
+          <t>1246367204</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>294039586</t>
+          <t>246525580</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2025-02-02</t>
+          <t>2025/02/02</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -8452,7 +8452,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>91121250780</t>
+          <t>78042806868</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Dworcowa 100, 85-009 Bydgoszcz</t>
+          <t>Warszawska 160, 40-009 Katowice</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -8484,22 +8484,22 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>0000072462</t>
+          <t>0000014267</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>1293960398</t>
+          <t>1246446398</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>294118771</t>
+          <t>246604776</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2018-09-11</t>
+          <t>11-09-2018</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>92011352171</t>
+          <t>69050708252</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -8531,7 +8531,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>ul. Szeroka 117/5, 87-100 Toruń</t>
+          <t>ul. Krakowskie Przedmieście 177/35, 20-002 Lublin</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -8541,22 +8541,22 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>0000072559</t>
+          <t>0000014364</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>1294118775</t>
+          <t>1246525583</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>294197960</t>
+          <t>246683965</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2021-01-29</t>
+          <t>2021-29-01</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -8566,7 +8566,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>93021453528</t>
+          <t>70061409609</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -8588,7 +8588,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>ul Chełmińska 134, 87-100 Toruń</t>
+          <t>ul Narutowicza 14, 20-004 Lublin</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -8598,22 +8598,22 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>0000072656</t>
+          <t>0000014461</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>1294118775</t>
+          <t>1246604779</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>294277156</t>
+          <t>246763150</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2022-07-31</t>
+          <t>20220731</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -8623,7 +8623,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>94031554913</t>
+          <t>71072110999</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -8645,7 +8645,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>ulica 3 Maja 151, 35-030 Rzeszów</t>
+          <t>ulica Lipowa 31, 15-424 Białystok</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -8655,22 +8655,22 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>0000072753</t>
+          <t>0000014558</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>1294197964</t>
+          <t>1246683968</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>294356341</t>
+          <t>246842346</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2023-04-15</t>
+          <t>15/04/2023</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -8680,7 +8680,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>95041656262</t>
+          <t>72082812349</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -8702,7 +8702,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Piłsudskiego 168, 35-074 Rzeszów</t>
+          <t>Sienkiewicza 48, 15-092 Białystok</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -8712,22 +8712,22 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>0000072850</t>
+          <t>0000014655</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>1294356345</t>
+          <t>1246763153</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>294435537</t>
+          <t>246921531</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025/28/08</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -8737,7 +8737,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>96051757657</t>
+          <t>73090713732</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -8759,7 +8759,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>ul. Sienkiewicza 5/57, 25-007 Kielce</t>
+          <t>ul. Gdańska 65/87, 85-005 Bydgoszcz</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -8769,22 +8769,22 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>0000072947</t>
+          <t>0000014752</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>1294356345</t>
+          <t>1246842349</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>294514722</t>
+          <t>247000721</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2022-10-30</t>
+          <t>30-10-2022</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -8794,7 +8794,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>97061859005</t>
+          <t>74101415085</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>ul Warszawska 22, 25-512 Kielce</t>
+          <t>ul Dworcowa 82, 85-009 Bydgoszcz</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -8826,22 +8826,22 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>0000073044</t>
+          <t>0000014849</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>1294435530</t>
+          <t>1246921534</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>294593911</t>
+          <t>247079912</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2017-01-31</t>
+          <t>2017-31-01</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -8851,7 +8851,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>98071960394</t>
+          <t>75112116471</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -8873,7 +8873,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>os. Kościuszki 39, 10-504 Olsztyn</t>
+          <t>ulica Szeroka 99, 87-100 Toruń</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -8883,22 +8883,22 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>0000073141</t>
+          <t>0000014946</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>1294514726</t>
+          <t>1247000724</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>294673107</t>
+          <t>247159108</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2020-12-20</t>
+          <t>20201220</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -8908,7 +8908,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>09082061740</t>
+          <t>76122817820</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -8930,7 +8930,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Dąbrowszczaków 56, 10-540 Olsztyn</t>
+          <t>Chełmińska 116, 87-100 Toruń</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -8940,22 +8940,22 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>0000073238</t>
+          <t>0000015043</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>1294593915</t>
+          <t>1247079915</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>294752290</t>
+          <t>247238291</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2019-09-28</t>
+          <t>28/09/2019</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -8965,7 +8965,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>00292163131</t>
+          <t>77010719219</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -8987,7 +8987,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>ul. Krakowska 73/19, 45-018 Opole</t>
+          <t>ul. 3 Maja 133/49, 35-030 Rzeszów</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -8997,22 +8997,22 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>0000073335</t>
+          <t>0000015140</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>1294673100</t>
+          <t>1247159100</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>294831486</t>
+          <t>247317487</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2023-11-13</t>
+          <t>2023/13/11</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -9022,7 +9022,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>01302264482</t>
+          <t>78021420561</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -9039,12 +9039,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Amber Paymen Spółka Akcyjna</t>
+          <t>Amber Paymen pSółka Akcyjna</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>ul Ozimska 90, 45-057 Opole</t>
+          <t>ul Piłsudskiego 150, 35-074 Rzeszów</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -9054,22 +9054,22 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>0000073432</t>
+          <t>0000015237</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>1294752294</t>
+          <t>1247238294</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>294910671</t>
+          <t>247396676</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2020-07-16</t>
+          <t>16-07-2020</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -9079,7 +9079,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>02312365877</t>
+          <t>79032121957</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>oWźniak</t>
+          <t>Woźniak</t>
         </is>
       </c>
     </row>
@@ -9101,7 +9101,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>ulica Bohaterów Westerplatte 107, 65-034 Zielona Góra</t>
+          <t>ulica Sienkiewicza 167, 25-007 Kielce</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -9111,22 +9111,22 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>0000073529</t>
+          <t>0000015334</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>1294910675</t>
+          <t>2247396679</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>294989862</t>
+          <t>247475861</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2019-01-27</t>
+          <t>2019-27-01</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>03322467225</t>
+          <t>80042823306</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -9158,7 +9158,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Kupiecka 124, 65-058 Zielona Góra</t>
+          <t>Warszawska 4, 25-512 Kielce</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -9168,22 +9168,22 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>0000073626</t>
+          <t>0000015431</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>1294910675</t>
+          <t>1247396679</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>295069052</t>
+          <t>247555057</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2019-01-01</t>
+          <t>20190101</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -9193,7 +9193,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>04212568615</t>
+          <t>81050724690</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -9215,7 +9215,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>ul. Świętojańska 141/71, 81-372 Gdynia</t>
+          <t>ul. Kościuszki 21/11, 10-504 Olsztyn</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -9225,22 +9225,22 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>0000073723</t>
+          <t>0000015528</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>1294989866</t>
+          <t>1247475864</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>295148248</t>
+          <t>247634242</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2023-04-03</t>
+          <t>03/04/2023</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -9250,7 +9250,7 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>05222669963</t>
+          <t>82061426049</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>Pawlak</t>
+          <t>Pawlak-Sikora</t>
         </is>
       </c>
     </row>
@@ -9272,7 +9272,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>ul 10 Lutego 158, 81-364 Gdynia</t>
+          <t>ul Dąbrowszczaków 38, 10-540 Olsztyn</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -9282,22 +9282,22 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>0000073820</t>
+          <t>0000015625</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>1295069056</t>
+          <t>1247634245</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>295227433</t>
+          <t>247713438</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2017-11-29</t>
+          <t>2017-29-11 08:02</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -9307,7 +9307,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>60032771358</t>
+          <t>83072127435</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -9329,7 +9329,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>ulica Bolesława Prusa 175, 05-800 Pruszków</t>
+          <t>ulica Krakowska 55, 45-018 Opole</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -9339,22 +9339,22 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>0000073917</t>
+          <t>0000015722</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>1295148241</t>
+          <t>1247634245</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>295306629</t>
+          <t>247792627</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>30-10-2025</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -9364,7 +9364,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>61042872705</t>
+          <t>84082828785</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Kościuszki 12, 05-500 Piaseczno</t>
+          <t>Ozimska 72, 45-057 Opole</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -9396,22 +9396,22 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>0000074014</t>
+          <t>0000015819</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>1295227437</t>
+          <t>1247713430</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>295385818</t>
+          <t>247871812</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2022-05-08</t>
+          <t>2022-08-05</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>62050174098</t>
+          <t>85090730172</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -9443,7 +9443,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>ul. Sienkiewicza 29/33, 32-020 Wieliczka</t>
+          <t>ul. Bohaterów Westerplatte 89/63, 65-034 Zielona Góra</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -9453,22 +9453,22 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>0000074111</t>
+          <t>0000015916</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>1295306622</t>
+          <t>1247871815</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>295465003</t>
+          <t>247951008</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>20251006</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -9478,7 +9478,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>63060275445</t>
+          <t>86101431523</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -9500,7 +9500,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>ul Dąbrowskiego 46, 32-600 Oświęcim</t>
+          <t>ul Kupiecka 106, 65-058 Zielona Góra</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -9510,22 +9510,22 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>0000074208</t>
+          <t>0000016013</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2295385811</t>
+          <t>1247871815</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>295544197</t>
+          <t>248030196</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
+          <t>28/09/2021</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -9535,7 +9535,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>64070376830</t>
+          <t>87112132919</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>ulica Rynek 63, 38-400 Krosno</t>
+          <t>ulica Świętojańska 123, 81-372 Gdynia</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -9567,22 +9567,22 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>0000074305</t>
+          <t>0000016110</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>1295465007</t>
+          <t>1247951000</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>295623382</t>
+          <t>248109383</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2021-03-03</t>
+          <t>2021/03/03</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -9592,7 +9592,7 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>65080478189</t>
+          <t>88122834260</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -9614,7 +9614,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Mickiewicza 80, 39-300 Mielec</t>
+          <t>10 Lutego 140, 81-364 Gdynia</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -9624,22 +9624,22 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>0000074402</t>
+          <t>0000016207</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>1295544190</t>
+          <t>1248030199</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>295702578</t>
+          <t>248188572</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2021-12-23</t>
+          <t>23-12-2021</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -9649,7 +9649,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>66090579574</t>
+          <t>89010735658</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -9671,7 +9671,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>ul. Długa 97/85, 58-100 Świdnica</t>
+          <t>ul. Bolesława Prusa 157/25, 05-800 Pruszków</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -9681,22 +9681,22 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>0000074499</t>
+          <t>0000016304</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>1295623386</t>
+          <t>1248109386</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>295781767</t>
+          <t>248267768</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2021-03-21</t>
+          <t>2021-21-03</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -9706,7 +9706,7 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>67100680927</t>
+          <t>90021437006</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -9728,7 +9728,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>ul Wojska Polskiego 114, 57-300 Kłodzko</t>
+          <t>ul Kościuszki 174, 05-500 Piaseczno</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -9738,22 +9738,22 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>0000074596</t>
+          <t>0000016401</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>1295702571</t>
+          <t>1248188575</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>295860952</t>
+          <t>248346953</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2020-02-17</t>
+          <t>20200217</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -9763,7 +9763,7 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>68110782313</t>
+          <t>91032138393</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -9785,7 +9785,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>ulica Chrobrego 131, 62-200 Gniezno</t>
+          <t>ulica Sienkiewicza 11, 32-020 Wieliczka</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -9795,22 +9795,22 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>0000074693</t>
+          <t>0000016498</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>1295781760</t>
+          <t>1248267760</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>295940148</t>
+          <t>248426149</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2023-06-21</t>
+          <t>21/06/2023</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -9820,7 +9820,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>69120883661</t>
+          <t>92042839742</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Słowiańska 148, 64-100 Leszno</t>
+          <t>Dąbrowskiego 28, 32-600 Oświęcim</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -9852,22 +9852,22 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>0000074790</t>
+          <t>0000016595</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>1295860956</t>
+          <t>1248346956</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>296098529</t>
+          <t>248505334</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2019-11-09</t>
+          <t>2019/09/11</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>70010985051</t>
+          <t>93050741139</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -9899,7 +9899,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>ul. Gdańska 165/47, 83-110 Tczew</t>
+          <t>ul. Rynek 45/77, 38-400 Krosno</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -9909,22 +9909,22 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>0000074887</t>
+          <t>0000016692</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>1295940141</t>
+          <t>1248426141</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>296098529</t>
+          <t>248584523</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2018-03-07</t>
+          <t>07-03-2018</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -9934,7 +9934,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>71021086407</t>
+          <t>94061442488</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -9956,7 +9956,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>ul Sobieskiego 2, 84-200 Wejherowo</t>
+          <t>ul Mickiewicza 62, 39-300 Mielec</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -9966,22 +9966,22 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>0000074984</t>
+          <t>0000016789</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>1296019333</t>
+          <t>1248505337</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>296177714</t>
+          <t>248663719</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-20-03</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -9991,7 +9991,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>72031187793</t>
+          <t>95072143874</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>ulica Głęboka 19, 43-400 Cieszyn</t>
+          <t>os. Długa 79, 58-100 Świdnica</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -10023,22 +10023,22 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>0000075081</t>
+          <t>0000016886</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>1296098522</t>
+          <t>1248584526</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>296336093</t>
+          <t>248742904</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2023-11-26</t>
+          <t>20231126</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -10048,7 +10048,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>73041289141</t>
+          <t>96082845224</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -10070,7 +10070,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Małachowskiego 36, 42-500 Będzin</t>
+          <t>96, 57-300 Kłodzko</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -10080,22 +10080,22 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>0000075178</t>
+          <t>0000016983</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>1296177718</t>
+          <t>1248663711</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>296336093</t>
+          <t>248822098</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>17/11/2025</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -10105,7 +10105,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>74051390539</t>
+          <t>97090746617</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -10127,7 +10127,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>ul. Królowej Jadwigi 53/9, 88-100 Inowrocław</t>
+          <t>ul. Chrobrego 113/39, 62-200 Gniezno</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -10137,22 +10137,22 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>0000075275</t>
+          <t>0000017080</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>1296256903</t>
+          <t>1248742907</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>296415289</t>
+          <t>248901283</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2018-09-01</t>
+          <t>2018/01/09</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -10162,7 +10162,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>75061491887</t>
+          <t>98101447969</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -10184,7 +10184,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>ul Wybickiego 70, 86-300 Grudziądz</t>
+          <t>ul Słowiańska 130, 64-100 Leszno</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -10194,22 +10194,22 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>0000075372</t>
+          <t>0000017177</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>1296336097</t>
+          <t>1248822090</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>296494478</t>
+          <t>248980472</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2021-07-11</t>
+          <t>11-07-2021</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -10219,7 +10219,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>76071593273</t>
+          <t>99112149356</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>ulica Czarnieckiego 87, 14-100 Ostróda</t>
+          <t>ulica Gdańska 147, 83-110 Tczew</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -10251,22 +10251,22 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>0000075469</t>
+          <t>0000017274</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>1296415282</t>
+          <t>1248901286</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>296573663</t>
+          <t>249059664</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -10276,7 +10276,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>77081694620</t>
+          <t>00322850703</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -10298,7 +10298,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Warszawska 104, 11-500 Giżycko</t>
+          <t>Sobieskiego 164, 84-200 Wejherowo</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -10308,22 +10308,22 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>0000075566</t>
+          <t>0000017371</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>1296494471</t>
+          <t>1248980475</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>296652859</t>
+          <t>249218045</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>2018-11-05</t>
+          <t>20181105</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -10333,7 +10333,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>78091796016</t>
+          <t>01210752093</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -10355,7 +10355,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>ul. Lubelska 121/61, 24-100 Puławy</t>
+          <t>ul. Głęboka 1/1, 43-400 Cieszyn</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -10365,22 +10365,22 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>0000075663</t>
+          <t>0000017468</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>1296573667</t>
+          <t>1249059667</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>296732044</t>
+          <t>249218045</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2017-07-19</t>
+          <t>19/07/2017</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -10390,7 +10390,7 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>79101897367</t>
+          <t>02221453441</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -10412,7 +10412,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>ul Staszica 138, 22-400 Zamość</t>
+          <t>ul Małachowskiego 18, 42-500 Będzin</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -10422,22 +10422,22 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>0000075760</t>
+          <t>0000017565</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>1296652852</t>
+          <t>1249138852</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>296890429</t>
+          <t>249297234</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>2018-12-10</t>
+          <t>2018/10/12</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -10447,7 +10447,7 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>80111998751</t>
+          <t>03232154837</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -10469,7 +10469,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>ulica 3 Maja 155, 16-300 Augustów</t>
+          <t>ulica Królowej Jadwigi 35, 88-100 Inowrocław</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -10479,22 +10479,22 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>0000075857</t>
+          <t>0000017662</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>1296732048</t>
+          <t>1249218048</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>296890429</t>
+          <t>249455615</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2021-02-28</t>
+          <t>28-02-2021</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -10504,7 +10504,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>81122000101</t>
+          <t>04242856188</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -10536,22 +10536,22 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>0000075954</t>
+          <t>0000017759</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>1296811233</t>
+          <t>1249297237</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>296969616</t>
+          <t>249455615</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>2022-08-27</t>
+          <t>2022-27-08</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -10561,7 +10561,7 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>82012101492</t>
+          <t>05250757571</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -10583,7 +10583,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>ul. Piastowska 9/23, 48-300 Nysa</t>
+          <t>ul. Czarnieckiego 69/53, 14-100 Ostróda</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -10593,22 +10593,22 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>0000076051</t>
+          <t>0000017856</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>1296890422</t>
+          <t>1249376422</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>297048806</t>
+          <t>249534800</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>20251104</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -10618,7 +10618,7 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>83022202849</t>
+          <t>60061458925</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -10640,7 +10640,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>ul Długa 26, 49-300 Brzeg</t>
+          <t>ul Warszawska 86, 11-500 Giżycko</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -10650,22 +10650,22 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>0000076148</t>
+          <t>000001795</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>1297127993</t>
+          <t>1249455618</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>297207185</t>
+          <t>249613994</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2023-07-04</t>
+          <t>04/07/2023</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>84032304235</t>
+          <t>61072160315</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
@@ -10697,7 +10697,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>ulica Rynek 43, 68-200 Żary</t>
+          <t>ulica Lubelska 103, 24-100 Puławy</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -10707,22 +10707,22 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>0000076245</t>
+          <t>0000018050</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>1297127993</t>
+          <t>1249534803</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>297207185</t>
+          <t>249693183</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>2017-08-29</t>
+          <t>2017/29/08</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -10732,7 +10732,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>85042405583</t>
+          <t>62082861665</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -10754,7 +10754,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Sikorskiego 60, 66-200 Świebodzin</t>
+          <t>Staszica 120, 22-400 Zamość</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -10764,22 +10764,22 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>0000076342</t>
+          <t>0000018147</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>1297127993</t>
+          <t>1249613997</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>297286374</t>
+          <t>249772379</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2018-05-12</t>
+          <t>12-05-2018</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -10789,7 +10789,7 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>86052506978</t>
+          <t>63090763059</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -10811,7 +10811,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>ul. Armii Krajowej 77/75, 78-100 Kołobrzeg</t>
+          <t>ul. 3 Maja 137/15, 16-300 Augustów</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -10821,22 +10821,22 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>0000076439</t>
+          <t>0000018244</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>1297207189</t>
+          <t>1249693186</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>297444755</t>
+          <t>249851564</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2022-09-08</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -10846,7 +10846,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>87062608326</t>
+          <t>64101464400</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -10868,7 +10868,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>ul Piłsudskiego 94, 73-110 Stargard</t>
+          <t>ul Kościuszki 154, 16-400 Suwałki</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -10878,22 +10878,22 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>0000076536</t>
+          <t>0000018341</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>1297286378</t>
+          <t>1249772371</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>397444755</t>
+          <t>350009941</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2020-04-24</t>
+          <t>20200424</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -10903,7 +10903,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>88072709711</t>
+          <t>65112165797</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -10925,7 +10925,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>ulica Mickiewicza 111, 27-600 Sandomierz</t>
+          <t>ulica Piastowska 171, 48-300 Nysa</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -10935,22 +10935,22 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>0000076633</t>
+          <t>0000018438</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>1297365563</t>
+          <t>1249851567</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>297523940</t>
+          <t>250009941</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>18/05/2024</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -10960,7 +10960,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>89082811063</t>
+          <t>66122867147</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -10982,7 +10982,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Sienkiewicza 128, 27-400 Ostrowiec Świętokrzyski</t>
+          <t>Długa 8, 49-300 Brzeg</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -10992,22 +10992,22 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>0000076730</t>
+          <t>0000018535</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>1297444759</t>
+          <t>1249930752</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>297603136</t>
+          <t>250089130</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>2017-02-07</t>
+          <t>2017/07/02</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -11017,7 +11017,7 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>90090112453</t>
+          <t>67010768535</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -11039,7 +11039,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>ul. Marszałkowska 145/37, 00-590 Warszawa</t>
+          <t>ul. Rynek 25/67, 68-200 Żary</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -11049,22 +11049,22 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>0000076827</t>
+          <t>0000018632</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>1297523944</t>
+          <t>1250009942</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>297682325</t>
+          <t>250168326</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2022-01-24</t>
+          <t>24-01-2022</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>91100213803</t>
+          <t>68021469884</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -11096,7 +11096,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>ul Krakowskie Przedmieście 162, 00-071 Warszawa</t>
+          <t>ul Sikorskiego 42, 66-200 Świebodzin</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -11106,22 +11106,22 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>0000076924</t>
+          <t>0000018729</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>1297682329</t>
+          <t>1250089131</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>297761510</t>
+          <t>250247511</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>2022-10-19</t>
+          <t>2022-19-10</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -11131,7 +11131,7 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>92110315190</t>
+          <t>69032171274</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -11153,7 +11153,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>ulica Floriańska 179, 31-019 Kraków</t>
+          <t>ulica Armii Krajowej 59, 78-100 Kołobrzeg</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -11163,22 +11163,22 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>0000077021</t>
+          <t>0000018826</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>1297682329</t>
+          <t>1250168327</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>297840706</t>
+          <t>250326707</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>2019-02-15</t>
+          <t>20190215</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -11188,7 +11188,7 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>93120416547</t>
+          <t>70042872622</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
@@ -11210,7 +11210,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Długa 16, 31-147 Kraków</t>
+          <t>Piłsudskiego 76, 73-110 Stargard</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -11220,22 +11220,22 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>0000077118</t>
+          <t>0000018923</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>1297761514</t>
+          <t>1250247512</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>297919891</t>
+          <t>250405890</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>2023-06-29</t>
+          <t>29/06/2023</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -11245,7 +11245,7 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>94010517937</t>
+          <t>81050774016</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -11267,7 +11267,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>ul. Piotrkowska 33/89, 90-102 Łódź</t>
+          <t>93/29, 27-600 Sandomierz</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -11277,22 +11277,22 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>0000077215</t>
+          <t>0000019020</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>1297919895</t>
+          <t>1250326708</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>297999080</t>
+          <t>250564275</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>2023-06-25</t>
+          <t>2023/25/06</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -11302,7 +11302,7 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>95020619286</t>
+          <t>72061475365</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -11324,7 +11324,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>ul Zachodnia 50, 90-402 Łódź</t>
+          <t>ul Sienkiewicza 110, 27-400 Ostrowiec Świętokrzyski</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -11334,22 +11334,22 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>0000077312</t>
+          <t>0000019117</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>1297919895</t>
+          <t>1250405891</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>298078270</t>
+          <t>250564275</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2022-11-02</t>
+          <t>02-11-2022</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -11359,7 +11359,7 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>96030720674</t>
+          <t>73072176751</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -11381,7 +11381,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>ulica Świdnicka 67, 50-066 Wrocław</t>
+          <t>ulica Marszałkowska 127, 00-590 Warszawa</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>0000077409</t>
+          <t>0000019214</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>1297999084</t>
+          <t>1250485080</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>298157466</t>
+          <t>250643460</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2020-10-29</t>
+          <t>2020-29-10</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -11416,7 +11416,7 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>97040822022</t>
+          <t>74082878101</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -11438,7 +11438,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Legnicka 84, 54-203 Wrocław</t>
+          <t>Krakowskie Przedmieście 144, 00-071 Warszawa</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -11448,22 +11448,22 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>0000077506</t>
+          <t>0000019311</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>1298078274</t>
+          <t>1250564276</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>298236651</t>
+          <t>250722656</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>2020-10-05</t>
+          <t>20201005</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -11473,7 +11473,7 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>98050923417</t>
+          <t>75090779495</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">

--- a/data/xlsx/KNF_Rejestr_firm_inwestycyjnych.xlsx
+++ b/data/xlsx/KNF_Rejestr_firm_inwestycyjnych.xlsx
@@ -130,17 +130,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>60021406849</t>
+          <t>60101434205</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Pawlak-Sikora</t>
+          <t>Szymańska</t>
         </is>
       </c>
     </row>
@@ -187,17 +187,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>61032108236</t>
+          <t>61112135592</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Michalski</t>
+          <t>Dąbrowski</t>
         </is>
       </c>
     </row>
@@ -224,7 +224,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1234963840</t>
+          <t>2234963840</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -244,17 +244,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>62042809586</t>
+          <t>62122836941</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Król</t>
+          <t>Mazur</t>
         </is>
       </c>
     </row>
@@ -301,17 +301,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63050710972</t>
+          <t>63010738330</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Wieczorek</t>
+          <t>Krawczyk</t>
         </is>
       </c>
     </row>
@@ -358,17 +358,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64061412321</t>
+          <t>64021439689</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Jabłońska</t>
+          <t>Woźniak</t>
         </is>
       </c>
     </row>
@@ -415,17 +415,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65072113717</t>
+          <t>65032141079</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Witkowski</t>
+          <t>Jankowski</t>
         </is>
       </c>
     </row>
@@ -472,17 +472,17 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>66082815068</t>
+          <t>66042842428</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Walczak</t>
+          <t>Grabowska</t>
         </is>
       </c>
     </row>
@@ -499,7 +499,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>przymjoanwie i przekazywanie zlceeń</t>
+          <t>przymjoanwie  przekazywanie zlceeń</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -524,22 +524,22 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>DFI/418/2026</t>
+          <t>DIF/418/2026</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>67090716451</t>
+          <t>67050743811</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Stępień</t>
+          <t>Pawlak</t>
         </is>
       </c>
     </row>
@@ -586,17 +586,17 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>68101417802</t>
+          <t>68061445161</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Baran</t>
+          <t>Michalska</t>
         </is>
       </c>
     </row>
@@ -643,17 +643,17 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>69112119190</t>
+          <t>69072146557</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Rutkowski</t>
+          <t>Król</t>
         </is>
       </c>
     </row>
@@ -700,17 +700,17 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>70122820541</t>
+          <t>70082847905</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Górska</t>
+          <t>Wieczorek</t>
         </is>
       </c>
     </row>
@@ -737,7 +737,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2235676551</t>
+          <t>1235676551</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -757,17 +757,17 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>71010721939</t>
+          <t>71090749290</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Sikora</t>
+          <t>Jabłoński</t>
         </is>
       </c>
     </row>
@@ -814,17 +814,17 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>72021423289</t>
+          <t>72101450644</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Ostrowska</t>
+          <t>Witkowska</t>
         </is>
       </c>
     </row>
@@ -871,17 +871,17 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>73032124675</t>
+          <t>73112152031</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Tomaszewski</t>
+          <t>Walczak</t>
         </is>
       </c>
     </row>
@@ -928,17 +928,17 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>74042826025</t>
+          <t>74122853381</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Zając</t>
+          <t>Stępień</t>
         </is>
       </c>
     </row>
@@ -985,17 +985,17 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>75050727418</t>
+          <t>75010754779</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Pietrzak</t>
+          <t>Baran</t>
         </is>
       </c>
     </row>
@@ -1042,17 +1042,17 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>76061428767</t>
+          <t>76021456128</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Wójcicka</t>
+          <t>Rutkowska</t>
         </is>
       </c>
     </row>
@@ -1099,17 +1099,17 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>77072130157</t>
+          <t>77032157514</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Czarnecki</t>
+          <t>Górski</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>78082831506</t>
+          <t>78042858864</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Lis</t>
+          <t>Sikora</t>
         </is>
       </c>
     </row>
@@ -1213,17 +1213,17 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>79090732890</t>
+          <t>79050760251</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Kołodziej</t>
+          <t>Ostrowski</t>
         </is>
       </c>
     </row>
@@ -1270,17 +1270,17 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>80101434241</t>
+          <t>80061461608</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Kaczmarek</t>
+          <t>Tomaszewska</t>
         </is>
       </c>
     </row>
@@ -1327,17 +1327,17 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>81112135637</t>
+          <t>81072162995</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Piątek</t>
+          <t>Zając</t>
         </is>
       </c>
     </row>
@@ -1384,17 +1384,17 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>82122836987</t>
+          <t>82082864345</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Sadowska</t>
+          <t>Pietrzak</t>
         </is>
       </c>
     </row>
@@ -1441,17 +1441,17 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>83010738376</t>
+          <t>83090765738</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Włodarczyk</t>
+          <t>Wójcicki</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>236864404</t>
+          <t>336864404</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1498,17 +1498,17 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>84021439724</t>
+          <t>84101467081</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Borkowska</t>
+          <t>Czarnecka</t>
         </is>
       </c>
     </row>
@@ -1555,17 +1555,17 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>85032141114</t>
+          <t>85112168477</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Kowalski</t>
+          <t>Lis</t>
         </is>
       </c>
     </row>
@@ -1612,17 +1612,17 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>86042842464</t>
+          <t>86122869826</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Nowacka</t>
+          <t>Kołodziej</t>
         </is>
       </c>
     </row>
@@ -1669,17 +1669,17 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>87050743857</t>
+          <t>87010771218</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Wiśniewski</t>
+          <t>Kaczmarek</t>
         </is>
       </c>
     </row>
@@ -1726,17 +1726,17 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>88061445206</t>
+          <t>88021472567</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Wójcik</t>
+          <t>Piątek</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0000002821</t>
+          <t>000000282</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1783,17 +1783,17 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>89072146593</t>
+          <t>89032173953</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Kowalczyk</t>
+          <t>Sadowski</t>
         </is>
       </c>
     </row>
@@ -1840,17 +1840,17 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>90082847941</t>
+          <t>90042875302</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Kamińska</t>
+          <t>Włodarczyk</t>
         </is>
       </c>
     </row>
@@ -1897,17 +1897,17 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>91090749335</t>
+          <t>91050776696</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Lewandowski</t>
+          <t>Borkowski</t>
         </is>
       </c>
     </row>
@@ -1954,17 +1954,17 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>92101450680</t>
+          <t>92061478045</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Zielińska</t>
+          <t>Kowalska-Krawczyk</t>
         </is>
       </c>
     </row>
@@ -2011,17 +2011,17 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>93112152077</t>
+          <t>93072179431</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Szymański</t>
+          <t>Nowacki</t>
         </is>
       </c>
     </row>
@@ -2068,17 +2068,17 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>94122853426</t>
+          <t>94082880784</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Dąbrowska</t>
+          <t>Wiśniewska</t>
         </is>
       </c>
     </row>
@@ -2125,17 +2125,17 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>95010754814</t>
+          <t>95090782178</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Mazur</t>
+          <t>Wójcik</t>
         </is>
       </c>
     </row>
@@ -2182,17 +2182,17 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>96021456164</t>
+          <t>96101483529</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Krawczyk</t>
+          <t>Kowalczyk</t>
         </is>
       </c>
     </row>
@@ -2239,17 +2239,17 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>97032157550</t>
+          <t>97112184915</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Woźniak</t>
+          <t>Kamiński</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>000000369</t>
+          <t>0000003694</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2296,17 +2296,17 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>98042858909</t>
+          <t>98122886266</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Jankowska</t>
+          <t>Lewandowska</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>338052254</t>
+          <t>238052254</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2353,17 +2353,17 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>99050760297</t>
+          <t>99010787654</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Grabowski</t>
+          <t>Zieliński</t>
         </is>
       </c>
     </row>
@@ -2410,17 +2410,17 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>00261461640</t>
+          <t>00221489008</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Pawlak-Sikora</t>
+          <t>Szymańska</t>
         </is>
       </c>
     </row>
@@ -2467,17 +2467,17 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>01272163037</t>
+          <t>01232190398</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Michalski</t>
+          <t>Dąbrowski</t>
         </is>
       </c>
     </row>
@@ -2524,17 +2524,17 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>02282864387</t>
+          <t>02242891747</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Król</t>
+          <t>Mazur</t>
         </is>
       </c>
     </row>
@@ -2581,17 +2581,17 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>03290765770</t>
+          <t>03250793131</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Wieczorek</t>
+          <t>Krawczyk</t>
         </is>
       </c>
     </row>
@@ -2638,17 +2638,17 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>04301467122</t>
+          <t>04261494480</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Jabłońska</t>
+          <t>Woźniak</t>
         </is>
       </c>
     </row>
@@ -2695,17 +2695,17 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>05312168518</t>
+          <t>05272195876</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Witkowski</t>
+          <t>Jankowski</t>
         </is>
       </c>
     </row>
@@ -2752,17 +2752,17 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>60122869864</t>
+          <t>60082897222</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Walczak</t>
+          <t>Grabowska</t>
         </is>
       </c>
     </row>
@@ -2809,17 +2809,17 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>61010771256</t>
+          <t>61090798615</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Stępień</t>
+          <t>Pawlak</t>
         </is>
       </c>
     </row>
@@ -2866,17 +2866,17 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>72021472604</t>
+          <t>62101499967</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Baran</t>
+          <t>Michalska</t>
         </is>
       </c>
     </row>
@@ -2923,17 +2923,17 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>63032173991</t>
+          <t>63112101357</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Rutkowski</t>
+          <t>Król</t>
         </is>
       </c>
     </row>
@@ -2980,17 +2980,17 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>64042875341</t>
+          <t>64122802706</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Górska</t>
+          <t>Wieczorek</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1238844150</t>
+          <t>2238844150</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3037,17 +3037,17 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>65050776734</t>
+          <t>65010704096</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Sikora</t>
+          <t>Jabłoński</t>
         </is>
       </c>
     </row>
@@ -3094,17 +3094,17 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>66061478084</t>
+          <t>66021405444</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Ostrowska</t>
+          <t>Witkowska</t>
         </is>
       </c>
     </row>
@@ -3151,17 +3151,17 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>67072179470</t>
+          <t>67032106830</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Tomaszewski</t>
+          <t>Walczak</t>
         </is>
       </c>
     </row>
@@ -3208,17 +3208,17 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>68082880822</t>
+          <t>68042808181</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Zając</t>
+          <t>Stępień</t>
         </is>
       </c>
     </row>
@@ -3265,17 +3265,17 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>69090782216</t>
+          <t>69050709574</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Pietrzak</t>
+          <t>Baran</t>
         </is>
       </c>
     </row>
@@ -3322,17 +3322,17 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>70101483567</t>
+          <t>70061410924</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Wójcicka</t>
+          <t>Rutkowska</t>
         </is>
       </c>
     </row>
@@ -3349,7 +3349,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>wykonywain lzeceń na rachunek klientów</t>
+          <t>wykonyawin lzeceń na rachunek klientów</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3374,22 +3374,22 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>IDF/221/2021</t>
+          <t>DIF/221/2021</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>71112184953</t>
+          <t>71072112311</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Czarnecki</t>
+          <t>Górski</t>
         </is>
       </c>
     </row>
@@ -3436,17 +3436,17 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>72122886303</t>
+          <t>72082813661</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Lis</t>
+          <t>Sikora</t>
         </is>
       </c>
     </row>
@@ -3493,17 +3493,17 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>73010787692</t>
+          <t>73090715055</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Kołodziej</t>
+          <t>Ostrowski</t>
         </is>
       </c>
     </row>
@@ -3530,7 +3530,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2239556861</t>
+          <t>1239556861</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3550,17 +3550,17 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>74021489041</t>
+          <t>74101416406</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Kaczmarek</t>
+          <t>Tomaszewska</t>
         </is>
       </c>
     </row>
@@ -3607,17 +3607,17 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>75032190430</t>
+          <t>75112117793</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Piątek</t>
+          <t>Zając</t>
         </is>
       </c>
     </row>
@@ -3664,17 +3664,17 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>76042891780</t>
+          <t>76122819143</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Sadowska</t>
+          <t>Pietrzak</t>
         </is>
       </c>
     </row>
@@ -3721,17 +3721,17 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>77050793174</t>
+          <t>77010720534</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Włodarczyk</t>
+          <t>Wójcicki</t>
         </is>
       </c>
     </row>
@@ -3778,17 +3778,17 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>78061494522</t>
+          <t>78021421883</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Borkowska</t>
+          <t>Czarnecka</t>
         </is>
       </c>
     </row>
@@ -3835,17 +3835,17 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>79072195918</t>
+          <t>79032123270</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Kowalski</t>
+          <t>Lis</t>
         </is>
       </c>
     </row>
@@ -3892,17 +3892,17 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>80082897268</t>
+          <t>80042824628</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Nowacka</t>
+          <t>Kołodziej</t>
         </is>
       </c>
     </row>
@@ -3949,17 +3949,17 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>81090798651</t>
+          <t>81050726012</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Wiśniewski</t>
+          <t>Kaczmarek</t>
         </is>
       </c>
     </row>
@@ -4006,17 +4006,17 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>82101400006</t>
+          <t>82061427361</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Wójcik</t>
+          <t>Piątek</t>
         </is>
       </c>
     </row>
@@ -4063,17 +4063,17 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>83112101393</t>
+          <t>83072128757</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Kowalczyk</t>
+          <t>Sadowski</t>
         </is>
       </c>
     </row>
@@ -4120,17 +4120,17 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>84122802742</t>
+          <t>84082830100</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Kamińska</t>
+          <t>Włodarczyk</t>
         </is>
       </c>
     </row>
@@ -4177,17 +4177,17 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>85010704131</t>
+          <t>85090731494</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Lewandowski</t>
+          <t>Borkowski</t>
         </is>
       </c>
     </row>
@@ -4234,17 +4234,17 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>86021405480</t>
+          <t>60021406849</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Zielińska</t>
+          <t>Kowalska-Krawczyk</t>
         </is>
       </c>
     </row>
@@ -4291,17 +4291,17 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>87032106876</t>
+          <t>61032108236</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Szymański</t>
+          <t>Nowacki</t>
         </is>
       </c>
     </row>
@@ -4333,7 +4333,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>240903093</t>
+          <t>340903093</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>88042808226</t>
+          <t>62042809586</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Dąbrowska</t>
+          <t>Wiśniewska</t>
         </is>
       </c>
     </row>
@@ -4405,17 +4405,17 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>89050709619</t>
+          <t>63050710972</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Mazur</t>
+          <t>Wójcik</t>
         </is>
       </c>
     </row>
@@ -4462,17 +4462,17 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>90061410960</t>
+          <t>64061412321</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Krawczyk</t>
+          <t>Kowalczyk</t>
         </is>
       </c>
     </row>
@@ -4519,17 +4519,17 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>91072112357</t>
+          <t>65072113717</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Woźniak</t>
+          <t>Kamiński</t>
         </is>
       </c>
     </row>
@@ -4551,7 +4551,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>0000007574</t>
+          <t>000000757</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4576,17 +4576,17 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>92082813706</t>
+          <t>66082815068</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Jankowska</t>
+          <t>Lewandowska</t>
         </is>
       </c>
     </row>
@@ -4633,17 +4633,17 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>93090715091</t>
+          <t>67090716451</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Grabowski</t>
+          <t>Zieliński</t>
         </is>
       </c>
     </row>
@@ -4690,17 +4690,17 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>94101416442</t>
+          <t>68101417802</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Pawlak-Sikora</t>
+          <t>Szymańska</t>
         </is>
       </c>
     </row>
@@ -4747,17 +4747,17 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>95112117838</t>
+          <t>69112119190</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Michalski</t>
+          <t>Dąbrowski</t>
         </is>
       </c>
     </row>
@@ -4804,17 +4804,17 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>96122819189</t>
+          <t>70122820541</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Król</t>
+          <t>Mazur</t>
         </is>
       </c>
     </row>
@@ -4861,17 +4861,17 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>97010720570</t>
+          <t>71010721939</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Wieczorek</t>
+          <t>Krawczyk</t>
         </is>
       </c>
     </row>
@@ -4918,17 +4918,17 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>98021421928</t>
+          <t>72021423289</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Jabłońska</t>
+          <t>Woźniak</t>
         </is>
       </c>
     </row>
@@ -4975,17 +4975,17 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>99032123315</t>
+          <t>73032124675</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Witkowski</t>
+          <t>Jankowski</t>
         </is>
       </c>
     </row>
@@ -5032,17 +5032,17 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>00242824660</t>
+          <t>74042826025</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Walczak</t>
+          <t>Grabowska</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>000000844</t>
+          <t>0000008447</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5089,17 +5089,17 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>01250726054</t>
+          <t>75050727418</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>Stępień</t>
+          <t>Pawlak</t>
         </is>
       </c>
     </row>
@@ -5146,17 +5146,17 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>02261427402</t>
+          <t>76061428767</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>Baran</t>
+          <t>Michalska</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>342090949</t>
+          <t>242090949</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -5203,17 +5203,17 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>03272128799</t>
+          <t>77072130157</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>Rutkowski</t>
+          <t>Król</t>
         </is>
       </c>
     </row>
@@ -5260,17 +5260,17 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>04282830142</t>
+          <t>78082831506</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>Górska</t>
+          <t>Wieczorek</t>
         </is>
       </c>
     </row>
@@ -5317,17 +5317,17 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>05290731535</t>
+          <t>79090732890</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Sikora</t>
+          <t>Jabłoński</t>
         </is>
       </c>
     </row>
@@ -5374,17 +5374,17 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>60101432883</t>
+          <t>80101434241</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Ostrowska</t>
+          <t>Witkowska</t>
         </is>
       </c>
     </row>
@@ -5431,17 +5431,17 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>61112134270</t>
+          <t>81112135637</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>Tomaszewski</t>
+          <t>Walczak</t>
         </is>
       </c>
     </row>
@@ -5488,17 +5488,17 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>62122835629</t>
+          <t>82122836987</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Zając</t>
+          <t>Stępień</t>
         </is>
       </c>
     </row>
@@ -5545,17 +5545,17 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>63010737018</t>
+          <t>83010738376</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>Pietrzak</t>
+          <t>Baran</t>
         </is>
       </c>
     </row>
@@ -5602,17 +5602,17 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>64021438367</t>
+          <t>84021439724</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>Wójcicka</t>
+          <t>Rutkowska</t>
         </is>
       </c>
     </row>
@@ -5659,17 +5659,17 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>75032139753</t>
+          <t>85032141114</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>Czarnecki</t>
+          <t>Górski</t>
         </is>
       </c>
     </row>
@@ -5716,17 +5716,17 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>66042841106</t>
+          <t>86042842464</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>Lis</t>
+          <t>Sikora</t>
         </is>
       </c>
     </row>
@@ -5773,17 +5773,17 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>67050742490</t>
+          <t>87050743857</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Kołodziej</t>
+          <t>Ostrowski</t>
         </is>
       </c>
     </row>
@@ -5810,7 +5810,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>1242724469</t>
+          <t>2242724469</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -5830,17 +5830,17 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>68061443848</t>
+          <t>88061445206</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>Kaczmarek</t>
+          <t>Tomaszewska</t>
         </is>
       </c>
     </row>
@@ -5887,17 +5887,17 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>69072145235</t>
+          <t>89072146593</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>Piątek</t>
+          <t>Zając</t>
         </is>
       </c>
     </row>
@@ -5944,17 +5944,17 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>70082846584</t>
+          <t>70042873944</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>Sadowska</t>
+          <t>Pietrzak</t>
         </is>
       </c>
     </row>
@@ -6001,17 +6001,17 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>71090747977</t>
+          <t>71050775338</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>Włodarczyk</t>
+          <t>Wójcicki</t>
         </is>
       </c>
     </row>
@@ -6058,17 +6058,17 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>72101449329</t>
+          <t>72061476687</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>Borkowska</t>
+          <t>Czarnecka</t>
         </is>
       </c>
     </row>
@@ -6115,17 +6115,17 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>73112150718</t>
+          <t>73072178074</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>Kowalski</t>
+          <t>Lis</t>
         </is>
       </c>
     </row>
@@ -6172,17 +6172,17 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>74122852069</t>
+          <t>74082879423</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>Nowacka</t>
+          <t>Kołodziej</t>
         </is>
       </c>
     </row>
@@ -6229,17 +6229,17 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>75010753457</t>
+          <t>75090780819</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>Wiśinewski</t>
+          <t>Kacmzarek</t>
         </is>
       </c>
     </row>
@@ -6286,17 +6286,17 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>76021454805</t>
+          <t>76101482162</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>Wójcik</t>
+          <t>Piątek</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2243516365</t>
+          <t>1243516365</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -6343,17 +6343,17 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>77032156193</t>
+          <t>77112183558</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>Kowalczyk</t>
+          <t>Sadowski</t>
         </is>
       </c>
     </row>
@@ -6400,17 +6400,17 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>78042857542</t>
+          <t>78122884907</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>Kamińska</t>
+          <t>Włodarczyk</t>
         </is>
       </c>
     </row>
@@ -6457,17 +6457,17 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>79050758935</t>
+          <t>79010786297</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>Lewandowski</t>
+          <t>Borkowski</t>
         </is>
       </c>
     </row>
@@ -6514,17 +6514,17 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>80061460287</t>
+          <t>80021487644</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>Zielińska</t>
+          <t>Kowalska-Krawczyk</t>
         </is>
       </c>
     </row>
@@ -6571,17 +6571,17 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>81072161673</t>
+          <t>81032189031</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>Szymański</t>
+          <t>Nowacki</t>
         </is>
       </c>
     </row>
@@ -6628,17 +6628,17 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>82082863023</t>
+          <t>82042890384</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>Dąbrowska</t>
+          <t>Wiśniewska</t>
         </is>
       </c>
     </row>
@@ -6685,17 +6685,17 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>83090764416</t>
+          <t>83050791777</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>Mazur</t>
+          <t>Wójcik</t>
         </is>
       </c>
     </row>
@@ -6742,17 +6742,17 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>84101465768</t>
+          <t>84061493126</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Krawczyk</t>
+          <t>Kowalczyk</t>
         </is>
       </c>
     </row>
@@ -6799,17 +6799,17 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>85112167155</t>
+          <t>85072194512</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>Woźniak</t>
+          <t>Kamiński</t>
         </is>
       </c>
     </row>
@@ -6856,17 +6856,17 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>86122868504</t>
+          <t>86082895862</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>Jankowska</t>
+          <t>Lewandowska</t>
         </is>
       </c>
     </row>
@@ -6913,17 +6913,17 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>87010769893</t>
+          <t>87090797256</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>Grabowski</t>
+          <t>Zieliński</t>
         </is>
       </c>
     </row>
@@ -6970,17 +6970,17 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>88021471245</t>
+          <t>88101498607</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>Pawlak-Sikora</t>
+          <t>Szymańska</t>
         </is>
       </c>
     </row>
@@ -7027,17 +7027,17 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>89032172631</t>
+          <t>89112199994</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>Michalski</t>
+          <t>Dąbrowski</t>
         </is>
       </c>
     </row>
@@ -7084,17 +7084,17 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>90042873980</t>
+          <t>90122801346</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>Król</t>
+          <t>Mazur</t>
         </is>
       </c>
     </row>
@@ -7141,17 +7141,17 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>91050775374</t>
+          <t>91010702734</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>Wieczorek</t>
+          <t>Krawczyk</t>
         </is>
       </c>
     </row>
@@ -7183,7 +7183,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>244783409</t>
+          <t>344783409</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -7198,17 +7198,17 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>92061476722</t>
+          <t>92021404084</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>Jabłońska</t>
+          <t>Woźniak</t>
         </is>
       </c>
     </row>
@@ -7255,17 +7255,17 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>93072178119</t>
+          <t>93032105470</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>Witkowski</t>
+          <t>Jankowski</t>
         </is>
       </c>
     </row>
@@ -7312,17 +7312,17 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>94082879469</t>
+          <t>94042806829</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>Walczak</t>
+          <t>Grabowska</t>
         </is>
       </c>
     </row>
@@ -7344,7 +7344,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>0000012327</t>
+          <t>000001232</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -7369,17 +7369,17 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>95090780855</t>
+          <t>95050708213</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>Stępień</t>
+          <t>Pawlak</t>
         </is>
       </c>
     </row>
@@ -7426,17 +7426,17 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>96101482207</t>
+          <t>96061409562</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>Baran</t>
+          <t>Michalska</t>
         </is>
       </c>
     </row>
@@ -7483,17 +7483,17 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>97112183594</t>
+          <t>97072110951</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>Rutkowski</t>
+          <t>Król</t>
         </is>
       </c>
     </row>
@@ -7540,17 +7540,17 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>98122884943</t>
+          <t>98082812301</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>Górska</t>
+          <t>Wieczorek</t>
         </is>
       </c>
     </row>
@@ -7597,17 +7597,17 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>99010786332</t>
+          <t>99090713695</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>Sikora</t>
+          <t>Jabłoński</t>
         </is>
       </c>
     </row>
@@ -7654,17 +7654,17 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>00221487686</t>
+          <t>00301415042</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>Ostrowska</t>
+          <t>Witkowska</t>
         </is>
       </c>
     </row>
@@ -7711,17 +7711,17 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>01232189073</t>
+          <t>01312116438</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>Tomaszewski</t>
+          <t>Walczak</t>
         </is>
       </c>
     </row>
@@ -7768,17 +7768,17 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>02242890425</t>
+          <t>02322817788</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>Zając</t>
+          <t>Stępień</t>
         </is>
       </c>
     </row>
@@ -7825,17 +7825,17 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>03250791818</t>
+          <t>03210719177</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>Pietrzak</t>
+          <t>Baran</t>
         </is>
       </c>
     </row>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>000001320</t>
+          <t>0000013200</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -7882,17 +7882,17 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>04261493168</t>
+          <t>04221420528</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>Wójcicka</t>
+          <t>Rutkowska</t>
         </is>
       </c>
     </row>
@@ -7939,17 +7939,17 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>05272194554</t>
+          <t>05232121914</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>Czarnecki</t>
+          <t>Górski</t>
         </is>
       </c>
     </row>
@@ -7996,17 +7996,17 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>60082895909</t>
+          <t>60042823261</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>Lis</t>
+          <t>Sikora</t>
         </is>
       </c>
     </row>
@@ -8038,7 +8038,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>345971254</t>
+          <t>245971254</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -8053,17 +8053,17 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>61090797294</t>
+          <t>61050724654</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>Kołodziej</t>
+          <t>Ostrowski</t>
         </is>
       </c>
     </row>
@@ -8110,17 +8110,17 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>62101498645</t>
+          <t>62061426003</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>Kaczmarek</t>
+          <t>Tomaszewska</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>63112100035</t>
+          <t>63072127390</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>Piątek</t>
+          <t>Zając</t>
         </is>
       </c>
     </row>
@@ -8224,17 +8224,17 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>64122801385</t>
+          <t>64082828749</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>Sadowska</t>
+          <t>Pietrzak</t>
         </is>
       </c>
     </row>
@@ -8281,17 +8281,17 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>65010702773</t>
+          <t>75090730136</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>Włodarczyk</t>
+          <t>Wójcicki</t>
         </is>
       </c>
     </row>
@@ -8338,17 +8338,17 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>66021404122</t>
+          <t>66101431488</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>Borkowska</t>
+          <t>Czarnecka</t>
         </is>
       </c>
     </row>
@@ -8395,17 +8395,17 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>67032105518</t>
+          <t>67112132874</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>Kowalski</t>
+          <t>Lis</t>
         </is>
       </c>
     </row>
@@ -8452,17 +8452,17 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>78042806868</t>
+          <t>68122834224</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>Nowacka</t>
+          <t>Kołodziej</t>
         </is>
       </c>
     </row>
@@ -8509,17 +8509,17 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>69050708252</t>
+          <t>69010735612</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>Wiśniewski</t>
+          <t>Kaczmarek</t>
         </is>
       </c>
     </row>
@@ -8566,17 +8566,17 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>70061409609</t>
+          <t>70021436960</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>Wójcik</t>
+          <t>Piątek</t>
         </is>
       </c>
     </row>
@@ -8603,7 +8603,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>1246604779</t>
+          <t>2246604779</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -8623,17 +8623,17 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>71072110999</t>
+          <t>71032138357</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>Kowalczyk</t>
+          <t>Sadowski</t>
         </is>
       </c>
     </row>
@@ -8680,17 +8680,17 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>72082812349</t>
+          <t>72042839706</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>Kamińska</t>
+          <t>Włodarczyk</t>
         </is>
       </c>
     </row>
@@ -8737,17 +8737,17 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>73090713732</t>
+          <t>73050741094</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>Lewandowski</t>
+          <t>Borkowski</t>
         </is>
       </c>
     </row>
@@ -8794,17 +8794,17 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>74101415085</t>
+          <t>74061442442</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>Zielińska</t>
+          <t>Kowalska-Krawczyk</t>
         </is>
       </c>
     </row>
@@ -8851,17 +8851,17 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>75112116471</t>
+          <t>75072143838</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>Szymański</t>
+          <t>Nowacki</t>
         </is>
       </c>
     </row>
@@ -8908,17 +8908,17 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>76122817820</t>
+          <t>76082845189</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>Dąbrowska</t>
+          <t>Wiśniewska</t>
         </is>
       </c>
     </row>
@@ -8965,17 +8965,17 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>77010719219</t>
+          <t>77090746572</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>Mazur</t>
+          <t>Wójcik</t>
         </is>
       </c>
     </row>
@@ -9022,17 +9022,17 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>78021420561</t>
+          <t>78101447923</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>Krawczyk</t>
+          <t>Kowalczyk</t>
         </is>
       </c>
     </row>
@@ -9079,17 +9079,17 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>79032121957</t>
+          <t>79112149310</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>Woźniak</t>
+          <t>Kamiński</t>
         </is>
       </c>
     </row>
@@ -9116,7 +9116,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2247396679</t>
+          <t>1247396679</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -9136,17 +9136,17 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>80042823306</t>
+          <t>80122850662</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>Jankowska</t>
+          <t>Lewandowska</t>
         </is>
       </c>
     </row>
@@ -9193,17 +9193,17 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>81050724690</t>
+          <t>81010752051</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>Grabowski</t>
+          <t>Zieliński</t>
         </is>
       </c>
     </row>
@@ -9250,17 +9250,17 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>82061426049</t>
+          <t>82021453409</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>Pawlak-Sikora</t>
+          <t>Szymańska</t>
         </is>
       </c>
     </row>
@@ -9307,17 +9307,17 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>83072127435</t>
+          <t>83032154796</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>Michalski</t>
+          <t>Dąbrowski</t>
         </is>
       </c>
     </row>
@@ -9364,17 +9364,17 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>84082828785</t>
+          <t>84042856146</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>Król</t>
+          <t>Mazur</t>
         </is>
       </c>
     </row>
@@ -9421,17 +9421,17 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>85090730172</t>
+          <t>85050757539</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>Wieczorek</t>
+          <t>Krawczyk</t>
         </is>
       </c>
     </row>
@@ -9478,17 +9478,17 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>86101431523</t>
+          <t>86061458888</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>Jabłońska</t>
+          <t>Woźniak</t>
         </is>
       </c>
     </row>
@@ -9535,17 +9535,17 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>87112132919</t>
+          <t>87072160278</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>Witkowski</t>
+          <t>Jankowski</t>
         </is>
       </c>
     </row>
@@ -9592,17 +9592,17 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>88122834260</t>
+          <t>88082861627</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>Walczak</t>
+          <t>Grabowska</t>
         </is>
       </c>
     </row>
@@ -9649,17 +9649,17 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>89010735658</t>
+          <t>89090763011</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>Stępień</t>
+          <t>Pawlak</t>
         </is>
       </c>
     </row>
@@ -9706,17 +9706,17 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>90021437006</t>
+          <t>90101464362</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>Baran</t>
+          <t>Michalska</t>
         </is>
       </c>
     </row>
@@ -9763,17 +9763,17 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>91032138393</t>
+          <t>91112165758</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>Rutkowski</t>
+          <t>Król</t>
         </is>
       </c>
     </row>
@@ -9820,17 +9820,17 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>92042839742</t>
+          <t>92122867108</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>Górska</t>
+          <t>Wieczorek</t>
         </is>
       </c>
     </row>
@@ -9877,17 +9877,17 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>93050741139</t>
+          <t>93010768497</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>Sikora</t>
+          <t>Jabłoński</t>
         </is>
       </c>
     </row>
@@ -9934,17 +9934,17 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>94061442488</t>
+          <t>94021469845</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>Ostrowska</t>
+          <t>Witkowska</t>
         </is>
       </c>
     </row>
@@ -9991,17 +9991,17 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>95072143874</t>
+          <t>95032171235</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>Tomaszewski</t>
+          <t>Walczak</t>
         </is>
       </c>
     </row>
@@ -10033,7 +10033,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>248742904</t>
+          <t>348742904</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -10048,17 +10048,17 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>96082845224</t>
+          <t>96042872585</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>Zając</t>
+          <t>Stępień</t>
         </is>
       </c>
     </row>
@@ -10105,17 +10105,17 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>97090746617</t>
+          <t>97050773978</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>Pietrzak</t>
+          <t>Baran</t>
         </is>
       </c>
     </row>
@@ -10137,7 +10137,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>0000017080</t>
+          <t>000001708</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -10162,17 +10162,17 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>98101447969</t>
+          <t>98061475327</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>Wójcicka</t>
+          <t>Rutkowska</t>
         </is>
       </c>
     </row>
@@ -10219,17 +10219,17 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>99112149356</t>
+          <t>99072176713</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>Czarnecki</t>
+          <t>Górski</t>
         </is>
       </c>
     </row>
@@ -10276,17 +10276,17 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>00322850703</t>
+          <t>00282878069</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>Lis</t>
+          <t>Sikora</t>
         </is>
       </c>
     </row>
@@ -10333,17 +10333,17 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>01210752093</t>
+          <t>01290779452</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>Kołodziej</t>
+          <t>Ostrowski</t>
         </is>
       </c>
     </row>
@@ -10390,17 +10390,17 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>02221453441</t>
+          <t>02301480806</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>Kaczmarek</t>
+          <t>Tomaszewska</t>
         </is>
       </c>
     </row>
@@ -10447,17 +10447,17 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>03232154837</t>
+          <t>03312182194</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>Piątek</t>
+          <t>Zając</t>
         </is>
       </c>
     </row>
@@ -10504,17 +10504,17 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>04242856188</t>
+          <t>04322883543</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>Sadowska</t>
+          <t>Pietrzak</t>
         </is>
       </c>
     </row>
@@ -10561,17 +10561,17 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>05250757571</t>
+          <t>05210784931</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>Włodarczyk</t>
+          <t>Wójcicki</t>
         </is>
       </c>
     </row>
@@ -10618,17 +10618,17 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>60061458925</t>
+          <t>60021486287</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>Borkowska</t>
+          <t>Czarnecka</t>
         </is>
       </c>
     </row>
@@ -10650,7 +10650,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>000001795</t>
+          <t>0000017953</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -10675,17 +10675,17 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>61072160315</t>
+          <t>61032187673</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>Kowalski</t>
+          <t>Lis</t>
         </is>
       </c>
     </row>
@@ -10732,17 +10732,17 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>62082861665</t>
+          <t>62042889023</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>Nowacka</t>
+          <t>Kołodziej</t>
         </is>
       </c>
     </row>
@@ -10789,17 +10789,17 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>63090763059</t>
+          <t>63050790419</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>Wiśniewski</t>
+          <t>Kaczmarek</t>
         </is>
       </c>
     </row>
@@ -10846,17 +10846,17 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>64101464400</t>
+          <t>64061491768</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>Wójcik</t>
+          <t>Piątek</t>
         </is>
       </c>
     </row>
@@ -10888,7 +10888,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>350009941</t>
+          <t>250009941</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -10903,17 +10903,17 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>65112165797</t>
+          <t>65072193155</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>Kowalczyk</t>
+          <t>Sadowski</t>
         </is>
       </c>
     </row>
@@ -10960,17 +10960,17 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>66122867147</t>
+          <t>66082894504</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>Kamińska</t>
+          <t>Włodarczyk</t>
         </is>
       </c>
     </row>
@@ -11017,17 +11017,17 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>67010768535</t>
+          <t>67090795898</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>Lewandowski</t>
+          <t>Borkowski</t>
         </is>
       </c>
     </row>
@@ -11074,17 +11074,17 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>68021469884</t>
+          <t>68101497240</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>Zielińska</t>
+          <t>Kowalska-Krawczyk</t>
         </is>
       </c>
     </row>
@@ -11131,17 +11131,17 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>69032171274</t>
+          <t>69112198636</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>Szymański</t>
+          <t>Nowacki</t>
         </is>
       </c>
     </row>
@@ -11188,17 +11188,17 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>70042872622</t>
+          <t>70122899985</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>Dąbrowska</t>
+          <t>Wiśniewska</t>
         </is>
       </c>
     </row>
@@ -11245,17 +11245,17 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>81050774016</t>
+          <t>71010701377</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>Mazur</t>
+          <t>Wójcik</t>
         </is>
       </c>
     </row>
@@ -11302,17 +11302,17 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>72061475365</t>
+          <t>72021402725</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>Krawczyk</t>
+          <t>Kowalczyk</t>
         </is>
       </c>
     </row>
@@ -11359,17 +11359,17 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>73072176751</t>
+          <t>73032104112</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>Woźniak</t>
+          <t>Kamiński</t>
         </is>
       </c>
     </row>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>1250485080</t>
+          <t>2250485080</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -11416,17 +11416,17 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>74082878101</t>
+          <t>74042805462</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>Jankowska</t>
+          <t>Lewandowska</t>
         </is>
       </c>
     </row>
@@ -11473,17 +11473,17 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>75090779495</t>
+          <t>75050706855</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>Grabowski</t>
+          <t>Zieliński</t>
         </is>
       </c>
     </row>

--- a/data/xlsx/KNF_Rejestr_firm_inwestycyjnych.xlsx
+++ b/data/xlsx/KNF_Rejestr_firm_inwestycyjnych.xlsx
@@ -83,6 +83,11 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
+          <t>CzlonekZarzadu1_DrugieImie</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>CzlonekZarzadu1_Nazwisko</t>
         </is>
       </c>
@@ -90,7 +95,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Polaris Capital Markets SP Z O O</t>
+          <t>Facebook - Meta</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -140,14 +145,19 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Szymańska</t>
+          <t>Karolina</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Kaczmarek</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Optima Trade spółka z ograniczoną odpowiedzialnością</t>
+          <t>Polskie Przetwory sp z oo</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -197,14 +207,19 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Dąbrowski</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Piątek</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Amber Payments spółka z ograniczoną odpowiedzialnością</t>
+          <t>Hurtownia Nabiału Mleczko sp. z o. o.</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -224,12 +239,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2234963840</t>
+          <t>1234963840</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>235122221</t>
+          <t>335122221</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -249,19 +264,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Aleksandra</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Mazur</t>
+          <t>Małgorzata</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Sadowska</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Vistula Fintech Services sp z oo</t>
+          <t>Agencja Reklamowa Kreatywni Sp. z o.o.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -291,7 +311,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2022-10-12</t>
+          <t>2022-12-10</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -306,19 +326,24 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Andrzej</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Krawczyk</t>
+          <t>Jakub</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Włodarczyk</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Nova Data Technologie S.A.</t>
+          <t>Kancelaria Prawna Sankcja SP Z O O</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -363,19 +388,24 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Marta</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Woźniak</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Borkowska</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Nova Data S.A.</t>
+          <t>Śląskie Zakłady Mechaniczne spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -420,19 +450,24 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Łukasz</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Jankowski</t>
+          <t>Artur</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Sawicki</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Orbis Retail Solutions sp. z o.o.</t>
+          <t>Fabryka Okien i Drzwi Profil Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -477,19 +512,24 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Paulina</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Grabowska</t>
+          <t>Iwona</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Dudek</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Vistula Fintech S.A.</t>
+          <t>Przedsiębiorstwo Robót Drogowych S.A.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -499,7 +539,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>przymjoanwie  przekazywanie zlceeń</t>
+          <t>przymjoanwi  przekazywanie zleceń</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -524,7 +564,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>DIF/418/2026</t>
+          <t>DF/418/2026</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -534,19 +574,24 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Mateusz</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Pawlak</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Adamczyk</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Astra Finance Holding Spółka Akcyjna</t>
+          <t>Krakowskie Biuro Nieruchomości SA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -576,7 +621,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2018-05-06</t>
+          <t>2018-06-05</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -591,19 +636,24 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Elżbieta</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Michalska</t>
+          <t>Renata</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Pawłowska</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Baltic Med Supply Finanse S.A.</t>
+          <t>Salon Samochodowy Auto-Hit S. A.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -648,19 +698,24 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Dawid</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Król</t>
+          <t>Maciej</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Nowicki</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Amber Payments Spółka Akcyjna</t>
+          <t>Klinika Stomatologiczna Dent-Med Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -705,19 +760,24 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Dorota</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Wieczorek</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Sokołowska</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Silesia Invest Services sp. z o.o.</t>
+          <t>Polski Tytoń sp. z o.o.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -762,19 +822,24 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Dariusz</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Jabłoński</t>
+          <t>Zbigniew</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Wróbel</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Polaris Capital Technologie sp z oo</t>
+          <t>Gdańska Stocznia Jachtowa sp z oo</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -819,19 +884,24 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Beata</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Witkowska</t>
+          <t>Patrycja</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Majewska</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Baltic Med Supply sp. z o.o.</t>
+          <t>Wytwórnia Makaronu Jajecznego sp. z o. o.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -861,7 +931,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2022-10-12</t>
+          <t>2022-12-10</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -876,19 +946,24 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Sławomir</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Walczak</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Olszewski</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Silesia Invest sp. z o.o.</t>
+          <t>Zakłady Mięsne Tradycja Sp. z o.o.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -933,19 +1008,24 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Urszula</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Stępień</t>
+          <t>Wiktoria</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Jaworska</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Silesia Invest Holding Spółka Akcyjna</t>
+          <t>Spółdzielnia Mleczarska Radomsko SP Z O O</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -990,19 +1070,24 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Mariusz</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Baran</t>
+          <t>Jacek</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Malinowski</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Polaris Capital SP Z O O</t>
+          <t>Kancelaria Finansowo-Księgowa Bilans spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1047,56 +1132,61 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Izabela</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Rutkowska</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Pająk</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>Zarząd Nieruchomości Komercyjnych Spółka z ograniczoną odpowiedzialnością</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ul Narutowicza 110, 20-004 Lublin</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>ul Narutowicza 110, 20-004 Lublin</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0000001657</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1236151690</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>236310077</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>0000001657</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>1236151690</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>236310077</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>77032157514</t>
@@ -1104,19 +1194,24 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Henryk</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Górski</t>
+          <t>Przemysław</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Szczepański</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Silesia Invest Markets sp z oo</t>
+          <t>Polskie Linie Oceaniczne S.A.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1146,7 +1241,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2021-11-06</t>
+          <t>2021-06-11</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1161,24 +1256,29 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Weronika</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Sikora</t>
+          <t>Kinga</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Czerwińska</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Astra Finance SP Z O O</t>
+          <t>Hurtownia Materiałów Budowlanych Cegiełka SA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Piłsudskiego 84, Rzeszów</t>
+          <t>Rynek 84, Opole</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1218,19 +1318,24 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Stanisław</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Ostrowski</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Kubiak</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Lumen Advisory SP Z O O</t>
+          <t>PPHU Studio Projektowe Architektura</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1275,19 +1380,24 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Tomaszewska</t>
+          <t>Kamila</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Wilk</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Silesia Invest sp. z o.o.</t>
+          <t>Centrum Medycyny Pracy Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1332,19 +1442,24 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Bartłomiej</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Zając</t>
+          <t>Daniel</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Wysocki</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Nova Data sp z oo</t>
+          <t>Przedsiębiorstwo Energetyki Cieplnej sp. z o.o.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1369,7 +1484,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>236785219</t>
+          <t>246706057</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1389,19 +1504,24 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Olga</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Pietrzak</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Chmielewska</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Baltic Med Supply sp. z o.o.</t>
+          <t>Gospodarstwo Rolno-Ogrodnicze sp z oo</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1446,19 +1566,24 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Damian</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Wójcicki</t>
+          <t>Waldemar</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Urbański</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Optima Trade Spółka Akcyjna</t>
+          <t>Drukarnia Wielkoformatowa Impress sp. z o. o.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1483,7 +1608,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>336864404</t>
+          <t>236864404</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1503,19 +1628,24 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Ewelina</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Czarnecka</t>
+          <t>Danuta</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Błaszczyk</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Orbis Retail Solutions Services S.A.</t>
+          <t>Klub Fitness Sylwetka Sp. z o.o.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1560,19 +1690,24 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Bartosz</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Lis</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Szulc</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Helios Markets Polska sp. z o.o.</t>
+          <t>Polska Grupa Energetyczna SP Z O O</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1617,19 +1752,24 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Sylwia</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Kołodziej</t>
+          <t>Aneta</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Kozak</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Silesia Invest sp. z o.o.</t>
+          <t>Mazowieckie Zakłady Drobiarskie spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1674,19 +1814,24 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Leszek</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Kaczmarek</t>
+          <t>Kacper</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Cieślak</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Silesia Invest sp z oo</t>
+          <t>Hurtownia Farmaceutyczna Aptekarz Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1731,19 +1876,24 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Grażyna</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Piątek</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Andrzejewska</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Aurum Invest Holding Spółka Akcyjna</t>
+          <t>Kancelaria Notarialna Lex S.A.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1758,7 +1908,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>000000282</t>
+          <t>0000002821</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1788,19 +1938,24 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Cezary</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Sadowski</t>
+          <t>Szymon</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Gajewski</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Silesia Invest SP Z O O</t>
+          <t>Biuro Podróży Wojażer SA</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1845,19 +2000,24 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Bożena</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Włodarczyk</t>
+          <t>Oliwia</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Laskowska</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Optima Trade Spółka Akcyjna</t>
+          <t>Szkoła Języków Obcych Lingua S. A.</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1902,19 +2062,24 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Filip</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Borkowski</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Mazurek</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Optima Trade SP Z O O</t>
+          <t>Centrum Logistyczne Podlasie Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1934,12 +2099,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1237418735</t>
+          <t>1247339575</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>237577115</t>
+          <t>247497957</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1959,19 +2124,24 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Zuzanna</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Kowalska-Krawczyk</t>
+          <t>Emilia</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Sobczak-Matusiak</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Nova Data Polska S.A.</t>
+          <t>Fabryka Mebli Drewnianych Dąb sp. z o.o.</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2016,19 +2186,24 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Mikołaj</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Nowacki</t>
+          <t>Ignacy</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Konieczny</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Astra Finance Technologie spółka z ograniczoną odpowiedzialnością</t>
+          <t>Polskie Sady sp z oo</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2073,19 +2248,24 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Lena</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Wiśniewska</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Brzezińska</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Aurum Invest Polska spółka z ograniczoną odpowiedzialnością</t>
+          <t>Wielkopolska Hurtownia Stali sp. z o. o.</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2105,7 +2285,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1237656305</t>
+          <t>1247577145</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2130,19 +2310,24 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Antoni</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Wójcik</t>
+          <t>Leon</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Makowski</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Amber Payments sp z oo</t>
+          <t>Zakład Oczyszczania Miasta Sp. z o.o.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2167,7 +2352,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>237893879</t>
+          <t>247814719</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2187,24 +2372,29 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Hanna</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Kowalczyk</t>
+          <t>Dominika</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Wrona</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Astra Finance SP Z O O</t>
+          <t>Przedsiębiorstwo Wodociągów i Kanalizacji SP Z O O</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>57-300 Kłodzko</t>
+          <t>70-435 Szczecin</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2244,19 +2434,24 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Franciszek</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Kamiński</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Bąk</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Orbis Retail Solutions sp z oo</t>
+          <t>Instytut Badań Rynkowych spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2301,19 +2496,24 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Amelia</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Lewandowska</t>
+          <t>Jagoda</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Kucharska</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Astra Finance Finanse S.A.</t>
+          <t>Agencja Ochrony Solidna Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2358,19 +2558,24 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Nikodem</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Zieliński</t>
+          <t>Jerzy</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Lisowski</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Astra Finance Spółka Akcyjna</t>
+          <t>Instagram - Meta</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2395,7 +2600,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>238210635</t>
+          <t>248131477</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2415,19 +2620,24 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Szymańska</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Słowik</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Astra Finance S.A.</t>
+          <t>Krajowa Izba Gospodarcza SA</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2472,19 +2682,24 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Miłosz</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Dąbrowski</t>
+          <t>Marian</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Kopeć</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Orbis Retail Solutions Technologie sp. z o.o.</t>
+          <t>Polskie Zakłady Lotnicze S. A.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2529,19 +2744,24 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Agata</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Mazur</t>
+          <t>Irena</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Czajka</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Baltic Med Supply Services Spółka Akcyjna</t>
+          <t>Hurtownia Elektryczna Wat Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2561,7 +2781,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1238289820</t>
+          <t>1248210665</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2586,19 +2806,24 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Tadeusz</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Krawczyk</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Matusiak</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Orbis Retail Solutions sp z oo</t>
+          <t>Centrum Ogrodnicze Zielona Oaza sp. z o.o.</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2643,19 +2868,24 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Helena</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Woźniak</t>
+          <t>Izabela</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Gajda</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Quantum Services Services spółka z ograniczoną odpowiedzialnością</t>
+          <t>Piekarnia i Cukiernia Chrupiący Rogalik sp z oo</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2700,19 +2930,24 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Stefan</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Jankowski</t>
+          <t>Mirosław</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Klimek</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Aurum Invest Spółka Akcyjna</t>
+          <t>Zakład Usług Komunalnych sp. z o. o.</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2757,19 +2992,24 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Jadwiga</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Grabowska</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Madej</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Orbis Retail Solutions spółka z ograniczoną odpowiedzialnością</t>
+          <t>Polski Komfort Sp. z o.o.</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2814,19 +3054,24 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Józef</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Pawlak</t>
+          <t>Piotr</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Krupa</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Vistula Fintech Holding sp z oo</t>
+          <t>Kancelaria Radców Prawnych Partnerzy SP Z O O</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2856,7 +3101,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2017-06-12</t>
+          <t>2017-12-06</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2876,14 +3121,19 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Michalska</t>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Kaczmarczyk</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Astra Finance SP Z O O</t>
+          <t>Centrum Dystrybucji Alkoholi spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2903,7 +3153,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1238764965</t>
+          <t>1248685807</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2928,19 +3178,24 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Król</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Wrona</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Helios Markets sp. z o.o.</t>
+          <t>Przedsiębiorstwo Spedycyjne Ładunek Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2985,19 +3240,24 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Sabina</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Wieczorek</t>
+          <t>Joanna</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Wasilewska</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Optima Trade S.A.</t>
+          <t>Fabryka Tekstyliów Splot S.A.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3017,7 +3277,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2238844150</t>
+          <t>1238844150</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3042,19 +3302,24 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Arkadiusz</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Jabłoński</t>
+          <t>Paweł</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Kalinowski</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Mazovia Broker Services S.A.</t>
+          <t>Górnośląskie Towarzystwo Finansowe SA</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3104,14 +3369,19 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Witkowska</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Zarychta</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Helios Markets Services spółka z ograniczoną odpowiedzialnością</t>
+          <t>Krajowa Agencja Informacyjna S. A.</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3161,14 +3431,19 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Walczak</t>
+          <t>Robert</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Przybylski</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Nova Data Spółka Akcyjna</t>
+          <t>Polskie Jagody Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3218,14 +3493,19 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Stępień</t>
+          <t>Agnieszka</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Michalak</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Helios Markets Finanse S.A.</t>
+          <t>Zielony Amber sp. z o.o.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3275,14 +3555,19 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Baran</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Szatkowski</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Orbis Retail Solutions sp. z o.o.</t>
+          <t>Zielony Bizon sp z oo</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3332,14 +3617,19 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Rutkowska</t>
+          <t>Justyna</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Bednarek</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Polaris Capital Markets sp. z o.o.</t>
+          <t>Zielony Canyon sp. z o. o.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3349,7 +3639,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>wykonyawin lzeceń na rachunek klientów</t>
+          <t>wykonywain lzeceń na archunek klientów</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3389,14 +3679,19 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Górski</t>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Podgórski</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Aurum Invest spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Delfin Sp. z o.o.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3446,14 +3741,19 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Sikora</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Śliwińska</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Helios Markets S.A.</t>
+          <t>Zielony Echo SP Z O O</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3503,14 +3803,19 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Ostrowski</t>
+          <t>Marcin</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Czajkowski</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Silesia Invest Spółka Akcyjna</t>
+          <t>P.P.H.U. Zielony Falcon</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3560,14 +3865,19 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Tomaszewska</t>
+          <t>Karolina</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Biernat</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Baltic Med Supply SP Z O O</t>
+          <t>Zielony Gryf Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3617,14 +3927,19 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Zając</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Panek</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Mazovia Broker spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Horyzont S.A.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3669,19 +3984,24 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Aleksandra</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Pietrzak</t>
+          <t>Małgorzata</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Prus</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Mazovia Broker S.A.</t>
+          <t>Zielony Ikar SA</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3726,19 +4046,24 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Andrzej</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Wójcicki</t>
+          <t>Jakub</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Janik</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Baltic Med Supply S.A.</t>
+          <t>Zielony Jantar S. A.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3783,19 +4108,24 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Marta</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Czarnecka</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Kowalska</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Amber Payments sp z oo</t>
+          <t>Zielony Koral Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3840,24 +4170,29 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Łukasz</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Lis</t>
+          <t>Artur</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Nowacki</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Polaris Capital sp z oo</t>
+          <t>Zielony Lotos sp. z o.o.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ulica Marszałkowska 43, 00-590 Warszawa</t>
+          <t>ulica Chmielna 43, 00-020 Warszawa</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3897,24 +4232,29 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Paulina</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Kołodziej</t>
+          <t>Iwona</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Wiśniewska</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Quantum Services sp z oo</t>
+          <t>Zielony Magnolia sp z oo</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Krakowskie Przedmieście 60, 00-071 Warszawa</t>
+          <t>Nowy Świat 60, 00-029 Warszawa</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3954,24 +4294,29 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Mateusz</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Kaczmarek</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Wójcik</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Polaris Capital sp. z o.o.</t>
+          <t>Zielony Neon sp. z o. o.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ul. Floriańska 77/75, 31-019 Kraków</t>
+          <t>ul. os. Przyjaźń 77/75, 01-355 Warszawa</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4011,24 +4356,29 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Elżbieta</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Piątek</t>
+          <t>Renata</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Kowalczyk</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Amber Payments Services sp. z o.o.</t>
+          <t>Zielony Oaza Sp. z o.o.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ul Długa 94, 31-147 Kraków</t>
+          <t>ul Jagiellońska 94, 05-120 Legionowo</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4068,24 +4418,29 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Dawid</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Sadowski</t>
+          <t>Maciej</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Kamiński</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Orbis Retail Solutions Spółka Akcyjna</t>
+          <t>Zielony Pegaz SP Z O O</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ulica Piotrkowska 111, 90-102 Łódź</t>
+          <t>ulica Piłsudskiego 111, 05-270 Marki</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4125,24 +4480,29 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Dorota</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Włodarczyk</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Lewandowska</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Orbis Retail Solutions Services SP Z O O</t>
+          <t>Zielony Rubin spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Zachodnia 128, 90-402 Łódź</t>
+          <t>Andriollego 128, 05-400 Otwock</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4182,24 +4542,29 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Dariusz</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Borkowski</t>
+          <t>Zbigniew</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Zieliński</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Nova Data Markets sp z oo</t>
+          <t>Zielony Szafir Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ul. Świdnicka 145/37, 50-066 Wrocław</t>
+          <t>ul. Żeromskiego 145/37, 26-600 Radom</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4243,6 +4608,11 @@
         </is>
       </c>
       <c r="K74" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
         <is>
           <t>Kowalska-Krawczyk</t>
         </is>
@@ -4251,12 +4621,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Aurum Invest sp. z o.o.</t>
+          <t>Zielony Tytan S.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ul Legnicka 162, 54-203 Wrocław</t>
+          <t>ul Tumska 162, 09-402 Płock</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4281,7 +4651,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
+          <t>2023-11-05</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -4300,6 +4670,11 @@
         </is>
       </c>
       <c r="K75" t="inlineStr">
+        <is>
+          <t>Robert</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
         <is>
           <t>Nowacki</t>
         </is>
@@ -4308,12 +4683,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Optima Trade sp. z o.o.</t>
+          <t>Zielony Uran SA</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ulica Święty Marcin 179, 61-806 Poznań</t>
+          <t>ulica Karmelicka 179, 31-128 Kraków</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4333,7 +4708,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>340903093</t>
+          <t>250823937</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4357,6 +4732,11 @@
         </is>
       </c>
       <c r="K76" t="inlineStr">
+        <is>
+          <t>Agnieszka</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
         <is>
           <t>Wiśniewska</t>
         </is>
@@ -4365,12 +4745,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Astra Finance Markets sp z oo</t>
+          <t>Zielony Wektor S. A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Głogowska 16, 60-734 Poznań</t>
+          <t>os. Na Stoku 16, 31-704 Kraków</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4414,6 +4794,11 @@
         </is>
       </c>
       <c r="K77" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
         <is>
           <t>Wójcik</t>
         </is>
@@ -4422,12 +4807,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Optima Trade Markets spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Zefir Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ul. Długa 33/89, 80-831 Gdańsk</t>
+          <t>ul. Krupówki 33/89, 34-500 Zakopane</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4471,6 +4856,11 @@
         </is>
       </c>
       <c r="K78" t="inlineStr">
+        <is>
+          <t>Justyna</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
         <is>
           <t>Kowalczyk</t>
         </is>
@@ -4479,12 +4869,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Mazovia Broker Technologie Spółka Akcyjna</t>
+          <t>Zielony Żubr sp. z o.o.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>ul Grunwaldzka 50, 80-236 Gdańsk</t>
+          <t>50, 34-600 Mordarka</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -4528,6 +4918,11 @@
         </is>
       </c>
       <c r="K79" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
         <is>
           <t>Kamiński</t>
         </is>
@@ -4536,12 +4931,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Aurum Invest Technologie Spółka Akcyjna</t>
+          <t>Zielony Sokół sp z oo</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ulica Jagiellońska 67, 70-435 Szczecin</t>
+          <t>ulica Galicyjska 67, 32-087 Zielonki</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4551,7 +4946,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>000000757</t>
+          <t>0000007574</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4566,7 +4961,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2023-07-09</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4585,6 +4980,11 @@
         </is>
       </c>
       <c r="K80" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
         <is>
           <t>Lewandowska</t>
         </is>
@@ -4593,12 +4993,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Nova Data Spółka Akcyjna</t>
+          <t>Zielony Orzeł sp. z o. o.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Wyszyńskiego 84, 70-200 Szczecin</t>
+          <t>84, 32-003 Podłęże</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4642,6 +5042,11 @@
         </is>
       </c>
       <c r="K81" t="inlineStr">
+        <is>
+          <t>Marcin</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
         <is>
           <t>Zieliński</t>
         </is>
@@ -4650,12 +5055,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Astra Finance sp. z o.o.</t>
+          <t>mBank</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ul. Mariacka 101/51, 40-014 Katowice</t>
+          <t>ul. Wałowa 101/51, 33-100 Tarnów</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4699,6 +5104,11 @@
         </is>
       </c>
       <c r="K82" t="inlineStr">
+        <is>
+          <t>Karolina</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
         <is>
           <t>Szymańska</t>
         </is>
@@ -4707,12 +5117,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Aurum Invest spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Barycz SP Z O O</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ul Warszawska 118, 40-009 Katowice</t>
+          <t>ul Narutowicza 118, 90-135 Łódź</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -4732,7 +5142,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>241457425</t>
+          <t>251378267</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -4756,6 +5166,11 @@
         </is>
       </c>
       <c r="K83" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
         <is>
           <t>Dąbrowski</t>
         </is>
@@ -4764,12 +5179,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Polaris Capital Services spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Noteć spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ulica Krakowskie Przedmieście 135, 20-002 Lublin</t>
+          <t>ulica os. Retkinia 135, 94-004 Łódź</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -4799,20 +5214,25 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
+          <t>DFI/156/2017</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>70122820541</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Aleksandra</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>70122820541</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>Anna</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
+      <c r="L84" t="inlineStr">
         <is>
           <t>Mazur</t>
         </is>
@@ -4821,12 +5241,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Lumen Advisory sp z oo</t>
+          <t>Zielony Pilica Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Chełmińska 92, 87-100</t>
+          <t>Piastowska 92, 48-300</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -4851,7 +5271,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2017-11-08</t>
+          <t>2017-08-11</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4866,10 +5286,15 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Andrzej</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
+        <is>
+          <t>Jakub</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
         <is>
           <t>Krawczyk</t>
         </is>
@@ -4878,12 +5303,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Quantum Services Spółka Akcyjna</t>
+          <t>Zielony Narew S.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ul. Lipowa 169/13, 15-424 Białystok</t>
+          <t>ul. Długa 169/13, 95-100 Zgierz</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4923,10 +5348,15 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Marta</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
         <is>
           <t>Woźniak</t>
         </is>
@@ -4935,12 +5365,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Lumen Advisory spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Jodełka SA</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>ul Sienkiewicza 6, 15-092 Białystok</t>
+          <t>ul Rynek 6, 50-101 Wrocław</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4980,10 +5410,15 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Łukasz</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
+        <is>
+          <t>Artur</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
         <is>
           <t>Jankowski</t>
         </is>
@@ -4992,12 +5427,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Vistula Fintech Polska Spółka Akcyjna</t>
+          <t>Zielony Kaktus S. A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>ulica Gdańska 23, 85-005 Bydgoszcz</t>
+          <t>ulica Jedności Narodowej 23, 50-260 Wrocław</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5012,7 +5447,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t/>
+          <t>1241615809</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -5037,10 +5472,15 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Paulina</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
+        <is>
+          <t>Iwona</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
         <is>
           <t>Grabowska</t>
         </is>
@@ -5049,12 +5489,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Polaris Capital Spółka Akcyjna</t>
+          <t>Zielony Szmaragd Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>os. Dworcowa 40, 85-009 Bydgoszcz</t>
+          <t>os. Konstytucji 3 Maja 40, 58-540 Karpacz</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5094,10 +5534,15 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Mateusz</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
         <is>
           <t>Pawlak</t>
         </is>
@@ -5106,12 +5551,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Baltic Med Supply SP Z O O</t>
+          <t>Zielony Topaz sp. z o.o.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ul. Szeroka 57/65, 87-100 Toruń</t>
+          <t>ul. Odrodzenia 57/65, 59-300 Lubin</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5126,12 +5571,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>1241774181</t>
+          <t/>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>242090949</t>
+          <t>251932597</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5151,10 +5596,15 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Elżbieta</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
+        <is>
+          <t>Renata</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
         <is>
           <t>Michalska</t>
         </is>
@@ -5163,12 +5613,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Baltic Med Supply Polska Spółka Akcyjna</t>
+          <t>Zielony Granit sp z oo</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ul Chełmińska 74, 87-100 Toruń</t>
+          <t>ul Słowackiego 74, 58-300 Wałbrzych</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -5188,7 +5638,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>242090949</t>
+          <t>252011787</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -5208,10 +5658,15 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Dawid</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
+        <is>
+          <t>Maciej</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
         <is>
           <t>Król</t>
         </is>
@@ -5220,12 +5675,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Orbis Retail Solutions Markets spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Marmur sp. z o. o.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ulica 3 Maja 91, 35-030 Rzeszów</t>
+          <t>ulica Półwiejska 91, 61-888 Poznań</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -5265,10 +5720,15 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Dorota</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
         <is>
           <t>Wieczorek</t>
         </is>
@@ -5277,12 +5737,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Quantum Services Markets sp. z o.o.</t>
+          <t>Zielony Syrena Sp. z o.o.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Piłsudskiego 108, 35-074 Rzeszów</t>
+          <t>os. Bolesława Chrobrego 108, 60-681 Poznań</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -5322,10 +5782,15 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Dariusz</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
+        <is>
+          <t>Zbigniew</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
         <is>
           <t>Jabłoński</t>
         </is>
@@ -5334,12 +5799,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Baltic Med Supply spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Zodiak SP Z O O</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ul. Sienkiewicza 125/27, 25-007 Kielce</t>
+          <t>ul. Główny Rynek 125/27, 62-800 Kalisz</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -5379,10 +5844,15 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Beata</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
+        <is>
+          <t>Patrycja</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
         <is>
           <t>Witkowska</t>
         </is>
@@ -5391,12 +5861,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Silesia Invest sp z oo</t>
+          <t>Zielony Olimp spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ul Warszawska 142, 25-512 Kielce</t>
+          <t>ul Kaliska 142, 63-400 Ostrów Wielkopolski</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -5436,10 +5906,15 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Sławomir</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
         <is>
           <t>Walczak</t>
         </is>
@@ -5448,12 +5923,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Quantum Services Finanse sp z oo</t>
+          <t>Zielony Zorza Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ulica Kościuszki 159, 10-504 Olsztyn</t>
+          <t>ulica Ogarna 159, 80-826 Gdańsk</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -5493,10 +5968,15 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Urszula</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
+        <is>
+          <t>Wiktoria</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
         <is>
           <t>Stępień</t>
         </is>
@@ -5505,12 +5985,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Lumen Advisory spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Krokus S.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Dąbrowszczaków 176, 10-540 Olsztyn</t>
+          <t>os. Jasień 176, 80-180 Gdańsk</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -5525,12 +6005,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>1242407705</t>
+          <t>1252328545</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>242566085</t>
+          <t>252486929</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -5550,10 +6030,15 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Mariusz</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
+        <is>
+          <t>Jacek</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
         <is>
           <t>Baran</t>
         </is>
@@ -5562,12 +6047,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Aurum Invest SP Z O O</t>
+          <t>Zielony Narcyz SA</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ul. Krakowska 13/79, 45-018 Opole</t>
+          <t>ul. Bohaterów Monte Cassino 13/79, 81-759 Sopot</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -5607,10 +6092,15 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Izabela</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
         <is>
           <t>Rutkowska</t>
         </is>
@@ -5619,12 +6109,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Orbis Retail Solutions sp. z o.o.</t>
+          <t>Zielony Giewont S. A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ul Ozimska 30, 45-057 Opole</t>
+          <t>30, 80-209 Chwaszczyno</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -5664,10 +6154,15 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Henryk</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
+        <is>
+          <t>Przemysław</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
         <is>
           <t>Górski</t>
         </is>
@@ -5676,12 +6171,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Vistula Fintech sp. z o.o.</t>
+          <t>Zielony Rysy Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ulica Bohaterów Westerplatte 47, 65-034 Zielona Góra</t>
+          <t>ulica 3 Maja 47, 40-096 Katowice</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -5721,10 +6216,15 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Weronika</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
+        <is>
+          <t>Kinga</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
         <is>
           <t>Sikora</t>
         </is>
@@ -5733,12 +6233,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Optima Trade S.A.</t>
+          <t>Zielony Kasprowy sp. z o.o.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Kupiecka 64, 65-058 Zielona Góra</t>
+          <t>os. Paderewskiego 64, 40-282 Katowice</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -5778,10 +6278,15 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Stanisław</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
         <is>
           <t>Ostrowski</t>
         </is>
@@ -5790,12 +6295,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Nova Data Spółka Akcyjna</t>
+          <t>PPHU Zielony Beskid</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ul. Świętojańska 81/41, 81-372 Gdynia</t>
+          <t>ul. Zwycięstwa 81/41, 44-100 Gliwice</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -5810,7 +6315,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2242724469</t>
+          <t>1242724469</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -5835,10 +6340,15 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
+        <is>
+          <t>Kamila</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
         <is>
           <t>Tomaszewska</t>
         </is>
@@ -5847,12 +6357,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Nebula Analytics Polska Spółka Akcyjna</t>
+          <t>Zielony Bieszczady sp. z o. o.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>ul Mickiewicza 38</t>
+          <t>ul Krupówki 38</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -5892,10 +6402,15 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Bartłomiej</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
         <is>
           <t>Zając</t>
         </is>
@@ -5904,12 +6419,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Optima Trade sp z oo</t>
+          <t>Zielony Karpaty Sp. z o.o.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>ulica Bolesława Prusa 115, 05-800 Pruszków</t>
+          <t>ulica Najświętszej Maryi Panny 115, 42-200 Częstochowa</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -5949,24 +6464,29 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Agata</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>Pietrzak</t>
+          <t>Irena</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>Włodarczyk</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Lumen Advisory spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Bałtyk SP Z O O</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Kościuszki 132, 05-500 Piaseczno</t>
+          <t>11 Listopada 132, 43-300 Bielsko-Biała</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -5991,7 +6511,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6006,24 +6526,29 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Tadeusz</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>Wójcicki</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>Borkowski</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Orbis Retail Solutions SP Z O O</t>
+          <t>Zielony Sudety spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>ul. Sienkiewicza 149/3, 32-020 Wieliczka</t>
+          <t>149/3, 36-047 Niechobrz</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6063,24 +6588,29 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Helena</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>Czarnecka</t>
+          <t>Izabela</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>Sawicka</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Optima Trade Finanse spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Amber Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>ul Dąbrowskiego 166, 32-600 Oświęcim</t>
+          <t>ul Franciszkańska 166, 37-700 Przemyśl</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6120,24 +6650,29 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Stefan</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>Lis</t>
+          <t>Mirosław</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>Dudek</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Aurum Invest Technologie SP Z O O</t>
+          <t>Niebieski Bizon S.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>ulica Rynek 3, 38-400 Krosno</t>
+          <t>ulica Kościuszki 3, 38-500 Sanok</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -6157,49 +6692,54 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
+          <t>243357981</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>2021/19/08</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>DFI/103/2026</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>74082879423</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Jadwiga</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>2021/19/08</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>DFI/103/2026</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>74082879423</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>Ewa</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>Kołodziej</t>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>Adamczyk</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Baltic Med Supply Holding S.A.</t>
+          <t>Niebieski Canyon SA</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Mickiewicza 20, 39-300 Mielec</t>
+          <t>Suraska 20, 15-422 Białystok</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>wykonywani zleceń na rachunek klientów</t>
+          <t>wykonywani zleceń n rachunek klientów</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -6234,24 +6774,29 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Józfe</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>Kacmzarek</t>
+          <t>Piotr</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>Pawłowski</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Polaris Capital SP Z O O</t>
+          <t>Niebieski Delfin S. A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>ul. Długa 37/55, 58-100 Świdnica</t>
+          <t>37/55, 16-030 Ogrodniczki</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -6296,19 +6841,24 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>Piątek</t>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>Nowicka</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Optima Trade Finanse S.A.</t>
+          <t>Niebieski Echo Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>ul Wojska Polskiego 54, 57-300 Kłodzko</t>
+          <t>ul 3 Maja 54, 17-200 Hajnówka</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -6323,7 +6873,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>1243516365</t>
+          <t>1253437207</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -6348,24 +6898,29 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>Sadowski</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>Sokołowski</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Baltic Med Supply SP Z O O</t>
+          <t>Niebieski Falcon sp. z o.o.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>ulica Chrobrego 71, 62-200 Gniezno</t>
+          <t>ulica os. LSM 71, 20-400 Lublin</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -6405,24 +6960,29 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Sabina</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>Włodarczyk</t>
+          <t>Joanna</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>Wróbel</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Silesia Invest Spółka Akcyjna</t>
+          <t>Niebieski Gryf sp z oo</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Słowiańska 88, 64-100 Leszno</t>
+          <t>88, 24-120 Mięćmierz</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -6462,24 +7022,29 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Arkadiusz</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>Borkowski</t>
+          <t>Paweł</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>Majewski</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Quantum Services Services S.A.</t>
+          <t>Niebieski Horyzont sp. z o. o.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>105/17, 83-110 Tczew</t>
+          <t>ul. Brzeska 105/17, 21-500 Biała Podlaska</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -6494,7 +7059,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>1243753935</t>
+          <t>1253674775</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -6524,19 +7089,24 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>Kowalska-Krawczyk</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>Olszewska-Błaszczyk</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Helios Markets sp z oo</t>
+          <t>Niebieski Ikar Sp. z o.o.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>ul Sobieskiego 122, 84-200 Wejherowo</t>
+          <t>ul Rynek Staromiejski 122, 87-100 Toruń</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -6546,7 +7116,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t/>
+          <t>0000010969</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -6561,7 +7131,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-01-06</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -6581,19 +7151,24 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>Nowacki</t>
+          <t>Robert</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>Jaworski</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Nebula Analytics Polska S.A.</t>
+          <t>Niebieski Jantar SP Z O O</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>ulica Głęboka 139, 43-400 Cieszyn</t>
+          <t>ulica Mostowa 139, 85-110 Bydgoszcz</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -6603,7 +7178,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>0000011066</t>
+          <t/>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -6613,7 +7188,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>243991502</t>
+          <t/>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -6638,19 +7213,24 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>Wiśniewska</t>
+          <t>Agnieszka</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>Malinowska</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Nova Data spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Koral spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Małachowskiego 156, 42-500 Będzin</t>
+          <t>Stare Miasto 156, 10-026 Olsztyn</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -6695,19 +7275,24 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>Wójcik</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>Pająk</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Quantum Services sp z oo</t>
+          <t>Niebieski Lotos Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>os. Królowej Jadwigi 173/69, 88-100 Inowrocław</t>
+          <t>os. Warszawska 173/69, 11-700 Mrągowo</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -6752,19 +7337,24 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Kowalczyk</t>
+          <t>Justyna</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>Szczepańska</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Baltic Med Supply S.A.</t>
+          <t>Niebieski Magnolia S.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>ul Wybickiego 10, 86-300 Grudziądz</t>
+          <t>ul Wojska Polskiego 10, 70-470 Szczecin</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -6809,14 +7399,19 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>Kamiński</t>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>Czerwiński</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Lumen Advisory S.A.</t>
+          <t>Niebieski Neon SA</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -6846,7 +7441,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2023-04-07</t>
+          <t>2023-07-04</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -6866,19 +7461,24 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>Lewandowska</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>Kubiak</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Vistula Fintech sp z oo</t>
+          <t>Niebieski Oaza S. A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Długa 164, Brzeg</t>
+          <t>Ogarna 164, Gdańsk</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -6923,19 +7523,24 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>Zieliński</t>
+          <t>Marcin</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>Wilk</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Aurum Invest Spółka Akcyjna</t>
+          <t>X - Twitter</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>ul. Lubelska 61/31, 24-100 Puławy</t>
+          <t>ul. Byczyńska 61/31, 46-200 Kluczbork</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -6980,19 +7585,24 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>Szymańska</t>
+          <t>Karolina</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>Wysocka</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Quantum Services sp. z o.o.</t>
+          <t>Niebieski Rubin sp. z o.o.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>ul Staszica 78, 22-400 Zamość</t>
+          <t>ul Chrobrego 78, 66-400 Gorzów Wielkopolski</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7037,19 +7647,24 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>Dąbrowski</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>Chmielewski</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Vistula Fintech sp z oo</t>
+          <t>Niebieski Szafir sp z oo</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>ulica 3 Maja 95, 16-300 Augustów</t>
+          <t>ulica 30 Stycznia 95, 66-300 Międzyrzecz</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -7089,24 +7704,29 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Aleksandra</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>Mazur</t>
+          <t>Małgorzata</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>Urbańska</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Silesia Invest Services sp z oo</t>
+          <t>Niebieski Tytan sp. z o. o.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Kościuszki 112, 16-400 Suwałki</t>
+          <t>Paderewskiego 112, 25-004 Kielce</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -7126,12 +7746,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>244783409</t>
+          <t>254704247</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2018-10-06</t>
+          <t>2018-06-10</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -7146,24 +7766,29 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Andrzej</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>Krawczyk</t>
+          <t>Jakub</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>Błaszczyk</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Quantum Services Technologie sp. z o.o.</t>
+          <t>Niebieski Uran Sp. z o.o.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>ul. Piastowska 129/83, 48-300 Nysa</t>
+          <t>ul. 1 Maja 129/83, 28-100 Busko-Zdrój</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -7183,7 +7808,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>344783409</t>
+          <t>244783409</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -7203,24 +7828,29 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Marta</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>Woźniak</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>Szulc</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Amber Payments S.A.</t>
+          <t>Niebieski Wektor SP Z O O</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>ul Długa 146, 49-300 Brzeg</t>
+          <t>ul Marszałkowska 146, 00-590 Warszawa</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -7260,24 +7890,29 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Łukasz</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>Jankowski</t>
+          <t>Artur</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>Kozak</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Nova Data Holding spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Zefir spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>163, 68-200 Żary</t>
+          <t>ulica Krakowskie Przedmieście 163, 00-071 Warszawa</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -7317,24 +7952,29 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Paulina</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>Grabowska</t>
+          <t>Iwona</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>Cieślak</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Baltic Med Supply sp. z o.o.</t>
+          <t>Niebieski Żubr Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Sikorskiego 180, 66-200 Świebodzin</t>
+          <t>Floriańska 180, 31-019 Kraków</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -7344,7 +7984,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>000001232</t>
+          <t>0000012327</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -7374,24 +8014,29 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Mateusz</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>Pawlak</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>Andrzejewski</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Aurum Invest sp. z o.o.</t>
+          <t>Niebieski Sokół S.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>ul. Armii Krajowej 17/45, 78-100 Kołobrzeg</t>
+          <t>ul. Długa 17/45, 31-147 Kraków</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -7416,7 +8061,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2018-04-03</t>
+          <t>2018-03-04</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -7431,24 +8076,29 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Elżbieta</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>Michalska</t>
+          <t>Renata</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>Gajewska</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Mazovia Broker Markets Spółka Akcyjna</t>
+          <t>Niebieski Orzeł SA</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>ul Piłsudskiego 34, 73-110 Stargard</t>
+          <t>ul Piotrkowska 34, 90-102 Łódź</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -7488,24 +8138,29 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Dawid</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>Król</t>
+          <t>Maciej</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>Laskowski</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Quantum Services spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Kormoran S. A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>ulica Mickiewicza 51, 27-600 Sandomierz</t>
+          <t>ulica Zachodnia 51, 90-402 Łódź</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -7525,7 +8180,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>245337735</t>
+          <t>255258577</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -7545,24 +8200,29 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Dorota</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>Wieczorek</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>Mazurek</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Vistula Fintech Polska Spółka Akcyjna</t>
+          <t>Niebieski Barycz Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Sienkiewicza 68, 27-400 Ostrowiec Świętokrzyski</t>
+          <t>Świdnicka 68, 50-066 Wrocław</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -7602,24 +8262,29 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Dariusz</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>Jabłoński</t>
+          <t>Zbigniew</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>Sobczak</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Orbis Retail Solutions Technologie SP Z O O</t>
+          <t>Niebieski Noteć sp. z o.o.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>ul. Marszałkowska 85/7, 00-590 Warszawa</t>
+          <t>ul. Legnicka 85/7, 54-203 Wrocław</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -7659,24 +8324,29 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Beata</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>Witkowska</t>
+          <t>Patrycja</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>Konieczna</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Optima Trade Spółka Akcyjna</t>
+          <t>Niebieski Pilica sp z oo</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>ul Krakowskie Przedmieście 102, 00-071 Warszawa</t>
+          <t>ul Święty Marcin 102, 61-806 Poznań</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -7696,12 +8366,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>245575305</t>
+          <t>255496147</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2017-03-01</t>
+          <t>2017-01-03</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -7716,24 +8386,29 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Sławomir</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>Walczak</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>Brzeziński</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Amber Payments Holding sp z oo</t>
+          <t>Niebieski Narew sp. z o. o.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>ulica Floriańska 119, 31-019 Kraków</t>
+          <t>ulica Głogowska 119, 60-734 Poznań</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -7773,24 +8448,29 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Urszula</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>Stępień</t>
+          <t>Wiktoria</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>Makowska</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Aurum Invest Markets SP Z O O</t>
+          <t>Niebieski Jodełka Sp. z o.o.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Długa 136, 31-147 Kraków</t>
+          <t>Długa 136, 80-831 Gdańsk</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -7830,24 +8510,29 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Mariusz</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>Baran</t>
+          <t>Jacek</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>Wrona</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Helios Markets Spółka Akcyjna</t>
+          <t>Niebieski Kaktus SP Z O O</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>ul. Piotrkowska 153/59, 90-102 Łódź</t>
+          <t>ul. Grunwaldzka 153/59, 80-236 Gdańsk</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -7887,24 +8572,29 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Izabela</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>Rutkowska</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>Bąk</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Astra Finance Spółka Akcyjna</t>
+          <t>Niebieski Szmaragd spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>80-236 Gdańsk</t>
+          <t>21-500 Biała Podlaska</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -7924,7 +8614,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>245892069</t>
+          <t>255812909</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -7944,24 +8634,29 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Henryk</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>Górski</t>
+          <t>Przemysław</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>Kucharski</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Helios Markets S.A.</t>
+          <t>Niebieski Topaz Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>ulica Świdnicka 7, 50-066 Wrocław</t>
+          <t>ulica Wyszyńskiego 7, 70-200 Szczecin</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -8001,24 +8696,29 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Weronika</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>Sikora</t>
+          <t>Kinga</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>Lisowska</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Nova Dta Spółka Akcyjna</t>
+          <t>Niebieski Granit S.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Legnicka 24, 54-203 Wrocław</t>
+          <t>Mariacka 24, 40-014 Katowice</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -8058,24 +8758,29 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Stanisław</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>Ostrowski</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>Słowik</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Polaris Capital S.A.</t>
+          <t>P.P.H.U. Niebieski Marmur</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>ul. Święty Marcin 41/21, 61-806 Poznań</t>
+          <t>ul. Warszawska 41/21, 40-009 Katowice</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -8115,24 +8820,29 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>Tomaszewska</t>
+          <t>Kamila</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>Kopeć</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Nebula Analytics Holding S.A.</t>
+          <t>Niebieski Syrena S. A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>ul Głogowska 58, 60-734 Poznań</t>
+          <t>ul Krakowskie Przedmieście 58, 20-002 Lublin</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -8172,24 +8882,29 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Bartłomiej</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>Zając</t>
+          <t>Daniel</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>Czajka</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Baltic Med Supply S.A.</t>
+          <t>Niebieski Zodiak Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>ulica Długa 75, 80-831 Gdańsk</t>
+          <t>ulica Narutowicza 75, 20-004 Lublin</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -8229,24 +8944,29 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Olga</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>Pietrzak</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>Matusiak</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Nebula Analytics Spółka Akcyjna</t>
+          <t>Niebieski Olimp sp. z o.o.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Grunwaldzka 92, 80-236 Gdańsk</t>
+          <t>Lipowa 92, 15-424 Białystok</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -8281,29 +9001,34 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>75090730136</t>
+          <t>65090730136</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Damian</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>Wójcicki</t>
+          <t>Waldemar</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>Gajda</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Astra Finance Markets Spółka Akcyjna</t>
+          <t>Niebieski Zorza sp z oo</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>ul. Jagiellońska 109/73, 70-435 Szczecin</t>
+          <t>ul. Sienkiewicza 109/73, 15-092 Białystok</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -8318,7 +9043,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>1246288019</t>
+          <t>1256208855</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -8343,24 +9068,29 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Ewelina</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>Czarnecka</t>
+          <t>Danuta</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>Klimek</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Silesia Invest S.A.</t>
+          <t>Niebieski Krokus sp. z o. o.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>os. Wyszyńskiego 126, 70-200 Szczecin</t>
+          <t>os. Gdańska 126, 85-005 Bydgoszcz</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -8400,24 +9130,29 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Bartosz</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>Lis</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>Madej</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Silesia Invest Polska spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Narcyz Sp. z o.o.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>ulica Mariacka 143, 40-014 Katowice</t>
+          <t>ulica Dworcowa 143, 85-009 Bydgoszcz</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -8457,24 +9192,29 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Sylwia</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>Kołodziej</t>
+          <t>Aneta</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>Krupa</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Silesia Invest SP Z O O</t>
+          <t>Niebieski Giewont SP Z O O</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Warszawska 160, 40-009 Katowice</t>
+          <t>Szeroka 160, 87-100 Toruń</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -8514,24 +9254,29 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Leszek</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>Kaczmarek</t>
+          <t>Kacper</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>Kaczmarczyk</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Silesia Invest sp. z o.o.</t>
+          <t>Niebieski Rysy spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>ul. Krakowskie Przedmieście 177/35, 20-002 Lublin</t>
+          <t>ul. Chełmińska 177/35, 87-100 Toruń</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -8571,24 +9316,29 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Grażyna</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>Piątek</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>Wrona</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Lumen Advisory spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Kasprowy Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>ul Narutowicza 14, 20-004 Lublin</t>
+          <t>ul 3 Maja 14, 35-030 Rzeszów</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -8603,7 +9353,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2246604779</t>
+          <t>1246604779</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -8628,24 +9378,29 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Cezary</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>Sadowski</t>
+          <t>Szymon</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>Wasilewski</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Aurum Invest spółka z ograniczoną odpowiedzialnością</t>
+          <t>Amber Budownictwo S.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>ulica Lipowa 31, 15-424 Białystok</t>
+          <t>ulica Piłsudskiego 31, 35-074 Rzeszów</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -8685,24 +9440,29 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Bożena</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>Włodarczyk</t>
+          <t>Oliwia</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>Kalinowska</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Vistula Fintech S.A.</t>
+          <t>Amber Transport SA</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Sienkiewicza 48, 15-092 Białystok</t>
+          <t>Sienkiewicza 48, 25-007 Kielce</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -8742,24 +9502,29 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Filip</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>Borkowski</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>Zarychta</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Aurum Invest sp z oo</t>
+          <t>Amber Spedycja S. A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>ul. Gdańska 65/87, 85-005 Bydgoszcz</t>
+          <t>ul. Warszawska 65/87, 25-512 Kielce</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -8799,24 +9564,29 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Zuzanna</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>Kowalska-Krawczyk</t>
+          <t>Emilia</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>Przybylska-Kowalska</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Baltic Med Supply S.A.</t>
+          <t>Amber Logistyka Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>ul Dworcowa 82, 85-009 Bydgoszcz</t>
+          <t>ul Kościuszki 82, 10-504 Olsztyn</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -8851,29 +9621,34 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>75072143838</t>
+          <t>85072143838</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Mikołaj</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>Nowacki</t>
+          <t>Ignacy</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>Michalak</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Optima Trade sp z oo</t>
+          <t>Amber Handel sp. z o.o.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>ulica Szeroka 99, 87-100 Toruń</t>
+          <t>ulica Dąbrowszczaków 99, 10-540 Olsztyn</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -8913,24 +9688,29 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Lena</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>Wiśniewska</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>Szatkowska</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Mazovia Broker S.A.</t>
+          <t>Amber Usługi sp z oo</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Chełmińska 116, 87-100 Toruń</t>
+          <t>Krakowska 116, 45-018 Opole</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -8970,24 +9750,29 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Antoni</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>Wójcik</t>
+          <t>Leon</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>Bednarek</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Mazovia Broker S.A.</t>
+          <t>Amber Finanse sp. z o. o.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>ul. 3 Maja 133/49, 35-030 Rzeszów</t>
+          <t>ul. Ozimska 133/49, 45-057 Opole</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -9027,29 +9812,34 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Hanna</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>Kowalczyk</t>
+          <t>Dominika</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>Podgórska</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Amber Paymen pSółka Akcyjna</t>
+          <t>Amber Doradztwo Sp. z o.o.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>ul Piłsudskiego 150, 35-074 Rzeszów</t>
+          <t>ul Bohaterów Westerplatte 150, 65-034 Zielona Góra</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>zarządaznie portfelami</t>
+          <t>zarzdąaznie portfelami</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -9084,24 +9874,29 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Franciszek</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>Kamiński</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>Śliwiński</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Quantum Services sp. z o.o.</t>
+          <t>Amber Szkolenia SP Z O O</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>ulica Sienkiewicza 167, 25-007 Kielce</t>
+          <t>ulica Kupiecka 167, 65-058 Zielona Góra</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -9116,7 +9911,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>1247396679</t>
+          <t>1257317517</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -9141,24 +9936,29 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Amelia</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>Lewandowska</t>
+          <t>Jagoda</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>Czajkowska</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Baltic Med Supply sp z oo</t>
+          <t>Amber Media spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Warszawska 4, 25-512 Kielce</t>
+          <t>Świętojańska 4, 81-372 Gdynia</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -9198,24 +9998,29 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Nikodem</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>Zieliński</t>
+          <t>Jerzy</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>Biernat</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Nebula Analytics sp. z o.o.</t>
+          <t>Facebook - Meta</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>ul. Kościuszki 21/11, 10-504 Olsztyn</t>
+          <t>ul. 10 Lutego 21/11, 81-364 Gdynia</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -9255,24 +10060,29 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>Szymańska</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>Panek</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Lumen Advisory spółka z ograniczoną odpowiedzialnością</t>
+          <t>Amber Marketing S.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>ul Dąbrowszczaków 38, 10-540 Olsztyn</t>
+          <t>ul Bolesława Prusa 38, 05-800 Pruszków</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -9287,7 +10097,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>1247634245</t>
+          <t>1257555085</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -9312,24 +10122,29 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Miłosz</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>Dąbrowski</t>
+          <t>Marian</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>Prus</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Amber Payments Spółka Akcyjna</t>
+          <t>Amber Druk SA</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>ulica Krakowska 55, 45-018 Opole</t>
+          <t>ulica Kościuszki 55, 05-500 Piaseczno</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -9369,24 +10184,29 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Agata</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>Mazur</t>
+          <t>Irena</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>Janik</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Nebula Analytics spółka z ograniczoną odpowiedzialnością</t>
+          <t>Amber Informatyka S. A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Ozimska 72, 45-057 Opole</t>
+          <t>Sienkiewicza 72, 32-020 Wieliczka</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -9411,7 +10231,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2022-08-05</t>
+          <t>2022-05-08</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -9426,24 +10246,29 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Tadeusz</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>Krawczyk</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>Kowalski</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Vistula Fintech sp z oo</t>
+          <t>Amber Oprogramowanie Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>ul. Bohaterów Westerplatte 89/63, 65-034 Zielona Góra</t>
+          <t>ul. Dąbrowskiego 89/63, 32-600 Oświęcim</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -9458,7 +10283,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>1247871815</t>
+          <t>1257792655</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -9483,24 +10308,29 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Helena</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>Woźniak</t>
+          <t>Izabela</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>Nowacka</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Nova Data Technologie SP Z O O</t>
+          <t>Amber Rolnictwo sp. z o.o.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>ul Kupiecka 106, 65-058 Zielona Góra</t>
+          <t>ul Rynek 106, 38-400 Krosno</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -9515,7 +10345,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>1247871815</t>
+          <t>2247871815</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -9540,24 +10370,29 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Stefan</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>Jankowski</t>
+          <t>Mirosław</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>Wiśniewski</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Polaris Capital Technologie S.A.</t>
+          <t>Amber Ogrodnictwo sp z oo</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>ulica Świętojańska 123, 81-372 Gdynia</t>
+          <t>ulica Mickiewicza 123, 39-300 Mielec</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -9597,24 +10432,29 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Jadwiga</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>Grabowska</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>Wójcik</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Quantum Services SP Z O O</t>
+          <t>Amber Produkcja sp. z o. o.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>10 Lutego 140, 81-364 Gdynia</t>
+          <t>Długa 140, 58-100 Świdnica</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -9654,24 +10494,29 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Józef</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>Pawlak</t>
+          <t>Piotr</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>Kowalczyk</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Amber Payments Services Spółka Akcyjna</t>
+          <t>Amber Przemysł Sp. z o.o.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>ul. Bolesława Prusa 157/25, 05-800 Pruszków</t>
+          <t>157/25, 57-300 Kłodzko</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -9716,19 +10561,24 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>Michalska</t>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>Kamińska</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Lumen Advisory spółka z ograniczoną odpowiedzialnością</t>
+          <t>Amber Ekologia SP Z O O</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>ul Kościuszki 174, 05-500 Piaseczno</t>
+          <t>ul Chrobrego 174, 62-200 Gniezno</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -9768,24 +10618,29 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>Król</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>Lewandowski</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Amber Payments sp z oo</t>
+          <t>Amber Energetyka spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>ulica Sienkiewicza 11, 32-020 Wieliczka</t>
+          <t>ulica Słowiańska 11, 64-100 Leszno</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -9825,24 +10680,29 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Sabina</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>Wieczorek</t>
+          <t>Joanna</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>Zielińska</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Quantum Services sp. z o.o.</t>
+          <t>Amber Instalacje Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Dąbrowskiego 28, 32-600 Oświęcim</t>
+          <t>Gdańska 28, 83-110 Tczew</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -9882,24 +10742,29 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Arkadiusz</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>Jabłoński</t>
+          <t>Paweł</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>Szymański</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Silesia Invest spółka z ograniczoną odpowiedzialnością</t>
+          <t>Amber Nieruchomości S.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>ul. Rynek 45/77, 38-400 Krosno</t>
+          <t>ul. Sobieskiego 45/77, 84-200 Wejherowo</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -9944,19 +10809,24 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>Witkowska</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>Dąbrowska</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Vistula Fintech sp z oo</t>
+          <t>Amber Inwestycje SA</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>ul Mickiewicza 62, 39-300 Mielec</t>
+          <t>ul Głęboka 62, 43-400 Cieszyn</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -10001,19 +10871,24 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>Walczak</t>
+          <t>Robert</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>Mazur</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Helios Markets sp z oo</t>
+          <t>Amber Medycyna S. A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>os. Długa 79, 58-100 Świdnica</t>
+          <t>os. Małachowskiego 79, 42-500 Będzin</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -10033,7 +10908,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>348742904</t>
+          <t>248742904</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -10058,19 +10933,24 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>Stępień</t>
+          <t>Agnieszka</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>Krawczyk</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Polaris Capital sp z oo</t>
+          <t>Amber Zdrowie Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>96, 57-300 Kłodzko</t>
+          <t>Królowej Jadwigi 96, 88-100 Inowrocław</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -10115,19 +10995,24 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>Baran</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>Woźniak</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Nova Data sp z oo</t>
+          <t>Amber Urody sp. z o.o.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>ul. Chrobrego 113/39, 62-200 Gniezno</t>
+          <t>ul. Wybickiego 113/39, 86-300 Grudziądz</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -10137,7 +11022,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>000001708</t>
+          <t>0000017080</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -10172,19 +11057,24 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>Rutkowska</t>
+          <t>Justyna</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>Jankowska</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Helios Markets spółka z ograniczoną odpowiedzialnością</t>
+          <t>Amber Turystyka sp z oo</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>ul Słowiańska 130, 64-100 Leszno</t>
+          <t>ul Czarnieckiego 130, 14-100 Ostróda</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -10229,19 +11119,24 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>Górski</t>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>Grabowski</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Mazovia Broker sp z oo</t>
+          <t>Amber Rozrywka sp. z o. o.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>ulica Gdańska 147, 83-110 Tczew</t>
+          <t>ulica Warszawska 147, 11-500 Giżycko</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -10266,7 +11161,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -10286,19 +11181,24 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>Sikora</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>Pawlak</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Vistula Fintech S.A.</t>
+          <t>Amber Gastronomia Sp. z o.o.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Sobieskiego 164, 84-200 Wejherowo</t>
+          <t>Lubelska 164, 24-100 Puławy</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -10318,7 +11218,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>249218045</t>
+          <t>259138887</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -10343,19 +11243,24 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>Ostrowski</t>
+          <t>Marcin</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>Michalski</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Lumen Advisory Spółka Akcyjna</t>
+          <t>PPHU Amber Moda</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>ul. Głęboka 1/1, 43-400 Cieszyn</t>
+          <t>ul. Staszica 1/1, 22-400 Zamość</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -10400,19 +11305,24 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>Tomaszewska</t>
+          <t>Karolina</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>Król</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Quantum Services sp z oo</t>
+          <t>Amber Tekstylia spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>ul Małachowskiego 18, 42-500 Będzin</t>
+          <t>ul 3 Maja 18, 16-300 Augustów</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -10457,19 +11367,24 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>Zając</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>Wieczorek</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Mazovia Broker SP Z O O</t>
+          <t>Amber Motoryzacja Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>ulica Królowej Jadwigi 35, 88-100 Inowrocław</t>
+          <t>ulica Kościuszki 35, 16-400 Suwałki</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -10489,7 +11404,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>249455615</t>
+          <t>259376457</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -10509,24 +11424,29 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Aleksandra</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>Pietrzak</t>
+          <t>Małgorzata</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>Jabłońska</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Aurum Invest Services spółka z ograniczoną odpowiedzialnością</t>
+          <t>Amber Ubezpieczenia S.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>os. Kościuszki 172, 16-400</t>
+          <t>os. Kupiecka 172, 65-058</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -10566,24 +11486,29 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Andrzej</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>Wójcicki</t>
+          <t>Jakub</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>Witkowski</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Mazovia Broker sp. z o.o.</t>
+          <t>Amber Spawalnictwo SA</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>ul. Czarnieckiego 69/53, 14-100 Ostróda</t>
+          <t>ul. Długa 69/53, 49-300 Brzeg</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -10623,24 +11548,29 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Marta</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>Czarnecka</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>Walczak</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Nova Data Spółka Akcyjna</t>
+          <t>Amber Ślusarstwo S. A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>ul Warszawska 86, 11-500 Giżycko</t>
+          <t>ul Rynek 86, 68-200 Żary</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -10680,24 +11610,29 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Łukasz</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>Lis</t>
+          <t>Artur</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>Stępień</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Polaris Capital sp. z o.o.</t>
+          <t>Amber Krawiectwo Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>ulica Lubelska 103, 24-100 Puławy</t>
+          <t>ulica Sikorskiego 103, 66-200 Świebodzin</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -10737,24 +11672,29 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Paulina</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>Kołodziej</t>
+          <t>Iwona</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>Baran</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Vistula Fintech S.A.</t>
+          <t>Amber Ochrona sp. z o.o.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Staszica 120, 22-400 Zamość</t>
+          <t>Armii Krajowej 120, 78-100 Kołobrzeg</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -10794,24 +11734,29 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Mateusz</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>Kaczmarek</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>Rutkowski</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Vistula Fintech Technologie Spółka Akcyjna</t>
+          <t>Amber Catering sp z oo</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>ul. 3 Maja 137/15, 16-300 Augustów</t>
+          <t>ul. Piłsudskiego 137/15, 73-110 Stargard</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -10836,7 +11781,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
+          <t>2022-08-09</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -10851,24 +11796,29 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Elżbieta</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>Piątek</t>
+          <t>Renata</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>Górska</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Nova Data Finanse SP Z O O</t>
+          <t>Amber Księgowość sp. z o. o.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>ul Kościuszki 154, 16-400 Suwałki</t>
+          <t>154, 27-600 Sandomierz</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -10888,7 +11838,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>250009941</t>
+          <t>259930787</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -10908,24 +11858,29 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Dawid</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>Sadowski</t>
+          <t>Maciej</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>Sikora</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Orbis Retail Solutions sp z oo</t>
+          <t>Bizon Budownictwo Sp. z o.o.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>ulica Piastowska 171, 48-300 Nysa</t>
+          <t>ulica Sienkiewicza 171, 27-400 Ostrowiec Świętokrzyski</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -10965,24 +11920,29 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Dorota</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>Włodarczyk</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>Ostrowska</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Polaris Capital sp z oo</t>
+          <t>Bizon Transport SP Z O O</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Długa 8, 49-300 Brzeg</t>
+          <t>Chmielna 8, 00-020 Warszawa</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -10992,7 +11952,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>0000018535</t>
+          <t>000001853</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -11002,7 +11962,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>250089130</t>
+          <t>350089130</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -11022,24 +11982,29 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Dariusz</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>Borkowski</t>
+          <t>Zbigniew</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>Tomaszewski</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Optima Trade spółka z ograniczoną odpowiedzialnością</t>
+          <t>Bizon Spedycja spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>ul. Rynek 25/67, 68-200 Żary</t>
+          <t>ul. Nowy Świat 25/67, 00-029 Warszawa</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -11079,24 +12044,29 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Beata</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>Kowalska-Krawczyk</t>
+          <t>Patrycja</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>Zając-Sawicka</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Baltic Med Supply Finanse sp. z o.o.</t>
+          <t>Bizon Logistyka Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>ul Sikorskiego 42, 66-200 Świebodzin</t>
+          <t>ul os. Przyjaźń 42, 01-355 Warszawa</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -11136,24 +12106,29 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Sławomir</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>Nowacki</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>Pietrzak</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Optima Trade Holding sp. z o.o.</t>
+          <t>Bizon Handel S.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>ulica Armii Krajowej 59, 78-100 Kołobrzeg</t>
+          <t>ulica Jagiellońska 59, 05-120 Legionowo</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -11193,24 +12168,29 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Urszula</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>Wiśniewska</t>
+          <t>Wiktoria</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>Wójcicka</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Silesia Invest sp. z o.o.</t>
+          <t>Bizon Usługi SA</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Piłsudskiego 76, 73-110 Stargard</t>
+          <t>Piłsudskiego 76, 05-270 Marki</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -11250,24 +12230,29 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Mariusz</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>Wójcik</t>
+          <t>Jacek</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>Czarnecki</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Lumen Advisory Spółka Akcyjna</t>
+          <t>Bizon Finanse S. A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>93/29, 27-600 Sandomierz</t>
+          <t>ul. Andriollego 93/29, 05-400 Otwock</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -11287,7 +12272,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>250564275</t>
+          <t>260485119</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -11307,24 +12292,29 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Izabela</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>Kowalczyk</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>Lis</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Lumen Advisory S.A.</t>
+          <t>Bizon Doradztwo Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>ul Sienkiewicza 110, 27-400 Ostrowiec Świętokrzyski</t>
+          <t>ul Żeromskiego 110, 26-600 Radom</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -11364,24 +12354,29 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Henryk</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>Kamiński</t>
+          <t>Przemysław</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>Kołodziej</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Baltic Med Supply sp z oo</t>
+          <t>Bizon Szkolenia sp. z o.o.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>ulica Marszałkowska 127, 00-590 Warszawa</t>
+          <t>ulica Tumska 127, 09-402 Płock</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -11396,7 +12391,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>2250485080</t>
+          <t>1250485080</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -11421,24 +12416,29 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Weronika</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>Lewandowska</t>
+          <t>Kinga</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>Kaczmarek</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Nebula Analytics SP Z O O</t>
+          <t>Bizon Media sp z oo</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Krakowskie Przedmieście 144, 00-071 Warszawa</t>
+          <t>Karmelicka 144, 31-128 Kraków</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -11478,12 +12478,17 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Stanisław</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>Zieliński</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>Piątek</t>
         </is>
       </c>
     </row>

--- a/data/xlsx/KNF_Rejestr_firm_inwestycyjnych.xlsx
+++ b/data/xlsx/KNF_Rejestr_firm_inwestycyjnych.xlsx
@@ -83,6 +83,11 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
+          <t>CzlonekZarzadu1_DrugieImie</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>CzlonekZarzadu1_Nazwisko</t>
         </is>
       </c>
@@ -90,7 +95,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Polaris Capital Markets SP Z O O</t>
+          <t>Facebook - Meta</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -130,24 +135,29 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>60021406849</t>
+          <t>60101434205</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Pawlak-Sikora</t>
+          <t>Karolina</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Kaczmarek</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Optima Trade spółka z ograniczoną odpowiedzialnością</t>
+          <t>Polskie Przetwory sp z oo</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -187,24 +197,29 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>61032108236</t>
+          <t>61112135592</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Michalski</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Piątek</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Amber Payments spółka z ograniczoną odpowiedzialnością</t>
+          <t>Hurtownia Nabiału Mleczko sp. z o. o.</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -229,7 +244,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>235122221</t>
+          <t>335122221</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -244,24 +259,29 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>62042809586</t>
+          <t>62122836941</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Aleksandra</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Król</t>
+          <t>Małgorzata</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Sadowska</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Vistula Fintech Services sp z oo</t>
+          <t>Agencja Reklamowa Kreatywni Sp. z o.o.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -291,7 +311,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2022-10-12</t>
+          <t>2022-12-10</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -301,24 +321,29 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63050710972</t>
+          <t>63010738330</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Andrzej</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Wieczorek</t>
+          <t>Jakub</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Włodarczyk</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Nova Data Technologie S.A.</t>
+          <t>Kancelaria Prawna Sankcja SP Z O O</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -358,24 +383,29 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64061412321</t>
+          <t>64021439689</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Marta</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Jabłońska</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Borkowska</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Nova Data S.A.</t>
+          <t>Śląskie Zakłady Mechaniczne spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -415,24 +445,29 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65072113717</t>
+          <t>65032141079</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Łukasz</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Witkowski</t>
+          <t>Artur</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Sawicki</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Orbis Retail Solutions sp. z o.o.</t>
+          <t>Fabryka Okien i Drzwi Profil Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -472,24 +507,29 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>66082815068</t>
+          <t>66042842428</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Paulina</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Walczak</t>
+          <t>Iwona</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Dudek</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Vistula Fintech S.A.</t>
+          <t>Przedsiębiorstwo Robót Drogowych S.A.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -499,7 +539,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>przymjoanwie i przekazywanie zlceeń</t>
+          <t>przymjoanwi  przekazywanie zleceń</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -524,29 +564,34 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>DFI/418/2026</t>
+          <t>DF/418/2026</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>67090716451</t>
+          <t>67050743811</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Mateusz</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Stępień</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Adamczyk</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Astra Finance Holding Spółka Akcyjna</t>
+          <t>Krakowskie Biuro Nieruchomości SA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -576,7 +621,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2018-05-06</t>
+          <t>2018-06-05</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -586,24 +631,29 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>68101417802</t>
+          <t>68061445161</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Elżbieta</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Baran</t>
+          <t>Renata</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Pawłowska</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Baltic Med Supply Finanse S.A.</t>
+          <t>Salon Samochodowy Auto-Hit S. A.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -643,24 +693,29 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>69112119190</t>
+          <t>69072146557</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Dawid</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Rutkowski</t>
+          <t>Maciej</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Nowicki</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Amber Payments Spółka Akcyjna</t>
+          <t>Klinika Stomatologiczna Dent-Med Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -700,24 +755,29 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>70122820541</t>
+          <t>70082847905</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Dorota</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Górska</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Sokołowska</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Silesia Invest Services sp. z o.o.</t>
+          <t>Polski Tytoń sp. z o.o.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -737,7 +797,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2235676551</t>
+          <t>1235676551</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -757,24 +817,29 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>71010721939</t>
+          <t>71090749290</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Dariusz</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Sikora</t>
+          <t>Zbigniew</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Wróbel</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Polaris Capital Technologie sp z oo</t>
+          <t>Gdańska Stocznia Jachtowa sp z oo</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -814,24 +879,29 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>72021423289</t>
+          <t>72101450644</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Beata</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Ostrowska</t>
+          <t>Patrycja</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Majewska</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Baltic Med Supply sp. z o.o.</t>
+          <t>Wytwórnia Makaronu Jajecznego sp. z o. o.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -861,7 +931,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2022-10-12</t>
+          <t>2022-12-10</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -871,24 +941,29 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>73032124675</t>
+          <t>73112152031</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Sławomir</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Tomaszewski</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Olszewski</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Silesia Invest sp. z o.o.</t>
+          <t>Zakłady Mięsne Tradycja Sp. z o.o.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -928,24 +1003,29 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>74042826025</t>
+          <t>74122853381</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Urszula</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Zając</t>
+          <t>Wiktoria</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Jaworska</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Silesia Invest Holding Spółka Akcyjna</t>
+          <t>Spółdzielnia Mleczarska Radomsko SP Z O O</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -985,24 +1065,29 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>75050727418</t>
+          <t>75010754779</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Mariusz</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Pietrzak</t>
+          <t>Jacek</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Malinowski</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Polaris Capital SP Z O O</t>
+          <t>Kancelaria Finansowo-Księgowa Bilans spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1042,81 +1127,91 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>76061428767</t>
+          <t>76021456128</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Izabela</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Wójcicka</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Pająk</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>Zarząd Nieruchomości Komercyjnych Spółka z ograniczoną odpowiedzialnością</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ul Narutowicza 110, 20-004 Lublin</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>ul Narutowicza 110, 20-004 Lublin</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0000001657</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1236151690</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>236310077</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>0000001657</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>1236151690</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>236310077</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>77072130157</t>
+          <t>77032157514</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Henryk</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Czarnecki</t>
+          <t>Przemysław</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Szczepański</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Silesia Invest Markets sp z oo</t>
+          <t>Polskie Linie Oceaniczne S.A.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1146,7 +1241,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2021-11-06</t>
+          <t>2021-06-11</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1156,29 +1251,34 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>78082831506</t>
+          <t>78042858864</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Weronika</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Lis</t>
+          <t>Kinga</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Czerwińska</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Astra Finance SP Z O O</t>
+          <t>Hurtownia Materiałów Budowlanych Cegiełka SA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Piłsudskiego 84, Rzeszów</t>
+          <t>Rynek 84, Opole</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1213,24 +1313,29 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>79090732890</t>
+          <t>79050760251</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Stanisław</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Kołodziej</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Kubiak</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Lumen Advisory SP Z O O</t>
+          <t>PPHU Studio Projektowe Architektura</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1270,24 +1375,29 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>80101434241</t>
+          <t>80061461608</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Kaczmarek</t>
+          <t>Kamila</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Wilk</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Silesia Invest sp. z o.o.</t>
+          <t>Centrum Medycyny Pracy Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1327,24 +1437,29 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>81112135637</t>
+          <t>81072162995</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Bartłomiej</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Piątek</t>
+          <t>Daniel</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Wysocki</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Nova Data sp z oo</t>
+          <t>Przedsiębiorstwo Energetyki Cieplnej sp. z o.o.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1369,7 +1484,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>236785219</t>
+          <t>246706057</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1384,24 +1499,29 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>82122836987</t>
+          <t>82082864345</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Olga</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Sadowska</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Chmielewska</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Baltic Med Supply sp. z o.o.</t>
+          <t>Gospodarstwo Rolno-Ogrodnicze sp z oo</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1441,24 +1561,29 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>83010738376</t>
+          <t>83090765738</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Damian</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Włodarczyk</t>
+          <t>Waldemar</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Urbański</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Optima Trade Spółka Akcyjna</t>
+          <t>Drukarnia Wielkoformatowa Impress sp. z o. o.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1498,24 +1623,29 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>84021439724</t>
+          <t>84101467081</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Ewelina</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Borkowska</t>
+          <t>Danuta</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Błaszczyk</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Orbis Retail Solutions Services S.A.</t>
+          <t>Klub Fitness Sylwetka Sp. z o.o.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1555,24 +1685,29 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>85032141114</t>
+          <t>85112168477</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Bartosz</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Kowalski</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Szulc</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Helios Markets Polska sp. z o.o.</t>
+          <t>Polska Grupa Energetyczna SP Z O O</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1612,24 +1747,29 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>86042842464</t>
+          <t>86122869826</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Sylwia</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Nowacka</t>
+          <t>Aneta</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Kozak</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Silesia Invest sp. z o.o.</t>
+          <t>Mazowieckie Zakłady Drobiarskie spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1669,24 +1809,29 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>87050743857</t>
+          <t>87010771218</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Leszek</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Wiśniewski</t>
+          <t>Kacper</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Cieślak</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Silesia Invest sp z oo</t>
+          <t>Hurtownia Farmaceutyczna Aptekarz Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1726,24 +1871,29 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>88061445206</t>
+          <t>88021472567</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Grażyna</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Wójcik</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Andrzejewska</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Aurum Invest Holding Spółka Akcyjna</t>
+          <t>Kancelaria Notarialna Lex S.A.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1783,24 +1933,29 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>89072146593</t>
+          <t>89032173953</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Cezary</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Kowalczyk</t>
+          <t>Szymon</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Gajewski</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Silesia Invest SP Z O O</t>
+          <t>Biuro Podróży Wojażer SA</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1840,24 +1995,29 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>90082847941</t>
+          <t>90042875302</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Bożena</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Kamińska</t>
+          <t>Oliwia</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Laskowska</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Optima Trade Spółka Akcyjna</t>
+          <t>Szkoła Języków Obcych Lingua S. A.</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1897,24 +2057,29 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>91090749335</t>
+          <t>91050776696</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Filip</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Lewandowski</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Mazurek</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Optima Trade SP Z O O</t>
+          <t>Centrum Logistyczne Podlasie Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1934,12 +2099,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1237418735</t>
+          <t>1247339575</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>237577115</t>
+          <t>247497957</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1954,24 +2119,29 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>92101450680</t>
+          <t>92061478045</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Zuzanna</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Zielińska</t>
+          <t>Emilia</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Sobczak-Matusiak</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Nova Data Polska S.A.</t>
+          <t>Fabryka Mebli Drewnianych Dąb sp. z o.o.</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2011,24 +2181,29 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>93112152077</t>
+          <t>93072179431</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Mikołaj</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Szymański</t>
+          <t>Ignacy</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Konieczny</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Astra Finance Technologie spółka z ograniczoną odpowiedzialnością</t>
+          <t>Polskie Sady sp z oo</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2068,24 +2243,29 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>94122853426</t>
+          <t>94082880784</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Lena</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Dąbrowska</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Brzezińska</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Aurum Invest Polska spółka z ograniczoną odpowiedzialnością</t>
+          <t>Wielkopolska Hurtownia Stali sp. z o. o.</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2105,7 +2285,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1237656305</t>
+          <t>1247577145</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2125,24 +2305,29 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>95010754814</t>
+          <t>95090782178</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Antoni</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Mazur</t>
+          <t>Leon</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Makowski</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Amber Payments sp z oo</t>
+          <t>Zakład Oczyszczania Miasta Sp. z o.o.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2167,7 +2352,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>237893879</t>
+          <t>247814719</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2182,29 +2367,34 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>96021456164</t>
+          <t>96101483529</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Hanna</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Krawczyk</t>
+          <t>Dominika</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Wrona</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Astra Finance SP Z O O</t>
+          <t>Przedsiębiorstwo Wodociągów i Kanalizacji SP Z O O</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>57-300 Kłodzko</t>
+          <t>70-435 Szczecin</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2239,24 +2429,29 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>97032157550</t>
+          <t>97112184915</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Franciszek</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Woźniak</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Bąk</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Orbis Retail Solutions sp z oo</t>
+          <t>Instytut Badań Rynkowych spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2271,7 +2466,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>000000369</t>
+          <t>0000003694</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2296,24 +2491,29 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>98042858909</t>
+          <t>98122886266</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Amelia</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Jankowska</t>
+          <t>Jagoda</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Kucharska</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Astra Finance Finanse S.A.</t>
+          <t>Agencja Ochrony Solidna Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2338,7 +2538,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>338052254</t>
+          <t>238052254</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2353,24 +2553,29 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>99050760297</t>
+          <t>99010787654</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Nikodem</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Grabowski</t>
+          <t>Jerzy</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Lisowski</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Astra Finance Spółka Akcyjna</t>
+          <t>Instagram - Meta</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2395,7 +2600,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>238210635</t>
+          <t>248131477</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2410,24 +2615,29 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>00261461640</t>
+          <t>00221489008</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Pawlak-Sikora</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Słowik</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Astra Finance S.A.</t>
+          <t>Krajowa Izba Gospodarcza SA</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2467,24 +2677,29 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>01272163037</t>
+          <t>01232190398</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Miłosz</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Michalski</t>
+          <t>Marian</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Kopeć</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Orbis Retail Solutions Technologie sp. z o.o.</t>
+          <t>Polskie Zakłady Lotnicze S. A.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2524,24 +2739,29 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>02282864387</t>
+          <t>02242891747</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Agata</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Król</t>
+          <t>Irena</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Czajka</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Baltic Med Supply Services Spółka Akcyjna</t>
+          <t>Hurtownia Elektryczna Wat Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2561,7 +2781,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1238289820</t>
+          <t>1248210665</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2581,24 +2801,29 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>03290765770</t>
+          <t>03250793131</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Tadeusz</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Wieczorek</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Matusiak</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Orbis Retail Solutions sp z oo</t>
+          <t>Centrum Ogrodnicze Zielona Oaza sp. z o.o.</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2638,24 +2863,29 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>04301467122</t>
+          <t>04261494480</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Helena</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Jabłońska</t>
+          <t>Izabela</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Gajda</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Quantum Services Services spółka z ograniczoną odpowiedzialnością</t>
+          <t>Piekarnia i Cukiernia Chrupiący Rogalik sp z oo</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2695,24 +2925,29 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>05312168518</t>
+          <t>05272195876</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Stefan</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Witkowski</t>
+          <t>Mirosław</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Klimek</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Aurum Invest Spółka Akcyjna</t>
+          <t>Zakład Usług Komunalnych sp. z o. o.</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2752,24 +2987,29 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>60122869864</t>
+          <t>60082897222</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Jadwiga</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Walczak</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Madej</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Orbis Retail Solutions spółka z ograniczoną odpowiedzialnością</t>
+          <t>Polski Komfort Sp. z o.o.</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2809,24 +3049,29 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>61010771256</t>
+          <t>61090798615</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Józef</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Stępień</t>
+          <t>Piotr</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Krupa</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Vistula Fintech Holding sp z oo</t>
+          <t>Kancelaria Radców Prawnych Partnerzy SP Z O O</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2856,7 +3101,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2017-06-12</t>
+          <t>2017-12-06</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2866,24 +3111,29 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>72021472604</t>
+          <t>62101499967</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Baran</t>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Kaczmarczyk</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Astra Finance SP Z O O</t>
+          <t>Centrum Dystrybucji Alkoholi spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2903,7 +3153,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1238764965</t>
+          <t>1248685807</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2923,24 +3173,29 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>63032173991</t>
+          <t>63112101357</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Rutkowski</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Wrona</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Helios Markets sp. z o.o.</t>
+          <t>Przedsiębiorstwo Spedycyjne Ładunek Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2980,24 +3235,29 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>64042875341</t>
+          <t>64122802706</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Sabina</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Górska</t>
+          <t>Joanna</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Wasilewska</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Optima Trade S.A.</t>
+          <t>Fabryka Tekstyliów Splot S.A.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3037,24 +3297,29 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>65050776734</t>
+          <t>65010704096</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Arkadiusz</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Sikora</t>
+          <t>Paweł</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Kalinowski</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Mazovia Broker Services S.A.</t>
+          <t>Górnośląskie Towarzystwo Finansowe SA</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3094,24 +3359,29 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>66061478084</t>
+          <t>66021405444</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Ostrowska</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Zarychta</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Helios Markets Services spółka z ograniczoną odpowiedzialnością</t>
+          <t>Krajowa Agencja Informacyjna S. A.</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3151,24 +3421,29 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>67072179470</t>
+          <t>67032106830</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Tomaszewski</t>
+          <t>Robert</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Przybylski</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Nova Data Spółka Akcyjna</t>
+          <t>Polskie Jagody Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3208,24 +3483,29 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>68082880822</t>
+          <t>68042808181</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Zając</t>
+          <t>Agnieszka</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Michalak</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Helios Markets Finanse S.A.</t>
+          <t>Zielony Amber sp. z o.o.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3265,24 +3545,29 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>69090782216</t>
+          <t>69050709574</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Pietrzak</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Szatkowski</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Orbis Retail Solutions sp. z o.o.</t>
+          <t>Zielony Bizon sp z oo</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3322,24 +3607,29 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>70101483567</t>
+          <t>70061410924</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Wójcicka</t>
+          <t>Justyna</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Bednarek</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Polaris Capital Markets sp. z o.o.</t>
+          <t>Zielony Canyon sp. z o. o.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3349,7 +3639,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>wykonywain lzeceń na rachunek klientów</t>
+          <t>wykonywain lzeceń na archunek klientów</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3374,29 +3664,34 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>IDF/221/2021</t>
+          <t>DIF/221/2021</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>71112184953</t>
+          <t>71072112311</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Czarnecki</t>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Podgórski</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Aurum Invest spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Delfin Sp. z o.o.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3436,24 +3731,29 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>72122886303</t>
+          <t>72082813661</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Lis</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Śliwińska</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Helios Markets S.A.</t>
+          <t>Zielony Echo SP Z O O</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3493,24 +3793,29 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>73010787692</t>
+          <t>73090715055</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Kołodziej</t>
+          <t>Marcin</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Czajkowski</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Silesia Invest Spółka Akcyjna</t>
+          <t>P.P.H.U. Zielony Falcon</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3530,7 +3835,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2239556861</t>
+          <t>1239556861</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3550,24 +3855,29 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>74021489041</t>
+          <t>74101416406</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Kaczmarek</t>
+          <t>Karolina</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Biernat</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Baltic Med Supply SP Z O O</t>
+          <t>Zielony Gryf Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3607,24 +3917,29 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>75032190430</t>
+          <t>75112117793</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Piątek</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Panek</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Mazovia Broker spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Horyzont S.A.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3664,24 +3979,29 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>76042891780</t>
+          <t>76122819143</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Aleksandra</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Sadowska</t>
+          <t>Małgorzata</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Prus</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Mazovia Broker S.A.</t>
+          <t>Zielony Ikar SA</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3721,24 +4041,29 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>77050793174</t>
+          <t>77010720534</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Andrzej</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Włodarczyk</t>
+          <t>Jakub</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Janik</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Baltic Med Supply S.A.</t>
+          <t>Zielony Jantar S. A.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3778,24 +4103,29 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>78061494522</t>
+          <t>78021421883</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Marta</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Borkowska</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Kowalska</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Amber Payments sp z oo</t>
+          <t>Zielony Koral Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3835,29 +4165,34 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>79072195918</t>
+          <t>79032123270</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Łukasz</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Kowalski</t>
+          <t>Artur</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Nowacki</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Polaris Capital sp z oo</t>
+          <t>Zielony Lotos sp. z o.o.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ulica Marszałkowska 43, 00-590 Warszawa</t>
+          <t>ulica Chmielna 43, 00-020 Warszawa</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3892,29 +4227,34 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>80082897268</t>
+          <t>80042824628</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Paulina</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Nowacka</t>
+          <t>Iwona</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Wiśniewska</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Quantum Services sp z oo</t>
+          <t>Zielony Magnolia sp z oo</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Krakowskie Przedmieście 60, 00-071 Warszawa</t>
+          <t>Nowy Świat 60, 00-029 Warszawa</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3949,29 +4289,34 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>81090798651</t>
+          <t>81050726012</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Mateusz</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Wiśniewski</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Wójcik</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Polaris Capital sp. z o.o.</t>
+          <t>Zielony Neon sp. z o. o.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ul. Floriańska 77/75, 31-019 Kraków</t>
+          <t>ul. os. Przyjaźń 77/75, 01-355 Warszawa</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4006,29 +4351,34 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>82101400006</t>
+          <t>82061427361</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Elżbieta</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Wójcik</t>
+          <t>Renata</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Kowalczyk</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Amber Payments Services sp. z o.o.</t>
+          <t>Zielony Oaza Sp. z o.o.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ul Długa 94, 31-147 Kraków</t>
+          <t>ul Jagiellońska 94, 05-120 Legionowo</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4063,29 +4413,34 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>83112101393</t>
+          <t>83072128757</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Dawid</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Kowalczyk</t>
+          <t>Maciej</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Kamiński</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Orbis Retail Solutions Spółka Akcyjna</t>
+          <t>Zielony Pegaz SP Z O O</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ulica Piotrkowska 111, 90-102 Łódź</t>
+          <t>ulica Piłsudskiego 111, 05-270 Marki</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4120,29 +4475,34 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>84122802742</t>
+          <t>84082830100</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Dorota</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Kamińska</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Lewandowska</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Orbis Retail Solutions Services SP Z O O</t>
+          <t>Zielony Rubin spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Zachodnia 128, 90-402 Łódź</t>
+          <t>Andriollego 128, 05-400 Otwock</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4177,29 +4537,34 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>85010704131</t>
+          <t>85090731494</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Dariusz</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Lewandowski</t>
+          <t>Zbigniew</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Zieliński</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Nova Data Markets sp z oo</t>
+          <t>Zielony Szafir Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ul. Świdnicka 145/37, 50-066 Wrocław</t>
+          <t>ul. Żeromskiego 145/37, 26-600 Radom</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4234,29 +4599,34 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>86021405480</t>
+          <t>60021406849</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Zielińska</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Kowalska-Krawczyk</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Aurum Invest sp. z o.o.</t>
+          <t>Zielony Tytan S.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ul Legnicka 162, 54-203 Wrocław</t>
+          <t>ul Tumska 162, 09-402 Płock</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4281,7 +4651,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
+          <t>2023-11-05</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -4291,29 +4661,34 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>87032106876</t>
+          <t>61032108236</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Szymański</t>
+          <t>Robert</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Nowacki</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Optima Trade sp. z o.o.</t>
+          <t>Zielony Uran SA</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ulica Święty Marcin 179, 61-806 Poznań</t>
+          <t>ulica Karmelicka 179, 31-128 Kraków</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4333,7 +4708,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>240903093</t>
+          <t>250823937</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4348,29 +4723,34 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>88042808226</t>
+          <t>62042809586</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Dąbrowska</t>
+          <t>Agnieszka</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Wiśniewska</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Astra Finance Markets sp z oo</t>
+          <t>Zielony Wektor S. A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Głogowska 16, 60-734 Poznań</t>
+          <t>os. Na Stoku 16, 31-704 Kraków</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4405,29 +4785,34 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>89050709619</t>
+          <t>63050710972</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Mazur</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Wójcik</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Optima Trade Markets spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Zefir Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ul. Długa 33/89, 80-831 Gdańsk</t>
+          <t>ul. Krupówki 33/89, 34-500 Zakopane</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4462,29 +4847,34 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>90061410960</t>
+          <t>64061412321</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Krawczyk</t>
+          <t>Justyna</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Kowalczyk</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Mazovia Broker Technologie Spółka Akcyjna</t>
+          <t>Zielony Żubr sp. z o.o.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>ul Grunwaldzka 50, 80-236 Gdańsk</t>
+          <t>50, 34-600 Mordarka</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -4519,29 +4909,34 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>91072112357</t>
+          <t>65072113717</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Woźniak</t>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Kamiński</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Aurum Invest Technologie Spółka Akcyjna</t>
+          <t>Zielony Sokół sp z oo</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ulica Jagiellońska 67, 70-435 Szczecin</t>
+          <t>ulica Galicyjska 67, 32-087 Zielonki</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4566,7 +4961,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2023-07-09</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4576,29 +4971,34 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>92082813706</t>
+          <t>66082815068</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Jankowska</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Lewandowska</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Nova Data Spółka Akcyjna</t>
+          <t>Zielony Orzeł sp. z o. o.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Wyszyńskiego 84, 70-200 Szczecin</t>
+          <t>84, 32-003 Podłęże</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4633,29 +5033,34 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>93090715091</t>
+          <t>67090716451</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Grabowski</t>
+          <t>Marcin</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>Zieliński</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Astra Finance sp. z o.o.</t>
+          <t>mBank</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ul. Mariacka 101/51, 40-014 Katowice</t>
+          <t>ul. Wałowa 101/51, 33-100 Tarnów</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4690,29 +5095,34 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>94101416442</t>
+          <t>68101417802</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Pawlak-Sikora</t>
+          <t>Karolina</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Szymańska</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Aurum Invest spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Barycz SP Z O O</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ul Warszawska 118, 40-009 Katowice</t>
+          <t>ul Narutowicza 118, 90-135 Łódź</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -4732,7 +5142,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>241457425</t>
+          <t>251378267</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -4747,29 +5157,34 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>95112117838</t>
+          <t>69112119190</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Michalski</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>Dąbrowski</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Polaris Capital Services spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Noteć spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ulica Krakowskie Przedmieście 135, 20-002 Lublin</t>
+          <t>ulica os. Retkinia 135, 94-004 Łódź</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -4799,34 +5214,39 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
+          <t>DFI/156/2017</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>70122820541</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Aleksandra</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>96122819189</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>Agnieszka</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>Król</t>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>Mazur</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Lumen Advisory sp z oo</t>
+          <t>Zielony Pilica Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Chełmińska 92, 87-100</t>
+          <t>Piastowska 92, 48-300</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -4851,7 +5271,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2017-11-08</t>
+          <t>2017-08-11</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4861,29 +5281,34 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>97010720570</t>
+          <t>71010721939</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Andrzej</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Wieczorek</t>
+          <t>Jakub</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>Krawczyk</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Quantum Services Spółka Akcyjna</t>
+          <t>Zielony Narew S.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ul. Lipowa 169/13, 15-424 Białystok</t>
+          <t>ul. Długa 169/13, 95-100 Zgierz</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4918,29 +5343,34 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>98021421928</t>
+          <t>72021423289</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Marta</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Jabłońska</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>Woźniak</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Lumen Advisory spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Jodełka SA</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>ul Sienkiewicza 6, 15-092 Białystok</t>
+          <t>ul Rynek 6, 50-101 Wrocław</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4975,29 +5405,34 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>99032123315</t>
+          <t>73032124675</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Łukasz</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Witkowski</t>
+          <t>Artur</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>Jankowski</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Vistula Fintech Polska Spółka Akcyjna</t>
+          <t>Zielony Kaktus S. A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>ulica Gdańska 23, 85-005 Bydgoszcz</t>
+          <t>ulica Jedności Narodowej 23, 50-260 Wrocław</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5012,7 +5447,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t/>
+          <t>1241615809</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -5032,29 +5467,34 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>00242824660</t>
+          <t>74042826025</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Paulina</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Walczak</t>
+          <t>Iwona</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>Grabowska</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Polaris Capital Spółka Akcyjna</t>
+          <t>Zielony Szmaragd Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>os. Dworcowa 40, 85-009 Bydgoszcz</t>
+          <t>os. Konstytucji 3 Maja 40, 58-540 Karpacz</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5064,7 +5504,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>000000844</t>
+          <t>0000008447</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5089,29 +5529,34 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>01250726054</t>
+          <t>75050727418</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Mateusz</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>Stępień</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>Pawlak</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Baltic Med Supply SP Z O O</t>
+          <t>Zielony Topaz sp. z o.o.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ul. Szeroka 57/65, 87-100 Toruń</t>
+          <t>ul. Odrodzenia 57/65, 59-300 Lubin</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5126,12 +5571,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>1241774181</t>
+          <t/>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>242090949</t>
+          <t>251932597</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5146,29 +5591,34 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>02261427402</t>
+          <t>76061428767</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Elżbieta</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>Baran</t>
+          <t>Renata</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>Michalska</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Baltic Med Supply Polska Spółka Akcyjna</t>
+          <t>Zielony Granit sp z oo</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ul Chełmińska 74, 87-100 Toruń</t>
+          <t>ul Słowackiego 74, 58-300 Wałbrzych</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -5188,7 +5638,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>342090949</t>
+          <t>252011787</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -5203,29 +5653,34 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>03272128799</t>
+          <t>77072130157</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Dawid</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>Rutkowski</t>
+          <t>Maciej</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>Król</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Orbis Retail Solutions Markets spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Marmur sp. z o. o.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ulica 3 Maja 91, 35-030 Rzeszów</t>
+          <t>ulica Półwiejska 91, 61-888 Poznań</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -5260,29 +5715,34 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>04282830142</t>
+          <t>78082831506</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Dorota</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>Górska</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>Wieczorek</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Quantum Services Markets sp. z o.o.</t>
+          <t>Zielony Syrena Sp. z o.o.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Piłsudskiego 108, 35-074 Rzeszów</t>
+          <t>os. Bolesława Chrobrego 108, 60-681 Poznań</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -5317,29 +5777,34 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>05290731535</t>
+          <t>79090732890</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Dariusz</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Sikora</t>
+          <t>Zbigniew</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>Jabłoński</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Baltic Med Supply spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Zodiak SP Z O O</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ul. Sienkiewicza 125/27, 25-007 Kielce</t>
+          <t>ul. Główny Rynek 125/27, 62-800 Kalisz</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -5374,29 +5839,34 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>60101432883</t>
+          <t>80101434241</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Beata</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Ostrowska</t>
+          <t>Patrycja</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>Witkowska</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Silesia Invest sp z oo</t>
+          <t>Zielony Olimp spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ul Warszawska 142, 25-512 Kielce</t>
+          <t>ul Kaliska 142, 63-400 Ostrów Wielkopolski</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -5431,29 +5901,34 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>61112134270</t>
+          <t>81112135637</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Sławomir</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>Tomaszewski</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>Walczak</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Quantum Services Finanse sp z oo</t>
+          <t>Zielony Zorza Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ulica Kościuszki 159, 10-504 Olsztyn</t>
+          <t>ulica Ogarna 159, 80-826 Gdańsk</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -5488,29 +5963,34 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>62122835629</t>
+          <t>82122836987</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Urszula</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Zając</t>
+          <t>Wiktoria</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>Stępień</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Lumen Advisory spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Krokus S.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Dąbrowszczaków 176, 10-540 Olsztyn</t>
+          <t>os. Jasień 176, 80-180 Gdańsk</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -5525,12 +6005,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>1242407705</t>
+          <t>1252328545</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>242566085</t>
+          <t>252486929</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -5545,29 +6025,34 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>63010737018</t>
+          <t>83010738376</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Mariusz</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>Pietrzak</t>
+          <t>Jacek</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>Baran</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Aurum Invest SP Z O O</t>
+          <t>Zielony Narcyz SA</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ul. Krakowska 13/79, 45-018 Opole</t>
+          <t>ul. Bohaterów Monte Cassino 13/79, 81-759 Sopot</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -5602,29 +6087,34 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>64021438367</t>
+          <t>84021439724</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Izabela</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>Wójcicka</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>Rutkowska</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Orbis Retail Solutions sp. z o.o.</t>
+          <t>Zielony Giewont S. A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ul Ozimska 30, 45-057 Opole</t>
+          <t>30, 80-209 Chwaszczyno</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -5659,29 +6149,34 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>75032139753</t>
+          <t>85032141114</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Henryk</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>Czarnecki</t>
+          <t>Przemysław</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>Górski</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Vistula Fintech sp. z o.o.</t>
+          <t>Zielony Rysy Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ulica Bohaterów Westerplatte 47, 65-034 Zielona Góra</t>
+          <t>ulica 3 Maja 47, 40-096 Katowice</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -5716,29 +6211,34 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>66042841106</t>
+          <t>86042842464</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Weronika</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>Lis</t>
+          <t>Kinga</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>Sikora</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Optima Trade S.A.</t>
+          <t>Zielony Kasprowy sp. z o.o.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Kupiecka 64, 65-058 Zielona Góra</t>
+          <t>os. Paderewskiego 64, 40-282 Katowice</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -5773,29 +6273,34 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>67050742490</t>
+          <t>87050743857</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Stanisław</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Kołodziej</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>Ostrowski</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Nova Data Spółka Akcyjna</t>
+          <t>PPHU Zielony Beskid</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ul. Świętojańska 81/41, 81-372 Gdynia</t>
+          <t>ul. Zwycięstwa 81/41, 44-100 Gliwice</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -5830,29 +6335,34 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>68061443848</t>
+          <t>88061445206</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>Kaczmarek</t>
+          <t>Kamila</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>Tomaszewska</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Nebula Analytics Polska Spółka Akcyjna</t>
+          <t>Zielony Bieszczady sp. z o. o.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>ul Mickiewicza 38</t>
+          <t>ul Krupówki 38</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -5887,29 +6397,34 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>69072145235</t>
+          <t>89072146593</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Bartłomiej</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>Piątek</t>
+          <t>Daniel</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>Zając</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Optima Trade sp z oo</t>
+          <t>Zielony Karpaty Sp. z o.o.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>ulica Bolesława Prusa 115, 05-800 Pruszków</t>
+          <t>ulica Najświętszej Maryi Panny 115, 42-200 Częstochowa</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -5944,29 +6459,34 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>70082846584</t>
+          <t>70042873944</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Agata</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>Sadowska</t>
+          <t>Irena</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>Włodarczyk</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Lumen Advisory spółka z ograniczoną odpowiedzialnością</t>
+          <t>Zielony Bałtyk SP Z O O</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Kościuszki 132, 05-500 Piaseczno</t>
+          <t>11 Listopada 132, 43-300 Bielsko-Biała</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -5991,7 +6511,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6001,29 +6521,34 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>71090747977</t>
+          <t>71050775338</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Tadeusz</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>Włodarczyk</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>Borkowski</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Orbis Retail Solutions SP Z O O</t>
+          <t>Zielony Sudety spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>ul. Sienkiewicza 149/3, 32-020 Wieliczka</t>
+          <t>149/3, 36-047 Niechobrz</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6058,29 +6583,34 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>72101449329</t>
+          <t>72061476687</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Helena</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>Borkowska</t>
+          <t>Izabela</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>Sawicka</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Optima Trade Finanse spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Amber Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>ul Dąbrowskiego 166, 32-600 Oświęcim</t>
+          <t>ul Franciszkańska 166, 37-700 Przemyśl</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6115,29 +6645,34 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>73112150718</t>
+          <t>73072178074</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Stefan</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>Kowalski</t>
+          <t>Mirosław</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>Dudek</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Aurum Invest Technologie SP Z O O</t>
+          <t>Niebieski Bizon S.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>ulica Rynek 3, 38-400 Krosno</t>
+          <t>ulica Kościuszki 3, 38-500 Sanok</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -6157,49 +6692,54 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
+          <t>243357981</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>2021/19/08</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>DFI/103/2026</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>74082879423</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Jadwiga</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>2021/19/08</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>DFI/103/2026</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>74122852069</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>Maria</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>Nowacka</t>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>Adamczyk</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Baltic Med Supply Holding S.A.</t>
+          <t>Niebieski Canyon SA</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Mickiewicza 20, 39-300 Mielec</t>
+          <t>Suraska 20, 15-422 Białystok</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>wykonywani zleceń na rachunek klientów</t>
+          <t>wykonywani zleceń n rachunek klientów</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -6229,29 +6769,34 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>75010753457</t>
+          <t>75090780819</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Józfe</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>Wiśinewski</t>
+          <t>Piotr</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>Pawłowski</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Polaris Capital SP Z O O</t>
+          <t>Niebieski Delfin S. A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>ul. Długa 37/55, 58-100 Świdnica</t>
+          <t>37/55, 16-030 Ogrodniczki</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -6286,29 +6831,34 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>76021454805</t>
+          <t>76101482162</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>Wójcik</t>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>Nowicka</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Optima Trade Finanse S.A.</t>
+          <t>Niebieski Echo Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>ul Wojska Polskiego 54, 57-300 Kłodzko</t>
+          <t>ul 3 Maja 54, 17-200 Hajnówka</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -6323,7 +6873,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2243516365</t>
+          <t>1253437207</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -6343,29 +6893,34 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>77032156193</t>
+          <t>77112183558</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>Kowalczyk</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>Sokołowski</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Baltic Med Supply SP Z O O</t>
+          <t>Niebieski Falcon sp. z o.o.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>ulica Chrobrego 71, 62-200 Gniezno</t>
+          <t>ulica os. LSM 71, 20-400 Lublin</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -6400,29 +6955,34 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>78042857542</t>
+          <t>78122884907</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Sabina</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>Kamińska</t>
+          <t>Joanna</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>Wróbel</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Silesia Invest Spółka Akcyjna</t>
+          <t>Niebieski Gryf sp z oo</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Słowiańska 88, 64-100 Leszno</t>
+          <t>88, 24-120 Mięćmierz</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -6457,29 +7017,34 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>79050758935</t>
+          <t>79010786297</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Arkadiusz</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>Lewandowski</t>
+          <t>Paweł</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>Majewski</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Quantum Services Services S.A.</t>
+          <t>Niebieski Horyzont sp. z o. o.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>105/17, 83-110 Tczew</t>
+          <t>ul. Brzeska 105/17, 21-500 Biała Podlaska</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -6494,7 +7059,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>1243753935</t>
+          <t>1253674775</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -6514,29 +7079,34 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>80061460287</t>
+          <t>80021487644</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>Zielińska</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>Olszewska-Błaszczyk</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Helios Markets sp z oo</t>
+          <t>Niebieski Ikar Sp. z o.o.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>ul Sobieskiego 122, 84-200 Wejherowo</t>
+          <t>ul Rynek Staromiejski 122, 87-100 Toruń</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -6546,7 +7116,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t/>
+          <t>0000010969</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -6561,7 +7131,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-01-06</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -6571,29 +7141,34 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>81072161673</t>
+          <t>81032189031</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>Szymański</t>
+          <t>Robert</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>Jaworski</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Nebula Analytics Polska S.A.</t>
+          <t>Niebieski Jantar SP Z O O</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>ulica Głęboka 139, 43-400 Cieszyn</t>
+          <t>ulica Mostowa 139, 85-110 Bydgoszcz</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -6603,7 +7178,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>0000011066</t>
+          <t/>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -6613,7 +7188,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>243991502</t>
+          <t/>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -6628,29 +7203,34 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>82082863023</t>
+          <t>82042890384</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>Dąbrowska</t>
+          <t>Agnieszka</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>Malinowska</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Nova Data spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Koral spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Małachowskiego 156, 42-500 Będzin</t>
+          <t>Stare Miasto 156, 10-026 Olsztyn</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -6685,29 +7265,34 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>83090764416</t>
+          <t>83050791777</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>Mazur</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>Pająk</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Quantum Services sp z oo</t>
+          <t>Niebieski Lotos Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>os. Królowej Jadwigi 173/69, 88-100 Inowrocław</t>
+          <t>os. Warszawska 173/69, 11-700 Mrągowo</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -6742,29 +7327,34 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>84101465768</t>
+          <t>84061493126</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Krawczyk</t>
+          <t>Justyna</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>Szczepańska</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Baltic Med Supply S.A.</t>
+          <t>Niebieski Magnolia S.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>ul Wybickiego 10, 86-300 Grudziądz</t>
+          <t>ul Wojska Polskiego 10, 70-470 Szczecin</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -6799,24 +7389,29 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>85112167155</t>
+          <t>85072194512</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>Woźniak</t>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>Czerwiński</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Lumen Advisory S.A.</t>
+          <t>Niebieski Neon SA</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -6846,7 +7441,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2023-04-07</t>
+          <t>2023-07-04</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -6856,29 +7451,34 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>86122868504</t>
+          <t>86082895862</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>Jankowska</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>Kubiak</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Vistula Fintech sp z oo</t>
+          <t>Niebieski Oaza S. A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Długa 164, Brzeg</t>
+          <t>Ogarna 164, Gdańsk</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -6913,29 +7513,34 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>87010769893</t>
+          <t>87090797256</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>Grabowski</t>
+          <t>Marcin</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>Wilk</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Aurum Invest Spółka Akcyjna</t>
+          <t>X - Twitter</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>ul. Lubelska 61/31, 24-100 Puławy</t>
+          <t>ul. Byczyńska 61/31, 46-200 Kluczbork</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -6970,29 +7575,34 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>88021471245</t>
+          <t>88101498607</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>Pawlak-Sikora</t>
+          <t>Karolina</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>Wysocka</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Quantum Services sp. z o.o.</t>
+          <t>Niebieski Rubin sp. z o.o.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>ul Staszica 78, 22-400 Zamość</t>
+          <t>ul Chrobrego 78, 66-400 Gorzów Wielkopolski</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7027,29 +7637,34 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>89032172631</t>
+          <t>89112199994</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>Michalski</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>Chmielewski</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Vistula Fintech sp z oo</t>
+          <t>Niebieski Szafir sp z oo</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>ulica 3 Maja 95, 16-300 Augustów</t>
+          <t>ulica 30 Stycznia 95, 66-300 Międzyrzecz</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -7084,29 +7699,34 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>90042873980</t>
+          <t>90122801346</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Aleksandra</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>Król</t>
+          <t>Małgorzata</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>Urbańska</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Silesia Invest Services sp z oo</t>
+          <t>Niebieski Tytan sp. z o. o.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Kościuszki 112, 16-400 Suwałki</t>
+          <t>Paderewskiego 112, 25-004 Kielce</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -7126,12 +7746,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>244783409</t>
+          <t>254704247</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2018-10-06</t>
+          <t>2018-06-10</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -7141,29 +7761,34 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>91050775374</t>
+          <t>91010702734</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Andrzej</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>Wieczorek</t>
+          <t>Jakub</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>Błaszczyk</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Quantum Services Technologie sp. z o.o.</t>
+          <t>Niebieski Uran Sp. z o.o.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>ul. Piastowska 129/83, 48-300 Nysa</t>
+          <t>ul. 1 Maja 129/83, 28-100 Busko-Zdrój</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -7198,29 +7823,34 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>92061476722</t>
+          <t>92021404084</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Marta</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>Jabłońska</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>Szulc</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Amber Payments S.A.</t>
+          <t>Niebieski Wektor SP Z O O</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>ul Długa 146, 49-300 Brzeg</t>
+          <t>ul Marszałkowska 146, 00-590 Warszawa</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -7255,29 +7885,34 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>93072178119</t>
+          <t>93032105470</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Łukasz</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>Witkowski</t>
+          <t>Artur</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>Kozak</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Nova Data Holding spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Zefir spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>163, 68-200 Żary</t>
+          <t>ulica Krakowskie Przedmieście 163, 00-071 Warszawa</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -7312,29 +7947,34 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>94082879469</t>
+          <t>94042806829</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Paulina</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>Walczak</t>
+          <t>Iwona</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>Cieślak</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Baltic Med Supply sp. z o.o.</t>
+          <t>Niebieski Żubr Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Sikorskiego 180, 66-200 Świebodzin</t>
+          <t>Floriańska 180, 31-019 Kraków</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -7369,29 +8009,34 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>95090780855</t>
+          <t>95050708213</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Mateusz</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>Stępień</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>Andrzejewski</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Aurum Invest sp. z o.o.</t>
+          <t>Niebieski Sokół S.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>ul. Armii Krajowej 17/45, 78-100 Kołobrzeg</t>
+          <t>ul. Długa 17/45, 31-147 Kraków</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -7416,7 +8061,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2018-04-03</t>
+          <t>2018-03-04</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -7426,29 +8071,34 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>96101482207</t>
+          <t>96061409562</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Elżbieta</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>Baran</t>
+          <t>Renata</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>Gajewska</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Mazovia Broker Markets Spółka Akcyjna</t>
+          <t>Niebieski Orzeł SA</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>ul Piłsudskiego 34, 73-110 Stargard</t>
+          <t>ul Piotrkowska 34, 90-102 Łódź</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -7483,29 +8133,34 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>97112183594</t>
+          <t>97072110951</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Dawid</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>Rutkowski</t>
+          <t>Maciej</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>Laskowski</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Quantum Services spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Kormoran S. A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>ulica Mickiewicza 51, 27-600 Sandomierz</t>
+          <t>ulica Zachodnia 51, 90-402 Łódź</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -7525,7 +8180,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>245337735</t>
+          <t>255258577</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -7540,29 +8195,34 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>98122884943</t>
+          <t>98082812301</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Dorota</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>Górska</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>Mazurek</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Vistula Fintech Polska Spółka Akcyjna</t>
+          <t>Niebieski Barycz Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Sienkiewicza 68, 27-400 Ostrowiec Świętokrzyski</t>
+          <t>Świdnicka 68, 50-066 Wrocław</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -7597,29 +8257,34 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>99010786332</t>
+          <t>99090713695</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Dariusz</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>Sikora</t>
+          <t>Zbigniew</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>Sobczak</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Orbis Retail Solutions Technologie SP Z O O</t>
+          <t>Niebieski Noteć sp. z o.o.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>ul. Marszałkowska 85/7, 00-590 Warszawa</t>
+          <t>ul. Legnicka 85/7, 54-203 Wrocław</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -7654,29 +8319,34 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>00221487686</t>
+          <t>00301415042</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Beata</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>Ostrowska</t>
+          <t>Patrycja</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>Konieczna</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Optima Trade Spółka Akcyjna</t>
+          <t>Niebieski Pilica sp z oo</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>ul Krakowskie Przedmieście 102, 00-071 Warszawa</t>
+          <t>ul Święty Marcin 102, 61-806 Poznań</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -7696,12 +8366,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>245575305</t>
+          <t>255496147</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2017-03-01</t>
+          <t>2017-01-03</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -7711,29 +8381,34 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>01232189073</t>
+          <t>01312116438</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Sławomir</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>Tomaszewski</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>Brzeziński</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Amber Payments Holding sp z oo</t>
+          <t>Niebieski Narew sp. z o. o.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>ulica Floriańska 119, 31-019 Kraków</t>
+          <t>ulica Głogowska 119, 60-734 Poznań</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -7768,29 +8443,34 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>02242890425</t>
+          <t>02322817788</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Urszula</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>Zając</t>
+          <t>Wiktoria</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>Makowska</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Aurum Invest Markets SP Z O O</t>
+          <t>Niebieski Jodełka Sp. z o.o.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Długa 136, 31-147 Kraków</t>
+          <t>Długa 136, 80-831 Gdańsk</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -7825,29 +8505,34 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>03250791818</t>
+          <t>03210719177</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Mariusz</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>Pietrzak</t>
+          <t>Jacek</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>Wrona</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Helios Markets Spółka Akcyjna</t>
+          <t>Niebieski Kaktus SP Z O O</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>ul. Piotrkowska 153/59, 90-102 Łódź</t>
+          <t>ul. Grunwaldzka 153/59, 80-236 Gdańsk</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -7857,7 +8542,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>000001320</t>
+          <t>0000013200</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -7882,29 +8567,34 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>04261493168</t>
+          <t>04221420528</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Izabela</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>Wójcicka</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>Bąk</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Astra Finance Spółka Akcyjna</t>
+          <t>Niebieski Szmaragd spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>80-236 Gdańsk</t>
+          <t>21-500 Biała Podlaska</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -7924,7 +8614,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>245892069</t>
+          <t>255812909</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -7939,29 +8629,34 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>05272194554</t>
+          <t>05232121914</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Henryk</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>Czarnecki</t>
+          <t>Przemysław</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>Kucharski</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Helios Markets S.A.</t>
+          <t>Niebieski Topaz Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>ulica Świdnicka 7, 50-066 Wrocław</t>
+          <t>ulica Wyszyńskiego 7, 70-200 Szczecin</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -7996,29 +8691,34 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>60082895909</t>
+          <t>60042823261</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Weronika</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>Lis</t>
+          <t>Kinga</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>Lisowska</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Nova Dta Spółka Akcyjna</t>
+          <t>Niebieski Granit S.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Legnicka 24, 54-203 Wrocław</t>
+          <t>Mariacka 24, 40-014 Katowice</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -8038,7 +8738,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>345971254</t>
+          <t>245971254</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -8053,29 +8753,34 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>61090797294</t>
+          <t>61050724654</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Stanisław</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>Kołodziej</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>Słowik</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Polaris Capital S.A.</t>
+          <t>P.P.H.U. Niebieski Marmur</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>ul. Święty Marcin 41/21, 61-806 Poznań</t>
+          <t>ul. Warszawska 41/21, 40-009 Katowice</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -8110,29 +8815,34 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>62101498645</t>
+          <t>62061426003</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>Kaczmarek</t>
+          <t>Kamila</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>Kopeć</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Nebula Analytics Holding S.A.</t>
+          <t>Niebieski Syrena S. A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>ul Głogowska 58, 60-734 Poznań</t>
+          <t>ul Krakowskie Przedmieście 58, 20-002 Lublin</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -8167,29 +8877,34 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>63112100035</t>
+          <t>63072127390</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Bartłomiej</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>Piątek</t>
+          <t>Daniel</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>Czajka</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Baltic Med Supply S.A.</t>
+          <t>Niebieski Zodiak Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>ulica Długa 75, 80-831 Gdańsk</t>
+          <t>ulica Narutowicza 75, 20-004 Lublin</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -8224,29 +8939,34 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>64122801385</t>
+          <t>64082828749</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Olga</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>Sadowska</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>Matusiak</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Nebula Analytics Spółka Akcyjna</t>
+          <t>Niebieski Olimp sp. z o.o.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Grunwaldzka 92, 80-236 Gdańsk</t>
+          <t>Lipowa 92, 15-424 Białystok</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -8281,29 +9001,34 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>65010702773</t>
+          <t>65090730136</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Damian</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>Włodarczyk</t>
+          <t>Waldemar</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>Gajda</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Astra Finance Markets Spółka Akcyjna</t>
+          <t>Niebieski Zorza sp z oo</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>ul. Jagiellońska 109/73, 70-435 Szczecin</t>
+          <t>ul. Sienkiewicza 109/73, 15-092 Białystok</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -8318,7 +9043,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>1246288019</t>
+          <t>1256208855</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -8338,29 +9063,34 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>66021404122</t>
+          <t>66101431488</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Ewelina</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>Borkowska</t>
+          <t>Danuta</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>Klimek</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Silesia Invest S.A.</t>
+          <t>Niebieski Krokus sp. z o. o.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>os. Wyszyńskiego 126, 70-200 Szczecin</t>
+          <t>os. Gdańska 126, 85-005 Bydgoszcz</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -8395,29 +9125,34 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>67032105518</t>
+          <t>67112132874</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Bartosz</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>Kowalski</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>Madej</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Silesia Invest Polska spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Narcyz Sp. z o.o.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>ulica Mariacka 143, 40-014 Katowice</t>
+          <t>ulica Dworcowa 143, 85-009 Bydgoszcz</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -8452,29 +9187,34 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>78042806868</t>
+          <t>68122834224</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Sylwia</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>Nowacka</t>
+          <t>Aneta</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>Krupa</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Silesia Invest SP Z O O</t>
+          <t>Niebieski Giewont SP Z O O</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Warszawska 160, 40-009 Katowice</t>
+          <t>Szeroka 160, 87-100 Toruń</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -8509,29 +9249,34 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>69050708252</t>
+          <t>69010735612</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Leszek</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>Wiśniewski</t>
+          <t>Kacper</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>Kaczmarczyk</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Silesia Invest sp. z o.o.</t>
+          <t>Niebieski Rysy spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>ul. Krakowskie Przedmieście 177/35, 20-002 Lublin</t>
+          <t>ul. Chełmińska 177/35, 87-100 Toruń</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -8566,29 +9311,34 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>70061409609</t>
+          <t>70021436960</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Grażyna</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>Wójcik</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>Wrona</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Lumen Advisory spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Kasprowy Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>ul Narutowicza 14, 20-004 Lublin</t>
+          <t>ul 3 Maja 14, 35-030 Rzeszów</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -8623,29 +9373,34 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>71072110999</t>
+          <t>71032138357</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Cezary</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>Kowalczyk</t>
+          <t>Szymon</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>Wasilewski</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Aurum Invest spółka z ograniczoną odpowiedzialnością</t>
+          <t>Amber Budownictwo S.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>ulica Lipowa 31, 15-424 Białystok</t>
+          <t>ulica Piłsudskiego 31, 35-074 Rzeszów</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -8680,29 +9435,34 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>72082812349</t>
+          <t>72042839706</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Bożena</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>Kamińska</t>
+          <t>Oliwia</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>Kalinowska</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Vistula Fintech S.A.</t>
+          <t>Amber Transport SA</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Sienkiewicza 48, 15-092 Białystok</t>
+          <t>Sienkiewicza 48, 25-007 Kielce</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -8737,29 +9497,34 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>73090713732</t>
+          <t>73050741094</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Filip</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>Lewandowski</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>Zarychta</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Aurum Invest sp z oo</t>
+          <t>Amber Spedycja S. A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>ul. Gdańska 65/87, 85-005 Bydgoszcz</t>
+          <t>ul. Warszawska 65/87, 25-512 Kielce</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -8794,29 +9559,34 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>74101415085</t>
+          <t>74061442442</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Zuzanna</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>Zielińska</t>
+          <t>Emilia</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>Przybylska-Kowalska</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Baltic Med Supply S.A.</t>
+          <t>Amber Logistyka Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>ul Dworcowa 82, 85-009 Bydgoszcz</t>
+          <t>ul Kościuszki 82, 10-504 Olsztyn</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -8851,29 +9621,34 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>75112116471</t>
+          <t>85072143838</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Mikołaj</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>Szymański</t>
+          <t>Ignacy</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>Michalak</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Optima Trade sp z oo</t>
+          <t>Amber Handel sp. z o.o.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>ulica Szeroka 99, 87-100 Toruń</t>
+          <t>ulica Dąbrowszczaków 99, 10-540 Olsztyn</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -8908,29 +9683,34 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>76122817820</t>
+          <t>76082845189</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Lena</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>Dąbrowska</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>Szatkowska</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Mazovia Broker S.A.</t>
+          <t>Amber Usługi sp z oo</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Chełmińska 116, 87-100 Toruń</t>
+          <t>Krakowska 116, 45-018 Opole</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -8965,29 +9745,34 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>77010719219</t>
+          <t>77090746572</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Antoni</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>Mazur</t>
+          <t>Leon</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>Bednarek</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Mazovia Broker S.A.</t>
+          <t>Amber Finanse sp. z o. o.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>ul. 3 Maja 133/49, 35-030 Rzeszów</t>
+          <t>ul. Ozimska 133/49, 45-057 Opole</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -9022,34 +9807,39 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>78021420561</t>
+          <t>78101447923</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Hanna</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>Krawczyk</t>
+          <t>Dominika</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>Podgórska</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Amber Paymen pSółka Akcyjna</t>
+          <t>Amber Doradztwo Sp. z o.o.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>ul Piłsudskiego 150, 35-074 Rzeszów</t>
+          <t>ul Bohaterów Westerplatte 150, 65-034 Zielona Góra</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>zarządaznie portfelami</t>
+          <t>zarzdąaznie portfelami</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -9079,29 +9869,34 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>79032121957</t>
+          <t>79112149310</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Franciszek</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>Woźniak</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>Śliwiński</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Quantum Services sp. z o.o.</t>
+          <t>Amber Szkolenia SP Z O O</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>ulica Sienkiewicza 167, 25-007 Kielce</t>
+          <t>ulica Kupiecka 167, 65-058 Zielona Góra</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -9116,7 +9911,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2247396679</t>
+          <t>1257317517</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -9136,29 +9931,34 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>80042823306</t>
+          <t>80122850662</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Amelia</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>Jankowska</t>
+          <t>Jagoda</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>Czajkowska</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Baltic Med Supply sp z oo</t>
+          <t>Amber Media spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Warszawska 4, 25-512 Kielce</t>
+          <t>Świętojańska 4, 81-372 Gdynia</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -9193,29 +9993,34 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>81050724690</t>
+          <t>81010752051</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Nikodem</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>Grabowski</t>
+          <t>Jerzy</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>Biernat</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Nebula Analytics sp. z o.o.</t>
+          <t>Facebook - Meta</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>ul. Kościuszki 21/11, 10-504 Olsztyn</t>
+          <t>ul. 10 Lutego 21/11, 81-364 Gdynia</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -9250,29 +10055,34 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>82061426049</t>
+          <t>82021453409</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>Pawlak-Sikora</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>Panek</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Lumen Advisory spółka z ograniczoną odpowiedzialnością</t>
+          <t>Amber Marketing S.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>ul Dąbrowszczaków 38, 10-540 Olsztyn</t>
+          <t>ul Bolesława Prusa 38, 05-800 Pruszków</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -9287,7 +10097,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>1247634245</t>
+          <t>1257555085</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -9307,29 +10117,34 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>83072127435</t>
+          <t>83032154796</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Miłosz</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>Michalski</t>
+          <t>Marian</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>Prus</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Amber Payments Spółka Akcyjna</t>
+          <t>Amber Druk SA</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>ulica Krakowska 55, 45-018 Opole</t>
+          <t>ulica Kościuszki 55, 05-500 Piaseczno</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -9364,29 +10179,34 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>84082828785</t>
+          <t>84042856146</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Agata</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>Król</t>
+          <t>Irena</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>Janik</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Nebula Analytics spółka z ograniczoną odpowiedzialnością</t>
+          <t>Amber Informatyka S. A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Ozimska 72, 45-057 Opole</t>
+          <t>Sienkiewicza 72, 32-020 Wieliczka</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -9411,7 +10231,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2022-08-05</t>
+          <t>2022-05-08</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -9421,29 +10241,34 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>85090730172</t>
+          <t>85050757539</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Tadeusz</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>Wieczorek</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>Kowalski</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Vistula Fintech sp z oo</t>
+          <t>Amber Oprogramowanie Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>ul. Bohaterów Westerplatte 89/63, 65-034 Zielona Góra</t>
+          <t>ul. Dąbrowskiego 89/63, 32-600 Oświęcim</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -9458,7 +10283,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>1247871815</t>
+          <t>1257792655</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -9478,29 +10303,34 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>86101431523</t>
+          <t>86061458888</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Helena</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>Jabłońska</t>
+          <t>Izabela</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>Nowacka</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Nova Data Technologie SP Z O O</t>
+          <t>Amber Rolnictwo sp. z o.o.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>ul Kupiecka 106, 65-058 Zielona Góra</t>
+          <t>ul Rynek 106, 38-400 Krosno</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -9515,7 +10345,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>1247871815</t>
+          <t>2247871815</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -9535,29 +10365,34 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>87112132919</t>
+          <t>87072160278</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Stefan</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>Witkowski</t>
+          <t>Mirosław</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>Wiśniewski</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Polaris Capital Technologie S.A.</t>
+          <t>Amber Ogrodnictwo sp z oo</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>ulica Świętojańska 123, 81-372 Gdynia</t>
+          <t>ulica Mickiewicza 123, 39-300 Mielec</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -9592,29 +10427,34 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>88122834260</t>
+          <t>88082861627</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Jadwiga</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>Walczak</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>Wójcik</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Quantum Services SP Z O O</t>
+          <t>Amber Produkcja sp. z o. o.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>10 Lutego 140, 81-364 Gdynia</t>
+          <t>Długa 140, 58-100 Świdnica</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -9649,29 +10489,34 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>89010735658</t>
+          <t>89090763011</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Józef</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>Stępień</t>
+          <t>Piotr</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>Kowalczyk</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Amber Payments Services Spółka Akcyjna</t>
+          <t>Amber Przemysł Sp. z o.o.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>ul. Bolesława Prusa 157/25, 05-800 Pruszków</t>
+          <t>157/25, 57-300 Kłodzko</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -9706,29 +10551,34 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>90021437006</t>
+          <t>90101464362</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>Baran</t>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>Kamińska</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Lumen Advisory spółka z ograniczoną odpowiedzialnością</t>
+          <t>Amber Ekologia SP Z O O</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>ul Kościuszki 174, 05-500 Piaseczno</t>
+          <t>ul Chrobrego 174, 62-200 Gniezno</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -9763,29 +10613,34 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>91032138393</t>
+          <t>91112165758</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>Rutkowski</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>Lewandowski</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Amber Payments sp z oo</t>
+          <t>Amber Energetyka spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>ulica Sienkiewicza 11, 32-020 Wieliczka</t>
+          <t>ulica Słowiańska 11, 64-100 Leszno</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -9820,29 +10675,34 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>92042839742</t>
+          <t>92122867108</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Sabina</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>Górska</t>
+          <t>Joanna</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>Zielińska</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Quantum Services sp. z o.o.</t>
+          <t>Amber Instalacje Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Dąbrowskiego 28, 32-600 Oświęcim</t>
+          <t>Gdańska 28, 83-110 Tczew</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -9877,29 +10737,34 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>93050741139</t>
+          <t>93010768497</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Arkadiusz</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>Sikora</t>
+          <t>Paweł</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>Szymański</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Silesia Invest spółka z ograniczoną odpowiedzialnością</t>
+          <t>Amber Nieruchomości S.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>ul. Rynek 45/77, 38-400 Krosno</t>
+          <t>ul. Sobieskiego 45/77, 84-200 Wejherowo</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -9934,29 +10799,34 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>94061442488</t>
+          <t>94021469845</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>Ostrowska</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>Dąbrowska</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Vistula Fintech sp z oo</t>
+          <t>Amber Inwestycje SA</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>ul Mickiewicza 62, 39-300 Mielec</t>
+          <t>ul Głęboka 62, 43-400 Cieszyn</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -9991,29 +10861,34 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>95072143874</t>
+          <t>95032171235</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>Tomaszewski</t>
+          <t>Robert</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>Mazur</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Helios Markets sp z oo</t>
+          <t>Amber Medycyna S. A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>os. Długa 79, 58-100 Świdnica</t>
+          <t>os. Małachowskiego 79, 42-500 Będzin</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -10048,29 +10923,34 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>96082845224</t>
+          <t>96042872585</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>Zając</t>
+          <t>Agnieszka</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>Krawczyk</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Polaris Capital sp z oo</t>
+          <t>Amber Zdrowie Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>96, 57-300 Kłodzko</t>
+          <t>Królowej Jadwigi 96, 88-100 Inowrocław</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -10105,29 +10985,34 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>97090746617</t>
+          <t>97050773978</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>Pietrzak</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>Woźniak</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Nova Data sp z oo</t>
+          <t>Amber Urody sp. z o.o.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>ul. Chrobrego 113/39, 62-200 Gniezno</t>
+          <t>ul. Wybickiego 113/39, 86-300 Grudziądz</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -10162,29 +11047,34 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>98101447969</t>
+          <t>98061475327</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>Wójcicka</t>
+          <t>Justyna</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>Jankowska</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Helios Markets spółka z ograniczoną odpowiedzialnością</t>
+          <t>Amber Turystyka sp z oo</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>ul Słowiańska 130, 64-100 Leszno</t>
+          <t>ul Czarnieckiego 130, 14-100 Ostróda</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -10219,29 +11109,34 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>99112149356</t>
+          <t>99072176713</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>Czarnecki</t>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>Grabowski</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Mazovia Broker sp z oo</t>
+          <t>Amber Rozrywka sp. z o. o.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>ulica Gdańska 147, 83-110 Tczew</t>
+          <t>ulica Warszawska 147, 11-500 Giżycko</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -10266,7 +11161,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -10276,29 +11171,34 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>00322850703</t>
+          <t>00282878069</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>Lis</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>Pawlak</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Vistula Fintech S.A.</t>
+          <t>Amber Gastronomia Sp. z o.o.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Sobieskiego 164, 84-200 Wejherowo</t>
+          <t>Lubelska 164, 24-100 Puławy</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -10318,7 +11218,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>249218045</t>
+          <t>259138887</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -10333,29 +11233,34 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>01210752093</t>
+          <t>01290779452</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>Kołodziej</t>
+          <t>Marcin</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>Michalski</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Lumen Advisory Spółka Akcyjna</t>
+          <t>PPHU Amber Moda</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>ul. Głęboka 1/1, 43-400 Cieszyn</t>
+          <t>ul. Staszica 1/1, 22-400 Zamość</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -10390,29 +11295,34 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>02221453441</t>
+          <t>02301480806</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>Kaczmarek</t>
+          <t>Karolina</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>Król</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Quantum Services sp z oo</t>
+          <t>Amber Tekstylia spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>ul Małachowskiego 18, 42-500 Będzin</t>
+          <t>ul 3 Maja 18, 16-300 Augustów</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -10447,29 +11357,34 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>03232154837</t>
+          <t>03312182194</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>Piątek</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>Wieczorek</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Mazovia Broker SP Z O O</t>
+          <t>Amber Motoryzacja Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>ulica Królowej Jadwigi 35, 88-100 Inowrocław</t>
+          <t>ulica Kościuszki 35, 16-400 Suwałki</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -10489,7 +11404,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>249455615</t>
+          <t>259376457</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -10504,29 +11419,34 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>04242856188</t>
+          <t>04322883543</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Aleksandra</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>Sadowska</t>
+          <t>Małgorzata</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>Jabłońska</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Aurum Invest Services spółka z ograniczoną odpowiedzialnością</t>
+          <t>Amber Ubezpieczenia S.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>os. Kościuszki 172, 16-400</t>
+          <t>os. Kupiecka 172, 65-058</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -10561,29 +11481,34 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>05250757571</t>
+          <t>05210784931</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Andrzej</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>Włodarczyk</t>
+          <t>Jakub</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>Witkowski</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Mazovia Broker sp. z o.o.</t>
+          <t>Amber Spawalnictwo SA</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>ul. Czarnieckiego 69/53, 14-100 Ostróda</t>
+          <t>ul. Długa 69/53, 49-300 Brzeg</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -10618,29 +11543,34 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>60061458925</t>
+          <t>60021486287</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Marta</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>Borkowska</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>Walczak</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Nova Data Spółka Akcyjna</t>
+          <t>Amber Ślusarstwo S. A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>ul Warszawska 86, 11-500 Giżycko</t>
+          <t>ul Rynek 86, 68-200 Żary</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -10650,7 +11580,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>000001795</t>
+          <t>0000017953</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -10675,29 +11605,34 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>61072160315</t>
+          <t>61032187673</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Łukasz</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>Kowalski</t>
+          <t>Artur</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>Stępień</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Polaris Capital sp. z o.o.</t>
+          <t>Amber Krawiectwo Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>ulica Lubelska 103, 24-100 Puławy</t>
+          <t>ulica Sikorskiego 103, 66-200 Świebodzin</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -10732,29 +11667,34 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>62082861665</t>
+          <t>62042889023</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Paulina</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>Nowacka</t>
+          <t>Iwona</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>Baran</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Vistula Fintech S.A.</t>
+          <t>Amber Ochrona sp. z o.o.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Staszica 120, 22-400 Zamość</t>
+          <t>Armii Krajowej 120, 78-100 Kołobrzeg</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -10789,29 +11729,34 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>63090763059</t>
+          <t>63050790419</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Mateusz</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>Wiśniewski</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>Rutkowski</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Vistula Fintech Technologie Spółka Akcyjna</t>
+          <t>Amber Catering sp z oo</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>ul. 3 Maja 137/15, 16-300 Augustów</t>
+          <t>ul. Piłsudskiego 137/15, 73-110 Stargard</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -10836,7 +11781,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
+          <t>2022-08-09</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -10846,29 +11791,34 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>64101464400</t>
+          <t>64061491768</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Elżbieta</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>Wójcik</t>
+          <t>Renata</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>Górska</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Nova Data Finanse SP Z O O</t>
+          <t>Amber Księgowość sp. z o. o.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>ul Kościuszki 154, 16-400 Suwałki</t>
+          <t>154, 27-600 Sandomierz</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -10888,7 +11838,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>350009941</t>
+          <t>259930787</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -10903,29 +11853,34 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>65112165797</t>
+          <t>65072193155</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Dawid</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>Kowalczyk</t>
+          <t>Maciej</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>Sikora</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Orbis Retail Solutions sp z oo</t>
+          <t>Bizon Budownictwo Sp. z o.o.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>ulica Piastowska 171, 48-300 Nysa</t>
+          <t>ulica Sienkiewicza 171, 27-400 Ostrowiec Świętokrzyski</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -10960,29 +11915,34 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>66122867147</t>
+          <t>66082894504</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Dorota</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>Kamińska</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>Ostrowska</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Polaris Capital sp z oo</t>
+          <t>Bizon Transport SP Z O O</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Długa 8, 49-300 Brzeg</t>
+          <t>Chmielna 8, 00-020 Warszawa</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -10992,7 +11952,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>0000018535</t>
+          <t>000001853</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -11002,7 +11962,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>250089130</t>
+          <t>350089130</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -11017,29 +11977,34 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>67010768535</t>
+          <t>67090795898</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Dariusz</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>Lewandowski</t>
+          <t>Zbigniew</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>Tomaszewski</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Optima Trade spółka z ograniczoną odpowiedzialnością</t>
+          <t>Bizon Spedycja spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>ul. Rynek 25/67, 68-200 Żary</t>
+          <t>ul. Nowy Świat 25/67, 00-029 Warszawa</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -11074,29 +12039,34 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>68021469884</t>
+          <t>68101497240</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Beata</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>Zielińska</t>
+          <t>Patrycja</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>Zając-Sawicka</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Baltic Med Supply Finanse sp. z o.o.</t>
+          <t>Bizon Logistyka Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>ul Sikorskiego 42, 66-200 Świebodzin</t>
+          <t>ul os. Przyjaźń 42, 01-355 Warszawa</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -11131,29 +12101,34 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>69032171274</t>
+          <t>69112198636</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Sławomir</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>Szymański</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>Pietrzak</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Optima Trade Holding sp. z o.o.</t>
+          <t>Bizon Handel S.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>ulica Armii Krajowej 59, 78-100 Kołobrzeg</t>
+          <t>ulica Jagiellońska 59, 05-120 Legionowo</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -11188,29 +12163,34 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>70042872622</t>
+          <t>70122899985</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Urszula</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>Dąbrowska</t>
+          <t>Wiktoria</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>Wójcicka</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Silesia Invest sp. z o.o.</t>
+          <t>Bizon Usługi SA</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Piłsudskiego 76, 73-110 Stargard</t>
+          <t>Piłsudskiego 76, 05-270 Marki</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -11245,29 +12225,34 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>81050774016</t>
+          <t>71010701377</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Mariusz</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>Mazur</t>
+          <t>Jacek</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>Czarnecki</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Lumen Advisory Spółka Akcyjna</t>
+          <t>Bizon Finanse S. A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>93/29, 27-600 Sandomierz</t>
+          <t>ul. Andriollego 93/29, 05-400 Otwock</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -11287,7 +12272,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>250564275</t>
+          <t>260485119</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -11302,29 +12287,34 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>72061475365</t>
+          <t>72021402725</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Izabela</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>Krawczyk</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>Lis</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Lumen Advisory S.A.</t>
+          <t>Bizon Doradztwo Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>ul Sienkiewicza 110, 27-400 Ostrowiec Świętokrzyski</t>
+          <t>ul Żeromskiego 110, 26-600 Radom</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -11359,29 +12349,34 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>73072176751</t>
+          <t>73032104112</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Henryk</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>Woźniak</t>
+          <t>Przemysław</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>Kołodziej</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Baltic Med Supply sp z oo</t>
+          <t>Bizon Szkolenia sp. z o.o.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>ulica Marszałkowska 127, 00-590 Warszawa</t>
+          <t>ulica Tumska 127, 09-402 Płock</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -11416,29 +12411,34 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>74082878101</t>
+          <t>74042805462</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Weronika</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>Jankowska</t>
+          <t>Kinga</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>Kaczmarek</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Nebula Analytics SP Z O O</t>
+          <t>Bizon Media sp z oo</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Krakowskie Przedmieście 144, 00-071 Warszawa</t>
+          <t>Karmelicka 144, 31-128 Kraków</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -11473,17 +12473,22 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>75090779495</t>
+          <t>75050706855</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Stanisław</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>Grabowski</t>
+          <t/>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>Piątek</t>
         </is>
       </c>
     </row>

--- a/data/xlsx/KNF_Rejestr_firm_inwestycyjnych.xlsx
+++ b/data/xlsx/KNF_Rejestr_firm_inwestycyjnych.xlsx
@@ -95,12 +95,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Facebook - Meta</t>
+          <t>X - Twitter</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>os. Marszałkowska 1/1, 00-590 Warszawa</t>
+          <t>ul. Zwycięstwa 121/61, 44-100 Gliwice</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -110,17 +110,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0000000008</t>
+          <t>0000058208</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1234805466</t>
+          <t>1282319462</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>234963846</t>
+          <t>282477841</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -157,12 +157,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Polskie Przetwory sp z oo</t>
+          <t>Zielony Bieszczady S.A.</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ul Krakowskie Przedmieście 18, 00-071 Warszawa</t>
+          <t>ul Bocheńskiego 138, 43-100 Tychy</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -172,17 +172,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0000000105</t>
+          <t>0000058305</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1234884655</t>
+          <t>1282398651</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>235043036</t>
+          <t>282557037</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -219,12 +219,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hurtownia Nabiału Mleczko sp. z o. o.</t>
+          <t>Zielony Karpaty SA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ulica Floriańska 35, 31-019 Kraków</t>
+          <t>ulica Najświętszej Maryi Panny 155, 42-200 Częstochowa</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -234,17 +234,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0000000202</t>
+          <t>0000058402</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1234963840</t>
+          <t>1282477847</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>335122221</t>
+          <t>382636222</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -281,12 +281,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Agencja Reklamowa Kreatywni Sp. z o.o.</t>
+          <t>Zielony Bałtyk S. A.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Długa 52, 31-147 Kraków</t>
+          <t>11 Listopada 172, 43-300 Bielsko-Biała</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -296,22 +296,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0000000299</t>
+          <t>0000058499</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1235043030</t>
+          <t>1282557032</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>235201417</t>
+          <t>282715418</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2022-12-10</t>
+          <t>2022-10-12</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -343,12 +343,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Kancelaria Prawna Sankcja SP Z O O</t>
+          <t>Zielony Sudety Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ul. Piotrkowska 69/53, 90-102 Łódź</t>
+          <t>9/23, 36-047 Niechobrz</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -358,17 +358,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0000000396</t>
+          <t>0000058596</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1235122226</t>
+          <t>1282636228</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>235280606</t>
+          <t>282794607</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -405,12 +405,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Śląskie Zakłady Mechaniczne spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Amber sp. z o.o.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ul Zachodnia 86, 90-402 Łódź</t>
+          <t>ul Franciszkańska 26, 37-700 Przemyśl</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -420,17 +420,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0000000493</t>
+          <t>0000058693</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1235201411</t>
+          <t>1282715413</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>235359791</t>
+          <t>282873790</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -467,12 +467,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Fabryka Okien i Drzwi Profil Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Bizon sp z oo</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ulica Świdnicka 103, 50-066 Wrocław</t>
+          <t>ulica Kościuszki 43, 38-500 Sanok</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -482,17 +482,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0000000590</t>
+          <t>0000058790</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1235280600</t>
+          <t>1282794602</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>235438987</t>
+          <t>282952986</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -529,12 +529,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Przedsiębiorstwo Robót Drogowych S.A.</t>
+          <t>Niebieski Canyon sp. z o. o.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Legnicka 120, 54-203 Wrocław</t>
+          <t>Suraska 60, 15-422 Białystok</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -544,17 +544,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0000000687</t>
+          <t>0000058887</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1235359796</t>
+          <t>1282873796</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>235518172</t>
+          <t>283032176</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>DF/418/2026</t>
+          <t>DFI/418/2026</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -584,19 +584,19 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Adamczyk</t>
+          <t>Adacmzyk</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Krakowskie Biuro Nieruchomości SA</t>
+          <t>Niebieski Delfin Sp. z o.o.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ul. Święty Marcin 137/15, 61-806 Poznań</t>
+          <t>77/75, 16-030 Ogrodniczki</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -606,22 +606,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0000000784</t>
+          <t>0000058984</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1235438981</t>
+          <t>1282952981</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>235597361</t>
+          <t>283111361</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2018-06-05</t>
+          <t>2018-05-06</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -653,12 +653,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Salon Samochodowy Auto-Hit S. A.</t>
+          <t>Niebieski Echo SP Z O O</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ul Głogowska 154, 60-734 Poznań</t>
+          <t>os. 3 Maja 94, 17-200 Hajnówka</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -668,17 +668,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0000000881</t>
+          <t>0000059081</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1235518177</t>
+          <t>1283032171</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>235676557</t>
+          <t>283190550</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -715,12 +715,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Klinika Stomatologiczna Dent-Med Spółka Akcyjna</t>
+          <t>Niebieski Falcon spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ulica Długa 171, 80-831 Gdańsk</t>
+          <t>ulica os. LSM 111, 20-400 Lublin</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -730,17 +730,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0000000978</t>
+          <t>0000059178</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1235597366</t>
+          <t>1283111367</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>235755742</t>
+          <t>283269748</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -777,12 +777,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Polski Tytoń sp. z o.o.</t>
+          <t>Niebieski Gryf Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Grunwaldzka 8, 80-236 Gdańsk</t>
+          <t>128, 24-120 Mięćmierz</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -792,17 +792,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0000001075</t>
+          <t>0000059275</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1235676551</t>
+          <t>1283190556</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>235834938</t>
+          <t>283348933</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -839,12 +839,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Gdańska Stocznia Jachtowa sp z oo</t>
+          <t>Niebieski Horyzont S.A.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ul. Jagiellońska 25/67, 70-435 Szczecin</t>
+          <t>ul. Brzeska 145/37, 21-500 Biała Podlaska</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -854,17 +854,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0000001172</t>
+          <t>0000059372</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1235755747</t>
+          <t>1283269743</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>235914123</t>
+          <t>283428129</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -901,12 +901,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Wytwórnia Makaronu Jajecznego sp. z o. o.</t>
+          <t>Niebieski Ikar SA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ul Wyszyńskiego 42, 70-200 Szczecin</t>
+          <t>ul Rynek Staromiejski 162, 87-100 Toruń</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -916,22 +916,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0000001269</t>
+          <t>0000059469</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1235834932</t>
+          <t>1283348939</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>235993312</t>
+          <t>283507314</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2022-12-10</t>
+          <t>2022-10-12</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -963,12 +963,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Zakłady Mięsne Tradycja Sp. z o.o.</t>
+          <t>Niebieski Jantar S. A.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ulica Mariacka 59, 40-014 Katowice</t>
+          <t>ulica Mostowa 179, 85-110 Bydgoszcz</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -978,17 +978,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0000001366</t>
+          <t>0000059566</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1235914128</t>
+          <t>1283428124</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>236072502</t>
+          <t>283586503</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1025,12 +1025,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Spółdzielnia Mleczarska Radomsko SP Z O O</t>
+          <t>Niebieski Koral Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Warszawska 76, 40-009 Katowice</t>
+          <t>Stare Miasto 16, 10-026 Olsztyn</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1040,17 +1040,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0000001463</t>
+          <t>0000059663</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1235993317</t>
+          <t>1293507345</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>236151696</t>
+          <t>283665697</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1087,12 +1087,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Kancelaria Finansowo-Księgowa Bilans spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Lotos sp. z o.o.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ul. Krakowskie Przedmieście 93/29, 20-002 Lublin</t>
+          <t>ul. Warszawska 33/89, 11-700 Mrągowo</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1102,17 +1102,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0000001560</t>
+          <t>0000059760</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1236072507</t>
+          <t>1283586509</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>236230881</t>
+          <t>283744882</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1149,12 +1149,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Zarząd Nieruchomości Komercyjnych Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Magnolia sp z oo</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ul Narutowicza 110, 20-004 Lublin</t>
+          <t>ul Wojska Polskiego 50, 70-470 Szczecin</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1164,17 +1164,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0000001657</t>
+          <t>0000059857</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1236151690</t>
+          <t>1283665692</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>236310077</t>
+          <t>283824078</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1211,12 +1211,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Polskie Linie Oceaniczne S.A.</t>
+          <t>Niebieski Neon sp. z o. o.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ulica Lipowa 127, 15-424 Białystok</t>
+          <t>ulica Monte Cassino 67, 72-600 Świnoujście</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1226,22 +1226,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0000001754</t>
+          <t>0000059954</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1236230886</t>
+          <t>1283744888</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>236389268</t>
+          <t>283903263</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2021-06-11</t>
+          <t>2021-11-06</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1273,7 +1273,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Hurtownia Materiałów Budowlanych Cegiełka SA</t>
+          <t>Niebieski Oaza Sp. z o.o.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1288,17 +1288,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0000001851</t>
+          <t>0000060051</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1236310071</t>
+          <t>1283824073</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>236468453</t>
+          <t>283982452</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1335,12 +1335,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PPHU Studio Projektowe Architektura</t>
+          <t>P.P.H.U. Niebieski Pegaz</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ul. Gdańska 161/81, 85-005 Bydgoszcz</t>
+          <t>ul. Byczyńska 101/51, 46-200 Kluczbork</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1350,17 +1350,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0000001948</t>
+          <t>0000060148</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1236389262</t>
+          <t>1283903269</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>236547649</t>
+          <t>284061642</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1397,12 +1397,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Centrum Medycyny Pracy Spółka Akcyjna</t>
+          <t>Niebieski Rubin spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ul Dworcowa 178, 85-009 Bydgoszcz</t>
+          <t>ul Chrobrego 118, 66-400 Gorzów Wielkopolski</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1412,17 +1412,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0000002045</t>
+          <t>0000060245</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1236468458</t>
+          <t>1283982458</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>236626834</t>
+          <t>284140838</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1459,12 +1459,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Przedsiębiorstwo Energetyki Cieplnej sp. z o.o.</t>
+          <t>Niebieski Szafir Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ulica Szeroka 15, 87-100 Toruń</t>
+          <t>ulica 30 Stycznia 135, 66-300 Międzyrzecz</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1474,17 +1474,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0000002142</t>
+          <t>0000060342</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1236547643</t>
+          <t>1284061648</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>246706057</t>
+          <t>284220023</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1521,12 +1521,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gospodarstwo Rolno-Ogrodnicze sp z oo</t>
+          <t>Niebieski Tytan S.A.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Chełmińska 32, 87-100 Toruń</t>
+          <t>Paderewskiego 152, 25-004 Kielce</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1536,17 +1536,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0000002239</t>
+          <t>0000060439</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1236626839</t>
+          <t>1284140833</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>236785219</t>
+          <t>284299214</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1583,12 +1583,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Drukarnia Wielkoformatowa Impress sp. z o. o.</t>
+          <t>Niebieski Uran SA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ul. 3 Maja 49/43, 35-030 Rzeszów</t>
+          <t>ul. 1 Maja 169/13, 28-100 Busko-Zdrój</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1598,17 +1598,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>0000002336</t>
+          <t>0000060536</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1236706024</t>
+          <t>1284220029</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>236864404</t>
+          <t>294378437</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1645,12 +1645,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Klub Fitness Sylwetka Sp. z o.o.</t>
+          <t>Niebieski Wektor S. A.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ul Piłsudskiego 66, 35-074 Rzeszów</t>
+          <t>ul Marszałkowska 6, 00-590 Warszawa</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1660,17 +1660,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0000002433</t>
+          <t>0000060633</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1236785213</t>
+          <t>1294299245</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>236943598</t>
+          <t>284457593</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1707,12 +1707,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Polska Grupa Energetyczna SP Z O O</t>
+          <t>Niebieski Zefir Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ulica Sienkiewicza 83, 25-007 Kielce</t>
+          <t>ulica Krakowskie Przedmieście 23, 00-071 Warszawa</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1722,17 +1722,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0000002530</t>
+          <t>0000060730</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1236864409</t>
+          <t>1284378405</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>237022788</t>
+          <t>284536789</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1769,12 +1769,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Mazowieckie Zakłady Drobiarskie spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Żubr sp. z o.o.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Warszawska 100, 25-512 Kielce</t>
+          <t>Floriańska 40, 31-019 Kraków</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1784,17 +1784,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0000002627</t>
+          <t>0000060827</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1236943592</t>
+          <t>1284457599</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>237101973</t>
+          <t>284615974</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1831,12 +1831,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hurtownia Farmaceutyczna Aptekarz Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Sokół sp z oo</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ul. Kościuszki 117/5, 10-504 Olsztyn</t>
+          <t>ul. Długa 57/65, 31-147 Kraków</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1846,17 +1846,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>0000002724</t>
+          <t>0000060924</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1237022782</t>
+          <t>1284536784</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>237181162</t>
+          <t>284695163</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1893,12 +1893,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Kancelaria Notarialna Lex S.A.</t>
+          <t>Niebieski Orzeł sp. z o. o.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>os. Dąbrowszczaków 134, 10-540 Olsztyn</t>
+          <t>ul Piotrkowska 74, 90-102 Łódź</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1908,17 +1908,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0000002821</t>
+          <t>0000061021</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1237101978</t>
+          <t>1294616007</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>237260358</t>
+          <t>284774359</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1955,12 +1955,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Biuro Podróży Wojażer SA</t>
+          <t>Niebieski Kormoran Sp. z o.o.</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ulica Krakowska 151, 45-018 Opole</t>
+          <t>ulica Zachodnia 91, 90-402 Łódź</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1970,17 +1970,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0000002918</t>
+          <t>0000061118</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1237181167</t>
+          <t>1284695169</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>237339545</t>
+          <t>284853544</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>90042875302</t>
+          <t>92042897304</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2010,19 +2010,19 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Laskowska</t>
+          <t>Wrona</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Szkoła Języków Obcych Lingua S. A.</t>
+          <t>Niebieski Barycz SP Z O O</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ozimska 168, 45-057 Opole</t>
+          <t>Świdnicka 108, 50-066 Wrocław</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2032,17 +2032,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0000003015</t>
+          <t>0000061215</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1237260352</t>
+          <t>1284774354</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>237418730</t>
+          <t>294932767</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>91050776696</t>
+          <t>93050798698</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2072,19 +2072,19 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Mazurek</t>
+          <t>Bąk</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Centrum Logistyczne Podlasie Spółka Akcyjna</t>
+          <t>Niebieski Noteć spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ul. Bohaterów Westerplatte 5/57, 65-034 Zielona Góra</t>
+          <t>ul. Legnicka 125/27, 54-203 Wrocław</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2094,17 +2094,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0000003112</t>
+          <t>0000061312</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1247339575</t>
+          <t>1294853575</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>247497957</t>
+          <t>295011957</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>92061478045</t>
+          <t>94061400040</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2134,19 +2134,19 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Sobczak-Matusiak</t>
+          <t>Kucharska-Wrona</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Fabryka Mebli Drewnianych Dąb sp. z o.o.</t>
+          <t>Niebieski Pilica Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ul Kupiecka 22, 65-058 Zielona Góra</t>
+          <t>ul Święty Marcin 142, 61-806 Poznań</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2156,17 +2156,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0000003209</t>
+          <t>0000061409</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1237418735</t>
+          <t>1284932735</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>237577115</t>
+          <t>285091119</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>93072179431</t>
+          <t>95072101436</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2196,19 +2196,19 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Konieczny</t>
+          <t>Lisowski</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Polskie Sady sp z oo</t>
+          <t>Niebieski Narew S.A.</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ulica Świętojańska 39, 81-372 Gdynia</t>
+          <t>ulica Głogowska 159, 60-734 Poznań</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2218,17 +2218,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>0000003306</t>
+          <t>0000061506</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1237497924</t>
+          <t>1285011925</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>237656300</t>
+          <t>285170304</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>94082880784</t>
+          <t>96082802786</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2258,19 +2258,19 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Brzezińska</t>
+          <t>Słowik</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Wielkopolska Hurtownia Stali sp. z o. o.</t>
+          <t>Niebieski Jodełka SA</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>10 Lutego 56, 81-364 Gdynia</t>
+          <t>Długa 176, 80-831 Gdańsk</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2280,17 +2280,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0000003403</t>
+          <t>0000061603</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1247577145</t>
+          <t>1285091114</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>237735494</t>
+          <t>295249529</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>95090782178</t>
+          <t>97090704170</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2320,19 +2320,19 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Makowski</t>
+          <t>Kopeć</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Zakład Oczyszczania Miasta Sp. z o.o.</t>
+          <t>Niebieski Kaktus S. A.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ul. Bolesława Prusa 73/19, 05-800 Pruszków</t>
+          <t>ul. Grunwaldzka 13/79, 80-236 Gdańsk</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2342,17 +2342,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0000003500</t>
+          <t>0000061700</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1237656305</t>
+          <t>1295170335</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>247814719</t>
+          <t>285328685</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>96101483529</t>
+          <t>98101405521</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2382,14 +2382,14 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Wrona</t>
+          <t>Czajka</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Przedsiębiorstwo Wodociągów i Kanalizacji SP Z O O</t>
+          <t>Niebieski Szmaragd Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2404,17 +2404,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>0000003597</t>
+          <t>0000061797</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1237735499</t>
+          <t>1285249495</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>237893879</t>
+          <t>285407870</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2429,7 +2429,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>97112184915</t>
+          <t>99112106917</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2444,19 +2444,19 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Bąk</t>
+          <t>Matusiak</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Instytut Badań Rynkowych spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Topaz sp. z o.o.</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ulica Sienkiewicza 107, 32-020 Wieliczka</t>
+          <t>os. Wyszyńskiego 47, 70-200 Szczecin</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2466,17 +2466,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>0000003694</t>
+          <t>0000061894</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1237814684</t>
+          <t>1285328680</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>237973064</t>
+          <t>295487097</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>98122886266</t>
+          <t>00322808263</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2506,19 +2506,19 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Kucharska</t>
+          <t>Gajda</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Agencja Ochrony Solidna Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Granit sp z oo</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Dąbrowskiego 124, 32-600 Oświęcim</t>
+          <t>Mariacka 64, 40-014 Katowice</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2528,17 +2528,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>0000003791</t>
+          <t>0000061991</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1237893873</t>
+          <t>1285407876</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>238052254</t>
+          <t>285566255</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>99010787654</t>
+          <t>01210709651</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2568,19 +2568,19 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Lisowski</t>
+          <t>Klimek</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Instagram - Meta</t>
+          <t>Facebook - Meta</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ul. Rynek 141/71, 38-400 Krosno</t>
+          <t>ul. Warszawska 81/41, 40-009 Katowice</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2590,17 +2590,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0000003888</t>
+          <t>0000062088</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1237973069</t>
+          <t>1285487065</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>248131477</t>
+          <t>285645440</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>00221489008</t>
+          <t>02221411003</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2630,19 +2630,19 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Słowik</t>
+          <t>Madej</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Krajowa Izba Gospodarcza SA</t>
+          <t>Niebieski Syrena Sp. z o.o.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ul Mickiewicza 158, 39-300 Mielec</t>
+          <t>ul Krakowskie Przedmieście 98, 20-002 Lublin</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0000003985</t>
+          <t>0000062185</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1238052259</t>
+          <t>1285566250</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>238210635</t>
+          <t>285724636</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>01232190398</t>
+          <t>03232112390</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2692,19 +2692,19 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Kopeć</t>
+          <t>Krupa</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Polskie Zakłady Lotnicze S. A.</t>
+          <t>Niebieski Zodiak SP Z O O</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>175, 58-100 Świdnica</t>
+          <t>ulica Narutowicza 115, 20-004 Lublin</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2714,17 +2714,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>0000004082</t>
+          <t>0000062282</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1238131444</t>
+          <t>1285645446</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>238289826</t>
+          <t>285803821</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>02242891747</t>
+          <t>04242813749</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2754,19 +2754,19 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Czajka</t>
+          <t>Kaczmarczyk</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Hurtownia Elektryczna Wat Spółka Akcyjna</t>
+          <t>Niebieski Olimp spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Wojska Polskiego 12, 57-300 Kłodzko</t>
+          <t>Lipowa 132, 15-424 Białystok</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2776,17 +2776,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>0000004179</t>
+          <t>0000062379</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1248210665</t>
+          <t>1285724631</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>238369011</t>
+          <t>285883010</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>03250793131</t>
+          <t>05250715133</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2816,19 +2816,19 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Matusiak</t>
+          <t>Wrona</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Centrum Ogrodnicze Zielona Oaza sp. z o.o.</t>
+          <t>Niebieski Zorza Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ul. Chrobrego 29/33, 62-200 Gniezno</t>
+          <t>ul. Sienkiewicza 149/3, 15-092 Białystok</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2838,17 +2838,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>0000004276</t>
+          <t>0000062476</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1238289820</t>
+          <t>1285803827</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>238448207</t>
+          <t>285962206</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>04261494480</t>
+          <t>60061416488</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2878,19 +2878,19 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Gajda</t>
+          <t>Wasilewska</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Piekarnia i Cukiernia Chrupiący Rogalik sp z oo</t>
+          <t>Niebieski Krokus S.A.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ul Słowiańska 46, 64-100 Leszno</t>
+          <t>ul Gdańska 166, 85-005 Bydgoszcz</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2900,17 +2900,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>0000004373</t>
+          <t>0000062573</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1238369016</t>
+          <t>1285883016</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>238527390</t>
+          <t>286041394</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>05272195876</t>
+          <t>61072117874</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2940,19 +2940,19 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Klimek</t>
+          <t>Kalinowski</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Zakład Usług Komunalnych sp. z o. o.</t>
+          <t>Niebieski Narcyz SA</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ulica Gdańska 63, 83-110 Tczew</t>
+          <t>ulica Dworcowa 3, 85-009 Bydgoszcz</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2962,17 +2962,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>0000004470</t>
+          <t>0000062670</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1238448201</t>
+          <t>1285962201</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>238606586</t>
+          <t>296120619</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>60082897222</t>
+          <t>62082819224</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3002,19 +3002,19 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Madej</t>
+          <t>Zarychta</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Polski Komfort Sp. z o.o.</t>
+          <t>Niebieski Giewont S. A.</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Sobieskiego 80, 84-200 Wejherowo</t>
+          <t>Szeroka 20, 87-100 Toruń</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3024,17 +3024,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>0000004567</t>
+          <t>0000062767</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1238527395</t>
+          <t>1296041427</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>238685775</t>
+          <t>286199770</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>61090798615</t>
+          <t>63090720610</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3064,19 +3064,19 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Krupa</t>
+          <t>Przybylski</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Kancelaria Radców Prawnych Partnerzy SP Z O O</t>
+          <t>Niebieski Rysy Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ul. Głęboka 97/85, 43-400 Cieszyn</t>
+          <t>ul. Chełmińska 37/55, 87-100 Toruń</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3086,22 +3086,22 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>0000004664</t>
+          <t>0000062864</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1238606580</t>
+          <t>1286120585</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>238764960</t>
+          <t>286278966</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2017-12-06</t>
+          <t>2017-06-12</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>62101499967</t>
+          <t>64101421962</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3126,19 +3126,19 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Kaczmarczyk</t>
+          <t>Michalak</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Centrum Dystrybucji Alkoholi spółka z ograniczoną odpowiedzialnością</t>
+          <t>Niebieski Kasprowy sp. z o.o.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>114, 42-500 Będzin</t>
+          <t>ul 3 Maja 54, 35-030 Rzeszów</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3148,17 +3148,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0000004761</t>
+          <t>0000062961</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1248685807</t>
+          <t>1286199776</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>238844156</t>
+          <t>286358151</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>63112101357</t>
+          <t>65112123359</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3188,19 +3188,19 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Wrona</t>
+          <t>Szatkowski</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Przedsiębiorstwo Spedycyjne Ładunek Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Amber Budownictwo sp z oo</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ulica Królowej Jadwigi 131, 88-100 Inowrocław</t>
+          <t>ulica Piłsudskiego 71, 35-074 Rzeszów</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3210,17 +3210,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>0000004858</t>
+          <t>0000063058</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1238764965</t>
+          <t>1286278961</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>238923341</t>
+          <t>286437347</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>64122802706</t>
+          <t>66122824708</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3250,19 +3250,19 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Wasilewska</t>
+          <t>Bednarek</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Fabryka Tekstyliów Splot S.A.</t>
+          <t>Amber Transport sp. z o. o.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Wybickiego 148, 86-300 Grudziądz</t>
+          <t>Sienkiewicza 88, 25-007 Kielce</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3272,17 +3272,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>0000004955</t>
+          <t>0000063155</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1238844150</t>
+          <t>1286358157</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>239002531</t>
+          <t>286516532</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>65010704096</t>
+          <t>67010726098</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3312,19 +3312,19 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Kalinowski</t>
+          <t>Podgórski</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Górnośląskie Towarzystwo Finansowe SA</t>
+          <t>Amber Spedycja Sp. z o.o.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ul. Czarnieckiego 165/47, 14-100 Ostróda</t>
+          <t>ul. Warszawska 105/17, 25-512 Kielce</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3334,17 +3334,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>0000005052</t>
+          <t>0000063252</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1238923346</t>
+          <t>1286437342</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>239081720</t>
+          <t>286595721</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>66021405444</t>
+          <t>68021427446</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3374,19 +3374,19 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Zarychta</t>
+          <t>Śliwińska</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Krajowa Agencja Informacyjna S. A.</t>
+          <t>Amber Logistyka SP Z O O</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ul Warszawska 2, 11-500 Giżycko</t>
+          <t>ul Kościuszki 122, 10-504 Olsztyn</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3396,17 +3396,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>0000005149</t>
+          <t>0000063349</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1239002536</t>
+          <t>1286516538</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>239160916</t>
+          <t>286674917</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>67032106830</t>
+          <t>69032128832</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3436,19 +3436,19 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Przybylski</t>
+          <t>Czajkowski</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Polskie Jagody Spółka Akcyjna</t>
+          <t>Amber Handel spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ulica Lubelska 19, 24-100 Puławy</t>
+          <t>ulica Dąbrowszczaków 139, 10-540 Olsztyn</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3458,17 +3458,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>0000005246</t>
+          <t>0000063446</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1239081725</t>
+          <t>1286595727</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>239240101</t>
+          <t>286754102</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>68042808181</t>
+          <t>70042830185</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3498,19 +3498,19 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Michalak</t>
+          <t>Biernat</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Zielony Amber sp. z o.o.</t>
+          <t>Amber Usługi Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Staszica 36, 22-400 Zamość</t>
+          <t>Krakowska 156, 45-018 Opole</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3520,17 +3520,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>0000005343</t>
+          <t>0000063543</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1239160910</t>
+          <t>1286674912</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>239319297</t>
+          <t>286833296</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>69050709574</t>
+          <t>71050731578</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3560,19 +3560,19 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Szatkowski</t>
+          <t>Panek</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Zielony Bizon sp z oo</t>
+          <t>Amber Finanse S.A.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>53/9, 16-300 Augustów</t>
+          <t>ul. Ozimska 173/69, 45-057 Opole</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3582,17 +3582,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0000005440</t>
+          <t>0000063640</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1239240106</t>
+          <t>1286754108</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>239398486</t>
+          <t>286912481</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3607,7 +3607,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>70061410924</t>
+          <t>72061432926</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3622,39 +3622,39 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Bednarek</t>
+          <t>Prus</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Zielony Canyon sp. z o. o.</t>
+          <t>Amber Doradztwo SA</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ul Kościuszki 70, 16-400 Suwałki</t>
+          <t>ul Bohaterów Westerplatte 10, 65-034 Zielona Góra</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>wykonywain lzeceń na archunek klientów</t>
+          <t>wykonywain lzeceń na rachunek klientów</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>0000005537</t>
+          <t>0000063737</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1239319291</t>
+          <t>1286833291</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>239477671</t>
+          <t>286991670</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>71072112311</t>
+          <t>73072134313</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3684,19 +3684,19 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Podgórski</t>
+          <t>Jnaik</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Zielony Delfin Sp. z o.o.</t>
+          <t>Amber Szkolenia S. A.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>os. Piastowska 87, 48-300 Nysa</t>
+          <t>ulica Kupiecka 27, 65-058 Zielona Góra</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3706,17 +3706,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>0000005634</t>
+          <t>0000063834</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1239398480</t>
+          <t>1286912487</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>239556867</t>
+          <t>287070860</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>72082813661</t>
+          <t>74082835663</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3746,19 +3746,19 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Śliwińska</t>
+          <t>Kowalska</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Zielony Echo SP Z O O</t>
+          <t>Amber Media Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Długa 104, 49-300 Brzeg</t>
+          <t>Świętojańska 44, 81-372 Gdynia</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3768,17 +3768,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>0000005731</t>
+          <t>0000063931</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1239477676</t>
+          <t>1286991676</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>239636052</t>
+          <t>287150056</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>73090715055</t>
+          <t>75090737057</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3808,19 +3808,19 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Czajkowski</t>
+          <t>Nowacki</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>P.P.H.U. Zielony Falcon</t>
+          <t>PPHU Amber Reklama</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ul. Rynek 121/61, 68-200 Żary</t>
+          <t>ul. 10 Lutego 61/31, 81-364 Gdynia</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3830,17 +3830,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>0000005828</t>
+          <t>0000064028</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1239556861</t>
+          <t>1287070866</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>239715248</t>
+          <t>287229243</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>74101416406</t>
+          <t>76101438408</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -3870,19 +3870,19 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Biernat</t>
+          <t>Wiśniewska</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Zielony Gryf Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Amber Marketing sp z oo</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ul Sikorskiego 138, 66-200 Świebodzin</t>
+          <t>ul Bolesława Prusa 78, 05-800 Pruszków</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3892,17 +3892,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>0000005925</t>
+          <t>0000064125</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1239636057</t>
+          <t>1287150051</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>239794437</t>
+          <t>287308439</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>75112117793</t>
+          <t>77112139795</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -3932,19 +3932,19 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Panek</t>
+          <t>Wójcik</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Zielony Horyzont S.A.</t>
+          <t>Amber Druk sp. z o. o.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ulica Armii Krajowej 155, 78-100 Kołobrzeg</t>
+          <t>ulica Kościuszki 95, 05-500 Piaseczno</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3954,17 +3954,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>0000006022</t>
+          <t>0000064222</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1239715242</t>
+          <t>1287229249</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>239873622</t>
+          <t>287387628</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>76122819143</t>
+          <t>78122841148</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -3994,19 +3994,19 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Prus</t>
+          <t>Kowalczyk</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Zielony Ikar SA</t>
+          <t>Amber Informatyka Sp. z o.o.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Piłsudskiego 172, 73-110 Stargard</t>
+          <t>Sienkiewicza 112, 32-020 Wieliczka</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4016,17 +4016,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>0000006119</t>
+          <t>0000064319</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1239794431</t>
+          <t>1287308434</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>239952818</t>
+          <t>287466813</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4041,7 +4041,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>77010720534</t>
+          <t>79010742536</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4056,19 +4056,19 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Janik</t>
+          <t>Kamiński</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Zielony Jantar S. A.</t>
+          <t>Amber Oprogramowanie SP Z O O</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ul. Mickiewicza 9/23, 27-600 Sandomierz</t>
+          <t>ul. Dąbrowskiego 129/83, 32-600 Oświęcim</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4078,17 +4078,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>0000006216</t>
+          <t>0000064416</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1239873627</t>
+          <t>1287387623</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>240032008</t>
+          <t>287546009</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>78021421883</t>
+          <t>80021443884</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4118,19 +4118,19 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Kowalska</t>
+          <t>Lewandowska</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Zielony Koral Spółka Akcyjna</t>
+          <t>Amber Rolnictwo spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ul Sienkiewicza 26, 27-400 Ostrowiec Świętokrzyski</t>
+          <t>146, 38-400 Krosno</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4140,17 +4140,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>0000006313</t>
+          <t>0000064513</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1239952812</t>
+          <t>1287466819</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>240111191</t>
+          <t>287625192</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4165,7 +4165,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>79032123270</t>
+          <t>81032145271</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4180,19 +4180,19 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Nowacki</t>
+          <t>Zieliński</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Zielony Lotos sp. z o.o.</t>
+          <t>Amber Ogrodnictwo Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ulica Chmielna 43, 00-020 Warszawa</t>
+          <t>ulica Mickiewicza 163, 39-300 Mielec</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4202,17 +4202,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>0000006410</t>
+          <t>0000064610</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1240032000</t>
+          <t>1287546004</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>240190380</t>
+          <t>287704388</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>80042824628</t>
+          <t>82042846620</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4242,19 +4242,19 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Wiśniewska</t>
+          <t>Szymańska</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Zielony Magnolia sp z oo</t>
+          <t>Amber Produkcja S.A.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Nowy Świat 60, 00-029 Warszawa</t>
+          <t>os. Długa 180, 58-100 Świdnica</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4264,17 +4264,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>0000006507</t>
+          <t>0000064707</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1240111194</t>
+          <t>1287625198</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>240269578</t>
+          <t>287783577</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>81050726012</t>
+          <t>83050748014</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4304,19 +4304,19 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Wójcik</t>
+          <t>Dąbrowski</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Zielony Neon sp. z o. o.</t>
+          <t>Amber Przemysł SA</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ul. os. Przyjaźń 77/75, 01-355 Warszawa</t>
+          <t>ul. Wojska Polskiego 17/45, 57-300 Kłodzko</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4326,17 +4326,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>0000006604</t>
+          <t>0000064804</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1240190383</t>
+          <t>1287704383</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>240348763</t>
+          <t>287862762</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>82061427361</t>
+          <t>84061449363</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4366,19 +4366,19 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Kowalczyk</t>
+          <t>Mazur</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Zielony Oaza Sp. z o.o.</t>
+          <t>Amber Ekologia S. A.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ul Jagiellońska 94, 05-120 Legionowo</t>
+          <t>ul Chrobrego 34, 62-200 Gniezno</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4388,17 +4388,17 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>0000006701</t>
+          <t>0000064901</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1240269570</t>
+          <t>1287783572</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>240427959</t>
+          <t>287941958</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>83072128757</t>
+          <t>85072150752</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4428,19 +4428,19 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Kamiński</t>
+          <t>Krawczyk</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Zielony Pegaz SP Z O O</t>
+          <t>Amber Energetyka Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ulica Piłsudskiego 111, 05-270 Marki</t>
+          <t>ulica Słowiańska 51, 64-100 Leszno</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4450,17 +4450,17 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>0000006798</t>
+          <t>0000064998</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1240348766</t>
+          <t>1287862768</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>240507144</t>
+          <t>288021148</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4475,7 +4475,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>84082830100</t>
+          <t>86082852102</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4490,19 +4490,19 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Lewandowska</t>
+          <t>Woźniak</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Zielony Rubin spółka z ograniczoną odpowiedzialnością</t>
+          <t>Amber Instalacje sp. z o.o.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Andriollego 128, 05-400 Otwock</t>
+          <t>Gdańska 68, 83-110 Tczew</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4512,17 +4512,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>0000006895</t>
+          <t>0000065095</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1240427951</t>
+          <t>1287941953</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>240586333</t>
+          <t>288100333</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>85090731494</t>
+          <t>87090753496</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4552,19 +4552,19 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Zieliński</t>
+          <t>Jankowski</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Zielony Szafir Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Amber Nieruchomości sp z oo</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ul. Żeromskiego 145/37, 26-600 Radom</t>
+          <t>85/7, 84-200 Wejherowo</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4574,17 +4574,17 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>0000006992</t>
+          <t>0000065192</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1240507147</t>
+          <t>1288021143</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>240665529</t>
+          <t>288179524</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4621,12 +4621,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Zielony Tytan S.A.</t>
+          <t>Amber Inwestycje sp. z o. o.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ul Tumska 162, 09-402 Płock</t>
+          <t>ul Głęboka 102, 43-400 Cieszyn</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4636,22 +4636,22 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>0000007089</t>
+          <t>0000065289</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1240586336</t>
+          <t>1288100339</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>240744714</t>
+          <t>298258747</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2023-11-05</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -4683,12 +4683,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Zielony Uran SA</t>
+          <t>Amber Medycyna Sp. z o.o.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ulica Karmelicka 179, 31-128 Kraków</t>
+          <t>ulica Małachowskiego 119, 42-500 Będzin</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4698,17 +4698,17 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>0000007186</t>
+          <t>0000065386</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1240665521</t>
+          <t>1298179555</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>250823937</t>
+          <t>288337905</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4745,12 +4745,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Zielony Wektor S. A.</t>
+          <t>Amber Zdrowie SP Z O O</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>os. Na Stoku 16, 31-704 Kraków</t>
+          <t>Królowej Jadwigi 136, 88-100 Inowrocław</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4760,17 +4760,17 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>0000007283</t>
+          <t>0000065483</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1240744717</t>
+          <t>1288258715</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>240903093</t>
+          <t>288417099</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -4807,12 +4807,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Zielony Zefir Spółka Akcyjna</t>
+          <t>Amber Urody spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ul. Krupówki 33/89, 34-500 Zakopane</t>
+          <t>ul. Wybickiego 153/59, 86-300 Grudziądz</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4822,17 +4822,17 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>0000007380</t>
+          <t>0000065580</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1240823902</t>
+          <t>1288337900</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>240982282</t>
+          <t>288496288</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -4869,12 +4869,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Zielony Żubr sp. z o.o.</t>
+          <t>Amber Turystyka Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>50, 34-600 Mordarka</t>
+          <t>ul Czarnieckiego 170, 14-100 Ostróda</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -4884,17 +4884,17 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>0000007477</t>
+          <t>0000065677</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>1240903096</t>
+          <t>1288417094</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>241061472</t>
+          <t>288575473</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -4931,12 +4931,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Zielony Sokół sp z oo</t>
+          <t>Amber Rozrywka S.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ulica Galicyjska 67, 32-087 Zielonki</t>
+          <t>ulica Warszawska 7, 11-500 Giżycko</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4946,22 +4946,22 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>0000007574</t>
+          <t>0000065774</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>1240982285</t>
+          <t>1288496283</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>241140668</t>
+          <t>288654669</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2023-07-09</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4993,12 +4993,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Zielony Orzeł sp. z o. o.</t>
+          <t>Amber Gastronomia SA</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>84, 32-003 Podłęże</t>
+          <t>24, 24-100 Puławy</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5008,17 +5008,17 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0000007671</t>
+          <t>0000065871</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>1241061475</t>
+          <t>1288575479</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>241219855</t>
+          <t>288733854</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -5055,12 +5055,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>mBank</t>
+          <t>Instagram - Meta</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ul. Wałowa 101/51, 33-100 Tarnów</t>
+          <t>ul. Staszica 41/21, 22-400 Zamość</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5070,17 +5070,17 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>0000007768</t>
+          <t>0000065968</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>1241140660</t>
+          <t>1288654664</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>241299044</t>
+          <t>298813077</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -5117,12 +5117,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Zielony Barycz SP Z O O</t>
+          <t>Amber Tekstylia Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ul Narutowicza 118, 90-135 Łódź</t>
+          <t>ul 3 Maja 58, 16-300 Augustów</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5132,17 +5132,17 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>0000007865</t>
+          <t>0000066065</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>1241219858</t>
+          <t>1298733885</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>251378267</t>
+          <t>288892239</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -5179,12 +5179,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Zielony Noteć spółka z ograniczoną odpowiedzialnością</t>
+          <t>Amber Motoryzacja sp. z o.o.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ulica os. Retkinia 135, 94-004 Łódź</t>
+          <t>ulica Kościuszki 75, 16-400 Suwałki</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5194,17 +5194,17 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>0000007962</t>
+          <t/>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>1241299047</t>
+          <t>1288813045</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>241457425</t>
+          <t>288971424</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t/>
+          <t>Małgorzata</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -5241,7 +5241,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Zielony Pilica Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Amber Ubezpieczenia sp z oo</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5256,22 +5256,22 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>0000008059</t>
+          <t>0000066259</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>1241378232</t>
+          <t>1288892234</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>241536610</t>
+          <t>289050614</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2017-08-11</t>
+          <t>2017-11-08</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5303,12 +5303,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Zielony Narew S.A.</t>
+          <t>Amber Spawalnictwo sp. z o. o.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ul. Długa 169/13, 95-100 Zgierz</t>
+          <t>ul. Długa 109/73, 49-300 Brzeg</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5318,17 +5318,17 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>0000008156</t>
+          <t>0000066356</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>1241457428</t>
+          <t>1298971455</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>241615806</t>
+          <t>289129801</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5365,12 +5365,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Zielony Jodełka SA</t>
+          <t>Amber Ślusarstwo Sp. z o.o.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>ul Rynek 6, 50-101 Wrocław</t>
+          <t>ul Rynek 126, 68-200 Żary</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5380,17 +5380,17 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>0000008253</t>
+          <t>0000066453</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>1241536613</t>
+          <t>1299050645</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>241694993</t>
+          <t>289208995</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -5427,12 +5427,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Zielony Kaktus S. A.</t>
+          <t>Amber Krawiectwo SP Z O O</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>ulica Jedności Narodowej 23, 50-260 Wrocław</t>
+          <t>143, 66-200 Świebodzin</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5442,17 +5442,17 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>0000008350</t>
+          <t>0000066550</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>1241615809</t>
+          <t>1289129807</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>241774189</t>
+          <t>289288184</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -5489,12 +5489,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Zielony Szmaragd Spółka Akcyjna</t>
+          <t>Amber Ochrona spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>os. Konstytucji 3 Maja 40, 58-540 Karpacz</t>
+          <t>Armii Krajowej 160, 78-100 Kołobrzeg</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5504,17 +5504,17 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>0000008447</t>
+          <t>0000066647</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>1241694996</t>
+          <t>1289208990</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>241853374</t>
+          <t>299367409</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -5551,12 +5551,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Zielony Topaz sp. z o.o.</t>
+          <t>Amber Catering Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ul. Odrodzenia 57/65, 59-300 Lubin</t>
+          <t>ul. Piłsudskiego 177/35, 73-110 Stargard</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5566,7 +5566,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>0000008544</t>
+          <t>0000066744</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>251932597</t>
+          <t>289446565</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5613,12 +5613,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Zielony Granit sp z oo</t>
+          <t>Amber Księgowość S.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ul Słowackiego 74, 58-300 Wałbrzych</t>
+          <t>ul Mickiewicza 14, 27-600 Sandomierz</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -5628,17 +5628,17 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>0000008641</t>
+          <t>0000066841</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>1241853377</t>
+          <t>1289367375</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>252011787</t>
+          <t>289525750</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -5675,12 +5675,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Zielony Marmur sp. z o. o.</t>
+          <t>Bizon Budownictwo SA</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ulica Półwiejska 91, 61-888 Poznań</t>
+          <t>ulica Sienkiewicza 31, 27-400 Ostrowiec Świętokrzyski</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -5690,17 +5690,17 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>0000008738</t>
+          <t>0000066938</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>1241932562</t>
+          <t>1289446560</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>242090949</t>
+          <t>289604946</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -5737,12 +5737,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Zielony Syrena Sp. z o.o.</t>
+          <t>Bizon Transport S. A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>os. Bolesława Chrobrego 108, 60-681 Poznań</t>
+          <t>Chmielna 48, 00-020 Warszawa</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -5752,17 +5752,17 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>0000008835</t>
+          <t>0000067035</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>1242011752</t>
+          <t>1289525756</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>242170134</t>
+          <t>289684135</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -5799,12 +5799,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Zielony Zodiak SP Z O O</t>
+          <t>Bizon Spedycja Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ul. Główny Rynek 125/27, 62-800 Kalisz</t>
+          <t>ul. Nowy Świat 65/87, 00-029 Warszawa</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -5814,17 +5814,17 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0000008932</t>
+          <t>0000067132</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>1242090941</t>
+          <t>1289604941</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>242249321</t>
+          <t>289763320</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -5861,12 +5861,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Zielony Olimp spółka z ograniczoną odpowiedzialnością</t>
+          <t>Bizon Logistyka sp. z o.o.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ul Kaliska 142, 63-400 Ostrów Wielkopolski</t>
+          <t>ul os. Przyjaźń 82, 01-355 Warszawa</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -5876,17 +5876,17 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>0000009029</t>
+          <t>0000067229</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>1242170137</t>
+          <t>1289684130</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>242328517</t>
+          <t>289842516</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -5923,12 +5923,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Zielony Zorza Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Bizon Handel sp z oo</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ulica Ogarna 159, 80-826 Gdańsk</t>
+          <t>ulica Jagiellońska 99, 05-120 Legionowo</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -5938,17 +5938,17 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>0000009126</t>
+          <t>0000067326</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>1242249324</t>
+          <t>1289763326</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>242407702</t>
+          <t>289921701</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -5985,12 +5985,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Zielony Krokus S.A.</t>
+          <t>Bizon Usługi sp. z o. o.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>os. Jasień 176, 80-180 Gdańsk</t>
+          <t>Piłsudskiego 116, 05-270 Marki</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6000,17 +6000,17 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>0000009223</t>
+          <t>0000067423</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>1252328545</t>
+          <t>1289842511</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>252486929</t>
+          <t>300000924</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -6047,12 +6047,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Zielony Narcyz SA</t>
+          <t>Bizon Finanse Sp. z o.o.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ul. Bohaterów Monte Cassino 13/79, 81-759 Sopot</t>
+          <t>os. Andriollego 133/49, 05-400 Otwock</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6062,17 +6062,17 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>0000009320</t>
+          <t>0000067520</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>1242407705</t>
+          <t>1289921707</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>242566085</t>
+          <t>290080089</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -6109,12 +6109,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Zielony Giewont S. A.</t>
+          <t>Bizon Doradztwo SP Z O O</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>30, 80-209 Chwaszczyno</t>
+          <t>ul Żeromskiego 150, 26-600 Radom</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6124,17 +6124,17 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>0000009417</t>
+          <t>0000067617</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>1242486892</t>
+          <t>1290000893</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>242645270</t>
+          <t>290159276</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -6171,12 +6171,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Zielony Rysy Spółka Akcyjna</t>
+          <t>Bizon Szkolenia spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ulica 3 Maja 47, 40-096 Katowice</t>
+          <t>ulica Tumska 167, 09-402 Płock</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6186,17 +6186,17 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>0000009514</t>
+          <t>0000067714</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>1242566088</t>
+          <t>1290080082</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>242724466</t>
+          <t>290238461</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -6233,12 +6233,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Zielony Kasprowy sp. z o.o.</t>
+          <t>Bizon Media Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>os. Paderewskiego 64, 40-282 Katowice</t>
+          <t>Karmelicka 4, 31-128 Kraków</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6248,17 +6248,17 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>0000009611</t>
+          <t>0000067811</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>1242645273</t>
+          <t>1300159308</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>242803651</t>
+          <t>290317657</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -6295,12 +6295,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>PPHU Zielony Beskid</t>
+          <t>P.P.H.U. Bizon Reklama</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ul. Zwycięstwa 81/41, 44-100 Gliwice</t>
+          <t>ul. os. Na Stoku 21/11, 31-704 Kraków</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6310,17 +6310,17 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>0000009708</t>
+          <t>0000067908</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>1242724469</t>
+          <t>1290238465</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>242882840</t>
+          <t>290396846</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -6357,7 +6357,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Zielony Bieszczady sp. z o. o.</t>
+          <t>Bizon Marketing SA</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6372,17 +6372,17 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>0000009805</t>
+          <t>0000068005</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>1242803654</t>
+          <t>1290317650</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>242962036</t>
+          <t>290476031</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -6419,12 +6419,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Zielony Karpaty Sp. z o.o.</t>
+          <t>Bizon Druk S. A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>ulica Najświętszej Maryi Panny 115, 42-200 Częstochowa</t>
+          <t>55, 34-600 Mordarka</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6434,17 +6434,17 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>0000009902</t>
+          <t>0000068102</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>1242882843</t>
+          <t>1300396876</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>243041226</t>
+          <t>290555227</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>70042873944</t>
+          <t>72042895946</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -6474,19 +6474,19 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>Włodarczyk</t>
+          <t>Nowicka</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Zielony Bałtyk SP Z O O</t>
+          <t>Bizon Informatyka Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>11 Listopada 132, 43-300 Bielsko-Biała</t>
+          <t>Galicyjska 72, 32-087 Zielonki</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6496,22 +6496,22 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>0000009999</t>
+          <t>0000068199</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>1242962039</t>
+          <t>1290476035</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>243120411</t>
+          <t>290634412</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6521,7 +6521,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>71050775338</t>
+          <t>73050797330</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -6536,19 +6536,19 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>Borkowski</t>
+          <t>Sokołowski</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Zielony Sudety spółka z ograniczoną odpowiedzialnością</t>
+          <t>Bizon Oprogramowanie sp. z o.o.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>149/3, 36-047 Niechobrz</t>
+          <t>89/63, 32-003 Podłęże</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6558,17 +6558,17 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>0000010096</t>
+          <t>0000068296</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>1243041229</t>
+          <t>1290555220</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>243199602</t>
+          <t>290713608</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>72061476687</t>
+          <t>74061498689</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -6598,19 +6598,19 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>Sawicka</t>
+          <t>Wróbel</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Niebieski Amber Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Bizon Rolnictwo sp z oo</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>ul Franciszkańska 166, 37-700 Przemyśl</t>
+          <t>ul Wałowa 106, 33-100 Tarnów</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6620,17 +6620,17 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>0000010193</t>
+          <t>0000068393</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>1243120414</t>
+          <t>1290634416</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>243278796</t>
+          <t>290792795</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -6645,7 +6645,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>73072178074</t>
+          <t>75072100079</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -6660,19 +6660,19 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>Dudek</t>
+          <t>Majewski</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Niebieski Bizon S.A.</t>
+          <t>Bizon Ogrodnictwo sp. z o. o.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>ulica Kościuszki 3, 38-500 Sanok</t>
+          <t>ulica Narutowicza 123, 90-135 Łódź</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -6682,17 +6682,17 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>0000010290</t>
+          <t>0000068490</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>1243199605</t>
+          <t>1290713601</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>243357981</t>
+          <t>290871980</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>74082879423</t>
+          <t>76082801428</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -6722,19 +6722,19 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>Adamczyk</t>
+          <t>Olszewska</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Niebieski Canyon SA</t>
+          <t>Bizon Produkcja Sp. z o.o.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Suraska 20, 15-422 Białystok</t>
+          <t>os. Retkinia 140, 94-004 Łódź</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -6744,17 +6744,17 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>0000010387</t>
+          <t>0000068587</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>1243278799</t>
+          <t>1290792799</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>243437177</t>
+          <t>290951176</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>75090780819</t>
+          <t>77090702811</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Józfe</t>
+          <t>Jóezf</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -6784,19 +6784,19 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>Pawłowski</t>
+          <t>Jaworski</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Niebieski Delfin S. A.</t>
+          <t>Bizon Przemysł SP Z O O</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>37/55, 16-030 Ogrodniczki</t>
+          <t>ul. Zamkowa 157/25, 95-200 Pabianice</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -6806,17 +6806,17 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>0000010484</t>
+          <t>0000068684</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>1243357984</t>
+          <t>1290871984</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>243516362</t>
+          <t>291030366</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>76101482162</t>
+          <t>78101404164</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -6846,19 +6846,19 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>Nowicka</t>
+          <t>Malinowska</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Niebieski Echo Spółka Akcyjna</t>
+          <t>Bizon Ekologia spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>ul 3 Maja 54, 17-200 Hajnówka</t>
+          <t>ul Długa 174, 95-100 Zgierz</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -6868,17 +6868,17 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>0000010581</t>
+          <t>0000068781</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>1253437207</t>
+          <t>1300951208</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>243595551</t>
+          <t>291109553</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>77112183558</t>
+          <t>79112105550</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -6908,19 +6908,19 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>Sokołowski</t>
+          <t>Pająk</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Niebieski Falcon sp. z o.o.</t>
+          <t>Bizon Energetyka Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>ulica os. LSM 71, 20-400 Lublin</t>
+          <t>ulica Rynek 11, 50-101 Wrocław</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -6930,17 +6930,17 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>0000010678</t>
+          <t>0000068878</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>1243516365</t>
+          <t>1301030396</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>243674747</t>
+          <t>291188742</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -6955,7 +6955,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>78122884907</t>
+          <t>80122806908</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -6970,19 +6970,19 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>Wróbel</t>
+          <t>Szczepańska</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Niebieski Gryf sp z oo</t>
+          <t>Bizon Instalacje S.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>88, 24-120 Mięćmierz</t>
+          <t>Jedności Narodowej 28, 50-260 Wrocław</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -6992,17 +6992,17 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>0000010775</t>
+          <t>0000068975</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>1243595554</t>
+          <t>1291109557</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>243753932</t>
+          <t>291267938</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -7017,7 +7017,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>79010786297</t>
+          <t>81010708298</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -7032,19 +7032,19 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>Majewski</t>
+          <t>Czerwiński</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Niebieski Horyzont sp. z o. o.</t>
+          <t>Bizon Nieruchomości SA</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>ul. Brzeska 105/17, 21-500 Biała Podlaska</t>
+          <t>ul. Konstytucji 3 Maja 45/77, 58-540 Karpacz</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7054,17 +7054,17 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>0000010872</t>
+          <t>0000069072</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>1253674775</t>
+          <t>1291188746</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>243833128</t>
+          <t>291347123</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -7079,7 +7079,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>80021487644</t>
+          <t>82021409646</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -7094,19 +7094,19 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>Olszewska-Błaszczyk</t>
+          <t>Kubiak-Laskowska</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Niebieski Ikar Sp. z o.o.</t>
+          <t>Bizon Inwestycje S. A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>ul Rynek Staromiejski 122, 87-100 Toruń</t>
+          <t>ul Odrodzenia 62, 59-300 Lubin</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7116,22 +7116,22 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>0000010969</t>
+          <t/>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>1243753935</t>
+          <t>1291267931</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>243912313</t>
+          <t>291426319</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2024-01-06</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>81032189031</t>
+          <t>83032111036</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -7156,19 +7156,19 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>Jaworski</t>
+          <t>Wilk</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Niebieski Jantar SP Z O O</t>
+          <t>Bizon Medycyna Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>ulica Mostowa 139, 85-110 Bydgoszcz</t>
+          <t>ulica Słowackiego 79, 58-300 Wałbrzych</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7178,19 +7178,19 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
+          <t>0000069266</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>1291347127</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>1243833120</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="G116" t="inlineStr">
         <is>
           <t>20210207</t>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>82042890384</t>
+          <t>84042812386</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -7218,19 +7218,19 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>Malinowska</t>
+          <t>Wysocka</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Niebieski Koral spółka z ograniczoną odpowiedzialnością</t>
+          <t>Bizon Zdrowie sp. z o.o.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Stare Miasto 156, 10-026 Olsztyn</t>
+          <t>Półwiejska 96, 61-888 Poznań</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7240,17 +7240,17 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>0000011163</t>
+          <t>0000069363</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>1243912316</t>
+          <t>1291426312</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>244070690</t>
+          <t>291584691</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -7265,7 +7265,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>83050791777</t>
+          <t>85050713779</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -7280,19 +7280,19 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>Pająk</t>
+          <t>Chmielewski</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Niebieski Lotos Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Bizon Urody sp z oo</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>os. Warszawska 173/69, 11-700 Mrągowo</t>
+          <t>ul. os. Bolesława Chrobrego 113/39, 60-681 Poznań</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7302,17 +7302,17 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>0000011260</t>
+          <t>0000069460</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>1243991505</t>
+          <t>1291505508</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>244149888</t>
+          <t>291663887</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -7327,7 +7327,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>84061493126</t>
+          <t>86061415128</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -7342,19 +7342,19 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>Szczepańska</t>
+          <t>Urbańska</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Niebieski Magnolia S.A.</t>
+          <t>Bizon Turystyka sp. z o. o.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>ul Wojska Polskiego 10, 70-470 Szczecin</t>
+          <t>ul Główny Rynek 130, 62-800 Kalisz</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7364,17 +7364,17 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>0000011357</t>
+          <t>0000069557</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>1244070693</t>
+          <t>1291584695</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>244229073</t>
+          <t>291743072</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -7389,7 +7389,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>85072194512</t>
+          <t>87072116514</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -7404,14 +7404,14 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>Czerwiński</t>
+          <t>Błaszczyk</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Niebieski Neon SA</t>
+          <t>Bizon Rozrywka Sp. z o.o.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7426,22 +7426,22 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>0000011454</t>
+          <t>0000069654</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>1244149880</t>
+          <t>1291663880</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>244308269</t>
+          <t>291822268</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2023-07-04</t>
+          <t>2023-04-07</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>86082895862</t>
+          <t>88082817864</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -7466,14 +7466,14 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>Kubiak</t>
+          <t>Szulc</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Niebieski Oaza S. A.</t>
+          <t>Bizon Gastronomia SP Z O O</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7488,17 +7488,17 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>0000011551</t>
+          <t>0000069751</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>1244229076</t>
+          <t>1291743076</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>244387458</t>
+          <t>291901453</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -7513,7 +7513,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>87090797256</t>
+          <t>89090719258</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -7528,19 +7528,19 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>Wilk</t>
+          <t>Kozak</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>X - Twitter</t>
+          <t>mBank</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>ul. Byczyńska 61/31, 46-200 Kluczbork</t>
+          <t>ul. os. Jasień 1/1, 80-180 Gdańsk</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7550,17 +7550,17 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>0000011648</t>
+          <t>0000069848</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>1244308261</t>
+          <t>1291822261</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>244466643</t>
+          <t>291980642</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>88101498607</t>
+          <t>90101420601</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -7590,19 +7590,19 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>Wysocka</t>
+          <t>Cieślak</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Niebieski Rubin sp. z o.o.</t>
+          <t>Bizon Tekstylia Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>ul Chrobrego 78, 66-400 Gorzów Wielkopolski</t>
+          <t>ul Bohaterów Monte Cassino 18, 81-759 Sopot</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7612,17 +7612,17 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>0000011745</t>
+          <t>0000069945</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>1244387450</t>
+          <t>1291901457</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>244545839</t>
+          <t>292059834</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -7637,7 +7637,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>89112199994</t>
+          <t>91112121998</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -7652,19 +7652,19 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>Chmielewski</t>
+          <t>Andrzejewski</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Niebieski Szafir sp z oo</t>
+          <t>Bizon Motoryzacja S.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>ulica 30 Stycznia 95, 66-300 Międzyrzecz</t>
+          <t>35, 80-209 Chwaszczyno</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -7674,17 +7674,17 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>0000011842</t>
+          <t>0000070042</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>1244466646</t>
+          <t>1291980646</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>244625024</t>
+          <t>302139052</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -7699,7 +7699,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>90122801346</t>
+          <t>92122823348</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -7714,19 +7714,19 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>Urbańska</t>
+          <t>Gajewska</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Niebieski Tytan sp. z o. o.</t>
+          <t>Bizon Ubezpieczenia SA</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Paderewskiego 112, 25-004 Kielce</t>
+          <t>3 Maja 52, 40-096 Katowice</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -7736,22 +7736,22 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>0000011939</t>
+          <t>0000070139</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>1244545831</t>
+          <t>1292059838</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>254704247</t>
+          <t>292218215</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2018-06-10</t>
+          <t>2018-10-06</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -7761,7 +7761,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>91010702734</t>
+          <t>93010724736</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -7776,19 +7776,19 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>Błaszczyk</t>
+          <t>Laskowski</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Niebieski Uran Sp. z o.o.</t>
+          <t>Bizon Spawalnictwo S. A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>ul. 1 Maja 129/83, 28-100 Busko-Zdrój</t>
+          <t>ul. os. Paderewskiego 69/53, 40-282 Katowice</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -7798,17 +7798,17 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>0000012036</t>
+          <t>0000070236</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>1244625027</t>
+          <t>1292139023</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>244783409</t>
+          <t>292297404</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -7823,7 +7823,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>92021404084</t>
+          <t>94021426086</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -7838,19 +7838,19 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>Szulc</t>
+          <t>Mazurek</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Niebieski Wektor SP Z O O</t>
+          <t>Bizon Ślusarstwo Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>ul Marszałkowska 146, 00-590 Warszawa</t>
+          <t>os. Zwycięstwa 86, 44-100 Gliwice</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -7860,17 +7860,17 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>0000012133</t>
+          <t>0000070333</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>1244704212</t>
+          <t>1292218219</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>244862592</t>
+          <t>292376598</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -7885,7 +7885,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>93032105470</t>
+          <t>95032127472</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -7900,19 +7900,19 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>Kozak</t>
+          <t>Sobczak</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Niebieski Zefir spółka z ograniczoną odpowiedzialnością</t>
+          <t>Bizon Krawiectwo sp. z o.o.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>ulica Krakowskie Przedmieście 163, 00-071 Warszawa</t>
+          <t>ulica Bocheńskiego 103, 43-100 Tychy</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -7922,17 +7922,17 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>0000012230</t>
+          <t>0000070430</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>1244783401</t>
+          <t>1292297408</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>244941788</t>
+          <t>292455783</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -7947,7 +7947,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>94042806829</t>
+          <t>96042828821</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -7962,19 +7962,19 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>Cieślak</t>
+          <t>Konieczna</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Niebieski Żubr Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Bizon Ochrona sp z oo</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Floriańska 180, 31-019 Kraków</t>
+          <t>Najświętszej Maryi Panny 120, 42-200 Częstochowa</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -7984,17 +7984,17 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>0000012327</t>
+          <t>0000070527</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>1244862595</t>
+          <t>1292376591</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>245020978</t>
+          <t>292534979</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -8009,7 +8009,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>95050708213</t>
+          <t>97050730218</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -8024,19 +8024,19 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>Andrzejewski</t>
+          <t>Brzeziński</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Niebieski Sokół S.A.</t>
+          <t>Bizon Catering sp. z o. o.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>ul. Długa 17/45, 31-147 Kraków</t>
+          <t>ul. 11 Listopada 137/15, 43-300 Bielsko-Biała</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8046,22 +8046,22 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>0000012424</t>
+          <t>0000070624</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>1244941780</t>
+          <t>1292455787</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>245100163</t>
+          <t>292614164</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2018-03-04</t>
+          <t>2018-04-03</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>96061409562</t>
+          <t>98061431567</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -8086,19 +8086,19 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>Gajewska</t>
+          <t>Makowska</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Niebieski Orzeł SA</t>
+          <t>Bizon Księgowość Sp. z o.o.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>ul Piotrkowska 34, 90-102 Łódź</t>
+          <t>154, 36-047 Niechobrz</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8108,17 +8108,17 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>0000012521</t>
+          <t>0000070721</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>1245020970</t>
+          <t>1292534972</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>245179354</t>
+          <t>292693353</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -8133,7 +8133,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>97072110951</t>
+          <t>99072132953</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -8148,19 +8148,19 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>Laskowski</t>
+          <t>Wrona</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Niebieski Kormoran S. A.</t>
+          <t>Canyon Budownictwo SP Z O O</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>ulica Zachodnia 51, 90-402 Łódź</t>
+          <t>ulica Franciszkańska 171, 37-700 Przemyśl</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8170,17 +8170,17 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>0000012618</t>
+          <t>0000070818</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>1245100166</t>
+          <t>1292614168</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>255258577</t>
+          <t>292772549</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -8195,7 +8195,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>98082812301</t>
+          <t>00282834308</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -8210,19 +8210,19 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>Mazurek</t>
+          <t>Bąk</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Niebieski Barycz Spółka Akcyjna</t>
+          <t>Canyon Transport spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Świdnicka 68, 50-066 Wrocław</t>
+          <t>Kościuszki 8, 38-500 Sanok</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8232,17 +8232,17 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>0000012715</t>
+          <t>0000070915</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>1245179357</t>
+          <t>1292693357</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>245337735</t>
+          <t>292851734</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -8257,7 +8257,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>99090713695</t>
+          <t>01290735692</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -8272,19 +8272,19 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>Sobczak</t>
+          <t>Kucharski</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Niebieski Noteć sp. z o.o.</t>
+          <t>Canyon Spedycja Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>ul. Legnicka 85/7, 54-203 Wrocław</t>
+          <t>ul. Suraska 25/67, 15-422 Białystok</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -8294,17 +8294,17 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>0000012812</t>
+          <t>0000071012</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>1245258542</t>
+          <t>1292772542</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>245416920</t>
+          <t>302930952</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -8319,7 +8319,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>00301415042</t>
+          <t>02301437044</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -8334,19 +8334,19 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>Konieczna</t>
+          <t>Lisowska</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Niebieski Pilica sp z oo</t>
+          <t>Canyon Logistyka S.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>ul Święty Marcin 102, 61-806 Poznań</t>
+          <t>42, 16-030 Ogrodniczki</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8356,22 +8356,22 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>0000012909</t>
+          <t>0000071109</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>1245337738</t>
+          <t>1292851738</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>255496147</t>
+          <t>303010142</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2017-01-03</t>
+          <t>2017-03-01</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8381,7 +8381,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>01312116438</t>
+          <t>03312138430</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -8396,19 +8396,19 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>Brzeziński</t>
+          <t>Słowik</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Niebieski Narew sp. z o. o.</t>
+          <t>Canyon Handel SA</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>ulica Głogowska 119, 60-734 Poznań</t>
+          <t>ulica 3 Maja 59, 17-200 Hajnówka</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -8418,17 +8418,17 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>0000013006</t>
+          <t>0000071206</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>1245416923</t>
+          <t>1292930923</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>245575305</t>
+          <t>293089300</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -8443,7 +8443,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>02322817788</t>
+          <t>04322839780</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -8458,19 +8458,19 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>Makowska</t>
+          <t>Kopeć</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Niebieski Jodełka Sp. z o.o.</t>
+          <t>Canyon Usługi S. A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Długa 136, 80-831 Gdańsk</t>
+          <t>os. LSM 76, 20-400 Lublin</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -8480,17 +8480,17 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>0000013103</t>
+          <t>0000071303</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>1245496112</t>
+          <t>1293010113</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>245654499</t>
+          <t>293168494</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -8505,7 +8505,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>03210719177</t>
+          <t>05210741172</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -8520,19 +8520,19 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>Wrona</t>
+          <t>Czajka</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Niebieski Kaktus SP Z O O</t>
+          <t>Canyon Finanse Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>ul. Grunwaldzka 153/59, 80-236 Gdańsk</t>
+          <t>93/29, 24-120 Mięćmierz</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -8542,17 +8542,17 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>0000013200</t>
+          <t>0000071400</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>1245575308</t>
+          <t>1293089304</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>245733684</t>
+          <t>303247714</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -8567,7 +8567,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>04221420528</t>
+          <t>60021442526</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -8582,14 +8582,14 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>Bąk</t>
+          <t>Matusiak</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Niebieski Szmaragd spółka z ograniczoną odpowiedzialnością</t>
+          <t>Canyon Doradztwo sp. z o.o.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8604,17 +8604,17 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>0000013297</t>
+          <t>0000071497</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>1245654491</t>
+          <t>1293168498</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>255812909</t>
+          <t>293326875</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -8629,7 +8629,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>05232121914</t>
+          <t>61032143912</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -8644,19 +8644,19 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>Kucharski</t>
+          <t>Gajda</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Niebieski Topaz Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Canyon Szkolenia sp z oo</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>ulica Wyszyńskiego 7, 70-200 Szczecin</t>
+          <t>ulica Rynek Staromiejski 127, 87-100 Toruń</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -8666,17 +8666,17 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>0000013394</t>
+          <t>0000071594</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>1245733687</t>
+          <t>1293247683</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>245892069</t>
+          <t>293406060</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -8691,7 +8691,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>60042823261</t>
+          <t>62042845263</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -8706,19 +8706,19 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>Lisowska</t>
+          <t>Klimek</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Niebieski Granit S.A.</t>
+          <t>Canyon Media sp. z o. o.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Mariacka 24, 40-014 Katowice</t>
+          <t>Mostowa 144, 85-110 Bydgoszcz</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -8728,17 +8728,17 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>0000013491</t>
+          <t>0000071691</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>1245812872</t>
+          <t>1293326879</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>245971254</t>
+          <t>303485282</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -8753,7 +8753,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>61050724654</t>
+          <t>63050746656</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -8768,19 +8768,19 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>Słowik</t>
+          <t>Madej</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>P.P.H.U. Niebieski Marmur</t>
+          <t>PPHU Canyon Reklama</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>ul. Warszawska 41/21, 40-009 Katowice</t>
+          <t>ul. Stare Miasto 161/81, 10-026 Olsztyn</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -8790,17 +8790,17 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>0000013588</t>
+          <t>0000071788</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>1245892061</t>
+          <t>1293406064</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>246050444</t>
+          <t>293564445</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -8815,7 +8815,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>62061426003</t>
+          <t>64061448005</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -8830,19 +8830,19 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>Kopeć</t>
+          <t>Krupa</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Niebieski Syrena S. A.</t>
+          <t>Canyon Marketing SP Z O O</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>ul Krakowskie Przedmieście 58, 20-002 Lublin</t>
+          <t>ul Warszawska 178, 11-700 Mrągowo</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -8852,17 +8852,17 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>0000013685</t>
+          <t>0000071885</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>1245971257</t>
+          <t>1293485253</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>246129631</t>
+          <t>293643630</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -8877,7 +8877,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>63072127390</t>
+          <t>65072149392</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -8892,19 +8892,19 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>Czajka</t>
+          <t>Kaczmarczyk</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Niebieski Zodiak Spółka Akcyjna</t>
+          <t>Canyon Druk spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>ulica Narutowicza 75, 20-004 Lublin</t>
+          <t>ulica Wojska Polskiego 15, 70-470 Szczecin</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -8914,17 +8914,17 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>0000013782</t>
+          <t>0000071982</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>1246050447</t>
+          <t>1293564449</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>246208827</t>
+          <t>293722826</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -8939,7 +8939,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>64082828749</t>
+          <t>66082850744</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -8954,19 +8954,19 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>Matusiak</t>
+          <t>Wrona</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Niebieski Olimp sp. z o.o.</t>
+          <t>Canyon Informatyka Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Lipowa 92, 15-424 Białystok</t>
+          <t>Monte Cassino 32, 72-600 Świnoujście</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -8976,17 +8976,17 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>0000013879</t>
+          <t>0000072079</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>1246129634</t>
+          <t>1293643634</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>246288016</t>
+          <t>293802011</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>65090730136</t>
+          <t>67090752138</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -9016,19 +9016,19 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>Gajda</t>
+          <t>Wasilewski</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Niebieski Zorza sp z oo</t>
+          <t>Canyon Oprogramowanie S.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>ul. Sienkiewicza 109/73, 15-092 Białystok</t>
+          <t>ul. Rynek 49/43, 45-015 Opole</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -9038,17 +9038,17 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>0000013976</t>
+          <t>0000072176</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>1256208855</t>
+          <t>1303722856</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>246367201</t>
+          <t>293881200</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -9063,7 +9063,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>66101431488</t>
+          <t>68101453480</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -9078,19 +9078,19 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>Klimek</t>
+          <t>Kalinowska</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Niebieski Krokus sp. z o. o.</t>
+          <t>Canyon Rolnictwo SA</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>os. Gdańska 126, 85-005 Bydgoszcz</t>
+          <t>ul Byczyńska 66, 46-200 Kluczbork</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -9100,17 +9100,17 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>0000014073</t>
+          <t>0000072273</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>1246288019</t>
+          <t>1293802015</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>246446395</t>
+          <t>293960394</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -9125,7 +9125,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>67112132874</t>
+          <t>69112154876</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -9140,19 +9140,19 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>Madej</t>
+          <t>Zarychta</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Niebieski Narcyz Sp. z o.o.</t>
+          <t>Canyon Ogrodnictwo S. A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>ulica Dworcowa 143, 85-009 Bydgoszcz</t>
+          <t>ulica Chrobrego 83, 66-400 Gorzów Wielkopolski</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -9162,17 +9162,17 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>0000014170</t>
+          <t>0000072370</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>1246367204</t>
+          <t>1293881204</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>246525580</t>
+          <t>294039586</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -9187,7 +9187,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>68122834224</t>
+          <t>70122856225</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -9202,19 +9202,19 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>Krupa</t>
+          <t>Przybylska</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Niebieski Giewont SP Z O O</t>
+          <t>Canyon Produkcja Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Szeroka 160, 87-100 Toruń</t>
+          <t>30 Stycznia 100, 66-300 Międzyrzecz</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -9224,17 +9224,17 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>0000014267</t>
+          <t>0000072467</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>1246446398</t>
+          <t>1293960398</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>246604776</t>
+          <t>294118771</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -9249,7 +9249,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>69010735612</t>
+          <t>71010757613</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -9264,19 +9264,19 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>Kaczmarczyk</t>
+          <t>Michalak</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Niebieski Rysy spółka z ograniczoną odpowiedzialnością</t>
+          <t>Canyon Przemysł sp. z o.o.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>ul. Chełmińska 177/35, 87-100 Toruń</t>
+          <t>ul. Paderewskiego 117/5, 25-004 Kielce</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -9286,17 +9286,17 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>0000014364</t>
+          <t>0000072564</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>1246525583</t>
+          <t>1304039618</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>246683965</t>
+          <t>294197960</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -9311,7 +9311,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>70021436960</t>
+          <t>72021458962</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -9326,19 +9326,19 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>Wrona</t>
+          <t>Szatkowska</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Niebieski Kasprowy Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Canyon Ekologia sp z oo</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>ul 3 Maja 14, 35-030 Rzeszów</t>
+          <t>ul 1 Maja 134, 28-100 Busko-Zdrój</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -9348,17 +9348,17 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>0000014461</t>
+          <t>0000072661</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>1246604779</t>
+          <t>1294118775</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>246763150</t>
+          <t>294277156</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -9373,7 +9373,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>71032138357</t>
+          <t>73032160352</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -9388,19 +9388,19 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>Wasilewski</t>
+          <t>Bednarek</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Amber Budownictwo S.A.</t>
+          <t>Canyon Energetyka sp. z o. o.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>ulica Piłsudskiego 31, 35-074 Rzeszów</t>
+          <t>ulica Marszałkowska 151, 00-590 Warszawa</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -9410,17 +9410,17 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>0000014558</t>
+          <t>0000072758</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>1246683968</t>
+          <t>1294197964</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>246842346</t>
+          <t>294356341</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -9435,7 +9435,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>72042839706</t>
+          <t>74042861701</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -9450,19 +9450,19 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>Kalinowska</t>
+          <t>Podgórska</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Amber Transport SA</t>
+          <t>Canyon Instalacje Sp. z o.o.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Sienkiewicza 48, 25-007 Kielce</t>
+          <t>Krakowskie Przedmieście 168, 00-071 Warszawa</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -9472,17 +9472,17 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>0000014655</t>
+          <t>0000072855</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>1246763153</t>
+          <t>1304277186</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>246921531</t>
+          <t>294435537</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -9497,7 +9497,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>73050741094</t>
+          <t>75050763096</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -9512,19 +9512,19 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>Zarychta</t>
+          <t>Śliwiński</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Amber Spedycja S. A.</t>
+          <t>Canyon Nieruchomości SP Z O O</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>ul. Warszawska 65/87, 25-512 Kielce</t>
+          <t>ul. Floriańska 5/57, 31-019 Kraków</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -9534,17 +9534,17 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>0000014752</t>
+          <t>0000072952</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>1246842349</t>
+          <t>1294356345</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>247000721</t>
+          <t>294514722</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -9559,7 +9559,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>74061442442</t>
+          <t>76061464444</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -9574,19 +9574,19 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>Przybylska-Kowalska</t>
+          <t>Czajkowska-Lewandowska</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Amber Logistyka Spółka Akcyjna</t>
+          <t>Canyon Inwestycje spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>ul Kościuszki 82, 10-504 Olsztyn</t>
+          <t>ul Długa 22, 31-147 Kraków</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -9596,17 +9596,17 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>0000014849</t>
+          <t>0000073049</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>1246921534</t>
+          <t>1294435530</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>247079912</t>
+          <t>294593911</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -9621,7 +9621,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>85072143838</t>
+          <t>87072165830</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -9636,19 +9636,19 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>Michalak</t>
+          <t>Biernat</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Amber Handel sp. z o.o.</t>
+          <t>Canyon Medycyna Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>ulica Dąbrowszczaków 99, 10-540 Olsztyn</t>
+          <t>os. Piotrkowska 39, 90-102 Łódź</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -9658,17 +9658,17 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>0000014946</t>
+          <t>0000073146</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>1247000724</t>
+          <t>1294514726</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>247159108</t>
+          <t>294673107</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -9683,7 +9683,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>76082845189</t>
+          <t>78082867181</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -9698,19 +9698,19 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>Szatkowska</t>
+          <t>Panek</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Amber Usługi sp z oo</t>
+          <t>Canyon Zdrowie S.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Krakowska 116, 45-018 Opole</t>
+          <t>Zachodnia 56, 90-402 Łódź</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -9720,17 +9720,17 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>0000015043</t>
+          <t>0000073243</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>1247079915</t>
+          <t>1294593915</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>247238291</t>
+          <t>294752290</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -9745,7 +9745,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>77090746572</t>
+          <t>79090768574</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -9760,19 +9760,19 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>Bednarek</t>
+          <t>Prus</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Amber Finanse sp. z o. o.</t>
+          <t>Canyon Urody SA</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>ul. Ozimska 133/49, 45-057 Opole</t>
+          <t>ul. Świdnicka 73/19, 50-066 Wrocław</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -9782,17 +9782,17 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>0000015140</t>
+          <t>0000073340</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>1247159100</t>
+          <t>1294673100</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>247317487</t>
+          <t>294831486</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -9807,7 +9807,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>78101447923</t>
+          <t>80101469924</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -9822,39 +9822,39 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>Podgórska</t>
+          <t>Janik</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Amber Doradztwo Sp. z o.o.</t>
+          <t>Canyon Turystyka S. A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>ul Bohaterów Westerplatte 150, 65-034 Zielona Góra</t>
+          <t>ul Legnicka 90, 54-203 Wrocław</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>zarzdąaznie portfelami</t>
+          <t>zarządaznie portfelami</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>0000015237</t>
+          <t>0000073437</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>1247238294</t>
+          <t>1294752294</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>247396676</t>
+          <t>294910671</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -9869,12 +9869,12 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>79112149310</t>
+          <t>81112171314</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>Franciszek</t>
+          <t>Fracniszek</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -9884,19 +9884,19 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>Śliwiński</t>
+          <t>Kowalski</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Amber Szkolenia SP Z O O</t>
+          <t>Canyon Rozrywka Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>ulica Kupiecka 167, 65-058 Zielona Góra</t>
+          <t>ulica Święty Marcin 107, 61-806 Poznań</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -9906,17 +9906,17 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>0000015334</t>
+          <t>0000073534</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>1257317517</t>
+          <t>1304831518</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>247475861</t>
+          <t>294989862</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -9931,7 +9931,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>80122850662</t>
+          <t>82122872664</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -9946,19 +9946,19 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>Czajkowska</t>
+          <t>Nowacka</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Amber Media spółka z ograniczoną odpowiedzialnością</t>
+          <t>Canyon Gastronomia sp. z o.o.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Świętojańska 4, 81-372 Gdynia</t>
+          <t>Głogowska 124, 60-734 Poznań</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -9968,17 +9968,17 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>0000015431</t>
+          <t>0000073631</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>1247396679</t>
+          <t>1294910675</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>247555057</t>
+          <t>295069052</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -9993,7 +9993,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>81010752051</t>
+          <t>83010774053</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -10008,19 +10008,19 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>Biernat</t>
+          <t>Wiśniewski</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Facebook - Meta</t>
+          <t>X - Twitter</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>ul. 10 Lutego 21/11, 81-364 Gdynia</t>
+          <t>ul. Długa 141/71, 80-831 Gdańsk</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -10030,17 +10030,17 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>0000015528</t>
+          <t>0000073728</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>1247475864</t>
+          <t>1294989866</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>247634242</t>
+          <t>295148248</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>82021453409</t>
+          <t>84021475401</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -10070,19 +10070,19 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>Panek</t>
+          <t>Wójcik</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Amber Marketing S.A.</t>
+          <t>Canyon Tekstylia sp. z o. o.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>ul Bolesława Prusa 38, 05-800 Pruszków</t>
+          <t>ul Grunwaldzka 158, 80-236 Gdańsk</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -10092,17 +10092,17 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>0000015625</t>
+          <t>0000073825</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>1257555085</t>
+          <t>1295069056</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>247713438</t>
+          <t>295227433</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -10117,7 +10117,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>83032154796</t>
+          <t>85032176798</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -10132,19 +10132,19 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>Prus</t>
+          <t>Kowalczyk</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Amber Druk SA</t>
+          <t>Canyon Motoryzacja Sp. z o.o.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>ulica Kościuszki 55, 05-500 Piaseczno</t>
+          <t>ulica Jagiellońska 175, 70-435 Szczecin</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -10154,17 +10154,17 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>0000015722</t>
+          <t>0000073922</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>1247634245</t>
+          <t>1295148241</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>247792627</t>
+          <t>295306629</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>84042856146</t>
+          <t>86042878148</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -10194,19 +10194,19 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>Janik</t>
+          <t>Kamińska</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Amber Informatyka S. A.</t>
+          <t>Canyon Ubezpieczenia SP Z O O</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Sienkiewicza 72, 32-020 Wieliczka</t>
+          <t>Wyszyńskiego 12, 70-200 Szczecin</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -10216,22 +10216,22 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>0000015819</t>
+          <t>0000074019</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>1247713430</t>
+          <t>1295227437</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>247871812</t>
+          <t>295385818</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2022-05-08</t>
+          <t>2022-08-05</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>85050757539</t>
+          <t>87050779531</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -10256,19 +10256,19 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>Kowalski</t>
+          <t>Lewandowski</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Amber Oprogramowanie Spółka Akcyjna</t>
+          <t>Canyon Spawalnictwo spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>ul. Dąbrowskiego 89/63, 32-600 Oświęcim</t>
+          <t>ul. Mariacka 29/33, 40-014 Katowice</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -10278,17 +10278,17 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>0000015916</t>
+          <t>0000074116</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>1257792655</t>
+          <t>1295306622</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>247951008</t>
+          <t>295465003</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -10303,7 +10303,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>86061458888</t>
+          <t>88061480883</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -10318,19 +10318,19 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>Nowacka</t>
+          <t>Zielińska</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Amber Rolnictwo sp. z o.o.</t>
+          <t>Canyon Ślusarstwo Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>ul Rynek 106, 38-400 Krosno</t>
+          <t>ul Warszawska 46, 40-009 Katowice</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -10340,17 +10340,17 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>0000016013</t>
+          <t>0000074213</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2247871815</t>
+          <t>2295385811</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>248030196</t>
+          <t>295544197</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -10365,7 +10365,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>87072160278</t>
+          <t>89072182270</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -10380,19 +10380,19 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>Wiśniewski</t>
+          <t>Szymański</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Amber Ogrodnictwo sp z oo</t>
+          <t>Canyon Krawiectwo S.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>ulica Mickiewicza 123, 39-300 Mielec</t>
+          <t>ulica Krakowskie Przedmieście 63, 20-002 Lublin</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -10402,17 +10402,17 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>0000016110</t>
+          <t>0000074310</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>1247951000</t>
+          <t>1295465007</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>248109383</t>
+          <t>295623382</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -10427,7 +10427,7 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>88082861627</t>
+          <t>90082883628</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -10442,19 +10442,19 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>Wójcik</t>
+          <t>Dąbrowska</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Amber Produkcja sp. z o. o.</t>
+          <t>Canyon Ochrona SA</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Długa 140, 58-100 Świdnica</t>
+          <t>Narutowicza 80, 20-004 Lublin</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -10464,17 +10464,17 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>0000016207</t>
+          <t>0000074407</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>1248030199</t>
+          <t>1295544190</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>248188572</t>
+          <t>295702578</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -10489,7 +10489,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>89090763011</t>
+          <t>91090785012</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -10504,19 +10504,19 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>Kowalczyk</t>
+          <t>Mazur</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Amber Przemysł Sp. z o.o.</t>
+          <t>Canyon Catering S. A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>157/25, 57-300 Kłodzko</t>
+          <t>ul. Lipowa 97/85, 15-424 Białystok</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -10526,17 +10526,17 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>0000016304</t>
+          <t>0000074504</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>1248109386</t>
+          <t>1295623386</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>248267768</t>
+          <t>295781767</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>90101464362</t>
+          <t>92101486364</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -10566,19 +10566,19 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>Kamińska</t>
+          <t>Krawczyk</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Amber Ekologia SP Z O O</t>
+          <t>Canyon Księgowość Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>ul Chrobrego 174, 62-200 Gniezno</t>
+          <t>ul Sienkiewicza 114, 15-092 Białystok</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -10588,17 +10588,17 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>0000016401</t>
+          <t>0000074601</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>1248188575</t>
+          <t>1295702571</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>248346953</t>
+          <t>295860952</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -10613,7 +10613,7 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>91112165758</t>
+          <t>93112187750</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -10628,19 +10628,19 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>Lewandowski</t>
+          <t>Woźniak</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Amber Energetyka spółka z ograniczoną odpowiedzialnością</t>
+          <t>Astra Group sp. z o.o.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>ulica Słowiańska 11, 64-100 Leszno</t>
+          <t>ulica Gdańska 131, 85-005 Bydgoszcz</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -10650,17 +10650,17 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>0000016498</t>
+          <t>0000074698</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>1248267760</t>
+          <t>1295781760</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>248426149</t>
+          <t>295940148</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>92122867108</t>
+          <t>94122889100</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -10690,19 +10690,19 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>Zielińska</t>
+          <t>Jankowska</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Amber Instalacje Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Astra Systems sp z oo</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Gdańska 28, 83-110 Tczew</t>
+          <t>Dworcowa 148, 85-009 Bydgoszcz</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -10712,17 +10712,17 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>0000016595</t>
+          <t>0000074795</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>1248346956</t>
+          <t>1295860956</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>248505334</t>
+          <t>306019362</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -10737,7 +10737,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>93010768497</t>
+          <t>95010790492</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -10752,19 +10752,19 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>Szymański</t>
+          <t>Grabowski</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Amber Nieruchomości S.A.</t>
+          <t>Astra Holding sp. z o. o.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>ul. Sobieskiego 45/77, 84-200 Wejherowo</t>
+          <t>ul. Szeroka 165/47, 87-100 Toruń</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -10774,17 +10774,17 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>0000016692</t>
+          <t>0000074892</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>1248426141</t>
+          <t>1295940141</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>248584523</t>
+          <t>296098529</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -10799,7 +10799,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>94021469845</t>
+          <t>96021491840</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -10814,19 +10814,19 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>Dąbrowska</t>
+          <t>Pawlak</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Amber Inwestycje SA</t>
+          <t>Astra Partners Sp. z o.o.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>ul Głęboka 62, 43-400 Cieszyn</t>
+          <t>ul Chełmińska 2, 87-100 Toruń</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -10836,17 +10836,17 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>0000016789</t>
+          <t>0000074989</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>1248505337</t>
+          <t>1296019333</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>248663719</t>
+          <t>296177714</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -10861,7 +10861,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>95032171235</t>
+          <t>97032193237</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -10876,19 +10876,19 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>Mazur</t>
+          <t>Michalski</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Amber Medycyna S. A.</t>
+          <t>Astra Polska SP Z O O</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>os. Małachowskiego 79, 42-500 Będzin</t>
+          <t>ulica 3 Maja 19, 35-030 Rzeszów</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -10898,17 +10898,17 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>0000016886</t>
+          <t>0000075086</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>1248584526</t>
+          <t>1296098522</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>248742904</t>
+          <t>306256932</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -10923,7 +10923,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>96042872585</t>
+          <t>98042894587</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -10938,19 +10938,19 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>Krawczyk</t>
+          <t>Król</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Amber Zdrowie Spółka Akcyjna</t>
+          <t>Astra Enterprise spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Królowej Jadwigi 96, 88-100 Inowrocław</t>
+          <t>Piłsudskiego 36, 35-074 Rzeszów</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -10960,17 +10960,17 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>0000016983</t>
+          <t>0000075183</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>1248663711</t>
+          <t>1296177718</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>248822098</t>
+          <t>296336093</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -10985,7 +10985,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>97050773978</t>
+          <t>99050795970</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -11000,19 +11000,19 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>Woźniak</t>
+          <t>Wieczorek</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Amber Urody sp. z o.o.</t>
+          <t>Astra Network Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>ul. Wybickiego 113/39, 86-300 Grudziądz</t>
+          <t>ul. Sienkiewicza 53/9, 25-007 Kielce</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -11022,17 +11022,17 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>0000017080</t>
+          <t>0000075280</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>1248742907</t>
+          <t>1296256903</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>248901283</t>
+          <t>296415289</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -11047,7 +11047,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>98061475327</t>
+          <t>00261497324</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -11062,19 +11062,19 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>Jankowska</t>
+          <t>Jabłońska</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Amber Turystyka sp z oo</t>
+          <t>Apex Group S.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>ul Czarnieckiego 130, 14-100 Ostróda</t>
+          <t>ul Warszawska 70, 25-512 Kielce</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -11084,17 +11084,17 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>0000017177</t>
+          <t>0000075377</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>1248822090</t>
+          <t>1296336097</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>248980472</t>
+          <t>296494478</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -11109,7 +11109,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>99072176713</t>
+          <t>01272198710</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -11124,19 +11124,19 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>Grabowski</t>
+          <t>Witkowski</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Amber Rozrywka sp. z o. o.</t>
+          <t>Apex Systems SA</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>ulica Warszawska 147, 11-500 Giżycko</t>
+          <t>ulica Kościuszki 87, 10-504 Olsztyn</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -11146,22 +11146,22 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>0000017274</t>
+          <t>0000075474</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>1248901286</t>
+          <t>1296415282</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>249059664</t>
+          <t>296573663</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>00282878069</t>
+          <t>02282800064</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -11186,19 +11186,19 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>Pawlak</t>
+          <t>Walczak</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Amber Gastronomia Sp. z o.o.</t>
+          <t>Apex Holding S. A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Lubelska 164, 24-100 Puławy</t>
+          <t>Dąbrowszczaków 104, 10-540 Olsztyn</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -11208,17 +11208,17 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>0000017371</t>
+          <t>0000075571</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>1248980475</t>
+          <t>1296494471</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>259138887</t>
+          <t>296652859</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -11233,7 +11233,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>01290779452</t>
+          <t>03290701457</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -11248,19 +11248,19 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>Michalski</t>
+          <t>Stępień</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>PPHU Amber Moda</t>
+          <t>P.P.H.U. Apex Partners</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>ul. Staszica 1/1, 22-400 Zamość</t>
+          <t>ul. Krakowska 121/61, 45-018 Opole</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -11270,17 +11270,17 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>0000017468</t>
+          <t>0000075668</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>1249059667</t>
+          <t>1296573667</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>249218045</t>
+          <t>296732044</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -11295,7 +11295,7 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>02301480806</t>
+          <t>04301402808</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -11310,19 +11310,19 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>Król</t>
+          <t>Baran</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Amber Tekstylia spółka z ograniczoną odpowiedzialnością</t>
+          <t>Apex Polska sp. z o.o.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>ul 3 Maja 18, 16-300 Augustów</t>
+          <t>ul Ozimska 138, 45-057 Opole</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -11332,17 +11332,17 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>0000017565</t>
+          <t>0000075765</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>1249138852</t>
+          <t>1296652852</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>249297234</t>
+          <t>306811262</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -11357,7 +11357,7 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>03312182194</t>
+          <t>05312104196</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -11372,19 +11372,19 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>Wieczorek</t>
+          <t>Rutkowski</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Amber Motoryzacja Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Apex Enterprise sp z oo</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>ulica Kościuszki 35, 16-400 Suwałki</t>
+          <t>ulica Bohaterów Westerplatte 155, 65-034 Zielona Góra</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -11394,17 +11394,17 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>0000017662</t>
+          <t>0000075862</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>1249218048</t>
+          <t>1296732048</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>259376457</t>
+          <t>296890429</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -11419,7 +11419,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>04322883543</t>
+          <t>60122805541</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -11434,14 +11434,14 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>Jabłońska</t>
+          <t>Górska</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Amber Ubezpieczenia S.A.</t>
+          <t>Apex Network sp. z o. o.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11456,17 +11456,17 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>0000017759</t>
+          <t>0000075959</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>1249297237</t>
+          <t>1296811233</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>249455615</t>
+          <t>296969616</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -11481,7 +11481,7 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>05210784931</t>
+          <t>61010706939</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -11496,19 +11496,19 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>Witkowski</t>
+          <t>Sikora</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Amber Spawalnictwo SA</t>
+          <t>Clarity Group Sp. z o.o.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>ul. Długa 69/53, 49-300 Brzeg</t>
+          <t>ul. Świętojańska 9/23, 81-372 Gdynia</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -11518,17 +11518,17 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>0000017856</t>
+          <t>0000076056</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>1249376422</t>
+          <t>1296890422</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>249534800</t>
+          <t>297048806</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -11543,7 +11543,7 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>60021486287</t>
+          <t>62021408289</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -11558,19 +11558,19 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>Walczak</t>
+          <t>Ostrowska</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Amber Ślusarstwo S. A.</t>
+          <t>Clarity Systems SP Z O O</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>ul Rynek 86, 68-200 Żary</t>
+          <t>ul 10 Lutego 26, 81-364 Gdynia</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -11580,17 +11580,17 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>0000017953</t>
+          <t>0000076153</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>1249455618</t>
+          <t>1306969646</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>249613994</t>
+          <t>307128024</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -11605,7 +11605,7 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>61032187673</t>
+          <t>63032109675</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
@@ -11620,19 +11620,19 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>Stępień</t>
+          <t>Tomaszewski</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Amber Krawiectwo Spółka Akcyjna</t>
+          <t>Clarity Holding spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>ulica Sikorskiego 103, 66-200 Świebodzin</t>
+          <t>ulica Bolesława Prusa 43, 05-800 Pruszków</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -11642,17 +11642,17 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>0000018050</t>
+          <t>0000076250</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>1249534803</t>
+          <t>1307048836</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>249693183</t>
+          <t>297207185</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -11667,7 +11667,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>62042889023</t>
+          <t>64042811028</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -11682,19 +11682,19 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>Baran</t>
+          <t>Zając</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Amber Ochrona sp. z o.o.</t>
+          <t>Clarity Partners Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Armii Krajowej 120, 78-100 Kołobrzeg</t>
+          <t>Kościuszki 60, 05-500 Piaseczno</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -11704,17 +11704,17 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>0000018147</t>
+          <t>0000076347</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>1249613997</t>
+          <t>1297127993</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>249772379</t>
+          <t>297286374</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -11729,7 +11729,7 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>63050790419</t>
+          <t>65050712411</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -11744,19 +11744,19 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>Rutkowski</t>
+          <t>Pietrzak</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Amber Catering sp z oo</t>
+          <t>Clarity Polska S.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>ul. Piłsudskiego 137/15, 73-110 Stargard</t>
+          <t>ul. Sienkiewicza 77/75, 32-020 Wieliczka</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -11766,22 +11766,22 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>0000018244</t>
+          <t>0000076444</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>1249693186</t>
+          <t>1297207189</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>249851564</t>
+          <t>307365592</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2022-09-08</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -11791,7 +11791,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>64061491768</t>
+          <t>66061413760</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -11806,19 +11806,19 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>Górska</t>
+          <t>Wójcicka</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Amber Księgowość sp. z o. o.</t>
+          <t>Clarity Enterprise SA</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>154, 27-600 Sandomierz</t>
+          <t>ul Dąbrowskiego 94, 32-600 Oświęcim</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -11828,17 +11828,17 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>0000018341</t>
+          <t>0000076541</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>1249772371</t>
+          <t>1297286378</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>259930787</t>
+          <t>297444755</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -11853,7 +11853,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>65072193155</t>
+          <t>67072115157</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -11868,19 +11868,19 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>Sikora</t>
+          <t>Czarnecki</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Bizon Budownictwo Sp. z o.o.</t>
+          <t>Clarity Network S. A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>ulica Sienkiewicza 171, 27-400 Ostrowiec Świętokrzyski</t>
+          <t>ulica Rynek 111, 38-400 Krosno</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -11890,17 +11890,17 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>0000018438</t>
+          <t>000007663</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>1249851567</t>
+          <t>1297365563</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>250009941</t>
+          <t>297523940</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -11915,7 +11915,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>66082894504</t>
+          <t>68082816506</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -11930,19 +11930,19 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>Ostrowska</t>
+          <t>Lis</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Bizon Transport SP Z O O</t>
+          <t>Core Group Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Chmielna 8, 00-020 Warszawa</t>
+          <t>128, 39-300 Mielec</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>000001853</t>
+          <t>0000076735</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>1249930752</t>
+          <t>1297444759</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>350089130</t>
+          <t>397603136</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -11977,7 +11977,7 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>67090795898</t>
+          <t>69090717890</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -11992,19 +11992,19 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>Tomaszewski</t>
+          <t>Kołodziej</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Bizon Spedycja spółka z ograniczoną odpowiedzialnością</t>
+          <t>Core Systems sp. z o.o.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>ul. Nowy Świat 25/67, 00-029 Warszawa</t>
+          <t>ul. Długa 145/37, 58-100 Świdnica</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -12014,17 +12014,17 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>0000018632</t>
+          <t>0000076832</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>1250009942</t>
+          <t>1297523944</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>250168326</t>
+          <t>297682325</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -12039,7 +12039,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>68101497240</t>
+          <t>70101419241</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -12054,19 +12054,19 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>Zając-Sawicka</t>
+          <t>Kaczmarek-Wróbel</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Bizon Logistyka Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Core Holding sp z oo</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>ul os. Przyjaźń 42, 01-355 Warszawa</t>
+          <t>ul Wojska Polskiego 162, 57-300 Kłodzko</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -12076,17 +12076,17 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>0000018729</t>
+          <t>0000076929</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>1250089131</t>
+          <t>1307603166</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>250247511</t>
+          <t>297761510</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -12101,7 +12101,7 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>69112198636</t>
+          <t>71112120630</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -12116,19 +12116,19 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>Pietrzak</t>
+          <t>Piątek</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Bizon Handel S.A.</t>
+          <t>Core Partners sp. z o. o.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>ulica Jagiellońska 59, 05-120 Legionowo</t>
+          <t>ulica Chrobrego 179, 62-200 Gniezno</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -12138,17 +12138,17 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>0000018826</t>
+          <t>0000077026</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>1250168327</t>
+          <t>1297682329</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>250326707</t>
+          <t>297840706</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -12163,7 +12163,7 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>70122899985</t>
+          <t>72122821980</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
@@ -12178,19 +12178,19 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>Wójcicka</t>
+          <t>Sadowska</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Bizon Usługi SA</t>
+          <t>Core Polska Sp. z o.o.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Piłsudskiego 76, 05-270 Marki</t>
+          <t>Słowiańska 16, 64-100 Leszno</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -12200,17 +12200,17 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>0000018923</t>
+          <t>0000077123</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>1250247512</t>
+          <t>1297761514</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>250405890</t>
+          <t>297919891</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -12225,7 +12225,7 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>71010701377</t>
+          <t>73010723379</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -12240,19 +12240,19 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>Czarnecki</t>
+          <t>Włodarczyk</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Bizon Finanse S. A.</t>
+          <t>Core Enterprise SP Z O O</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>ul. Andriollego 93/29, 05-400 Otwock</t>
+          <t>ul. Gdańska 33/89, 83-110 Tczew</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -12262,17 +12262,17 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>0000019020</t>
+          <t>0000077220</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>1250326708</t>
+          <t>1307840736</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>260485119</t>
+          <t>297999080</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -12287,7 +12287,7 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>72021402725</t>
+          <t>74021424727</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -12302,19 +12302,19 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>Lis</t>
+          <t>Borkowska</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Bizon Doradztwo Spółka Akcyjna</t>
+          <t>Core Network spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>ul Żeromskiego 110, 26-600 Radom</t>
+          <t>ul Sobieskiego 50, 84-200 Wejherowo</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -12324,17 +12324,17 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>0000019117</t>
+          <t>0000077317</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>1250405891</t>
+          <t>1297919895</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>250564275</t>
+          <t>298078270</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -12349,7 +12349,7 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>73032104112</t>
+          <t>75032126114</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -12364,19 +12364,19 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>Kołodziej</t>
+          <t>Sawicki</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Bizon Szkolenia sp. z o.o.</t>
+          <t>Direct Group Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>ulica Tumska 127, 09-402 Płock</t>
+          <t>67, 43-400 Cieszyn</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -12386,17 +12386,17 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>0000019214</t>
+          <t>0000077414</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>1250485080</t>
+          <t>1297999084</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>250643460</t>
+          <t>298157466</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -12411,7 +12411,7 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>74042805462</t>
+          <t>76042827464</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -12426,19 +12426,19 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>Kaczmarek</t>
+          <t>Dudek</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Bizon Media sp z oo</t>
+          <t>Direct Systems S.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Karmelicka 144, 31-128 Kraków</t>
+          <t>Małachowskiego 84, 42-500 Będzin</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -12448,17 +12448,17 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>0000019311</t>
+          <t>0000077511</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>1250564276</t>
+          <t>1298078274</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>250722656</t>
+          <t>298236651</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -12473,7 +12473,7 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>75050706855</t>
+          <t>77050728857</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -12488,7 +12488,7 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>Piątek</t>
+          <t>Adamczyk</t>
         </is>
       </c>
     </row>

--- a/data/xlsx/KNF_Rejestr_firm_inwestycyjnych.xlsx
+++ b/data/xlsx/KNF_Rejestr_firm_inwestycyjnych.xlsx
@@ -135,29 +135,29 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>60101434205</t>
+          <t>62021474200</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Karolina</t>
+          <t/>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Kaczmarek</t>
+          <t>Lewandowska</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Zielony Bieszczady S.A.</t>
+          <t>Pewny Delfin S.A.</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -197,29 +197,29 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>61112135592</t>
+          <t>96061444200</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t/>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Piątek</t>
+          <t>Michalska</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Zielony Karpaty SA</t>
+          <t>Dobry Koral SA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -244,7 +244,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>382636222</t>
+          <t>282636222</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -259,29 +259,29 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>62122836941</t>
+          <t>84101414205</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Aleksandra</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Małgorzata</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Sadowska</t>
+          <t>Sikora</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Zielony Bałtyk S. A.</t>
+          <t>Polski Szafir S. A.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -306,7 +306,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>282715418</t>
+          <t>382715418</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -321,29 +321,29 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63010738330</t>
+          <t>72021484202</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Andrzej</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Jakub</t>
+          <t/>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Włodarczyk</t>
+          <t>Piątek</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Zielony Sudety Spółka Akcyjna</t>
+          <t>Europejski Orzeł Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -383,29 +383,29 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64021439689</t>
+          <t>60061454204</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Marta</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t/>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Borkowska</t>
+          <t>Wróbel</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Niebieski Amber sp. z o.o.</t>
+          <t>Globalny Kaktus sp. z o.o.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -445,29 +445,29 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65032141079</t>
+          <t>94101424207</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Łukasz</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Artur</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Sawicki</t>
+          <t>Wysocka</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Niebieski Bizon sp z oo</t>
+          <t>Lokalny Olimp sp z oo</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -507,29 +507,29 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>66042842428</t>
+          <t>82021494204</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Paulina</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Iwona</t>
+          <t/>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Dudek</t>
+          <t>Mazurek</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Niebieski Canyon sp. z o. o.</t>
+          <t>Nowoczesny Beskid sp. z o. o.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>przymjoanwi  przekazywanie zleceń</t>
+          <t>przymjoawni  przekazywanie zleceń</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -564,34 +564,34 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>DFI/418/2026</t>
+          <t>DIF/418/2026</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>67050743811</t>
+          <t>70061464206</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Mateusz</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t/>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Adacmzyk</t>
+          <t>Kopeć</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Niebieski Delfin Sp. z o.o.</t>
+          <t>Tradycyjny Canyon Sp. z o.o.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -631,29 +631,29 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>68061445161</t>
+          <t>04301434205</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Elżbieta</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Renata</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Pawłowska</t>
+          <t>Kalinowska</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Niebieski Echo SP Z O O</t>
+          <t>Dynamiczny Jantar SP Z O O</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -693,29 +693,29 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>69072146557</t>
+          <t>92021404206</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Dawid</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Maciej</t>
+          <t/>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Nowicki</t>
+          <t>Panek</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Niebieski Falcon spółka z ograniczoną odpowiedzialnością</t>
+          <t>Stabilny Rubin spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -755,29 +755,29 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>70082847905</t>
+          <t>80061474208</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Dorota</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t/>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Sokołowska</t>
+          <t>Zielińska</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Niebieski Gryf Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Innowacyjny Sokół Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -817,29 +817,29 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>71090749290</t>
+          <t>68101444204</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Dariusz</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Zbigniew</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Wróbel</t>
+          <t>Król</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Niebieski Horyzont S.A.</t>
+          <t>Kreatywny Jodełka S.A.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -879,29 +879,29 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>72101450644</t>
+          <t>02221414204</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Beata</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Patrycja</t>
+          <t/>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Majewska</t>
+          <t>Ostrowska</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Niebieski Ikar SA</t>
+          <t>Aktywny Zodiak SA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -941,29 +941,29 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>73112152031</t>
+          <t>90061484200</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Sławomir</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t/>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Olszewski</t>
+          <t>Sadowska</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Niebieski Jantar S. A.</t>
+          <t>Jasny Kasprowy S. A.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1003,29 +1003,29 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>74122853381</t>
+          <t>78101454206</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Urszula</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Wiktoria</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Jaworska</t>
+          <t>Majewska</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Niebieski Koral Spółka Akcyjna</t>
+          <t>Green Bizon Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1065,29 +1065,29 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>75010754779</t>
+          <t>66021424203</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Mariusz</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Jacek</t>
+          <t/>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Malinowski</t>
+          <t>Chmielewska</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Niebieski Lotos sp. z o.o.</t>
+          <t>Blue Ikar sp. z o.o.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1127,29 +1127,29 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>76021456128</t>
+          <t>00261494208</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Izabela</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t/>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Pająk</t>
+          <t>Sobczak</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Niebieski Magnolia sp z oo</t>
+          <t>Gold Pegaz sp z oo</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1189,29 +1189,29 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>77032157514</t>
+          <t>88101464208</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Henryk</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Przemysław</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Szczepański</t>
+          <t>Czajka</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Niebieski Neon sp. z o. o.</t>
+          <t>Silver Żubr sp. z o. o.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1251,29 +1251,29 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>78042858864</t>
+          <t>76021434205</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Weronika</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Kinga</t>
+          <t/>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Czerwińska</t>
+          <t>Zarychta</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Niebieski Oaza Sp. z o.o.</t>
+          <t>Smart Narew Sp. z o.o.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1313,29 +1313,29 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>79050760251</t>
+          <t>64061404207</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Stanisław</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t/>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Kubiak</t>
+          <t>Prus</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P.P.H.U. Niebieski Pegaz</t>
+          <t>P.P.H.U. Fast Syrena</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1375,29 +1375,29 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>80061461608</t>
+          <t>98101474200</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Zofia</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Kamila</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Wilk</t>
+          <t>Szymańska</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Niebieski Rubin spółka z ograniczoną odpowiedzialnością</t>
+          <t>Safe Rysy spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1437,29 +1437,29 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>81072162995</t>
+          <t>86021444207</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Bartłomiej</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t/>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Wysocki</t>
+          <t>Wieczorek</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Niebieski Szafir Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Best Amber Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1499,29 +1499,29 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>82082864345</t>
+          <t>74061414209</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Olga</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t/>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Chmielewska</t>
+          <t>Tomaszewska</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Niebieski Tytan S.A.</t>
+          <t>Global Horyzont S.A.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1561,29 +1561,29 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>83090765738</t>
+          <t>62101484204</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Damian</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Waldemar</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Urbański</t>
+          <t>Włodarczyk</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Niebieski Uran SA</t>
+          <t>Future Oaza SA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1623,29 +1623,29 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>84101467081</t>
+          <t>96021454209</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Ewelina</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Danuta</t>
+          <t/>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Błaszczyk</t>
+          <t>Olszewska</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Niebieski Wektor S. A.</t>
+          <t>Wielkopolski Zefir S. A.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1685,29 +1685,29 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>85112168477</t>
+          <t>84061424201</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Bartosz</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t/>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Szulc</t>
+          <t>Urbańska</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Niebieski Zefir Spółka Akcyjna</t>
+          <t>Śląski Pilica Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1747,29 +1747,29 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>86122869826</t>
+          <t>72101494206</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Sylwia</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Aneta</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Kozak</t>
+          <t>Konieczna</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Niebieski Żubr sp. z o.o.</t>
+          <t>Mazowiecki Marmur sp. z o.o.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1809,29 +1809,29 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>87010771218</t>
+          <t>60021464203</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Leszek</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Kacper</t>
+          <t/>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Cieślak</t>
+          <t>Matusiak</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Niebieski Sokół sp z oo</t>
+          <t>Pomorski Giewont sp z oo</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1871,29 +1871,29 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>88021472567</t>
+          <t>94061434203</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Grażyna</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t/>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Andrzejewska</t>
+          <t>Przybylska</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Niebieski Orzeł sp. z o. o.</t>
+          <t>Dolnośląski Sudety sp. z o. o.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1933,29 +1933,29 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>89032173953</t>
+          <t>82101404208</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Cezary</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Szymon</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Gajewski</t>
+          <t>Janik</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Niebieski Kormoran Sp. z o.o.</t>
+          <t>Karpacki Gryf Sp. z o.o.</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1995,29 +1995,29 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>92042897304</t>
+          <t>70021474205</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Bożena</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Oliwia</t>
+          <t/>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Wrona</t>
+          <t>Dąbrowska</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Niebieski Barycz SP Z O O</t>
+          <t>Bałtycki Neon SP Z O O</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2057,29 +2057,29 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>93050798698</t>
+          <t>04261444201</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Filip</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t/>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Bąk</t>
+          <t>Jabłońska</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Niebieski Noteć spółka z ograniczoną odpowiedzialnością</t>
+          <t>Młody Wektor spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2119,29 +2119,29 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>94061400040</t>
+          <t>92101414200</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Zuzanna</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Emilia</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Kucharska-Wrona</t>
+          <t>Zając</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Niebieski Pilica Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Wspólny Noteć Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2181,29 +2181,29 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>95072101436</t>
+          <t>80021484207</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Mikołaj</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Ignacy</t>
+          <t/>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Lisowski</t>
+          <t>Borkowska</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Niebieski Narew S.A.</t>
+          <t>Pierwszy Granit S.A.</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2243,29 +2243,29 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>96082802786</t>
+          <t>68061454200</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Lena</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t/>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Słowik</t>
+          <t>Jaworska</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Niebieski Jodełka SA</t>
+          <t>Zielony Żubr SA</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2305,29 +2305,29 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>97090704170</t>
+          <t>02301424208</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Antoni</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Leon</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Kopeć</t>
+          <t>Błaszczyk</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Niebieski Kaktus S. A.</t>
+          <t>Niebieski Narew S. A.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2367,29 +2367,29 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>98101405521</t>
+          <t>90021494209</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Hanna</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Dominika</t>
+          <t/>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Czajka</t>
+          <t>Brzezińska</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Niebieski Szmaragd Spółka Akcyjna</t>
+          <t>Złoty Syrena Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2429,29 +2429,29 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>99112106917</t>
+          <t>78061464202</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Franciszek</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t/>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Matusiak</t>
+          <t>Gajda</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Niebieski Topaz sp. z o.o.</t>
+          <t>Srebrny Rysy sp. z o.o.</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2491,29 +2491,29 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>00322808263</t>
+          <t>66101434207</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Amelia</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Jagoda</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Gajda</t>
+          <t>Michalak</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Niebieski Granit sp z oo</t>
+          <t>Czysty Amber sp z oo</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2553,22 +2553,22 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>01210709651</t>
+          <t>00221404207</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Nikodem</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Jerzy</t>
+          <t/>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Klimek</t>
+          <t>Kowalska</t>
         </is>
       </c>
     </row>
@@ -2615,29 +2615,29 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>02221411003</t>
+          <t>88061474204</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Martyna</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t/>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Madej</t>
+          <t>Mazur</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Niebieski Syrena Sp. z o.o.</t>
+          <t>Pewny Oaza Sp. z o.o.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2677,29 +2677,29 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>03232112390</t>
+          <t>76101444209</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Miłosz</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Marian</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Krupa</t>
+          <t>Witkowska</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Niebieski Zodiak SP Z O O</t>
+          <t>Dobry Zefir SP Z O O</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2739,29 +2739,29 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>04242813749</t>
+          <t>64021414206</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Agata</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Irena</t>
+          <t/>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Kaczmarczyk</t>
+          <t>Pietrzak</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Niebieski Olimp spółka z ograniczoną odpowiedzialnością</t>
+          <t>Polski Pilica spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2801,29 +2801,29 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>05250715133</t>
+          <t>98061484206</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Tadeusz</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t/>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Wrona</t>
+          <t>Sawicka</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Niebieski Zorza Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Europejski Marmur Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2863,29 +2863,29 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>60061416488</t>
+          <t>86101454201</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Helena</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Izabela</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Wasilewska</t>
+          <t>Malinowska</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Niebieski Krokus S.A.</t>
+          <t>Globalny Giewont S.A.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2925,29 +2925,29 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>61072117874</t>
+          <t>74021424208</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Stefan</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Mirosław</t>
+          <t/>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Kalinowski</t>
+          <t>Szulc</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Niebieski Narcyz SA</t>
+          <t>Lokalny Sudety SA</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2987,29 +2987,29 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>62082819224</t>
+          <t>62061494200</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Jadwiga</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t/>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Zarychta</t>
+          <t>Makowska</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Niebieski Giewont S. A.</t>
+          <t>Nowoczesny Gryf S. A.</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3049,29 +3049,29 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>63090720610</t>
+          <t>96101464203</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Józef</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Przybylski</t>
+          <t>Klimek</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Niebieski Rysy Spółka Akcyjna</t>
+          <t>Tradycyjny Neon Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3111,29 +3111,29 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>64101421962</t>
+          <t>84021434200</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t/>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Michalak</t>
+          <t>Szatkowska</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Niebieski Kasprowy sp. z o.o.</t>
+          <t>Dynamiczny Wektor sp. z o.o.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3173,22 +3173,22 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>65112123359</t>
+          <t>72061404202</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t/>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Szatkowski</t>
+          <t>Nowacka</t>
         </is>
       </c>
     </row>
@@ -3235,29 +3235,29 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>66122824708</t>
+          <t>60101474207</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Sabina</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Bednarek</t>
+          <t>Krawczyk</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Amber Transport sp. z o. o.</t>
+          <t>Falcon Transport sp. z o. o.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3297,29 +3297,29 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>67010726098</t>
+          <t>94021444202</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Arkadiusz</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t/>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Podgórski</t>
+          <t>Walczak</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Amber Spedycja Sp. z o.o.</t>
+          <t>Koral Spedycja Sp. z o.o.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3359,29 +3359,29 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>68021427446</t>
+          <t>82061414204</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t/>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Śliwińska</t>
+          <t>Wójcicka</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Amber Logistyka SP Z O O</t>
+          <t>Pegaz Logistyka SP Z O O</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3421,29 +3421,29 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>69032128832</t>
+          <t>70101484209</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Czajkowski</t>
+          <t>Dudek</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Amber Handel spółka z ograniczoną odpowiedzialnością</t>
+          <t>Wektor Handel spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3483,29 +3483,29 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>70042830185</t>
+          <t>04221454200</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t/>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Biernat</t>
+          <t>Pająk</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Amber Usługi Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Kormoran Usługi Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3545,29 +3545,29 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>71050731578</t>
+          <t>92061424206</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t/>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Panek</t>
+          <t>Kozak</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Amber Finanse S.A.</t>
+          <t>Jodełka Finanse S.A.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3607,29 +3607,29 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>72061432926</t>
+          <t>80101494201</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Prus</t>
+          <t>Wrona</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Amber Doradztwo SA</t>
+          <t>Marmur Doradztwo SA</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3669,29 +3669,29 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>73072134313</t>
+          <t>68021464209</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t/>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Jnaik</t>
+          <t>Madje</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Amber Szkolenia S. A.</t>
+          <t>Krokus Szkolenia S. A.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3731,29 +3731,29 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>74082835663</t>
+          <t>02261434204</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t/>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Kowalska</t>
+          <t>Bednarek</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Amber Media Spółka Akcyjna</t>
+          <t>Beskid Media Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3793,22 +3793,22 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>75090737057</t>
+          <t>90101404203</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Marcin</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Nowacki</t>
+          <t>Wiśniewska</t>
         </is>
       </c>
     </row>
@@ -3855,29 +3855,29 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>76101438408</t>
+          <t>78021474201</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Karolina</t>
+          <t/>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Wiśniewska</t>
+          <t>Woźniak</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Amber Marketing sp z oo</t>
+          <t>Falcon Marketing sp z oo</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3917,29 +3917,29 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>77112139795</t>
+          <t>66061444203</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t/>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Wójcik</t>
+          <t>Stępień</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Amber Druk sp. z o. o.</t>
+          <t>Koral Druk sp. z o. o.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3979,29 +3979,29 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>78122841148</t>
+          <t>00301414201</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Aleksandra</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Małgorzata</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Kowalczyk</t>
+          <t>Czarnecka</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Amber Informatyka Sp. z o.o.</t>
+          <t>Pegaz Informatyka Sp. z o.o.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4041,29 +4041,29 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>79010742536</t>
+          <t>88021484203</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Andrzej</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Jakub</t>
+          <t/>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Kamiński</t>
+          <t>Adamczyk</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Amber Oprogramowanie SP Z O O</t>
+          <t>Wektor Oprogramowanie SP Z O O</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4103,29 +4103,29 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>80021443884</t>
+          <t>76061454205</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Marta</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t/>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Lewandowska</t>
+          <t>Szczepańska</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Amber Rolnictwo spółka z ograniczoną odpowiedzialnością</t>
+          <t>Kormoran Rolnictwo spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4165,29 +4165,29 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>81032145271</t>
+          <t>64101424200</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Łukasz</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Artur</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Zieliński</t>
+          <t>Cieślak</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Amber Ogrodnictwo Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Jodełka Ogrodnictwo Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4227,29 +4227,29 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>82042846620</t>
+          <t>98021494205</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Paulina</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Iwona</t>
+          <t/>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Szymańska</t>
+          <t>Bąk</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Amber Produkcja S.A.</t>
+          <t>Marmur Produkcja S.A.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4289,29 +4289,29 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>83050748014</t>
+          <t>86061464207</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Mateusz</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t/>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Dąbrowski</t>
+          <t>Krupa</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Amber Przemysł SA</t>
+          <t>Krokus Przemysł SA</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4351,29 +4351,29 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>84061449363</t>
+          <t>74101434202</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Elżbieta</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Renata</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Mazur</t>
+          <t>Podgórska</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Amber Ekologia S. A.</t>
+          <t>Beskid Ekologia S. A.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4413,22 +4413,22 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>85072150752</t>
+          <t>62021404209</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Dawid</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Maciej</t>
+          <t/>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Krawczyk</t>
+          <t>Wójcik</t>
         </is>
       </c>
     </row>
@@ -4475,29 +4475,29 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>86082852102</t>
+          <t>96061474209</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Dorota</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t/>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Woźniak</t>
+          <t>Jankowska</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Amber Instalacje sp. z o.o.</t>
+          <t>Falcon Instalacje sp. z o.o.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4537,29 +4537,29 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>87090753496</t>
+          <t>84101444204</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Dariusz</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Zbigniew</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Jankowski</t>
+          <t>Baran</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Amber Nieruchomości sp z oo</t>
+          <t>Koral Nieruchomości sp z oo</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4599,12 +4599,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>60021406849</t>
+          <t>72021414201</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -4614,14 +4614,14 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Kowalska-Krawczyk</t>
+          <t>Lis</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Amber Inwestycje sp. z o. o.</t>
+          <t>Pegaz Inwestycje sp. z o. o.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4661,29 +4661,29 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>61032108236</t>
+          <t>60061484203</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Nowacki</t>
+          <t>Pawłowska</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Amber Medycyna Sp. z o.o.</t>
+          <t>Wektor Medycyna Sp. z o.o.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4723,29 +4723,29 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>62042809586</t>
+          <t>94101454206</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Wiśniewska</t>
+          <t>Czerwińska</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Amber Zdrowie SP Z O O</t>
+          <t>Kormoran Zdrowie SP Z O O</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4785,12 +4785,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>63050710972</t>
+          <t>82021424203</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -4800,14 +4800,14 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Wójcik</t>
+          <t>Andrzejewska</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Amber Urody spółka z ograniczoną odpowiedzialnością</t>
+          <t>Jodełka Urody spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4847,29 +4847,29 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>64061412321</t>
+          <t>70061494205</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Kowalczyk</t>
+          <t>Kucharska</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Amber Turystyka Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Marmur Turystyka Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4909,29 +4909,29 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>65072113717</t>
+          <t>04301464204</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Kamiński</t>
+          <t>Kaczmarczyk</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Amber Rozrywka S.A.</t>
+          <t>Krokus Rozrywka S.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>66082815068</t>
+          <t>92021434205</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -4986,14 +4986,14 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Lewandowska</t>
+          <t>Śliwińska</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Amber Gastronomia SA</t>
+          <t>Beskid Gastronomia SA</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5033,22 +5033,22 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>67090716451</t>
+          <t>80061404207</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Marcin</t>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Zieliński</t>
+          <t>Kowalczyk</t>
         </is>
       </c>
     </row>
@@ -5095,7 +5095,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>68101417802</t>
+          <t>68101474203</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -5110,14 +5110,14 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Szymańska</t>
+          <t>Grabowska</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Amber Tekstylia Spółka Akcyjna</t>
+          <t>Falcon Tekstylia Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5157,12 +5157,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>69112119190</t>
+          <t>02221444203</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5172,14 +5172,14 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Dąbrowski</t>
+          <t>Rutkowska</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Amber Motoryzacja sp. z o.o.</t>
+          <t>Koral Motoryzacja sp. z o.o.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5194,19 +5194,19 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
+          <t>0000066162</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>1288813045</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>1288813045</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>288971424</t>
-        </is>
-      </c>
       <c r="G84" t="inlineStr">
         <is>
           <t>13-05-2017</t>
@@ -5219,29 +5219,29 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>70122820541</t>
+          <t>90061414209</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Aleksandra</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Małgorzata</t>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Mazur</t>
+          <t>Kołodziej</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Amber Ubezpieczenia sp z oo</t>
+          <t>Pegaz Ubezpieczenia sp z oo</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5281,29 +5281,29 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>71010721939</t>
+          <t>78101484205</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Andrzej</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Jakub</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>Krawczyk</t>
+          <t>Nowicka</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Amber Spawalnictwo sp. z o. o.</t>
+          <t>Wektor Spawalnictwo sp. z o. o.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5343,12 +5343,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>72021423289</t>
+          <t>66021454202</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Marta</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5358,14 +5358,14 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Woźniak</t>
+          <t>Kubiak</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Amber Ślusarstwo Sp. z o.o.</t>
+          <t>Kormoran Ślusarstwo Sp. z o.o.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5405,29 +5405,29 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>73032124675</t>
+          <t>00261424207</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Łukasz</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Artur</t>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>Jankowski</t>
+          <t>Gajewska</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Amber Krawiectwo SP Z O O</t>
+          <t>Jodełka Krawiectwo SP Z O O</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5467,29 +5467,29 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>74042826025</t>
+          <t>88101494207</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Paulina</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Iwona</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>Grabowska</t>
+          <t>Lisowska</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Amber Ochrona spółka z ograniczoną odpowiedzialnością</t>
+          <t>Marmur Ochrona spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5529,12 +5529,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>75050727418</t>
+          <t>76021464204</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Mateusz</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5544,14 +5544,14 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>Pawlak</t>
+          <t>Wrona</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Amber Catering Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Krokus Catering Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5591,29 +5591,29 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>76061428767</t>
+          <t>64061434206</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Elżbieta</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>Renata</t>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>Michalska</t>
+          <t>Czajkowska</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Amber Księgowość S.A.</t>
+          <t>Beskid Księgowość S.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5653,29 +5653,29 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>77072130157</t>
+          <t>98101404209</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Dawid</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>Maciej</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>Król</t>
+          <t>Kaczmarek</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Bizon Budownictwo SA</t>
+          <t>Jantar Budownictwo SA</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -5715,12 +5715,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>78082831506</t>
+          <t>86021474206</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Dorota</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -5730,14 +5730,14 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>Wieczorek</t>
+          <t>Sokołowska</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Bizon Transport S. A.</t>
+          <t>Oaza Transport S. A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -5777,29 +5777,29 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>79090732890</t>
+          <t>74061444208</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Dariusz</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Zbigniew</t>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>Jabłoński</t>
+          <t>Wilk</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Bizon Spedycja Spółka Akcyjna</t>
+          <t>Uran Spedycja Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -5839,29 +5839,29 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>80101434241</t>
+          <t>62101414203</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Beata</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Patrycja</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>Witkowska</t>
+          <t>Laskowska</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Bizon Logistyka sp. z o.o.</t>
+          <t>Orzeł Logistyka sp. z o.o.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>81112135637</t>
+          <t>96021484208</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Sławomir</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -5916,14 +5916,14 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>Walczak</t>
+          <t>Słowik</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Bizon Handel sp z oo</t>
+          <t>Narew Handel sp z oo</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -5963,29 +5963,29 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>82122836987</t>
+          <t>84061454200</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Urszula</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Wiktoria</t>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>Stępień</t>
+          <t>Wasilewska</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Bizon Usługi sp. z o. o.</t>
+          <t>Granit Usługi sp. z o. o.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6025,29 +6025,29 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>83010738376</t>
+          <t>72101424205</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Mariusz</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>Jacek</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>Baran</t>
+          <t>Biernat</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Bizon Finanse Sp. z o.o.</t>
+          <t>Zorza Finanse Sp. z o.o.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>84021439724</t>
+          <t>60021494202</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Izabela</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -6102,14 +6102,14 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>Rutkowska</t>
+          <t>Lewandowska</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Bizon Doradztwo SP Z O O</t>
+          <t>Kasprowy Doradztwo SP Z O O</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6149,29 +6149,29 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>85032141114</t>
+          <t>94061464202</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Henryk</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>Przemysław</t>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>Górski</t>
+          <t>Michalska</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Bizon Szkolenia spółka z ograniczoną odpowiedzialnością</t>
+          <t>Sudety Szkolenia spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6211,17 +6211,17 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>86042842464</t>
+          <t>82101434207</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Weronika</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>Kinga</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -6233,7 +6233,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Bizon Media Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Echo Media Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>87050743857</t>
+          <t>70021404204</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Stanisław</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -6288,14 +6288,14 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>Ostrowski</t>
+          <t>Piątek</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>P.P.H.U. Bizon Reklama</t>
+          <t>P.P.H.U. Jantar Reklama</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>88061445206</t>
+          <t>04261474200</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -6350,14 +6350,14 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>Tomaszewska</t>
+          <t>Wróbel</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Bizon Marketing SA</t>
+          <t>Oaza Marketing SA</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6397,29 +6397,29 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>89072146593</t>
+          <t>92101444209</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Bartłomiej</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>Zając</t>
+          <t>Wysocka</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Bizon Druk S. A.</t>
+          <t>Uran Druk S. A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6459,29 +6459,29 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>72042895946</t>
+          <t>80021414206</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Agata</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>Irena</t>
+          <t/>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>Nowicka</t>
+          <t>Mazurek</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Bizon Informatyka Spółka Akcyjna</t>
+          <t>Orzeł Informatyka Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6521,29 +6521,29 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>73050797330</t>
+          <t>68061484209</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Tadeusz</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t/>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>Sokołowski</t>
+          <t>Kopeć</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Bizon Oprogramowanie sp. z o.o.</t>
+          <t>Narew Oprogramowanie sp. z o.o.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6583,29 +6583,29 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>74061498689</t>
+          <t>02301454207</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Helena</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>Izabela</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>Wróbel</t>
+          <t>Kalinowska</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Bizon Rolnictwo sp z oo</t>
+          <t>Granit Rolnictwo sp z oo</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6645,29 +6645,29 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>75072100079</t>
+          <t>90021424208</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Stefan</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>Mirosław</t>
+          <t/>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>Majewski</t>
+          <t>Panek</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Bizon Ogrodnictwo sp. z o. o.</t>
+          <t>Zorza Ogrodnictwo sp. z o. o.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6707,29 +6707,29 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>76082801428</t>
+          <t>78061494201</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Jadwiga</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t/>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>Olszewska</t>
+          <t>Zielińska</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Bizon Produkcja Sp. z o.o.</t>
+          <t>Kasprowy Produkcja Sp. z o.o.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -6769,29 +6769,29 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>77090702811</t>
+          <t>66101464206</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Jóezf</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>Jaworski</t>
+          <t>Król</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Bizon Przemysł SP Z O O</t>
+          <t>Sudety Przemysł SP Z O O</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -6831,29 +6831,29 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>78101404164</t>
+          <t>00221434206</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t/>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>Malinowska</t>
+          <t>Ostrowska</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Bizon Ekologia spółka z ograniczoną odpowiedzialnością</t>
+          <t>Echo Ekologia spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -6893,29 +6893,29 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>79112105550</t>
+          <t>88061404203</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t/>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>Pająk</t>
+          <t>Sadowska</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Bizon Energetyka Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Jantar Energetyka Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -6955,29 +6955,29 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>80122806908</t>
+          <t>76101474208</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Sabina</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>Szczepańska</t>
+          <t>Majewska</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Bizon Instalacje S.A.</t>
+          <t>Oaza Instalacje S.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7017,29 +7017,29 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>81010708298</t>
+          <t>64021444205</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Arkadiusz</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t/>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>Czerwiński</t>
+          <t>Chmielewska</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Bizon Nieruchomości SA</t>
+          <t>Uran Nieruchomości SA</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>0000069072</t>
+          <t/>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -7079,29 +7079,29 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>82021409646</t>
+          <t>98061414205</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t/>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>Kubiak-Laskowska</t>
+          <t>Sobczak</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Bizon Inwestycje S. A.</t>
+          <t>Orzeł Inwestycje S. A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7116,7 +7116,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t/>
+          <t>0000069169</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7141,29 +7141,29 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>83032111036</t>
+          <t>86101484200</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>Wilk</t>
+          <t>Czajka</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Bizon Medycyna Spółka Akcyjna</t>
+          <t>Narew Medycyna Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7188,44 +7188,44 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
+          <t>291505504</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>20210207</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>DFI/765/2022</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>74021454207</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>Martyna</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>20210207</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>DFI/765/2022</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>84042812386</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>Katarzyna</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>Agnieszka</t>
-        </is>
-      </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>Wysocka</t>
+          <t>Zarychta</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Bizon Zdrowie sp. z o.o.</t>
+          <t>Granit Zdrowie sp. z o.o.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7265,29 +7265,29 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>85050713779</t>
+          <t>62061424209</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t/>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>Chmielewski</t>
+          <t>Prus</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Bizon Urody sp z oo</t>
+          <t>Zorza Urody sp z oo</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7312,7 +7312,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>291663887</t>
+          <t/>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -7327,29 +7327,29 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>86061415128</t>
+          <t>96101494202</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>Urbańska</t>
+          <t>Szymańska</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Bizon Turystyka sp. z o. o.</t>
+          <t>Kasprowy Turystyka sp. z o. o.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7389,29 +7389,29 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>87072116514</t>
+          <t>84021464209</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t/>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>Błaszczyk</t>
+          <t>Wieczorek</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Bizon Rozrywka Sp. z o.o.</t>
+          <t>Sudety Rozrywka Sp. z o.o.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7451,29 +7451,29 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>88082817864</t>
+          <t>72061434201</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t/>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>Szulc</t>
+          <t>Tomaszewska</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Bizon Gastronomia SP Z O O</t>
+          <t>Echo Gastronomia SP Z O O</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7513,22 +7513,22 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>89090719258</t>
+          <t>60101404206</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>Marcin</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>Kozak</t>
+          <t>Włodarczyk</t>
         </is>
       </c>
     </row>
@@ -7575,29 +7575,29 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>90101420601</t>
+          <t>94021474201</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>Karolina</t>
+          <t/>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>Cieślak</t>
+          <t>Olszewska</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Bizon Tekstylia Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Oaza Tekstylia Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7637,29 +7637,29 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>91112121998</t>
+          <t>82061444203</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t/>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>Andrzejewski</t>
+          <t>Urbańska</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Bizon Motoryzacja S.A.</t>
+          <t>Uran Motoryzacja S.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7699,29 +7699,29 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>92122823348</t>
+          <t>70101414208</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Aleksandra</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>Małgorzata</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>Gajewska</t>
+          <t>Konieczna</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Bizon Ubezpieczenia SA</t>
+          <t>Orzeł Ubezpieczenia SA</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -7761,29 +7761,29 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>93010724736</t>
+          <t>04221484209</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Andrzej</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>Jakub</t>
+          <t/>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>Laskowski</t>
+          <t>Matusiak</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Bizon Spawalnictwo S. A.</t>
+          <t>Narew Spawalnictwo S. A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -7823,29 +7823,29 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>94021426086</t>
+          <t>92061454205</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Marta</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t/>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>Mazurek</t>
+          <t>Przybylska</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Bizon Ślusarstwo Spółka Akcyjna</t>
+          <t>Granit Ślusarstwo Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -7885,29 +7885,29 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>95032127472</t>
+          <t>80101424200</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>Łukasz</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>Artur</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>Sobczak</t>
+          <t>Janik</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Bizon Krawiectwo sp. z o.o.</t>
+          <t>Zorza Krawiectwo sp. z o.o.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -7947,29 +7947,29 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>96042828821</t>
+          <t>68021494208</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Paulina</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>Iwona</t>
+          <t/>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>Konieczna</t>
+          <t>Dąbrowska</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Bizon Ochrona sp z oo</t>
+          <t>Kasprowy Ochrona sp z oo</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8009,29 +8009,29 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>97050730218</t>
+          <t>02261464203</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>Mateusz</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t/>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>Brzeziński</t>
+          <t>Jabłońska</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Bizon Catering sp. z o. o.</t>
+          <t>Sudety Catering sp. z o. o.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8071,29 +8071,29 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>98061431567</t>
+          <t>90101434202</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Elżbieta</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>Renata</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>Makowska</t>
+          <t>Zając</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Bizon Księgowość Sp. z o.o.</t>
+          <t>Echo Księgowość Sp. z o.o.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8133,29 +8133,29 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>99072132953</t>
+          <t>78021404200</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>Dawid</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>Maciej</t>
+          <t/>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>Wrona</t>
+          <t>Borkowska</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Canyon Budownictwo SP Z O O</t>
+          <t>Tytan Budownictwo SP Z O O</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8195,29 +8195,29 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>00282834308</t>
+          <t>66061474202</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Dorota</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t/>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>Bąk</t>
+          <t>Jaworska</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Canyon Transport spółka z ograniczoną odpowiedzialnością</t>
+          <t>Sokół Transport spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8257,29 +8257,29 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>01290735692</t>
+          <t>00301444200</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Dariusz</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>Zbigniew</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>Kucharski</t>
+          <t>Błaszczyk</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Canyon Spedycja Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Pilica Spedycja Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8319,29 +8319,29 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>02301437044</t>
+          <t>88021414202</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Beata</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>Patrycja</t>
+          <t/>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>Lisowska</t>
+          <t>Brzezińska</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Canyon Logistyka S.A.</t>
+          <t>Topaz Logistyka S.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8381,29 +8381,29 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>03312138430</t>
+          <t>76061484204</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Sławomir</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t/>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>Słowik</t>
+          <t>Gajda</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Canyon Handel SA</t>
+          <t>Olimp Handel SA</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8443,29 +8443,29 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>04322839780</t>
+          <t>64101454209</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>Urszula</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>Wiktoria</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>Kopeć</t>
+          <t>Michalak</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Canyon Usługi S. A.</t>
+          <t>Rysy Usługi S. A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8505,29 +8505,29 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>05210741172</t>
+          <t>98021424204</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>Mariusz</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>Jacek</t>
+          <t/>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>Czajka</t>
+          <t>Kowalska</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Canyon Finanse Spółka Akcyjna</t>
+          <t>Bałtyk Finanse Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8567,29 +8567,29 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>60021442526</t>
+          <t>86061494206</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>Izabela</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t/>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>Matusiak</t>
+          <t>Mazur</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Canyon Doradztwo sp. z o.o.</t>
+          <t>Delfin Doradztwo sp. z o.o.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8629,29 +8629,29 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>61032143912</t>
+          <t>74101464201</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Henryk</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>Przemysław</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>Gajda</t>
+          <t>Witkowska</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Canyon Szkolenia sp z oo</t>
+          <t>Ikar Szkolenia sp z oo</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8691,29 +8691,29 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>62042845263</t>
+          <t>62021434208</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Weronika</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>Kinga</t>
+          <t/>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>Klimek</t>
+          <t>Pietrzak</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Canyon Media sp. z o. o.</t>
+          <t>Neon Media sp. z o. o.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -8753,29 +8753,29 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>63050746656</t>
+          <t>96061404208</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Stanisław</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t/>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>Madej</t>
+          <t>Sawicka</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>PPHU Canyon Reklama</t>
+          <t>PPHU Tytan Reklama</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -8815,29 +8815,29 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>64061448005</t>
+          <t>84101474203</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Zofia</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>Kamila</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>Krupa</t>
+          <t>Malinowska</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Canyon Marketing SP Z O O</t>
+          <t>Sokół Marketing SP Z O O</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -8877,29 +8877,29 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>65072149392</t>
+          <t>72021444200</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Bartłomiej</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t/>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>Kaczmarczyk</t>
+          <t>Szulc</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Canyon Druk spółka z ograniczoną odpowiedzialnością</t>
+          <t>Pilica Druk spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -8939,29 +8939,29 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>66082850744</t>
+          <t>60061414202</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>Olga</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t/>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>Wrona</t>
+          <t>Makowska</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Canyon Informatyka Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Topaz Informatyka Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9001,29 +9001,29 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>67090752138</t>
+          <t>94101484205</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>Damian</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>Waldemar</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>Wasilewski</t>
+          <t>Klimek</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Canyon Oprogramowanie S.A.</t>
+          <t>Olimp Oprogramowanie S.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9063,29 +9063,29 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>68101453480</t>
+          <t>82021454202</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>Ewelina</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>Danuta</t>
+          <t/>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>Kalinowska</t>
+          <t>Szatkowska</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Canyon Rolnictwo SA</t>
+          <t>Rysy Rolnictwo SA</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9125,29 +9125,29 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>69112154876</t>
+          <t>70061424204</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Bartosz</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t/>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>Zarychta</t>
+          <t>Nowacka</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Canyon Ogrodnictwo S. A.</t>
+          <t>Bałtyk Ogrodnictwo S. A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9187,29 +9187,29 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>70122856225</t>
+          <t>04301494203</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>Sylwia</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>Aneta</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>Przybylska</t>
+          <t>Krawczyk</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Canyon Produkcja Spółka Akcyjna</t>
+          <t>Delfin Produkcja Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9249,29 +9249,29 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>71010757613</t>
+          <t>92021464204</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>Leszek</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>Kacper</t>
+          <t/>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>Michalak</t>
+          <t>Walczak</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Canyon Przemysł sp. z o.o.</t>
+          <t>Ikar Przemysł sp. z o.o.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9311,29 +9311,29 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>72021458962</t>
+          <t>80061434206</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>Grażyna</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t/>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>Szatkowska</t>
+          <t>Wójcicka</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Canyon Ekologia sp z oo</t>
+          <t>Neon Ekologia sp z oo</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9373,29 +9373,29 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>73032160352</t>
+          <t>68101404202</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>Cezary</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>Szymon</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>Bednarek</t>
+          <t>Dudek</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Canyon Energetyka sp. z o. o.</t>
+          <t>Tytan Energetyka sp. z o. o.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9435,29 +9435,29 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>74042861701</t>
+          <t>02221474202</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>Bożena</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>Oliwia</t>
+          <t/>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>Podgórska</t>
+          <t>Pająk</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Canyon Instalacje Sp. z o.o.</t>
+          <t>Sokół Instalacje Sp. z o.o.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9497,29 +9497,29 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>75050763096</t>
+          <t>00061444208</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>Filip</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t/>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>Śliwiński</t>
+          <t>Kozak</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Canyon Nieruchomości SP Z O O</t>
+          <t>Pilica Nieruchomości SP Z O O</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9559,29 +9559,29 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>76061464444</t>
+          <t>78101414204</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>Zuzanna</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>Emilia</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>Czajkowska-Lewandowska</t>
+          <t>Wrona</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Canyon Inwestycje spółka z ograniczoną odpowiedzialnością</t>
+          <t>Topaz Inwestycje spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -9621,29 +9621,29 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>87072165830</t>
+          <t>66021484201</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>Mikołaj</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>Ignacy</t>
+          <t/>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>Biernat</t>
+          <t>Madej</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Canyon Medycyna Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Olimp Medycyna Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -9683,29 +9683,29 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>78082867181</t>
+          <t>00261454206</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>Lena</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t/>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>Panek</t>
+          <t>Bednarek</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Canyon Zdrowie S.A.</t>
+          <t>Rysy Zdrowie S.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -9745,29 +9745,29 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>79090768574</t>
+          <t>88101424206</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>Antoni</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>Leon</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>Prus</t>
+          <t>Wiśniewska</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Canyon Urody SA</t>
+          <t>Bałtyk Urody SA</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -9807,29 +9807,29 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>80101469924</t>
+          <t>76021494203</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>Hanna</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>Dominika</t>
+          <t/>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>Janik</t>
+          <t>Woźniak</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Canyon Turystyka S. A.</t>
+          <t>Delfin Turystyka S. A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -9869,29 +9869,29 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>81112171314</t>
+          <t>64061464205</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>Fracniszek</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t/>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>Kowalski</t>
+          <t>tSępień</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Canyon Rozrywka Spółka Akcyjna</t>
+          <t>Ikar Rozrywka Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -9931,29 +9931,29 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>82122872664</t>
+          <t>98101434208</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>Amelia</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>Jagoda</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>Nowacka</t>
+          <t>Czarnecka</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Canyon Gastronomia sp. z o.o.</t>
+          <t>Neon Gastronomia sp. z o.o.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -9993,22 +9993,22 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>83010774053</t>
+          <t>86021404205</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>Nikodem</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>Jerzy</t>
+          <t/>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>Wiśniewski</t>
+          <t>Adamczyk</t>
         </is>
       </c>
     </row>
@@ -10055,29 +10055,29 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>84021475401</t>
+          <t>74061474207</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>Martyna</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t/>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>Wójcik</t>
+          <t>Szczepańska</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Canyon Tekstylia sp. z o. o.</t>
+          <t>Sokół Tekstylia sp. z o. o.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10117,29 +10117,29 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>85032176798</t>
+          <t>62101444202</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>Miłosz</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>Marian</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>Kowalczyk</t>
+          <t>Cieślak</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Canyon Motoryzacja Sp. z o.o.</t>
+          <t>Pilica Motoryzacja Sp. z o.o.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10179,29 +10179,29 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>86042878148</t>
+          <t>96021414207</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>Agata</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>Irena</t>
+          <t/>
         </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>Kamińska</t>
+          <t>Bąk</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Canyon Ubezpieczenia SP Z O O</t>
+          <t>Topaz Ubezpieczenia SP Z O O</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10241,29 +10241,29 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>87050779531</t>
+          <t>84061484209</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>Tadeusz</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t/>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>Lewandowski</t>
+          <t>Krupa</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Canyon Spawalnictwo spółka z ograniczoną odpowiedzialnością</t>
+          <t>Olimp Spawalnictwo spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10303,29 +10303,29 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>88061480883</t>
+          <t>72101454204</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>Helena</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>Izabela</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>Zielińska</t>
+          <t>Podgórska</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Canyon Ślusarstwo Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Rysy Ślusarstwo Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10365,29 +10365,29 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>89072182270</t>
+          <t>60021424201</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>Stefan</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>Mirosław</t>
+          <t/>
         </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>Szymański</t>
+          <t>Wójcik</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Canyon Krawiectwo S.A.</t>
+          <t>Bałtyk Krawiectwo S.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10427,29 +10427,29 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>90082883628</t>
+          <t>94061494201</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>Jadwiga</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t/>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>Dąbrowska</t>
+          <t>Jankowska</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Canyon Ochrona SA</t>
+          <t>Delfin Ochrona SA</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10489,29 +10489,29 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>91090785012</t>
+          <t>82101464206</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>Józef</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>Mazur</t>
+          <t>Baran</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Canyon Catering S. A.</t>
+          <t>Ikar Catering S. A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10551,29 +10551,29 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>92101486364</t>
+          <t>70021434203</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t/>
         </is>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>Krawczyk</t>
+          <t>Lis</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Canyon Księgowość Spółka Akcyjna</t>
+          <t>Neon Księgowość Spółka Akcyjna</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10613,22 +10613,22 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>93112187750</t>
+          <t>04261404209</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t/>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>Woźniak</t>
+          <t>Pawłowska</t>
         </is>
       </c>
     </row>
@@ -10675,22 +10675,22 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>94122889100</t>
+          <t>92101474208</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>Sabina</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>Jankowska</t>
+          <t>Czerwińska</t>
         </is>
       </c>
     </row>
@@ -10737,22 +10737,22 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>95010790492</t>
+          <t>80021444205</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>Arkadiusz</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t/>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>Grabowski</t>
+          <t>Andrzejewska</t>
         </is>
       </c>
     </row>
@@ -10799,22 +10799,22 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>96021491840</t>
+          <t>68061414208</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t/>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>Pawlak</t>
+          <t>Kucharska</t>
         </is>
       </c>
     </row>
@@ -10861,22 +10861,22 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>97032193237</t>
+          <t>02301484206</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>Michalski</t>
+          <t>Kaczmarczyk</t>
         </is>
       </c>
     </row>
@@ -10923,22 +10923,22 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>98042894587</t>
+          <t>90021454207</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t/>
         </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>Król</t>
+          <t>Śliwińska</t>
         </is>
       </c>
     </row>
@@ -10985,22 +10985,22 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>99050795970</t>
+          <t>78061424200</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t/>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>Wieczorek</t>
+          <t>Kowalczyk</t>
         </is>
       </c>
     </row>
@@ -11047,22 +11047,22 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>00261497324</t>
+          <t>66101494205</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>Jabłońska</t>
+          <t>Grabowska</t>
         </is>
       </c>
     </row>
@@ -11109,22 +11109,22 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>01272198710</t>
+          <t>00221464205</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t/>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>Witkowski</t>
+          <t>Rutkowska</t>
         </is>
       </c>
     </row>
@@ -11171,22 +11171,22 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>02282800064</t>
+          <t>88061434202</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t/>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>Walczak</t>
+          <t>Kołodziej</t>
         </is>
       </c>
     </row>
@@ -11233,22 +11233,22 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>03290701457</t>
+          <t>76101404207</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>Marcin</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>Stępień</t>
+          <t>Nowicka</t>
         </is>
       </c>
     </row>
@@ -11295,22 +11295,22 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>04301402808</t>
+          <t>64021474204</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>Karolina</t>
+          <t/>
         </is>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>Baran</t>
+          <t>Kubiak</t>
         </is>
       </c>
     </row>
@@ -11357,22 +11357,22 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>05312104196</t>
+          <t>98061444204</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t/>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>Rutkowski</t>
+          <t>Gajewska</t>
         </is>
       </c>
     </row>
@@ -11419,22 +11419,22 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>60122805541</t>
+          <t>86101414209</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>Aleksandra</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>Małgorzata</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>Górska</t>
+          <t>Lisowska</t>
         </is>
       </c>
     </row>
@@ -11481,22 +11481,22 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>61010706939</t>
+          <t>74021484206</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>Andrzej</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>Jakub</t>
+          <t/>
         </is>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>Sikora</t>
+          <t>Wrona</t>
         </is>
       </c>
     </row>
@@ -11543,22 +11543,22 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>62021408289</t>
+          <t>62061454208</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>Marta</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t/>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>Ostrowska</t>
+          <t>Czajkowska</t>
         </is>
       </c>
     </row>
@@ -11605,22 +11605,22 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>63032109675</t>
+          <t>96101424201</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>Łukasz</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>Artur</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>Tomaszewski</t>
+          <t>Kamińska</t>
         </is>
       </c>
     </row>
@@ -11667,22 +11667,22 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>64042811028</t>
+          <t>84021494208</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>Paulina</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>Iwona</t>
+          <t/>
         </is>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>Zając</t>
+          <t>Pawlak</t>
         </is>
       </c>
     </row>
@@ -11729,22 +11729,22 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>65050712411</t>
+          <t>72061464200</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>Mateusz</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t/>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>Pietrzak</t>
+          <t>Górska</t>
         </is>
       </c>
     </row>
@@ -11791,22 +11791,22 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>66061413760</t>
+          <t>60101434205</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>Elżbieta</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>Renata</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>Wójcicka</t>
+          <t>Kaczmarek</t>
         </is>
       </c>
     </row>
@@ -11828,7 +11828,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>0000076541</t>
+          <t>000007654</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -11853,22 +11853,22 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>67072115157</t>
+          <t>94021404200</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>Dawid</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>Maciej</t>
+          <t/>
         </is>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>Czarnecki</t>
+          <t>Sokołowska</t>
         </is>
       </c>
     </row>
@@ -11890,7 +11890,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>000007663</t>
+          <t>0000076638</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -11915,22 +11915,22 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>68082816506</t>
+          <t>82061474202</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>Dorota</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t/>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>Lis</t>
+          <t>Wilk</t>
         </is>
       </c>
     </row>
@@ -11962,7 +11962,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>397603136</t>
+          <t>297603136</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -11977,22 +11977,22 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>69090717890</t>
+          <t>70101444207</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>Dariusz</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>Zbigniew</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>Kołodziej</t>
+          <t>Laskowska</t>
         </is>
       </c>
     </row>
@@ -12039,22 +12039,22 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>70101419241</t>
+          <t>04221414208</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>Beata</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>Patrycja</t>
+          <t/>
         </is>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>Kaczmarek-Wróbel</t>
+          <t>Słowik</t>
         </is>
       </c>
     </row>
@@ -12086,7 +12086,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>297761510</t>
+          <t>397761510</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -12101,22 +12101,22 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>71112120630</t>
+          <t>92061484204</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>Sławomir</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t/>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>Piątek</t>
+          <t>Wasilewska</t>
         </is>
       </c>
     </row>
@@ -12163,22 +12163,22 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>72122821980</t>
+          <t>80101454209</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>Urszula</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>Wiktoria</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>Sadowska</t>
+          <t>Biernat</t>
         </is>
       </c>
     </row>
@@ -12225,22 +12225,22 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>73010723379</t>
+          <t>68021424207</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>Mariusz</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>Jacek</t>
+          <t/>
         </is>
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>Włodarczyk</t>
+          <t>Lewandowska</t>
         </is>
       </c>
     </row>
@@ -12287,22 +12287,22 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>74021424727</t>
+          <t>02261494202</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>Izabela</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t/>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>Borkowska</t>
+          <t>Michalska</t>
         </is>
       </c>
     </row>
@@ -12349,22 +12349,22 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>75032126114</t>
+          <t>90101464201</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>Henryk</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>Przemysław</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>Sawicki</t>
+          <t>Sikora</t>
         </is>
       </c>
     </row>
@@ -12411,22 +12411,22 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>76042827464</t>
+          <t>78021434209</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>Weronika</t>
+          <t>Martyna</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>Kinga</t>
+          <t/>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>Dudek</t>
+          <t>Piątek</t>
         </is>
       </c>
     </row>
@@ -12473,22 +12473,22 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>77050728857</t>
+          <t>66061404201</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>Stanisław</t>
+          <t>Zofia</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t/>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>Adamczyk</t>
+          <t>Wróbel</t>
         </is>
       </c>
     </row>
